--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>13-Sep 13:30</t>
+          <t>13-Sep 18:56</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>13-Sep 13:29</t>
+          <t>13-Sep 19:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -699,12 +699,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹18 (15.25%) 18 ↓ / 18 ↑</t>
+          <t>₹27 (22.88%) 27 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>13-Sep 13:34</t>
+          <t>13-Sep 18:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>13-Sep 13:28</t>
+          <t>13-Sep 18:56</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>13-Sep 13:36</t>
+          <t>13-Sep 19:00</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹99 (23.35%) 30 ↓ / 106 ↑</t>
+          <t>₹110 (25.94%) 30 ↓ / 110 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>13-Sep 13:37</t>
+          <t>13-Sep 18:59</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>13-Sep 13:30</t>
+          <t>13-Sep 18:57</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>13-Sep 13:32</t>
+          <t>13-Sep 18:59</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>13-Sep 13:37</t>
+          <t>13-Sep 19:00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>13-Sep 13:28</t>
+          <t>13-Sep 19:02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>13-Sep 13:30</t>
+          <t>13-Sep 18:53</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>13-Sep 13:30</t>
+          <t>13-Sep 19:01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>13-Sep 13:34</t>
+          <t>13-Sep 18:56</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>13-Sep 13:32</t>
+          <t>13-Sep 18:57</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>13-Sep 13:31</t>
+          <t>13-Sep 18:55</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>13-Sep 13:30</t>
+          <t>13-Sep 19:00</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>13-Sep 13:37</t>
+          <t>13-Sep 18:55</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹48 (25.81%) 15 ↓ / 48 ↑</t>
+          <t>₹50 (26.88%) 15 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>13-Sep 13:30</t>
+          <t>13-Sep 18:56</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>13-Sep 13:30</t>
+          <t>13-Sep 19:02</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>13-Sep 13:28</t>
+          <t>13-Sep 19:02</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹21.5 (26.54%) 18 ↓ / 23 ↑</t>
+          <t>₹21 (25.93%) 18 ↓ / 23 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>13-Sep 13:28</t>
+          <t>13-Sep 18:59</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>13-Sep 13:31</t>
+          <t>13-Sep 18:59</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>13-Sep 13:33</t>
+          <t>13-Sep 19:00</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>13-Sep 13:32</t>
+          <t>13-Sep 18:54</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹160 (39.60%) 79 ↓ / 160 ↑</t>
+          <t>₹145 (35.89%) 79 ↓ / 160 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>13-Sep 13:34</t>
+          <t>13-Sep 18:57</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>13-Sep 13:31</t>
+          <t>13-Sep 18:58</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>13-Sep 13:29</t>
+          <t>13-Sep 18:59</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>13-Sep 13:36</t>
+          <t>13-Sep 18:58</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>13-Sep 13:32</t>
+          <t>13-Sep 18:55</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹51 (28.02%) 20 ↓ / 66 ↑</t>
+          <t>₹52 (28.57%) 20 ↓ / 66 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>13-Sep 13:28</t>
+          <t>13-Sep 18:53</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>13-Sep 13:29</t>
+          <t>13-Sep 18:59</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>13-Sep 13:34</t>
+          <t>13-Sep 18:56</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>13-Sep 13:33</t>
+          <t>13-Sep 19:00</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,7 +548,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13-Sep 5:55</t>
+          <t>14-Sep 5:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -560,7 +560,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMEU</t>
+          <t>S.K.Offset BSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -580,42 +580,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹49.81 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>13-Sep 18:56</t>
+          <t>14-Sep 13:59</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kheria Autocomp NSE SMEU</t>
+          <t>Robokidz Eduventures BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -647,12 +647,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹46.44 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -662,27 +662,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>13-Sep 19:02</t>
+          <t>14-Sep 13:57</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -694,17 +694,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMEU</t>
+          <t>FX Multitech BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹27 (22.88%) 27 ↓ / 27 ↑</t>
+          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,44 +712,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹42.52 Cr</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>13-Sep 18:57</t>
+          <t>14-Sep 12:30</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -761,7 +753,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sonaselection India IPOU</t>
+          <t>Axiom Gas Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -781,42 +773,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹141.57 Cr</t>
+          <t>₹49.81 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>13-Sep 18:56</t>
+          <t>14-Sep 14:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -833,7 +825,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹208 (11.65%) 192 ↓ / 310 ↑</t>
+          <t>₹210 (11.76%) 192 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -883,7 +875,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>13-Sep 19:00</t>
+          <t>14-Sep 14:00</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -895,12 +887,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SS Retail IPOU</t>
+          <t>SpectraA Technology Solutions NSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹110 (25.94%) 30 ↓ / 110 ↑</t>
+          <t>₹40 (33.90%) 27 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -915,42 +907,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹42.52 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>13-Sep 18:59</t>
+          <t>14-Sep 13:57</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -962,17 +954,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hero Motors IPOU</t>
+          <t>Sonaselection India IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹24 (28.57%) 8 ↓ / 24 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -982,42 +974,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹1000.00 Cr</t>
+          <t>₹141.57 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>13-Sep 18:57</t>
+          <t>14-Sep 14:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1029,17 +1021,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOU</t>
+          <t>Kheria Autocomp NSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹25 (26.88%) 11 ↓ / 25 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1049,42 +1041,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹46.44 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>13-Sep 18:59</t>
+          <t>14-Sep 13:53</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1096,17 +1088,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Quanto Agroworld BSE SMEU</t>
+          <t>Jindal Supreme IPOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹27 (29.03%) 11 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1116,64 +1108,64 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹31.02 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>13-Sep 19:00</t>
+          <t>14-Sep 13:55</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shakti Polytarp BSE SMEU</t>
+          <t>Hero Motors IPOU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹24 (28.57%) 8 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1183,42 +1175,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹26.93 Cr</t>
+          <t>₹1000.00 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>13-Sep 19:02</t>
+          <t>14-Sep 13:56</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1230,17 +1222,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vama Wovenfab BSE SMEU</t>
+          <t>SS Retail IPOU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹136 (32.08%) 30 ↓ / 136 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1250,59 +1242,59 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹49.54 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>13-Sep 18:53</t>
+          <t>14-Sep 13:55</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Injecto Polymers BSE SMEO</t>
+          <t>Vama Wovenfab BSE SMEU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹10 (2.93%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1312,59 +1304,59 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.29x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹56.12 Cr</t>
+          <t>₹49.54 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 0</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>13-Sep 19:01</t>
+          <t>14-Sep 14:00</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Century Business Media BSE SMEO</t>
+          <t>Shakti Polytarp BSE SMEU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1379,47 +1371,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.15x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹17.11 Cr</t>
+          <t>₹26.93 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 0</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>13-Sep 18:56</t>
+          <t>14-Sep 13:56</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1431,67 +1423,67 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Manika Plastech IPOO</t>
+          <t>Quanto Agroworld BSE SMEU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹11 (25.58%) 7 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.49x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹125.50 Cr</t>
+          <t>₹31.02 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>13-Sep 18:57</t>
+          <t>14-Sep 13:55</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1565,62 +1557,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Raksan Transformers BSE SMEO</t>
+          <t>Injecto Polymers BSE SMEO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹30 (10.99%) 25 ↓ / 30 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.31x</t>
+          <t>0.29x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹150.50 Cr</t>
+          <t>₹56.12 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 28</t>
+          <t>11-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>13-Sep 18:55</t>
+          <t>14-Sep 14:02</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1632,7 +1624,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Om Galaxy BSE SMEO</t>
+          <t>Century Business Media BSE SMEO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1647,17 +1639,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.95x</t>
+          <t>1.15x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹105.00 Cr</t>
+          <t>₹17.11 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1667,27 +1659,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 0</t>
+          <t>11-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>13-Sep 19:00</t>
+          <t>14-Sep 13:58</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1699,109 +1691,109 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Panchatv Bharat BSE SMEO</t>
+          <t>Manika Plastech IPOO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹11 (7.86%) 7 ↓ / 11 ↑</t>
+          <t>₹11 (25.58%) 7 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.04x</t>
+          <t>1.49x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹24.58 Cr</t>
+          <t>₹125.50 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 7</t>
+          <t>11-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>13-Sep 18:55</t>
+          <t>14-Sep 14:01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Maharaja &amp; Speedex India BSE SMEO</t>
+          <t>Veegaland Developers IPOO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹50 (26.88%) 15 ↓ / 50 ↑</t>
+          <t>₹22 (15.71%) 15 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.48x</t>
+          <t>1.25x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹80.13 Cr</t>
+          <t>₹210.00 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 30</t>
+          <t>10-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1821,7 +1813,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>13-Sep 18:56</t>
+          <t>14-Sep 14:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1833,12 +1825,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Veegaland Developers IPOO</t>
+          <t>Panchatv Bharat BSE SMEO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹15 (10.71%) 15 ↓ / 33 ↑</t>
+          <t>₹18 (12.86%) 7 ↓ / 18 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1848,7 +1840,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.25x</t>
+          <t>0.04x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1858,17 +1850,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹210.00 Cr</t>
+          <t>₹24.58 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 25</t>
+          <t>10-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1888,74 +1880,74 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>13-Sep 19:02</t>
+          <t>14-Sep 13:59</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Manipal Payment and Identity Solutions IPOC</t>
+          <t>Maharaja &amp; Speedex India BSE SMEO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹-2 (-0.59%) -2 ↓ / 38 ↑</t>
+          <t>₹45 (24.19%) 15 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>0.48x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹805.00 Cr</t>
+          <t>₹80.13 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 8</t>
+          <t>10-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>13-Sep 19:02</t>
+          <t>14-Sep 14:01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1967,62 +1959,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Steamhouse IPOC</t>
+          <t>Raksan Transformers BSE SMEO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹21 (25.93%) 18 ↓ / 23 ↑</t>
+          <t>₹30 (10.99%) 25 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>32.07x</t>
+          <t>1.31x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>273</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹414.00 Cr</t>
+          <t>₹150.50 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>10-Sep GMP: 28</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 21</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>13-Sep 18:59</t>
+          <t>14-Sep 14:01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2034,32 +2026,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Amtech Esters BSE SMEC</t>
+          <t>Om Galaxy BSE SMEO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹7 (9.33%) 5 ↓ / 11 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>25.7x</t>
+          <t>0.95x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹17.88 Cr</t>
+          <t>₹105.00 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2069,27 +2061,27 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 11</t>
+          <t>10-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>13-Sep 18:59</t>
+          <t>14-Sep 13:58</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2101,47 +2093,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LCC Projects IPOC</t>
+          <t>Amtech Esters BSE SMEC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹64 (43.84%) 17 ↓ / 78 ↑</t>
+          <t>₹7 (9.33%) 5 ↓ / 11 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.57x</t>
+          <t>25.7x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹427.14 Cr</t>
+          <t>₹17.88 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 40</t>
+          <t>9-Sep GMP: 11</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 78</t>
+          <t>11-Sep GMP: 7</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2156,7 +2148,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>13-Sep 19:00</t>
+          <t>14-Sep 13:53</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2168,47 +2160,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Karamtara Engineering IPOC</t>
+          <t>Manipal Payment and Identity Solutions IPOC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹71 (27.95%) 40 ↓ / 75 ↑</t>
+          <t>₹-2 (-0.59%) -2 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>66.01x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>339</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹875.00 Cr</t>
+          <t>₹805.00 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 75</t>
+          <t>9-Sep GMP: 8</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 67</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2223,7 +2215,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>13-Sep 18:54</t>
+          <t>14-Sep 13:58</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2235,47 +2227,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rentomojo IPOC</t>
+          <t>Vinod Texworld NSE SMEC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹145 (35.89%) 79 ↓ / 160 ↑</t>
+          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>72.89x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹1255.57 Cr</t>
+          <t>₹42.83 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 143</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 148</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2290,24 +2282,24 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>13-Sep 18:57</t>
+          <t>14-Sep 14:01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Vinod Texworld NSE SMEC</t>
+          <t>Infrax Renewable BSE SMEC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2317,17 +2309,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>2.05x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹42.83 Cr</t>
+          <t>₹40.88 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2337,12 +2329,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>9-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>11-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2357,7 +2349,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>13-Sep 18:58</t>
+          <t>14-Sep 14:00</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2369,47 +2361,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Infrax Renewable BSE SMEC</t>
+          <t>Asset Reconstruction IPOC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹16 (11.51%) 14 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>20.1x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹40.88 Cr</t>
+          <t>₹732.97 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 0</t>
+          <t>9-Sep GMP: 24</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 0</t>
+          <t>11-Sep GMP: 14.5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2424,59 +2416,59 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>13-Sep 18:59</t>
+          <t>14-Sep 13:55</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Asset Reconstruction IPOC</t>
+          <t>Karamtara Engineering IPOC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹14 (10.07%) 14 ↓ / 30 ↑</t>
+          <t>₹71 (27.95%) 40 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20.1x</t>
+          <t>66.01x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹732.97 Cr</t>
+          <t>₹875.00 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 24</t>
+          <t>9-Sep GMP: 75</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 14.5</t>
+          <t>11-Sep GMP: 67</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2491,7 +2483,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>13-Sep 18:58</t>
+          <t>14-Sep 13:54</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2503,12 +2495,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kanohar Electricals IPOCAllotted</t>
+          <t>LCC Projects IPOC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹244 (38.61%) 190 ↓ / 244 ↑</t>
+          <t>₹64 (43.84%) 17 ↓ / 78 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2518,47 +2510,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>90.59x</t>
+          <t>49.57x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹1055.74 Cr</t>
+          <t>₹427.14 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 218</t>
+          <t>9-Sep GMP: 40</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 240</t>
+          <t>11-Sep GMP: 78</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>13-Sep 18:55</t>
+          <t>14-Sep 13:57</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2637,12 +2629,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Glass Wall Systems IPOCAllotted</t>
+          <t>Rentomojo IPOC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹52 (28.57%) 20 ↓ / 66 ↑</t>
+          <t>₹158 (39.11%) 79 ↓ / 160 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2652,47 +2644,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>81.65x</t>
+          <t>72.89x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹427.89 Cr</t>
+          <t>₹1255.57 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 56</t>
+          <t>9-Sep GMP: 143</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 45</t>
+          <t>11-Sep GMP: 148</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>13-Sep 18:53</t>
+          <t>14-Sep 13:56</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2704,62 +2696,62 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Prasol Chemicals IPOCAllotted</t>
+          <t>Steamhouse IPOC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹-15 (-2.22%) -15 ↓ / 165 ↑</t>
+          <t>₹22 (27.16%) 18 ↓ / 23 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.47x</t>
+          <t>32.07x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹414.00 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 30</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 0</t>
+          <t>11-Sep GMP: 21</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>13-Sep 18:59</t>
+          <t>14-Sep 13:55</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2771,12 +2763,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pranav Constructions IPOCAllotted</t>
+          <t>Glass Wall Systems IPOCAllotted</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹45 (36.29%) 23 ↓ / 52 ↑</t>
+          <t>₹52.5 (28.85%) 20 ↓ / 66 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2786,47 +2778,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>126.34x</t>
+          <t>81.65x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹351.03 Cr</t>
+          <t>₹427.89 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>7-Sep GMP: 42.5</t>
+          <t>8-Sep GMP: 56</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 40</t>
+          <t>10-Sep GMP: 45</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>13-Sep 18:56</t>
+          <t>14-Sep 13:59</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2838,12 +2830,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Apana Logistics BSE SMECAllotted</t>
+          <t>Prasol Chemicals IPOCAllotted</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
+          <t>₹-15 (-2.22%) -15 ↓ / 165 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2853,52 +2845,119 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.26x</t>
+          <t>3.47x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹34.14 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>7-Sep GMP: 10</t>
+          <t>8-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 1</t>
+          <t>10-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>13-Sep 19:00</t>
+          <t>14-Sep 14:00</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Kanohar Electricals IPOCAllotted</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>₹241 (38.13%) 190 ↓ / 241 ↑</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>90.59x</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>₹1055.74 Cr</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>8-Sep GMP: 218</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10-Sep GMP: 240</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>14-Sep 13:55</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14-Sep 13:59</t>
+          <t>14-Sep 20:53</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -632,12 +632,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹45 (42.45%) 45 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>14-Sep 13:57</t>
+          <t>14-Sep 21:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>14-Sep 14:02</t>
+          <t>14-Sep 20:58</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹210 (11.76%) 192 ↓ / 310 ↑</t>
+          <t>₹208 (11.65%) 192 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>14-Sep 14:00</t>
+          <t>14-Sep 21:00</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹40 (33.90%) 27 ↓ / 40 ↑</t>
+          <t>₹44 (37.29%) 27 ↓ / 44 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>14-Sep 13:57</t>
+          <t>14-Sep 20:54</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>14-Sep 14:02</t>
+          <t>14-Sep 20:56</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>14-Sep 13:53</t>
+          <t>14-Sep 21:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>14-Sep 13:55</t>
+          <t>14-Sep 20:59</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹24 (28.57%) 8 ↓ / 24 ↑</t>
+          <t>₹22 (26.19%) 8 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>14-Sep 13:56</t>
+          <t>14-Sep 20:54</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹136 (32.08%) 30 ↓ / 136 ↑</t>
+          <t>₹140 (33.02%) 30 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>14-Sep 13:55</t>
+          <t>14-Sep 21:00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>14-Sep 14:00</t>
+          <t>14-Sep 21:01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>14-Sep 13:56</t>
+          <t>14-Sep 21:00</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>14-Sep 13:55</t>
+          <t>14-Sep 21:00</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>14-Sep 14:02</t>
+          <t>14-Sep 21:00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>14-Sep 13:58</t>
+          <t>14-Sep 20:55</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>14-Sep 14:01</t>
+          <t>14-Sep 20:58</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹22 (15.71%) 15 ↓ / 33 ↑</t>
+          <t>₹23 (16.43%) 15 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>14-Sep 14:00</t>
+          <t>14-Sep 21:02</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>14-Sep 13:59</t>
+          <t>14-Sep 20:59</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹45 (24.19%) 15 ↓ / 48 ↑</t>
+          <t>₹40 (21.51%) 15 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>14-Sep 14:01</t>
+          <t>14-Sep 21:01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹30 (10.99%) 25 ↓ / 30 ↑</t>
+          <t>₹58 (21.25%) 25 ↓ / 58 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>14-Sep 14:01</t>
+          <t>14-Sep 20:53</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>14-Sep 13:58</t>
+          <t>14-Sep 20:54</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>14-Sep 13:53</t>
+          <t>14-Sep 20:56</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹-2 (-0.59%) -2 ↓ / 38 ↑</t>
+          <t>₹1 (0.29%) -2 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>14-Sep 13:58</t>
+          <t>14-Sep 20:53</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>14-Sep 14:01</t>
+          <t>14-Sep 20:54</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>14-Sep 14:00</t>
+          <t>14-Sep 20:56</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>14-Sep 13:55</t>
+          <t>14-Sep 20:58</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>14-Sep 13:54</t>
+          <t>14-Sep 20:58</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹64 (43.84%) 17 ↓ / 78 ↑</t>
+          <t>₹63 (43.15%) 17 ↓ / 78 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>14-Sep 13:57</t>
+          <t>14-Sep 20:53</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>14-Sep 13:56</t>
+          <t>14-Sep 21:01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹22 (27.16%) 18 ↓ / 23 ↑</t>
+          <t>₹24 (29.63%) 18 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>14-Sep 13:55</t>
+          <t>14-Sep 20:58</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>14-Sep 13:59</t>
+          <t>14-Sep 20:58</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹-15 (-2.22%) -15 ↓ / 165 ↑</t>
+          <t>₹-13 (-1.92%) -15 ↓ / 165 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>14-Sep 14:00</t>
+          <t>14-Sep 20:58</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹241 (38.13%) 190 ↓ / 241 ↑</t>
+          <t>₹240 (37.97%) 190 ↓ / 241 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>14-Sep 13:55</t>
+          <t>14-Sep 21:01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,7 +548,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>14-Sep 5:55</t>
+          <t>15-Sep 5:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14-Sep 20:53</t>
+          <t>15-Sep 14:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -632,12 +632,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹45 (42.45%) 45 ↓ / 45 ↑</t>
+          <t>₹15 (14.15%) 15 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>14-Sep 21:00</t>
+          <t>15-Sep 13:57</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>14-Sep 12:30</t>
+          <t>15-Sep 5:55</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>14-Sep 20:58</t>
+          <t>15-Sep 13:54</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹208 (11.65%) 192 ↓ / 310 ↑</t>
+          <t>₹179 (10.03%) 179 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>14-Sep 21:00</t>
+          <t>15-Sep 13:55</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹44 (37.29%) 27 ↓ / 44 ↑</t>
+          <t>₹50 (42.37%) 27 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>14-Sep 20:54</t>
+          <t>15-Sep 14:00</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹5 (5.05%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>14-Sep 20:56</t>
+          <t>15-Sep 13:58</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>14-Sep 21:02</t>
+          <t>15-Sep 13:55</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>14-Sep 20:59</t>
+          <t>15-Sep 14:00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>14-Sep 20:54</t>
+          <t>15-Sep 13:56</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹140 (33.02%) 30 ↓ / 140 ↑</t>
+          <t>₹145 (34.20%) 30 ↓ / 145 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>14-Sep 21:00</t>
+          <t>15-Sep 13:58</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1289,7 +1289,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vama Wovenfab BSE SMEU</t>
+          <t>Vama Wovenfab BSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>15-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>14-Sep 21:01</t>
+          <t>15-Sep 14:01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1356,7 +1356,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shakti Polytarp BSE SMEU</t>
+          <t>Shakti Polytarp BSE SMEO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.34x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>15-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>14-Sep 21:00</t>
+          <t>15-Sep 14:02</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Quanto Agroworld BSE SMEU</t>
+          <t>Quanto Agroworld BSE SMEO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>15-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>14-Sep 21:00</t>
+          <t>15-Sep 13:56</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.29x</t>
+          <t>0.44x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>14-Sep 21:00</t>
+          <t>15-Sep 13:53</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.15x</t>
+          <t>1.27x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>14-Sep 20:55</t>
+          <t>15-Sep 13:57</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹11 (25.58%) 7 ↓ / 20 ↑</t>
+          <t>₹4 (9.30%) 4 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.49x</t>
+          <t>6.88x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>14-Sep 20:58</t>
+          <t>15-Sep 13:59</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1758,22 +1758,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Veegaland Developers IPOO</t>
+          <t>Veegaland Developers IPOCT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹23 (16.43%) 15 ↓ / 33 ↑</t>
+          <t>₹5 (3.57%) 5 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.25x</t>
+          <t>8.47x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>15-Sep GMP: 5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>14-Sep 21:02</t>
+          <t>15-Sep 13:59</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1825,12 +1825,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Panchatv Bharat BSE SMEO</t>
+          <t>Panchatv Bharat BSE SMECT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹18 (12.86%) 7 ↓ / 18 ↑</t>
+          <t>₹21 (15.00%) 7 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.04x</t>
+          <t>0.72x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>15-Sep GMP: 21</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>14-Sep 20:59</t>
+          <t>15-Sep 13:55</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1892,22 +1892,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Maharaja &amp; Speedex India BSE SMEO</t>
+          <t>Maharaja &amp; Speedex India BSE SMECT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹40 (21.51%) 15 ↓ / 48 ↑</t>
+          <t>₹20 (10.75%) 15 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.48x</t>
+          <t>13.45x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>15-Sep GMP: 20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>14-Sep 21:01</t>
+          <t>15-Sep 13:55</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1959,22 +1959,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Raksan Transformers BSE SMEO</t>
+          <t>Raksan Transformers BSE SMECT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹58 (21.25%) 25 ↓ / 58 ↑</t>
+          <t>₹50 (18.32%) 25 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.31x</t>
+          <t>16.34x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>15-Sep GMP: 50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>14-Sep 20:53</t>
+          <t>15-Sep 14:00</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Om Galaxy BSE SMEO</t>
+          <t>Om Galaxy BSE SMECT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.95x</t>
+          <t>1.31x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>15-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>14-Sep 20:54</t>
+          <t>15-Sep 14:00</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>14-Sep 20:56</t>
+          <t>15-Sep 14:00</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹1 (0.29%) -2 ↓ / 38 ↑</t>
+          <t>₹-10 (-2.95%) -10 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>14-Sep 20:53</t>
+          <t>15-Sep 14:00</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>14-Sep 20:54</t>
+          <t>15-Sep 13:54</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>14-Sep 20:56</t>
+          <t>15-Sep 13:57</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹16 (11.51%) 14 ↓ / 30 ↑</t>
+          <t>₹15 (10.79%) 14 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>14-Sep 20:58</t>
+          <t>15-Sep 14:01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹71 (27.95%) 40 ↓ / 75 ↑</t>
+          <t>₹65 (25.59%) 40 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>14-Sep 20:58</t>
+          <t>15-Sep 13:54</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹63 (43.15%) 17 ↓ / 78 ↑</t>
+          <t>₹54 (36.99%) 17 ↓ / 78 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>14-Sep 20:53</t>
+          <t>15-Sep 14:00</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹158 (39.11%) 79 ↓ / 160 ↑</t>
+          <t>₹150 (37.13%) 79 ↓ / 160 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>14-Sep 21:01</t>
+          <t>15-Sep 14:00</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹24 (29.63%) 18 ↓ / 24 ↑</t>
+          <t>₹23 (28.40%) 18 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>14-Sep 20:58</t>
+          <t>15-Sep 13:56</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹52.5 (28.85%) 20 ↓ / 66 ↑</t>
+          <t>₹41 (22.53%) 20 ↓ / 66 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>14-Sep 20:58</t>
+          <t>15-Sep 14:00</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>14-Sep 20:58</t>
+          <t>15-Sep 14:02</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹240 (37.97%) 190 ↓ / 241 ↑</t>
+          <t>₹200 (31.65%) 190 ↓ / 241 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2952,10 +2952,211 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>14-Sep 21:01</t>
+          <t>15-Sep 13:55</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Pranav Constructions IPOL@165.00 (33.06%)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>₹53 (42.74%) 23 ↓ / 53 ↑</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>126.34x</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>₹351.03 Cr</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>7-Sep GMP: 42.5</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>9-Sep GMP: 40</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>15-Sep GMP: 53</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>15-Sep 9:33</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Apana Logistics BSE SMEL@60.00 (0%)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.26x</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>₹34.14 Cr</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>7-Sep GMP: 10</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>9-Sep GMP: 1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>15-Sep GMP: 0</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>15-Sep 9:28</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Qualiance International NSE SMEL@224.90 (77.09%)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>₹81 (63.78%) 50 ↓ / 81 ↑</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>459.22x</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>₹45.11 Cr</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>4-Sep GMP: 55</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>8-Sep GMP: 65</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>9-Sep</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>11-Sep GMP: 81</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>11-Sep 9:34</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>15-Sep 14:02</t>
+          <t>15-Sep 19:28</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>15-Sep 13:57</t>
+          <t>15-Sep 19:30</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15-Sep 13:54</t>
+          <t>15-Sep 19:30</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -820,17 +820,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NSE IPOU</t>
+          <t>Sonaselection India IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹179 (10.03%) 179 ↓ / 310 ↑</t>
+          <t>₹8 (8.08%) 8 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹22561.57 Cr</t>
+          <t>₹141.57 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>15-Sep 13:55</t>
+          <t>15-Sep 19:36</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>15-Sep 14:00</t>
+          <t>15-Sep 19:33</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -954,12 +954,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sonaselection India IPOU</t>
+          <t>NSE IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹5 (5.05%) 5 ↓ / 5 ↑</t>
+          <t>₹169 (9.47%) 169 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹141.57 Cr</t>
+          <t>₹22561.57 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>15-Sep 13:58</t>
+          <t>15-Sep 19:31</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹10 (9.90%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>15-Sep 13:55</t>
+          <t>15-Sep 19:30</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1088,12 +1088,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOU</t>
+          <t>SS Retail IPOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹27 (29.03%) 11 ↓ / 27 ↑</t>
+          <t>₹145 (34.20%) 30 ↓ / 145 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1108,17 +1108,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>15-Sep 14:00</t>
+          <t>15-Sep 19:32</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15-Sep 13:56</t>
+          <t>15-Sep 19:28</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1222,12 +1222,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SS Retail IPOU</t>
+          <t>Jindal Supreme IPOU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹145 (34.20%) 30 ↓ / 145 ↑</t>
+          <t>₹27 (29.03%) 11 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1242,17 +1242,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>15-Sep 13:58</t>
+          <t>15-Sep 19:34</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vama Wovenfab BSE SMEO</t>
+          <t>Quanto Agroworld BSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹10 (2.93%) 10 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1304,27 +1304,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.01x</t>
+          <t>0.02x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹49.54 Cr</t>
+          <t>₹31.02 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 10</t>
+          <t>15-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>15-Sep 14:01</t>
+          <t>15-Sep 19:31</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1356,12 +1356,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shakti Polytarp BSE SMEO</t>
+          <t>Vama Wovenfab BSE SMEO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹10 (2.93%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1371,27 +1371,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.34x</t>
+          <t>0.01x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹26.93 Cr</t>
+          <t>₹49.54 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 0</t>
+          <t>15-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1411,19 +1411,19 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>15-Sep 14:02</t>
+          <t>15-Sep 19:28</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Quanto Agroworld BSE SMEO</t>
+          <t>Shakti Polytarp BSE SMEO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.01x</t>
+          <t>0.64x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹31.02 Cr</t>
+          <t>₹26.93 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>15-Sep 13:56</t>
+          <t>15-Sep 19:32</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Injecto Polymers BSE SMEO</t>
+          <t>Century Business Media BSE SMEO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1572,22 +1572,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.44x</t>
+          <t>1.45x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹56.12 Cr</t>
+          <t>₹17.11 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>15-Sep 13:53</t>
+          <t>15-Sep 19:31</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1624,7 +1624,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Century Business Media BSE SMEO</t>
+          <t>Injecto Polymers BSE SMEO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1639,22 +1639,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.27x</t>
+          <t>0.85x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹17.11 Cr</t>
+          <t>₹56.12 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>15-Sep 13:57</t>
+          <t>15-Sep 19:28</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹4 (9.30%) 4 ↓ / 20 ↑</t>
+          <t>₹3 (6.98%) 3 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6.88x</t>
+          <t>8.78x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>15-Sep 13:59</t>
+          <t>15-Sep 19:31</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1758,12 +1758,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Veegaland Developers IPOCT</t>
+          <t>Panchatv Bharat BSE SMEC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹5 (3.57%) 5 ↓ / 33 ↑</t>
+          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.47x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1783,22 +1783,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹210.00 Cr</t>
+          <t>₹24.58 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 25</t>
+          <t>10-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 5</t>
+          <t>15-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1813,24 +1813,24 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>15-Sep 13:59</t>
+          <t>15-Sep 19:35</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Panchatv Bharat BSE SMECT</t>
+          <t>Raksan Transformers BSE SMEC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹21 (15.00%) 7 ↓ / 21 ↑</t>
+          <t>₹50 (18.32%) 25 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1840,32 +1840,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.72x</t>
+          <t>47.43x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>273</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹24.58 Cr</t>
+          <t>₹150.50 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 7</t>
+          <t>10-Sep GMP: 28</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 21</t>
+          <t>15-Sep GMP: 50</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1880,59 +1880,59 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>15-Sep 13:55</t>
+          <t>15-Sep 19:29</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Maharaja &amp; Speedex India BSE SMECT</t>
+          <t>Om Galaxy BSE SMEC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹20 (10.75%) 15 ↓ / 48 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13.45x</t>
+          <t>2.07x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹80.13 Cr</t>
+          <t>₹105.00 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 30</t>
+          <t>10-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 20</t>
+          <t>15-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>15-Sep 13:55</t>
+          <t>15-Sep 19:33</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1959,12 +1959,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Raksan Transformers BSE SMECT</t>
+          <t>Maharaja &amp; Speedex India BSE SMEC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹50 (18.32%) 25 ↓ / 61 ↑</t>
+          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1974,32 +1974,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16.34x</t>
+          <t>32.41x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹150.50 Cr</t>
+          <t>₹80.13 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 28</t>
+          <t>10-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 50</t>
+          <t>15-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>15-Sep 14:00</t>
+          <t>15-Sep 19:31</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2026,47 +2026,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Om Galaxy BSE SMECT</t>
+          <t>Veegaland Developers IPOC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹7 (5.00%) 7 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.31x</t>
+          <t>14.6x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹105.00 Cr</t>
+          <t>₹210.00 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 0</t>
+          <t>10-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 0</t>
+          <t>15-Sep GMP: 7</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>15-Sep 14:00</t>
+          <t>15-Sep 19:36</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2093,47 +2093,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Amtech Esters BSE SMEC</t>
+          <t>Steamhouse IPOC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹7 (9.33%) 5 ↓ / 11 ↑</t>
+          <t>₹23 (28.40%) 18 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>25.7x</t>
+          <t>32.07x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹17.88 Cr</t>
+          <t>₹414.00 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 11</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>11-Sep GMP: 21</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>15-Sep 14:00</t>
+          <t>15-Sep 19:30</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>15-Sep 14:00</t>
+          <t>15-Sep 19:29</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2227,47 +2227,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Vinod Texworld NSE SMEC</t>
+          <t>Asset Reconstruction IPOC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
+          <t>₹15.5 (11.15%) 14 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>20.1x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹42.83 Cr</t>
+          <t>₹732.97 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>9-Sep GMP: 24</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>11-Sep GMP: 14.5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2282,59 +2282,59 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>15-Sep 13:54</t>
+          <t>15-Sep 19:28</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Infrax Renewable BSE SMEC</t>
+          <t>LCC Projects IPOC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹54 (36.99%) 17 ↓ / 78 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>49.57x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹40.88 Cr</t>
+          <t>₹427.14 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 0</t>
+          <t>9-Sep GMP: 40</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 0</t>
+          <t>11-Sep GMP: 78</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2349,59 +2349,59 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>15-Sep 13:57</t>
+          <t>15-Sep 19:30</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Asset Reconstruction IPOC</t>
+          <t>Vinod Texworld NSE SMEC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹15 (10.79%) 14 ↓ / 30 ↑</t>
+          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20.1x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹732.97 Cr</t>
+          <t>₹42.83 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 24</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 14.5</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2416,59 +2416,59 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>15-Sep 14:01</t>
+          <t>15-Sep 19:28</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Karamtara Engineering IPOC</t>
+          <t>Amtech Esters BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹65 (25.59%) 40 ↓ / 75 ↑</t>
+          <t>₹7 (9.33%) 5 ↓ / 11 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>66.01x</t>
+          <t>25.7x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹875.00 Cr</t>
+          <t>₹17.88 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 75</t>
+          <t>9-Sep GMP: 11</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 67</t>
+          <t>11-Sep GMP: 7</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>15-Sep 13:54</t>
+          <t>15-Sep 19:33</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2495,12 +2495,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LCC Projects IPOC</t>
+          <t>Karamtara Engineering IPOC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹54 (36.99%) 17 ↓ / 78 ↑</t>
+          <t>₹65 (25.59%) 40 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>49.57x</t>
+          <t>66.01x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹427.14 Cr</t>
+          <t>₹875.00 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 40</t>
+          <t>9-Sep GMP: 75</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 78</t>
+          <t>11-Sep GMP: 67</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>15-Sep 14:00</t>
+          <t>15-Sep 19:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹150 (37.13%) 79 ↓ / 160 ↑</t>
+          <t>₹142 (35.15%) 79 ↓ / 160 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>15-Sep 14:00</t>
+          <t>15-Sep 19:36</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2696,47 +2696,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Steamhouse IPOC</t>
+          <t>Infrax Renewable BSE SMEC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹23 (28.40%) 18 ↓ / 24 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>32.07x</t>
+          <t>2.05x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹414.00 Cr</t>
+          <t>₹40.88 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>9-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 21</t>
+          <t>11-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2751,59 +2751,59 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>15-Sep 13:56</t>
+          <t>15-Sep 19:34</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Glass Wall Systems IPOCAllotted</t>
+          <t>Prasol Chemicals IPOCAllotted</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹41 (22.53%) 20 ↓ / 66 ↑</t>
+          <t>₹-13 (-1.92%) -15 ↓ / 165 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>81.65x</t>
+          <t>3.47x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹427.89 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 56</t>
+          <t>8-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 45</t>
+          <t>10-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>15-Sep 14:00</t>
+          <t>15-Sep 19:36</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2830,47 +2830,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Prasol Chemicals IPOCAllotted</t>
+          <t>Glass Wall Systems IPOCAllotted</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹-13 (-1.92%) -15 ↓ / 165 ↑</t>
+          <t>₹41 (22.53%) 20 ↓ / 66 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.47x</t>
+          <t>81.65x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹427.89 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 30</t>
+          <t>8-Sep GMP: 56</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 0</t>
+          <t>10-Sep GMP: 45</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>15-Sep 14:02</t>
+          <t>15-Sep 19:37</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹200 (31.65%) 190 ↓ / 241 ↑</t>
+          <t>₹205 (32.44%) 190 ↓ / 241 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>15-Sep 13:55</t>
+          <t>15-Sep 19:33</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2964,64 +2964,52 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pranav Constructions IPOL@165.00 (33.06%)</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>₹53 (42.74%) 23 ↓ / 53 ↑</t>
-        </is>
-      </c>
+          <t>One Mobikwik Systems IPOCAllotted</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>126.34x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>279</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹351.03 Cr</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>₹572.00 Cr</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>7-Sep GMP: 42.5</t>
+          <t>11-Dec</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 40</t>
+          <t>13-Dec</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>16-Dec</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 53</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>15-Sep 9:33</t>
-        </is>
-      </c>
+          <t>18-Dec</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3098,65 +3086,132 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Pranav Constructions IPOL@165.00 (33.06%)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>₹53 (42.74%) 23 ↓ / 53 ↑</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>126.34x</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>₹351.03 Cr</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>7-Sep GMP: 42.5</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>9-Sep GMP: 40</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>15-Sep GMP: 53</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>15-Sep 9:33</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Qualiance International NSE SMEL@224.90 (77.09%)</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>₹81 (63.78%) 50 ↓ / 81 ↑</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>459.22x</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>₹45.11 Cr</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>4-Sep GMP: 55</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>8-Sep GMP: 65</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>9-Sep</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>11-Sep GMP: 81</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>11-Sep 9:34</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,7 +548,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15-Sep 5:55</t>
+          <t>16-Sep 5:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>15-Sep 19:28</t>
+          <t>16-Sep 12:53</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,17 +627,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEU</t>
+          <t>Himalaya Nutravedics BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹15 (14.15%) 15 ↓ / 45 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -662,27 +662,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>15-Sep 19:30</t>
+          <t>16-Sep 12:57</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -694,12 +694,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMEU</t>
+          <t>Vivekanand Cotspin BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -712,13 +712,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>₹24.05 Cr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>21-Sep</t>
@@ -741,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>15-Sep 5:55</t>
+          <t>16-Sep 12:58</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -753,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMEU</t>
+          <t>FX Multitech BSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -773,42 +781,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹49.81 Cr</t>
+          <t>₹45.24 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15-Sep 19:30</t>
+          <t>16-Sep 12:59</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -820,17 +828,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sonaselection India IPOU</t>
+          <t>Robokidz Eduventures BSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹8 (8.08%) 8 ↓ / 8 ↑</t>
+          <t>₹45 (42.45%) 45 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -840,42 +848,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹141.57 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>15-Sep 19:36</t>
+          <t>16-Sep 12:53</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -887,17 +895,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMEU</t>
+          <t>Axiom Gas Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹50 (42.37%) 27 ↓ / 50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -907,42 +915,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹42.52 Cr</t>
+          <t>₹49.81 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>15-Sep 19:33</t>
+          <t>16-Sep 13:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -959,7 +967,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹169 (9.47%) 169 ↓ / 310 ↑</t>
+          <t>₹160 (8.96%) 160 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1009,7 +1017,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>15-Sep 19:31</t>
+          <t>16-Sep 12:55</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1076,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>15-Sep 19:30</t>
+          <t>16-Sep 12:53</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1088,17 +1096,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SS Retail IPOU</t>
+          <t>Sonaselection India IPOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹145 (34.20%) 30 ↓ / 145 ↑</t>
+          <t>₹8 (8.08%) 8 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1108,42 +1116,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹141.57 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>15-Sep 19:32</t>
+          <t>16-Sep 12:56</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1155,12 +1163,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hero Motors IPOU</t>
+          <t>SpectraA Technology Solutions NSE SMEU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹22 (26.19%) 8 ↓ / 24 ↑</t>
+          <t>₹50 (42.37%) 27 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,42 +1183,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹1000.00 Cr</t>
+          <t>₹42.52 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15-Sep 19:28</t>
+          <t>16-Sep 12:56</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1222,42 +1230,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOU</t>
+          <t>Hero Motors IPOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹27 (29.03%) 11 ↓ / 27 ↑</t>
+          <t>₹5 (5.95%) 5 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.96x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹1000.00 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>16-Sep GMP: 5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1277,7 +1285,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>15-Sep 19:34</t>
+          <t>16-Sep 12:59</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1289,141 +1297,141 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Quanto Agroworld BSE SMEO</t>
+          <t>Jindal Supreme IPOO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹24 (25.81%) 11 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.02x</t>
+          <t>4.23x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹31.02 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 0</t>
+          <t>16-Sep GMP: 24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>15-Sep 19:31</t>
+          <t>16-Sep 12:53</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vama Wovenfab BSE SMEO</t>
+          <t>SS Retail IPOO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹10 (2.93%) 10 ↓ / 10 ↑</t>
+          <t>₹105 (24.76%) 30 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.01x</t>
+          <t>0.77x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹49.54 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 10</t>
+          <t>16-Sep GMP: 105</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>15-Sep 19:28</t>
+          <t>16-Sep 12:57</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Shakti Polytarp BSE SMEO</t>
+          <t>Quanto Agroworld BSE SMEO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1438,17 +1446,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.64x</t>
+          <t>0.05x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹26.93 Cr</t>
+          <t>₹31.02 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1478,12 +1486,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>15-Sep 19:32</t>
+          <t>16-Sep 13:00</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1565,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Century Business Media BSE SMEO</t>
+          <t>Shakti Polytarp BSE SMEO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1572,47 +1580,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.45x</t>
+          <t>0.66x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹17.11 Cr</t>
+          <t>₹26.93 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 0</t>
+          <t>15-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>15-Sep 19:31</t>
+          <t>16-Sep 12:58</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1624,114 +1632,114 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Injecto Polymers BSE SMEO</t>
+          <t>Vama Wovenfab BSE SMEO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹70 (20.53%) 10 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.85x</t>
+          <t>0.07x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹56.12 Cr</t>
+          <t>₹49.54 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 0</t>
+          <t>15-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>15-Sep 19:28</t>
+          <t>16-Sep 13:01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Manika Plastech IPOO</t>
+          <t>Century Business Media BSE SMECT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹3 (6.98%) 3 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.78x</t>
+          <t>5.28x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹125.50 Cr</t>
+          <t>₹17.11 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>11-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>16-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1746,7 +1754,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>15-Sep 19:31</t>
+          <t>16-Sep 12:56</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1758,12 +1766,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Panchatv Bharat BSE SMEC</t>
+          <t>Injecto Polymers BSE SMECT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1773,64 +1781,64 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>1.01x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹24.58 Cr</t>
+          <t>₹56.12 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 7</t>
+          <t>11-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 3</t>
+          <t>16-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>15-Sep 19:35</t>
+          <t>16-Sep 12:55</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Raksan Transformers BSE SMEC</t>
+          <t>Manika Plastech IPOCT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹50 (18.32%) 25 ↓ / 61 ↑</t>
+          <t>₹5 (11.63%) 3 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1840,47 +1848,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.43x</t>
+          <t>13.45x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹150.50 Cr</t>
+          <t>₹125.50 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 28</t>
+          <t>11-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 50</t>
+          <t>16-Sep GMP: 5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>15-Sep 19:29</t>
+          <t>16-Sep 12:55</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1892,47 +1900,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Om Galaxy BSE SMEC</t>
+          <t>Raksan Transformers BSE SMEC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹50 (18.32%) 25 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.07x</t>
+          <t>47.43x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>273</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹105.00 Cr</t>
+          <t>₹150.50 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 0</t>
+          <t>10-Sep GMP: 28</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 0</t>
+          <t>15-Sep GMP: 50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1947,7 +1955,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>15-Sep 19:33</t>
+          <t>16-Sep 12:55</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2014,7 +2022,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>15-Sep 19:31</t>
+          <t>16-Sep 12:55</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2026,47 +2034,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Veegaland Developers IPOC</t>
+          <t>Om Galaxy BSE SMEC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹7 (5.00%) 7 ↓ / 33 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>14.6x</t>
+          <t>2.07x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹210.00 Cr</t>
+          <t>₹105.00 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 25</t>
+          <t>10-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 7</t>
+          <t>15-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2081,7 +2089,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>15-Sep 19:36</t>
+          <t>16-Sep 13:01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2093,62 +2101,62 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Steamhouse IPOC</t>
+          <t>Veegaland Developers IPOC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹23 (28.40%) 18 ↓ / 24 ↑</t>
+          <t>₹6 (4.29%) 6 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>32.07x</t>
+          <t>14.6x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹414.00 Cr</t>
+          <t>₹210.00 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>10-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 21</t>
+          <t>15-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>15-Sep 19:30</t>
+          <t>16-Sep 12:58</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2160,12 +2168,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Manipal Payment and Identity Solutions IPOC</t>
+          <t>Panchatv Bharat BSE SMEC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹-10 (-2.95%) -10 ↓ / 38 ↑</t>
+          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2175,99 +2183,99 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹805.00 Cr</t>
+          <t>₹24.58 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 8</t>
+          <t>10-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>15-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>15-Sep 19:29</t>
+          <t>16-Sep 12:54</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Asset Reconstruction IPOC</t>
+          <t>Vinod Texworld NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹15.5 (11.15%) 14 ↓ / 30 ↑</t>
+          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20.1x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹732.97 Cr</t>
+          <t>₹42.83 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 24</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 14.5</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2282,24 +2290,24 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>15-Sep 19:28</t>
+          <t>16-Sep 13:00</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LCC Projects IPOC</t>
+          <t>LCC Projects IPOCAllotted</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹54 (36.99%) 17 ↓ / 78 ↑</t>
+          <t>₹44 (30.14%) 17 ↓ / 78 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2349,7 +2357,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>15-Sep 19:30</t>
+          <t>16-Sep 12:58</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2361,12 +2369,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Vinod Texworld NSE SMEC</t>
+          <t>Infrax Renewable BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2376,17 +2384,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>2.05x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹42.83 Cr</t>
+          <t>₹40.88 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2396,12 +2404,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>9-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>11-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2416,7 +2424,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>15-Sep 19:28</t>
+          <t>16-Sep 12:54</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2428,47 +2436,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Amtech Esters BSE SMECAllotted</t>
+          <t>Karamtara Engineering IPOCAllotted</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹7 (9.33%) 5 ↓ / 11 ↑</t>
+          <t>₹40 (15.75%) 40 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>25.7x</t>
+          <t>66.01x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹17.88 Cr</t>
+          <t>₹875.00 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 11</t>
+          <t>9-Sep GMP: 75</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>11-Sep GMP: 67</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2483,7 +2491,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>15-Sep 19:33</t>
+          <t>16-Sep 12:53</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2495,12 +2503,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Karamtara Engineering IPOC</t>
+          <t>Rentomojo IPOCAllotted</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹65 (25.59%) 40 ↓ / 75 ↑</t>
+          <t>₹107 (26.49%) 79 ↓ / 160 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2510,32 +2518,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>66.01x</t>
+          <t>72.89x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹875.00 Cr</t>
+          <t>₹1255.57 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 75</t>
+          <t>9-Sep GMP: 143</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 67</t>
+          <t>11-Sep GMP: 148</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2550,7 +2558,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>15-Sep 19:37</t>
+          <t>16-Sep 12:55</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2629,47 +2637,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Rentomojo IPOC</t>
+          <t>Asset Reconstruction IPOCAllotted</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹142 (35.15%) 79 ↓ / 160 ↑</t>
+          <t>₹10 (7.19%) 10 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>72.89x</t>
+          <t>20.1x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹1255.57 Cr</t>
+          <t>₹732.97 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 143</t>
+          <t>9-Sep GMP: 24</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 148</t>
+          <t>11-Sep GMP: 14.5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2684,7 +2692,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>15-Sep 19:36</t>
+          <t>16-Sep 12:58</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2696,12 +2704,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Infrax Renewable BSE SMEC</t>
+          <t>Manipal Payment and Identity Solutions IPOCAllotted</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-10 (-2.95%) -10 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,32 +2719,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>339</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹40.88 Cr</t>
+          <t>₹805.00 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 0</t>
+          <t>9-Sep GMP: 8</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 0</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2751,74 +2759,74 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>15-Sep 19:34</t>
+          <t>16-Sep 12:58</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Prasol Chemicals IPOCAllotted</t>
+          <t>Steamhouse IPOCAllotted</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹-13 (-1.92%) -15 ↓ / 165 ↑</t>
+          <t>₹16 (19.75%) 16 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.47x</t>
+          <t>32.07x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹414.00 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 30</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 0</t>
+          <t>11-Sep GMP: 21</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>15-Sep 19:36</t>
+          <t>16-Sep 12:59</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2830,62 +2838,62 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Glass Wall Systems IPOCAllotted</t>
+          <t>Amtech Esters BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹41 (22.53%) 20 ↓ / 66 ↑</t>
+          <t>₹13 (17.33%) 5 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>81.65x</t>
+          <t>25.7x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹427.89 Cr</t>
+          <t>₹17.88 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 56</t>
+          <t>9-Sep GMP: 11</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 45</t>
+          <t>11-Sep GMP: 7</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>15-Sep 19:37</t>
+          <t>16-Sep 12:56</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2897,47 +2905,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kanohar Electricals IPOCAllotted</t>
+          <t>Prasol Chemicals IPOL@610.00 (-9.76%)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹205 (32.44%) 190 ↓ / 241 ↑</t>
+          <t>₹-13 (-1.92%) -15 ↓ / 165 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>90.59x</t>
+          <t>3.47x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹1055.74 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 218</t>
+          <t>8-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 240</t>
+          <t>10-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2947,12 +2955,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>16-Sep GMP: -13</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>15-Sep 19:33</t>
+          <t>16-Sep 9:36</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2964,52 +2972,64 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>One Mobikwik Systems IPOCAllotted</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>Glass Wall Systems IPOL@194.00 (6.59%)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>₹39 (21.43%) 20 ↓ / 66 ↑</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81.65x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹572.00 Cr</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>₹427.89 Cr</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>11-Dec</t>
+          <t>8-Sep GMP: 56</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>13-Dec</t>
+          <t>10-Sep GMP: 45</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>16-Dec</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>18-Dec</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
+          <t>16-Sep GMP: 39</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>16-Sep 9:36</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3019,199 +3039,65 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Apana Logistics BSE SMEL@60.00 (0%)</t>
+          <t>Kanohar Electricals IPOL@685.50 (8.47%)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
+          <t>₹182 (28.80%) 182 ↓ / 241 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.26x</t>
+          <t>90.59x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹34.14 Cr</t>
+          <t>₹1055.74 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>7-Sep GMP: 10</t>
+          <t>8-Sep GMP: 218</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 1</t>
+          <t>10-Sep GMP: 240</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 0</t>
+          <t>16-Sep GMP: 182</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>15-Sep 9:28</t>
+          <t>16-Sep 9:33</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Pranav Constructions IPOL@165.00 (33.06%)</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>₹53 (42.74%) 23 ↓ / 53 ↑</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>126.34x</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>₹351.03 Cr</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>7-Sep GMP: 42.5</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>9-Sep GMP: 40</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>10-Sep</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>15-Sep GMP: 53</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>15-Sep 9:33</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Qualiance International NSE SMEL@224.90 (77.09%)</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>₹81 (63.78%) 50 ↓ / 81 ↑</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>459.22x</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>₹45.11 Cr</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>4-Sep GMP: 55</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8-Sep GMP: 65</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>9-Sep</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>11-Sep GMP: 81</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>11-Sep 9:34</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16-Sep 12:53</t>
+          <t>16-Sep 18:56</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>16-Sep 12:57</t>
+          <t>16-Sep 18:54</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>16-Sep 12:58</t>
+          <t>16-Sep 19:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>16-Sep 12:59</t>
+          <t>16-Sep 18:59</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>16-Sep 12:53</t>
+          <t>16-Sep 18:58</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16-Sep 13:02</t>
+          <t>16-Sep 18:54</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹160 (8.96%) 160 ↓ / 310 ↑</t>
+          <t>₹157 (8.80%) 157 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16-Sep 12:55</t>
+          <t>16-Sep 18:57</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16-Sep 12:53</t>
+          <t>16-Sep 19:01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹8 (8.08%) 8 ↓ / 8 ↑</t>
+          <t>₹7 (7.07%) 7 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16-Sep 12:56</t>
+          <t>16-Sep 19:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16-Sep 12:56</t>
+          <t>16-Sep 18:56</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1235,17 +1235,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹5 (5.95%) 5 ↓ / 24 ↑</t>
+          <t>₹13 (15.48%) 8 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.96x</t>
+          <t>1.48x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 5</t>
+          <t>16-Sep GMP: 13</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>16-Sep 12:59</t>
+          <t>16-Sep 19:02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹24 (25.81%) 11 ↓ / 27 ↑</t>
+          <t>₹25 (26.88%) 11 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.23x</t>
+          <t>7.56x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 24</t>
+          <t>16-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>16-Sep 12:53</t>
+          <t>16-Sep 18:54</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹105 (24.76%) 30 ↓ / 140 ↑</t>
+          <t>₹100 (23.58%) 30 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.77x</t>
+          <t>1.52x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 105</t>
+          <t>16-Sep GMP: 100</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>16-Sep 12:57</t>
+          <t>16-Sep 18:57</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.05x</t>
+          <t>0.06x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>16-Sep 13:00</t>
+          <t>16-Sep 18:54</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.66x</t>
+          <t>0.72x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>16-Sep 12:58</t>
+          <t>16-Sep 18:54</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.07x</t>
+          <t>0.45x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>16-Sep 13:01</t>
+          <t>16-Sep 18:54</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Century Business Media BSE SMECT</t>
+          <t>Century Business Media BSE SMEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5.28x</t>
+          <t>57.93x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>16-Sep 12:56</t>
+          <t>16-Sep 19:00</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1766,7 +1766,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Injecto Polymers BSE SMECT</t>
+          <t>Injecto Polymers BSE SMEC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.01x</t>
+          <t>1.23x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>16-Sep 12:55</t>
+          <t>16-Sep 18:55</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1833,22 +1833,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Manika Plastech IPOCT</t>
+          <t>Manika Plastech IPOC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹5 (11.63%) 3 ↓ / 20 ↑</t>
+          <t>₹2 (4.65%) 2 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13.45x</t>
+          <t>29.46x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 5</t>
+          <t>16-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>16-Sep 12:55</t>
+          <t>16-Sep 18:55</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>16-Sep 12:55</t>
+          <t>16-Sep 19:02</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
+          <t>₹25 (13.44%) 15 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>16-Sep 12:55</t>
+          <t>16-Sep 19:01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>16-Sep 13:01</t>
+          <t>16-Sep 18:58</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹6 (4.29%) 6 ↓ / 33 ↑</t>
+          <t>₹8 (5.71%) 8 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>16-Sep 12:58</t>
+          <t>16-Sep 19:00</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2168,7 +2168,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Panchatv Bharat BSE SMEC</t>
+          <t>Panchatv Bharat BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>16-Sep 12:54</t>
+          <t>16-Sep 18:58</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>16-Sep 13:00</t>
+          <t>16-Sep 18:53</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹44 (30.14%) 17 ↓ / 78 ↑</t>
+          <t>₹40 (27.40%) 17 ↓ / 78 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>16-Sep 12:58</t>
+          <t>16-Sep 18:59</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>16-Sep 12:54</t>
+          <t>16-Sep 18:54</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹40 (15.75%) 40 ↓ / 75 ↑</t>
+          <t>₹44 (17.32%) 40 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>16-Sep 12:53</t>
+          <t>16-Sep 18:53</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹107 (26.49%) 79 ↓ / 160 ↑</t>
+          <t>₹83 (20.54%) 79 ↓ / 160 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>16-Sep 12:55</t>
+          <t>16-Sep 18:53</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹10 (7.19%) 10 ↓ / 30 ↑</t>
+          <t>₹10.5 (7.55%) 10.50 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>16-Sep 12:58</t>
+          <t>16-Sep 18:54</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹-10 (-2.95%) -10 ↓ / 38 ↑</t>
+          <t>₹-15 (-4.42%) -15 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>16-Sep 12:58</t>
+          <t>16-Sep 18:56</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹16 (19.75%) 16 ↓ / 24 ↑</t>
+          <t>₹15 (18.52%) 15 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>16-Sep 12:59</t>
+          <t>16-Sep 19:01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>16-Sep 12:56</t>
+          <t>16-Sep 18:59</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,12 +506,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
+          <t>₹53 (13.09%) 53 ↓ / 53 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,13 +519,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>₹405.00 Cr</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>24-Sep</t>
@@ -548,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-Sep 5:55</t>
+          <t>17-Sep 13:54</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -560,12 +568,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEU</t>
+          <t>Liqvd Digital BSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -578,21 +586,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹29.06 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>23-Sep</t>
@@ -615,26 +611,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16-Sep 18:56</t>
+          <t>17-Sep 13:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
-        </is>
-      </c>
+          <t>Sai Urja Indo BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -647,12 +639,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -662,29 +654,25 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>29-Sep</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>16-Sep 18:54</t>
-        </is>
-      </c>
+          <t>30-Sep</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
@@ -694,7 +682,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMEU</t>
+          <t>S.K.Offset BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -714,42 +702,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹24.05 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>16-Sep 19:00</t>
+          <t>17-Sep 13:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -761,12 +749,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMEU</t>
+          <t>ArMee Infotech IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -779,44 +767,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹45.24 Cr</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>16-Sep 18:59</t>
+          <t>17-Sep 9:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -828,17 +808,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEU</t>
+          <t>Himalaya Nutravedics BSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹45 (42.45%) 45 ↓ / 45 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -853,7 +833,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -863,27 +843,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>16-Sep 18:58</t>
+          <t>17-Sep 13:54</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -895,7 +875,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMEU</t>
+          <t>Varmora Granito IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -915,42 +895,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹49.81 Cr</t>
+          <t>₹708.02 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16-Sep 18:54</t>
+          <t>17-Sep 13:58</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -962,17 +942,13 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NSE IPOU</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>₹157 (8.80%) 157 ↓ / 310 ↑</t>
-        </is>
-      </c>
+          <t>Anand Seamless BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -982,64 +958,60 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹22561.57 Cr</t>
+          <t>₹25.52 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>24-Sep</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>16-Sep 18:57</t>
-        </is>
-      </c>
+          <t>29-Sep</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kheria Autocomp NSE SMEU</t>
+          <t>Vivekanand Cotspin BSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹10 (9.90%) 10 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1049,42 +1021,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹46.44 Cr</t>
+          <t>₹22.20 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16-Sep 19:01</t>
+          <t>17-Sep 14:01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1096,17 +1068,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sonaselection India IPOU</t>
+          <t>FX Multitech BSE SMEU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹7 (7.07%) 7 ↓ / 8 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1116,42 +1088,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹141.57 Cr</t>
+          <t>₹45.24 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16-Sep 19:02</t>
+          <t>17-Sep 13:59</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1163,12 +1135,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMEU</t>
+          <t>Robokidz Eduventures BSE SMEU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹50 (42.37%) 27 ↓ / 50 ↑</t>
+          <t>₹51 (48.11%) 45 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1183,12 +1155,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹42.52 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1198,27 +1170,27 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16-Sep 18:56</t>
+          <t>17-Sep 13:56</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1230,62 +1202,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hero Motors IPOO</t>
+          <t>Axiom Gas Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹13 (15.48%) 8 ↓ / 24 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.48x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹1000.00 Cr</t>
+          <t>₹50.75 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 13</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>16-Sep 19:02</t>
+          <t>17-Sep 13:54</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1297,12 +1269,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOO</t>
+          <t>SpectraA Technology Solutions NSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹25 (26.88%) 11 ↓ / 27 ↑</t>
+          <t>₹30 (25.42%) 27 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1312,47 +1284,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.56x</t>
+          <t>3.77x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹42.52 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 25</t>
+          <t>17-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>16-Sep 18:54</t>
+          <t>17-Sep 14:02</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1364,62 +1336,62 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SS Retail IPOO</t>
+          <t>NSE IPOO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹100 (23.58%) 30 ↓ / 140 ↑</t>
+          <t>₹150 (8.40%) 145 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.52x</t>
+          <t>0.33x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹22561.57 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 100</t>
+          <t>17-Sep GMP: 150</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>16-Sep 18:57</t>
+          <t>17-Sep 13:56</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1431,67 +1403,67 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Quanto Agroworld BSE SMEO</t>
+          <t>Kheria Autocomp NSE SMEO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹10 (9.90%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.06x</t>
+          <t>0.08x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹31.02 Cr</t>
+          <t>₹46.44 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 0</t>
+          <t>17-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>16-Sep 18:54</t>
+          <t>17-Sep 13:58</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1537,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shakti Polytarp BSE SMEO</t>
+          <t>Sonaselection India IPOO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹3 (3.03%) 3 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1580,47 +1552,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.72x</t>
+          <t>0.33x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹26.93 Cr</t>
+          <t>₹141.57 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 0</t>
+          <t>17-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>16-Sep 18:54</t>
+          <t>17-Sep 13:54</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1632,129 +1604,129 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Vama Wovenfab BSE SMEO</t>
+          <t>Hero Motors IPOO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹70 (20.53%) 10 ↓ / 70 ↑</t>
+          <t>₹7 (8.33%) 7 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.45x</t>
+          <t>2.92x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹49.54 Cr</t>
+          <t>₹1000.00 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 30</t>
+          <t>16-Sep GMP: 13</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>16-Sep 18:54</t>
+          <t>17-Sep 13:54</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Century Business Media BSE SMEC</t>
+          <t>Jindal Supreme IPOO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹28 (30.11%) 11 ↓ / 28 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>57.93x</t>
+          <t>21.26x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹17.11 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 0</t>
+          <t>16-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 0</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>16-Sep 19:00</t>
+          <t>17-Sep 13:55</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1766,62 +1738,62 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Injecto Polymers BSE SMEC</t>
+          <t>SS Retail IPOO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹127 (29.95%) 30 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.23x</t>
+          <t>3.98x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹56.12 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 0</t>
+          <t>16-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 0</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>16-Sep 18:55</t>
+          <t>17-Sep 14:01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1833,12 +1805,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Manika Plastech IPOC</t>
+          <t>Vama Wovenfab BSE SMECT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹2 (4.65%) 2 ↓ / 20 ↑</t>
+          <t>₹3 (0.88%) 3 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1848,114 +1820,114 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>29.46x</t>
+          <t>2.16x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹125.50 Cr</t>
+          <t>₹49.54 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>15-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 2</t>
+          <t>17-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>16-Sep 18:55</t>
+          <t>17-Sep 13:54</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Raksan Transformers BSE SMEC</t>
+          <t>Shakti Polytarp BSE SMECT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹50 (18.32%) 25 ↓ / 61 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.43x</t>
+          <t>1.12x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹150.50 Cr</t>
+          <t>₹26.93 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 28</t>
+          <t>15-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 50</t>
+          <t>17-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>16-Sep 19:02</t>
+          <t>17-Sep 14:02</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1967,74 +1939,74 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Maharaja &amp; Speedex India BSE SMEC</t>
+          <t>Quanto Agroworld BSE SMECT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹25 (13.44%) 15 ↓ / 48 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>32.41x</t>
+          <t>0.55x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹80.13 Cr</t>
+          <t>₹31.02 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 30</t>
+          <t>15-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 28</t>
+          <t>17-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>16-Sep 19:01</t>
+          <t>17-Sep 13:57</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Om Galaxy BSE SMEC</t>
+          <t>Century Business Media BSE SMEC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2049,17 +2021,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.07x</t>
+          <t>57.93x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹105.00 Cr</t>
+          <t>₹17.11 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2069,27 +2041,27 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 0</t>
+          <t>11-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 0</t>
+          <t>16-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>16-Sep 18:58</t>
+          <t>17-Sep 13:57</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2101,62 +2073,62 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Veegaland Developers IPOC</t>
+          <t>Injecto Polymers BSE SMEC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹8 (5.71%) 8 ↓ / 33 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>14.6x</t>
+          <t>1.23x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹210.00 Cr</t>
+          <t>₹56.12 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 25</t>
+          <t>11-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 10</t>
+          <t>16-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>16-Sep 19:00</t>
+          <t>17-Sep 13:59</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2168,12 +2140,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Panchatv Bharat BSE SMECAllotted</t>
+          <t>Manika Plastech IPOC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
+          <t>₹2 (4.65%) 2 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2183,64 +2155,64 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>29.46x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹24.58 Cr</t>
+          <t>₹125.50 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 7</t>
+          <t>11-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 3</t>
+          <t>16-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>16-Sep 18:58</t>
+          <t>17-Sep 13:53</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Vinod Texworld NSE SMECAllotted</t>
+          <t>Panchatv Bharat BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
+          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2250,47 +2222,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹42.83 Cr</t>
+          <t>₹24.58 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>10-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>15-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>16-Sep 18:53</t>
+          <t>17-Sep 13:54</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2302,62 +2274,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LCC Projects IPOCAllotted</t>
+          <t>Om Galaxy BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹40 (27.40%) 17 ↓ / 78 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49.57x</t>
+          <t>2.07x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹427.14 Cr</t>
+          <t>₹105.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 40</t>
+          <t>10-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 78</t>
+          <t>15-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>16-Sep 18:59</t>
+          <t>17-Sep 14:01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2369,129 +2341,129 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Infrax Renewable BSE SMECAllotted</t>
+          <t>Maharaja &amp; Speedex India BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>32.41x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹40.88 Cr</t>
+          <t>₹80.13 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 0</t>
+          <t>10-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 0</t>
+          <t>15-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>16-Sep 18:54</t>
+          <t>17-Sep 13:53</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Karamtara Engineering IPOCAllotted</t>
+          <t>Veegaland Developers IPOCAllotted</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹44 (17.32%) 40 ↓ / 75 ↑</t>
+          <t>₹6 (4.29%) 5 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>66.01x</t>
+          <t>14.6x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹875.00 Cr</t>
+          <t>₹210.00 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 75</t>
+          <t>10-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 67</t>
+          <t>15-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>16-Sep 18:53</t>
+          <t>17-Sep 13:55</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2503,62 +2475,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rentomojo IPOCAllotted</t>
+          <t>Raksan Transformers BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹83 (20.54%) 79 ↓ / 160 ↑</t>
+          <t>₹21 (7.69%) 21 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>72.89x</t>
+          <t>47.43x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>273</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹1255.57 Cr</t>
+          <t>₹150.50 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 143</t>
+          <t>10-Sep GMP: 28</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 148</t>
+          <t>15-Sep GMP: 50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>16-Sep 18:53</t>
+          <t>17-Sep 13:56</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2637,12 +2609,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Asset Reconstruction IPOCAllotted</t>
+          <t>Asset Reconstruction IPOL@139.00 (0%)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹10.5 (7.55%) 10.50 ↓ / 30 ↑</t>
+          <t>₹12 (8.63%) 12 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2687,12 +2659,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>17-Sep GMP: 12</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>16-Sep 18:54</t>
+          <t>17-Sep 9:30</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2704,47 +2676,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Manipal Payment and Identity Solutions IPOCAllotted</t>
+          <t>Steamhouse IPOL@94.50 (16.67%)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹-15 (-4.42%) -15 ↓ / 38 ↑</t>
+          <t>₹13.5 (16.67%) 13.50 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>32.07x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹805.00 Cr</t>
+          <t>₹414.00 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 8</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>11-Sep GMP: 21</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,12 +2726,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>17-Sep GMP: 13.5</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>16-Sep 18:56</t>
+          <t>17-Sep 9:34</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2771,37 +2743,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Steamhouse IPOCAllotted</t>
+          <t>Vinod Texworld NSE SMEL@94.00 (0%)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹15 (18.52%) 15 ↓ / 24 ↑</t>
+          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>32.07x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹414.00 Cr</t>
+          <t>₹42.83 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2811,7 +2783,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 21</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2821,285 +2793,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>17-Sep GMP: 1</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>16-Sep 19:01</t>
+          <t>17-Sep 9:33</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Amtech Esters BSE SMECAllotted</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>₹13 (17.33%) 5 ↓ / 13 ↑</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>25.7x</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>₹17.88 Cr</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>9-Sep GMP: 11</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>11-Sep GMP: 7</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>15-Sep</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>17-Sep</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>16-Sep 18:59</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Prasol Chemicals IPOL@610.00 (-9.76%)</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>₹-13 (-1.92%) -15 ↓ / 165 ↑</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>3.47x</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>₹500.00 Cr</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>8-Sep GMP: 30</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10-Sep GMP: 0</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>11-Sep</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>16-Sep GMP: -13</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>16-Sep 9:36</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Glass Wall Systems IPOL@194.00 (6.59%)</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>₹39 (21.43%) 20 ↓ / 66 ↑</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>81.65x</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>₹427.89 Cr</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>8-Sep GMP: 56</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10-Sep GMP: 45</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>11-Sep</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>16-Sep GMP: 39</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>16-Sep 9:36</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Kanohar Electricals IPOL@685.50 (8.47%)</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>₹182 (28.80%) 182 ↓ / 241 ↑</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>90.59x</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>₹1055.74 Cr</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>8-Sep GMP: 218</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10-Sep GMP: 240</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>11-Sep</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>16-Sep GMP: 182</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>16-Sep 9:33</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹53 (13.09%) 53 ↓ / 53 ↑</t>
+          <t>₹55 (13.58%) 55 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>17-Sep 13:54</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>17-Sep 13:57</t>
+          <t>17-Sep 19:28</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -770,7 +770,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>17-Sep 13:54</t>
+          <t>17-Sep 19:32</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>17-Sep 13:58</t>
+          <t>17-Sep 19:32</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -945,7 +945,11 @@
           <t>Anand Seamless BSE SMEU</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -991,7 +995,11 @@
           <t>29-Sep</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>17-Sep 19:31</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>❌</t>
@@ -1056,7 +1064,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>17-Sep 14:01</t>
+          <t>17-Sep 19:33</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1123,7 +1131,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17-Sep 13:59</t>
+          <t>17-Sep 19:33</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1190,7 +1198,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>17-Sep 13:56</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1257,7 +1265,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17-Sep 13:54</t>
+          <t>17-Sep 19:31</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1292,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.77x</t>
+          <t>5.66x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1324,7 +1332,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>17-Sep 14:02</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1341,7 +1349,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹150 (8.40%) 145 ↓ / 310 ↑</t>
+          <t>₹148 (8.29%) 145 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1351,7 +1359,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.33x</t>
+          <t>0.43x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1371,7 +1379,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 150</t>
+          <t>17-Sep GMP: 148</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1391,7 +1399,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>17-Sep 13:56</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1408,17 +1416,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹10 (9.90%) 10 ↓ / 10 ↑</t>
+          <t>₹12 (11.88%) 10 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.08x</t>
+          <t>0.21x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1438,7 +1446,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 10</t>
+          <t>17-Sep GMP: 12</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1458,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>17-Sep 13:58</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1542,7 +1550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹3 (3.03%) 3 ↓ / 8 ↑</t>
+          <t>₹4 (4.04%) 4 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1552,7 +1560,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.33x</t>
+          <t>0.47x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1572,7 +1580,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 3</t>
+          <t>17-Sep GMP: 4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1592,7 +1600,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>17-Sep 13:54</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1609,7 +1617,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹7 (8.33%) 7 ↓ / 24 ↑</t>
+          <t>₹6.5 (7.74%) 6.50 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1619,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.92x</t>
+          <t>3.58x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1659,7 +1667,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>17-Sep 13:54</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1676,7 +1684,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹28 (30.11%) 11 ↓ / 28 ↑</t>
+          <t>₹30 (32.26%) 11 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1686,7 +1694,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>21.26x</t>
+          <t>31.54x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1726,7 +1734,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>17-Sep 13:55</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1743,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹127 (29.95%) 30 ↓ / 140 ↑</t>
+          <t>₹132 (31.13%) 30 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1753,7 +1761,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.98x</t>
+          <t>6.1x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1793,7 +1801,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>17-Sep 14:01</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1805,7 +1813,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Vama Wovenfab BSE SMECT</t>
+          <t>Vama Wovenfab BSE SMEC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,7 +1828,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.16x</t>
+          <t>2.53x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1860,7 +1868,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>17-Sep 13:54</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1872,22 +1880,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shakti Polytarp BSE SMECT</t>
+          <t>Shakti Polytarp BSE SMEC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6 (10.17%) 6 ↓ / 6 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.12x</t>
+          <t>11.87x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1907,12 +1915,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 0</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 0</t>
+          <t>17-Sep GMP: 6</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1927,7 +1935,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>17-Sep 14:02</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1939,7 +1947,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quanto Agroworld BSE SMECT</t>
+          <t>Quanto Agroworld BSE SMEC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1954,7 +1962,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.55x</t>
+          <t>1.39x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1974,7 +1982,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 0</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1994,7 +2002,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>17-Sep 13:57</t>
+          <t>17-Sep 19:28</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2041,12 +2049,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 0</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 0</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2061,7 +2069,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>17-Sep 13:57</t>
+          <t>17-Sep 19:30</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2108,12 +2116,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 0</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 0</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2128,7 +2136,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>17-Sep 13:59</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2195,7 +2203,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>17-Sep 13:53</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2262,7 +2270,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>17-Sep 13:54</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2309,12 +2317,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 0</t>
+          <t>10-Sep</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 0</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2329,7 +2337,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>17-Sep 14:01</t>
+          <t>17-Sep 19:33</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2396,7 +2404,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>17-Sep 13:53</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2463,7 +2471,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>17-Sep 13:55</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2480,12 +2488,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹21 (7.69%) 21 ↓ / 61 ↑</t>
+          <t>₹10 (3.66%) 10 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2530,7 +2538,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>17-Sep 13:56</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹55 (13.58%) 55 ↓ / 55 ↑</t>
+          <t>₹56 (13.83%) 55 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>17-Sep 13:00</t>
+          <t>18-Sep 5:55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEU</t>
+          <t>Pooja Logistics NSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -639,12 +639,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,7 +682,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEU</t>
+          <t>Sai Urja Indo BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>17-Sep 19:28</t>
+          <t>18-Sep 13:32</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -749,12 +749,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOU</t>
+          <t>Unitec Fibres BSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -767,13 +767,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>₹34.47 Cr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>23-Sep</t>
@@ -796,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>17-Sep 9:00</t>
+          <t>18-Sep 13:32</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -808,7 +816,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEU</t>
+          <t>Elevate Campuses IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -828,42 +836,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>17-Sep 19:32</t>
+          <t>18-Sep 13:34</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -875,7 +883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOU</t>
+          <t>S.K.Offset BSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -895,42 +903,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹708.02 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>17-Sep 19:32</t>
+          <t>18-Sep 13:35</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -942,12 +950,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMEU</t>
+          <t>Swastika Infra IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹3 (1.62%) 3 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -962,54 +970,54 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹25.52 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>17-Sep 19:31</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMEU</t>
+          <t>ArMee Infotech IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1029,42 +1037,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹22.20 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>17-Sep 19:33</t>
+          <t>18-Sep 13:35</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1076,7 +1084,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMEU</t>
+          <t>Adroit Industries IPOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1096,42 +1104,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹45.24 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17-Sep 19:33</t>
+          <t>18-Sep 13:35</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1143,17 +1151,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEU</t>
+          <t>Varmora Granito IPOU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹51 (48.11%) 45 ↓ / 51 ↑</t>
+          <t>₹7 (4.73%) 7 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1163,42 +1171,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹708.02 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1210,7 +1218,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMEU</t>
+          <t>Himalaya Nutravedics BSE SMEU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1230,42 +1238,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹50.75 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17-Sep 19:31</t>
+          <t>18-Sep 13:31</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1277,129 +1285,129 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMEO</t>
+          <t>Anand Seamless BSE SMEU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹30 (25.42%) 27 ↓ / 50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.66x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹42.52 Cr</t>
+          <t>₹25.52 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 30</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:28</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NSE IPOO</t>
+          <t>FX Multitech BSE SMEU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹148 (8.29%) 145 ↓ / 310 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.43x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹22561.57 Cr</t>
+          <t>₹45.24 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 148</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:35</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1411,32 +1419,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kheria Autocomp NSE SMEO</t>
+          <t>Robokidz Eduventures BSE SMEU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹12 (11.88%) 10 ↓ / 12 ↑</t>
+          <t>₹51 (48.11%) 45 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.21x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹46.44 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1446,27 +1454,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 12</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1545,12 +1553,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sonaselection India IPOO</t>
+          <t>Vivekanand Cotspin BSE SMEU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹4 (4.04%) 4 ↓ / 8 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1560,47 +1568,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.47x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹141.57 Cr</t>
+          <t>₹22.20 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 4</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:31</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1612,62 +1620,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hero Motors IPOO</t>
+          <t>Axiom Gas Engineering NSE SMEO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹6.5 (7.74%) 6.50 ↓ / 24 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.58x</t>
+          <t>0.3x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹1000.00 Cr</t>
+          <t>₹50.75 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 13</t>
+          <t>18-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:35</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1679,62 +1687,62 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOO</t>
+          <t>Sonaselection India IPOO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹30 (32.26%) 11 ↓ / 30 ↑</t>
+          <t>₹2 (2.02%) 2 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31.54x</t>
+          <t>0.66x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹141.57 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 25</t>
+          <t>17-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1746,62 +1754,62 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SS Retail IPOO</t>
+          <t>NSE IPOO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹132 (31.13%) 30 ↓ / 140 ↑</t>
+          <t>₹114 (6.39%) 114 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6.1x</t>
+          <t>1.43x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹22561.57 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 90</t>
+          <t>17-Sep GMP: 142</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1813,129 +1821,129 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Vama Wovenfab BSE SMEC</t>
+          <t>SpectraA Technology Solutions NSE SMEO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹3 (0.88%) 3 ↓ / 70 ↑</t>
+          <t>₹30 (25.42%) 27 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.53x</t>
+          <t>14.36x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹49.54 Cr</t>
+          <t>₹42.52 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 30</t>
+          <t>17-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 3</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shakti Polytarp BSE SMEC</t>
+          <t>Kheria Autocomp NSE SMEO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹6 (10.17%) 6 ↓ / 6 ↑</t>
+          <t>₹6 (5.94%) 6 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>11.87x</t>
+          <t>0.26x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹26.93 Cr</t>
+          <t>₹46.44 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>17-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 6</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1947,12 +1955,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quanto Agroworld BSE SMEC</t>
+          <t>Hero Motors IPOCT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
+          <t>₹4 (4.76%) 4 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1962,114 +1970,114 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>7.93x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹31.02 Cr</t>
+          <t>₹1000.00 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep GMP: 13</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 0</t>
+          <t>18-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>17-Sep 19:28</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Century Business Media BSE SMEC</t>
+          <t>Jindal Supreme IPOCT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹33 (35.48%) 11 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>57.93x</t>
+          <t>135.05x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹17.11 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>16-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep GMP: 33</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>17-Sep 19:30</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2081,62 +2089,62 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Injecto Polymers BSE SMEC</t>
+          <t>SS Retail IPOCT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹149 (35.14%) 30 ↓ / 149 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.23x</t>
+          <t>45.84x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹56.12 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>16-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep GMP: 149</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2148,12 +2156,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Manika Plastech IPOC</t>
+          <t>Quanto Agroworld BSE SMEC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹2 (4.65%) 2 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2163,131 +2171,131 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>29.46x</t>
+          <t>1.39x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹125.50 Cr</t>
+          <t>₹31.02 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 2</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:35</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Panchatv Bharat BSE SMECAllotted</t>
+          <t>Shakti Polytarp BSE SMEC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
+          <t>₹6 (10.17%) 6 ↓ / 6 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>11.87x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹24.58 Cr</t>
+          <t>₹26.93 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 7</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 3</t>
+          <t>17-Sep GMP: 6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Om Galaxy BSE SMECAllotted</t>
+          <t>Vama Wovenfab BSE SMEC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹3 (0.88%) 3 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2297,114 +2305,114 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.07x</t>
+          <t>2.53x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹105.00 Cr</t>
+          <t>₹49.54 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>15-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>17-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>17-Sep 19:33</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Maharaja &amp; Speedex India BSE SMECAllotted</t>
+          <t>Manika Plastech IPOCAllotted</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
+          <t>₹2.25 (5.23%) 2 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>32.41x</t>
+          <t>29.46x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹80.13 Cr</t>
+          <t>₹125.50 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 30</t>
+          <t>11-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 28</t>
+          <t>16-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2416,12 +2424,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Veegaland Developers IPOCAllotted</t>
+          <t>Century Business Media BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹6 (4.29%) 5 ↓ / 33 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2431,47 +2439,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>14.6x</t>
+          <t>57.93x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹210.00 Cr</t>
+          <t>₹17.11 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 25</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 10</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:29</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2483,12 +2491,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Raksan Transformers BSE SMECAllotted</t>
+          <t>Injecto Polymers BSE SMEC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹10 (3.66%) 10 ↓ / 61 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2498,47 +2506,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>47.43x</t>
+          <t>1.23x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹150.50 Cr</t>
+          <t>₹56.12 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 28</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 50</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:30</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2617,62 +2625,62 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Asset Reconstruction IPOL@139.00 (0%)</t>
+          <t>Raksan Transformers BSE SMEL@273.00 (0%)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹12 (8.63%) 12 ↓ / 30 ↑</t>
+          <t>₹12 (4.40%) 11 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20.1x</t>
+          <t>47.43x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>273</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹732.97 Cr</t>
+          <t>₹150.50 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 24</t>
+          <t>10-Sep GMP: 28</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 14.5</t>
+          <t>15-Sep GMP: 50</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 12</t>
+          <t>18-Sep GMP: 12</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>17-Sep 9:30</t>
+          <t>18-Sep 9:37</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2684,134 +2692,1340 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Steamhouse IPOL@94.50 (16.67%)</t>
+          <t>Panchatv Bharat BSE SMEL@128.95 (-7.89%)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹13.5 (16.67%) 13.50 ↓ / 24 ↑</t>
+          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>32.07x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹414.00 Cr</t>
+          <t>₹24.58 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>10-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 21</t>
+          <t>15-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 13.5</t>
+          <t>18-Sep GMP: 3</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>17-Sep 9:34</t>
+          <t>18-Sep 9:37</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Maharaja &amp; Speedex India BSE SMEL@250.00 (34.41%)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>32.41x</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>₹80.13 Cr</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>10-Sep GMP: 30</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>15-Sep GMP: 28</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>18-Sep GMP: 28</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>18-Sep 9:37</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Veegaland Developers IPOL@154.00 (10%)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>₹8 (5.71%) 5 ↓ / 33 ↑</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>14.6x</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>₹210.00 Cr</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>10-Sep GMP: 25</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>15-Sep GMP: 10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>18-Sep GMP: 8</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>18-Sep 9:37</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Om Galaxy BSE SMEL@90.20 (0.22%)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2.07x</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>₹105.00 Cr</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>18-Sep GMP: 0</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>18-Sep 9:36</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Vinod Texworld NSE SMEL@94.00 (0%)</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>1.6x</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>₹42.83 Cr</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>9-Sep GMP: 20</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>11-Sep GMP: 1</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>15-Sep</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>17-Sep GMP: 1</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>17-Sep 9:33</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Asset Reconstruction IPOL@139.00 (0%)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>₹12 (8.63%) 12 ↓ / 30 ↑</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>20.1x</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>₹732.97 Cr</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9-Sep GMP: 24</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>11-Sep GMP: 14.5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>17-Sep GMP: 12</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>17-Sep 9:30</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Manipal Payment and Identity Solutions IPOL@330.00 (-2.65%)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>₹-6 (-1.77%) -10 ↓ / 38 ↑</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.42x</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>₹805.00 Cr</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>9-Sep GMP: 8</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>11-Sep GMP: 1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>17-Sep GMP: -6</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>17-Sep 9:36</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Amtech Esters BSE SMEL@100.00 (33.33%)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>₹16 (21.33%) 5 ↓ / 16 ↑</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>25.7x</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>₹17.88 Cr</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>9-Sep GMP: 11</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>11-Sep GMP: 7</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>17-Sep GMP: 16</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>17-Sep 9:36</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>LCC Projects IPOL@189.00 (29.45%)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>₹36 (24.66%) 17 ↓ / 78 ↑</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>49.57x</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>₹427.14 Cr</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>9-Sep GMP: 40</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>11-Sep GMP: 78</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>17-Sep GMP: 36</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>17-Sep 9:34</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Karamtara Engineering IPOL@320.00 (25.98%)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>₹46 (18.11%) 40 ↓ / 75 ↑</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>66.01x</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>₹875.00 Cr</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>9-Sep GMP: 75</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>11-Sep GMP: 67</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>17-Sep GMP: 46</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>17-Sep 9:29</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Rentomojo IPOL@482.45 (19.42%)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>₹87 (21.53%) 79 ↓ / 160 ↑</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>72.89x</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>₹1255.57 Cr</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>9-Sep GMP: 143</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>11-Sep GMP: 148</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>17-Sep GMP: 87</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>17-Sep 9:32</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Infrax Renewable BSE SMEL@104.00 (0%)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2.05x</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>₹40.88 Cr</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>9-Sep</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>17-Sep GMP: 0</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>17-Sep 9:31</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Steamhouse IPOL@94.50 (16.67%)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>₹13.5 (16.67%) 13.50 ↓ / 24 ↑</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>32.07x</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>₹414.00 Cr</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>9-Sep GMP: 20</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>11-Sep GMP: 21</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>17-Sep GMP: 13.5</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>17-Sep 9:34</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Kanohar Electricals IPOL@685.50 (8.47%)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>₹182 (28.80%) 182 ↓ / 241 ↑</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>90.59x</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>₹1055.74 Cr</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>8-Sep GMP: 218</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10-Sep GMP: 240</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>16-Sep GMP: 182</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>16-Sep 9:33</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>GMP</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sub</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Price (₹)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>IPO Size</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>BoA Dt</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Updated-On</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Prasol Chemicals IPOL@610.00 (-9.76%)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>₹-13 (-1.92%) -15 ↓ / 165 ↑</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3.47x</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>₹500.00 Cr</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>8-Sep GMP: 30</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10-Sep GMP: 0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>16-Sep GMP: -13</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>16-Sep 9:36</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Glass Wall Systems IPOL@194.00 (6.59%)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>₹39 (21.43%) 20 ↓ / 66 ↑</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>81.65x</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>₹427.89 Cr</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>8-Sep GMP: 56</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10-Sep GMP: 45</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>16-Sep GMP: 39</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>16-Sep 9:36</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Apana Logistics BSE SMEL@60.00 (0%)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1.26x</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>₹34.14 Cr</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>7-Sep GMP: 10</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>9-Sep GMP: 1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>15-Sep GMP: 0</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>15-Sep 9:28</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Pranav Constructions IPOL@165.00 (33.06%)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>₹53 (42.74%) 23 ↓ / 53 ↑</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>126.34x</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>₹351.03 Cr</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>7-Sep GMP: 42.5</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>9-Sep GMP: 40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>15-Sep GMP: 53</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>15-Sep 9:33</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Qualiance International NSE SMEL@224.90 (77.09%)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>₹81 (63.78%) 50 ↓ / 81 ↑</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>459.22x</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>₹45.11 Cr</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4-Sep GMP: 55</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>8-Sep GMP: 65</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>9-Sep</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>11-Sep GMP: 81</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>11-Sep 9:34</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹56 (13.83%) 55 ↓ / 56 ↑</t>
+          <t>₹57 (14.07%) 55 ↓ / 57 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -626,7 +626,11 @@
           <t>Pooja Logistics NSE SMEU</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -672,7 +676,11 @@
           <t>30-Sep</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>18-Sep 18:31</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
@@ -737,7 +745,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>18-Sep 13:32</t>
+          <t>18-Sep 18:29</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -804,7 +812,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>18-Sep 13:32</t>
+          <t>18-Sep 18:32</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -821,7 +829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹15 (4.14%) 15 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -871,7 +879,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>18-Sep 13:34</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -938,7 +946,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>18-Sep 13:35</t>
+          <t>18-Sep 18:32</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -955,7 +963,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹3 (1.62%) 3 ↓ / 3 ↑</t>
+          <t>₹5 (2.70%) 5 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1005,7 +1013,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1072,7 +1080,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>18-Sep 13:35</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1089,12 +1097,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹9 (6.72%) 9 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1139,7 +1147,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>18-Sep 13:35</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1156,12 +1164,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹7 (4.73%) 7 ↓ / 10 ↑</t>
+          <t>₹15 (10.14%) 10 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1206,7 +1214,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1273,7 +1281,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>18-Sep 13:31</t>
+          <t>18-Sep 18:35</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1340,7 +1348,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>18-Sep 13:28</t>
+          <t>18-Sep 18:34</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1407,7 +1415,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>18-Sep 13:35</t>
+          <t>18-Sep 18:35</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1474,7 +1482,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1608,7 +1616,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>18-Sep 13:31</t>
+          <t>18-Sep 18:30</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1635,7 +1643,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.3x</t>
+          <t>0.62x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1675,7 +1683,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>18-Sep 13:35</t>
+          <t>18-Sep 18:31</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1702,7 +1710,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.66x</t>
+          <t>0.47x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1742,7 +1750,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1759,7 +1767,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹114 (6.39%) 114 ↓ / 310 ↑</t>
+          <t>₹110 (6.16%) 110 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1769,7 +1777,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.43x</t>
+          <t>1.04x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1809,7 +1817,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1826,7 +1834,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹30 (25.42%) 27 ↓ / 50 ↑</t>
+          <t>₹45 (38.14%) 27 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1836,7 +1844,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>14.36x</t>
+          <t>19.9x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1876,7 +1884,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1893,7 +1901,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹6 (5.94%) 6 ↓ / 10 ↑</t>
+          <t>₹10 (9.90%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1903,7 +1911,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.26x</t>
+          <t>0.41x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1943,7 +1951,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1955,12 +1963,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hero Motors IPOCT</t>
+          <t>Hero Motors IPOC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹4 (4.76%) 4 ↓ / 24 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1970,7 +1978,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7.93x</t>
+          <t>7.01x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1995,7 +2003,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 4</t>
+          <t>18-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2010,7 +2018,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2022,12 +2030,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOCT</t>
+          <t>Jindal Supreme IPOC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹33 (35.48%) 11 ↓ / 33 ↑</t>
+          <t>₹31 (33.33%) 11 ↓ / 31 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2037,7 +2045,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>135.05x</t>
+          <t>177.03x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2062,7 +2070,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 33</t>
+          <t>18-Sep GMP: 31</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2077,7 +2085,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2089,12 +2097,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SS Retail IPOCT</t>
+          <t>SS Retail IPOC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹149 (35.14%) 30 ↓ / 149 ↑</t>
+          <t>₹144 (33.96%) 30 ↓ / 144 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2104,7 +2112,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>45.84x</t>
+          <t>107.41x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2129,7 +2137,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 149</t>
+          <t>18-Sep GMP: 144</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2144,7 +2152,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2211,7 +2219,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>18-Sep 13:35</t>
+          <t>18-Sep 18:28</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2278,7 +2286,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2345,7 +2353,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2362,12 +2370,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹2.25 (5.23%) 2 ↓ / 20 ↑</t>
+          <t>₹2 (4.65%) 2 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2412,7 +2420,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2479,7 +2487,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>18-Sep 13:29</t>
+          <t>18-Sep 18:28</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2546,7 +2554,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>18-Sep 13:30</t>
+          <t>18-Sep 18:28</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A-One Steels IPOU</t>
+          <t>Bench Mark Infotech Services NSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹57 (14.07%) 55 ↓ / 57 ↑</t>
+          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,44 +519,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 11:50</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -568,17 +560,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEU</t>
+          <t>A-One Steels IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
+          <t>₹62 (15.31%) 55 ↓ / 62 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -586,54 +578,66 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹405.00 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>18-Sep 5:55</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEU</t>
+          <t>Adroit Industries IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹37 (27.61%) 37 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -643,17 +647,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -678,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>18-Sep 18:31</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -690,7 +694,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEU</t>
+          <t>ArMee Infotech IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -710,17 +714,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -745,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>18-Sep 18:29</t>
+          <t>19-Sep 13:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -757,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEU</t>
+          <t>Liqvd Digital BSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -777,17 +781,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -812,24 +816,24 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>18-Sep 18:32</t>
+          <t>19-Sep 12:56</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOU</t>
+          <t>Swastika Infra IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹15 (4.14%) 15 ↓ / 15 ↑</t>
+          <t>₹3 (1.62%) 3 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -844,17 +848,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -879,7 +883,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -946,7 +950,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>18-Sep 18:32</t>
+          <t>19-Sep 12:57</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -958,12 +962,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOU</t>
+          <t>Sai Urja Indo BSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹5 (2.70%) 5 ↓ / 5 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -978,17 +982,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹160.88 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1013,7 +1017,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1025,12 +1029,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOU</t>
+          <t>Elevate Campuses IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹16 (4.42%) 15 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1045,17 +1049,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1080,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1092,17 +1096,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOU</t>
+          <t>Unitec Fibres BSE SMEU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹9 (6.72%) 9 ↓ / 9 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1112,17 +1116,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1147,7 +1151,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1159,17 +1163,13 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOU</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>₹15 (10.14%) 10 ↓ / 15 ↑</t>
-        </is>
-      </c>
+          <t>Core Integra Consulting NSE SMEU</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1179,54 +1179,50 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹708.02 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>29-Sep</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>18-Sep 18:37</t>
-        </is>
-      </c>
+          <t>30-Sep</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEU</t>
+          <t>Pooja Logistics NSE SMEU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1246,12 +1242,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1261,27 +1257,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>18-Sep 18:35</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1293,7 +1289,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMEU</t>
+          <t>Himalaya Nutravedics BSE SMEU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1313,17 +1309,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹25.52 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1348,19 +1344,19 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>18-Sep 18:34</t>
+          <t>19-Sep 13:01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMEU</t>
+          <t>Anand Seamless BSE SMEU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1380,64 +1376,64 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹45.24 Cr</t>
+          <t>₹25.52 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>18-Sep 18:35</t>
+          <t>19-Sep 12:59</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEU</t>
+          <t>Varmora Granito IPOU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹51 (48.11%) 45 ↓ / 51 ↑</t>
+          <t>₹15 (10.14%) 10 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1447,42 +1443,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹708.02 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1616,7 +1612,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>18-Sep 18:30</t>
+          <t>19-Sep 12:53</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1628,62 +1624,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMEO</t>
+          <t>Robokidz Eduventures BSE SMEU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹51 (48.11%) 45 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.62x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹50.75 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 0</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>18-Sep 18:31</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1695,12 +1691,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sonaselection India IPOO</t>
+          <t>FX Multitech BSE SMEU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹2 (2.02%) 2 ↓ / 8 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1710,47 +1706,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.47x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹141.57 Cr</t>
+          <t>₹45.24 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 2</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:00</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1762,62 +1758,62 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NSE IPOO</t>
+          <t>Axiom Gas Engineering NSE SMEO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹110 (6.16%) 110 ↓ / 310 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.04x</t>
+          <t>0.62x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹22561.57 Cr</t>
+          <t>₹50.75 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 142</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1829,32 +1825,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMEO</t>
+          <t>Kheria Autocomp NSE SMEO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹45 (38.14%) 27 ↓ / 50 ↑</t>
+          <t>₹7 (6.93%) 7 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19.9x</t>
+          <t>0.41x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹42.52 Cr</t>
+          <t>₹46.44 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1864,7 +1860,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 30</t>
+          <t>17-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1884,7 +1880,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1896,42 +1892,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kheria Autocomp NSE SMEO</t>
+          <t>NSE IPOO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹10 (9.90%) 10 ↓ / 10 ↑</t>
+          <t>₹83 (4.65%) 83 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.41x</t>
+          <t>1.04x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹46.44 Cr</t>
+          <t>₹22561.57 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 10</t>
+          <t>17-Sep GMP: 142</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1951,7 +1947,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1963,62 +1959,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hero Motors IPOC</t>
+          <t>SpectraA Technology Solutions NSE SMEO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 24 ↑</t>
+          <t>₹45 (38.14%) 27 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7.01x</t>
+          <t>19.93x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹1000.00 Cr</t>
+          <t>₹42.52 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 13</t>
+          <t>17-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 0</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2030,62 +2026,62 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOC</t>
+          <t>Sonaselection India IPOO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹31 (33.33%) 11 ↓ / 31 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>177.03x</t>
+          <t>0.47x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹141.57 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 25</t>
+          <t>17-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 31</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2097,12 +2093,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SS Retail IPOC</t>
+          <t>Jindal Supreme IPOC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹144 (33.96%) 30 ↓ / 144 ↑</t>
+          <t>₹26.5 (28.49%) 11 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2112,32 +2108,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>107.41x</t>
+          <t>177.03x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 90</t>
+          <t>16-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 144</t>
+          <t>18-Sep GMP: 26.5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2152,7 +2148,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2164,129 +2160,129 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quanto Agroworld BSE SMEC</t>
+          <t>SS Retail IPOC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹147 (34.67%) 30 ↓ / 147 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>107.41x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹31.02 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep GMP: 145</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>18-Sep 18:28</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Shakti Polytarp BSE SMEC</t>
+          <t>Hero Motors IPOC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹6 (10.17%) 6 ↓ / 6 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11.87x</t>
+          <t>7.01x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹26.93 Cr</t>
+          <t>₹1000.00 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep GMP: 13</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 6</t>
+          <t>18-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2298,47 +2294,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Vama Wovenfab BSE SMEC</t>
+          <t>Shakti Polytarp BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹3 (0.88%) 3 ↓ / 70 ↑</t>
+          <t>₹5 (8.47%) 5 ↓ / 6 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.53x</t>
+          <t>11.87x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹49.54 Cr</t>
+          <t>₹26.93 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 30</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 3</t>
+          <t>17-Sep GMP: 6</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2353,24 +2349,24 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Manika Plastech IPOCAllotted</t>
+          <t>Vama Wovenfab BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹2 (4.65%) 2 ↓ / 20 ↑</t>
+          <t>₹3 (0.88%) 3 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2380,59 +2376,59 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>29.46x</t>
+          <t>2.53x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹125.50 Cr</t>
+          <t>₹49.54 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>15-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 2</t>
+          <t>17-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Century Business Media BSE SMECAllotted</t>
+          <t>Quanto Agroworld BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2447,64 +2443,64 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>57.93x</t>
+          <t>1.39x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹17.11 Cr</t>
+          <t>₹31.02 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>18-Sep 18:28</t>
+          <t>19-Sep 12:55</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Injecto Polymers BSE SMEC</t>
+          <t>Manika Plastech IPOCAllotted</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹2 (4.65%) 1.60 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2514,32 +2510,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.23x</t>
+          <t>29.46x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹56.12 Cr</t>
+          <t>₹125.50 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>11-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>16-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2554,7 +2550,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>18-Sep 18:28</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2633,12 +2629,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Raksan Transformers BSE SMEL@273.00 (0%)</t>
+          <t>Century Business Media BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹12 (4.40%) 11 ↓ / 61 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2648,47 +2644,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>47.43x</t>
+          <t>57.93x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹150.50 Cr</t>
+          <t>₹17.11 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 28</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 50</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 12</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>19-Sep 12:53</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2700,12 +2696,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Panchatv Bharat BSE SMEL@128.95 (-7.89%)</t>
+          <t>Injecto Polymers BSE SMEC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2715,99 +2711,99 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>1.23x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹24.58 Cr</t>
+          <t>₹56.12 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 7</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 3</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 3</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>19-Sep 12:57</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Maharaja &amp; Speedex India BSE SMEL@250.00 (34.41%)</t>
+          <t>Om Galaxy BSE SMEL@90.20 (0.22%)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>32.41x</t>
+          <t>2.07x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹80.13 Cr</t>
+          <t>₹105.00 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 30</t>
+          <t>10-Sep</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 28</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2817,12 +2813,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 28</t>
+          <t>18-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>18-Sep 9:36</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2834,47 +2830,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Veegaland Developers IPOL@154.00 (10%)</t>
+          <t>Raksan Transformers BSE SMEL@273.00 (0%)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹8 (5.71%) 5 ↓ / 33 ↑</t>
+          <t>₹12 (4.40%) 11 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>14.6x</t>
+          <t>47.43x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>273</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹210.00 Cr</t>
+          <t>₹150.50 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 25</t>
+          <t>10-Sep GMP: 28</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 10</t>
+          <t>15-Sep GMP: 50</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,7 +2880,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 8</t>
+          <t>18-Sep GMP: 12</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2901,47 +2897,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Om Galaxy BSE SMEL@90.20 (0.22%)</t>
+          <t>Veegaland Developers IPOL@154.00 (10%)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹8 (5.71%) 5 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.07x</t>
+          <t>14.6x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹105.00 Cr</t>
+          <t>₹210.00 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>10-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>15-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2951,12 +2947,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 0</t>
+          <t>18-Sep GMP: 8</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>18-Sep 9:36</t>
+          <t>18-Sep 9:37</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2968,12 +2964,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Vinod Texworld NSE SMEL@94.00 (0%)</t>
+          <t>Panchatv Bharat BSE SMEL@128.95 (-7.89%)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
+          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2983,47 +2979,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹42.83 Cr</t>
+          <t>₹24.58 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>10-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>15-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 1</t>
+          <t>18-Sep GMP: 3</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>17-Sep 9:33</t>
+          <t>18-Sep 9:37</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3035,62 +3031,62 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Asset Reconstruction IPOL@139.00 (0%)</t>
+          <t>Maharaja &amp; Speedex India BSE SMEL@250.00 (34.41%)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹12 (8.63%) 12 ↓ / 30 ↑</t>
+          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20.1x</t>
+          <t>32.41x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹732.97 Cr</t>
+          <t>₹80.13 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 24</t>
+          <t>10-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 14.5</t>
+          <t>15-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 12</t>
+          <t>18-Sep GMP: 28</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>17-Sep 9:30</t>
+          <t>18-Sep 9:37</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3102,47 +3098,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Manipal Payment and Identity Solutions IPOL@330.00 (-2.65%)</t>
+          <t>Karamtara Engineering IPOL@320.00 (25.98%)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>₹-6 (-1.77%) -10 ↓ / 38 ↑</t>
+          <t>₹46 (18.11%) 40 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>66.01x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹805.00 Cr</t>
+          <t>₹875.00 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 8</t>
+          <t>9-Sep GMP: 75</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>11-Sep GMP: 67</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3152,12 +3148,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>17-Sep GMP: -6</t>
+          <t>17-Sep GMP: 46</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>17-Sep 9:36</t>
+          <t>17-Sep 9:29</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3236,47 +3232,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LCC Projects IPOL@189.00 (29.45%)</t>
+          <t>Vinod Texworld NSE SMEL@94.00 (0%)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>₹36 (24.66%) 17 ↓ / 78 ↑</t>
+          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>49.57x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹427.14 Cr</t>
+          <t>₹42.83 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 40</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 78</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3286,64 +3282,64 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 36</t>
+          <t>17-Sep GMP: 1</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>17-Sep 9:34</t>
+          <t>17-Sep 9:33</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Karamtara Engineering IPOL@320.00 (25.98%)</t>
+          <t>Infrax Renewable BSE SMEL@104.00 (0%)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹46 (18.11%) 40 ↓ / 75 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>66.01x</t>
+          <t>2.05x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹875.00 Cr</t>
+          <t>₹40.88 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 75</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 67</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3353,64 +3349,64 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 46</t>
+          <t>17-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>17-Sep 9:29</t>
+          <t>17-Sep 9:31</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Rentomojo IPOL@482.45 (19.42%)</t>
+          <t>Asset Reconstruction IPOL@139.00 (0%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>₹87 (21.53%) 79 ↓ / 160 ↑</t>
+          <t>₹12 (8.63%) 12 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>72.89x</t>
+          <t>20.1x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹1255.57 Cr</t>
+          <t>₹732.97 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 143</t>
+          <t>9-Sep GMP: 24</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 148</t>
+          <t>11-Sep GMP: 14.5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3420,12 +3416,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 87</t>
+          <t>17-Sep GMP: 12</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>17-Sep 9:32</t>
+          <t>17-Sep 9:30</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3437,47 +3433,47 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Infrax Renewable BSE SMEL@104.00 (0%)</t>
+          <t>Steamhouse IPOL@94.50 (16.67%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹13.5 (16.67%) 13.50 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>32.07x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹40.88 Cr</t>
+          <t>₹414.00 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>11-Sep GMP: 21</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3487,64 +3483,64 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 0</t>
+          <t>17-Sep GMP: 13.5</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>17-Sep 9:31</t>
+          <t>17-Sep 9:34</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Steamhouse IPOL@94.50 (16.67%)</t>
+          <t>Rentomojo IPOL@482.45 (19.42%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>₹13.5 (16.67%) 13.50 ↓ / 24 ↑</t>
+          <t>₹87 (21.53%) 79 ↓ / 160 ↑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>32.07x</t>
+          <t>72.89x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹414.00 Cr</t>
+          <t>₹1255.57 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>9-Sep GMP: 143</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 21</t>
+          <t>11-Sep GMP: 148</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3554,12 +3550,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 13.5</t>
+          <t>17-Sep GMP: 87</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>17-Sep 9:34</t>
+          <t>17-Sep 9:32</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3571,62 +3567,62 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kanohar Electricals IPOL@685.50 (8.47%)</t>
+          <t>Manipal Payment and Identity Solutions IPOL@330.00 (-2.65%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹182 (28.80%) 182 ↓ / 241 ↑</t>
+          <t>₹-6 (-1.77%) -10 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>90.59x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>339</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹1055.74 Cr</t>
+          <t>₹805.00 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 218</t>
+          <t>9-Sep GMP: 8</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 240</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 182</t>
+          <t>17-Sep GMP: -6</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>16-Sep 9:33</t>
+          <t>17-Sep 9:36</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3705,62 +3701,62 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Prasol Chemicals IPOL@610.00 (-9.76%)</t>
+          <t>LCC Projects IPOL@189.00 (29.45%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹-13 (-1.92%) -15 ↓ / 165 ↑</t>
+          <t>₹36 (24.66%) 17 ↓ / 78 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3.47x</t>
+          <t>49.57x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹427.14 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 30</t>
+          <t>9-Sep GMP: 40</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 0</t>
+          <t>11-Sep GMP: 78</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>16-Sep GMP: -13</t>
+          <t>17-Sep GMP: 36</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>16-Sep 9:36</t>
+          <t>17-Sep 9:34</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3772,12 +3768,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Glass Wall Systems IPOL@194.00 (6.59%)</t>
+          <t>Kanohar Electricals IPOL@685.50 (8.47%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹39 (21.43%) 20 ↓ / 66 ↑</t>
+          <t>₹182 (28.80%) 182 ↓ / 241 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3787,32 +3783,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>81.65x</t>
+          <t>90.59x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹427.89 Cr</t>
+          <t>₹1055.74 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 56</t>
+          <t>8-Sep GMP: 218</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 45</t>
+          <t>10-Sep GMP: 240</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3822,12 +3818,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 39</t>
+          <t>16-Sep GMP: 182</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>16-Sep 9:36</t>
+          <t>16-Sep 9:33</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3839,12 +3835,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Apana Logistics BSE SMEL@60.00 (0%)</t>
+          <t>Prasol Chemicals IPOL@610.00 (-9.76%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
+          <t>₹-13 (-1.92%) -15 ↓ / 165 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3854,64 +3850,64 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.26x</t>
+          <t>3.47x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹34.14 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>7-Sep GMP: 10</t>
+          <t>8-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 1</t>
+          <t>10-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 0</t>
+          <t>16-Sep GMP: -13</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>15-Sep 9:28</t>
+          <t>16-Sep 9:36</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Pranav Constructions IPOL@165.00 (33.06%)</t>
+          <t>Glass Wall Systems IPOL@194.00 (6.59%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹53 (42.74%) 23 ↓ / 53 ↑</t>
+          <t>₹39 (21.43%) 20 ↓ / 66 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3921,47 +3917,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>126.34x</t>
+          <t>81.65x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹351.03 Cr</t>
+          <t>₹427.89 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>7-Sep GMP: 42.5</t>
+          <t>8-Sep GMP: 56</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 40</t>
+          <t>10-Sep GMP: 45</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 53</t>
+          <t>16-Sep GMP: 39</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>15-Sep 9:33</t>
+          <t>16-Sep 9:36</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3973,67 +3969,67 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Qualiance International NSE SMEL@224.90 (77.09%)</t>
+          <t>Apana Logistics BSE SMEL@60.00 (0%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>₹81 (63.78%) 50 ↓ / 81 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>459.22x</t>
+          <t>1.26x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹45.11 Cr</t>
+          <t>₹34.14 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4-Sep GMP: 55</t>
+          <t>7-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 65</t>
+          <t>9-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>10-Sep</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 81</t>
+          <t>15-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>11-Sep 9:34</t>
+          <t>15-Sep 9:28</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹62 (15.31%) 55 ↓ / 62 ↑</t>
+          <t>₹64 (15.80%) 55 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹37 (27.61%) 37 ↓ / 37 ↑</t>
+          <t>₹41 (30.60%) 37 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (0.27%) 1 ↓ / 1 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>19-Sep 13:00</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19-Sep 12:56</t>
+          <t>19-Sep 17:55</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>19-Sep 12:57</t>
+          <t>19-Sep 17:53</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>19-Sep 13:01</t>
+          <t>19-Sep 17:53</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 17:58</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19-Sep 13:01</t>
+          <t>19-Sep 17:55</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>19-Sep 12:59</t>
+          <t>19-Sep 17:56</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹15 (10.14%) 10 ↓ / 15 ↑</t>
+          <t>₹12 (8.11%) 10 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>19-Sep 12:53</t>
+          <t>19-Sep 17:58</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>19-Sep 13:00</t>
+          <t>19-Sep 17:57</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>19-Sep 13:00</t>
+          <t>19-Sep 17:56</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹83 (4.65%) 83 ↓ / 310 ↑</t>
+          <t>₹73 (4.09%) 73 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
+          <t>₹2 (2.02%) 2 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹26.5 (28.49%) 11 ↓ / 30 ↑</t>
+          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 24 ↑</t>
+          <t>₹-2 (-2.38%) -2 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>19-Sep 12:55</t>
+          <t>19-Sep 17:57</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>19-Sep 12:53</t>
+          <t>19-Sep 18:01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>19-Sep 12:57</t>
+          <t>19-Sep 17:57</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19-Sep 11:50</t>
+          <t>20-Sep 5:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -627,17 +627,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOU</t>
+          <t>Peshwa Wheat BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹41 (30.60%) 37 ↓ / 41 ↑</t>
+          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -645,61 +645,53 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 5:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOU</t>
+          <t>Unitec Fibres BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹1 (0.27%) 1 ↓ / 1 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -714,17 +706,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -749,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:34</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -761,7 +753,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEU</t>
+          <t>Core Integra Consulting NSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -781,17 +773,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -816,7 +808,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19-Sep 17:55</t>
+          <t>20-Sep 5:55</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -883,7 +875,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -950,7 +942,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>19-Sep 17:53</t>
+          <t>20-Sep 13:34</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -962,12 +954,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEU</t>
+          <t>Elevate Campuses IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹16 (4.42%) 15 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -982,17 +974,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1017,7 +1009,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>19-Sep 17:53</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1029,12 +1021,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOU</t>
+          <t>ArMee Infotech IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹16 (4.42%) 15 ↓ / 16 ↑</t>
+          <t>₹1 (0.27%) 1 ↓ / 1 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1049,17 +1041,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1084,7 +1076,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1096,7 +1088,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEU</t>
+          <t>Sai Urja Indo BSE SMEU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1116,17 +1108,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1151,7 +1143,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>19-Sep 17:58</t>
+          <t>20-Sep 13:29</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1163,13 +1155,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEU</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>Adroit Industries IPOU</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>₹35 (26.12%) 35 ↓ / 37 ↑</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1179,17 +1175,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1212,10 +1208,14 @@
           <t>30-Sep</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>20-Sep 13:37</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:31</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1289,7 +1289,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEU</t>
+          <t>Liqvd Digital BSE SMEU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1309,64 +1309,64 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19-Sep 17:55</t>
+          <t>20-Sep 13:36</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMEU</t>
+          <t>Varmora Granito IPOU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹12 (8.11%) 10 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1376,17 +1376,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹25.52 Cr</t>
+          <t>₹708.02 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1411,29 +1411,29 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>19-Sep 17:56</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOU</t>
+          <t>Himalaya Nutravedics BSE SMEU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹12 (8.11%) 10 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1443,17 +1443,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹708.02 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:31</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1557,7 +1557,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMEU</t>
+          <t>Anand Seamless BSE SMEU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1577,64 +1577,64 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹22.20 Cr</t>
+          <t>₹25.52 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>19-Sep 17:58</t>
+          <t>20-Sep 13:33</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEU</t>
+          <t>Vivekanand Cotspin BSE SMEU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹51 (48.11%) 45 ↓ / 51 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1644,17 +1644,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹22.20 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:31</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>19-Sep 17:57</t>
+          <t>20-Sep 13:28</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1758,62 +1758,62 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMEO</t>
+          <t>Robokidz Eduventures BSE SMEU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹51 (48.11%) 45 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.62x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹50.75 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>19-Sep 17:56</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1825,62 +1825,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kheria Autocomp NSE SMEO</t>
+          <t>Axiom Gas Engineering NSE SMEO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹7 (6.93%) 7 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.41x</t>
+          <t>0.62x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹46.44 Cr</t>
+          <t>₹50.75 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 10</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:29</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1892,42 +1892,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NSE IPOO</t>
+          <t>Kheria Autocomp NSE SMEO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹73 (4.09%) 73 ↓ / 310 ↑</t>
+          <t>₹7 (6.93%) 7 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.04x</t>
+          <t>0.41x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹22561.57 Cr</t>
+          <t>₹46.44 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 142</t>
+          <t>17-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1959,42 +1959,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMEO</t>
+          <t>Sonaselection India IPOO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹45 (38.14%) 27 ↓ / 50 ↑</t>
+          <t>₹2 (2.02%) 2 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19.93x</t>
+          <t>0.47x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹42.52 Cr</t>
+          <t>₹141.57 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 30</t>
+          <t>17-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2026,12 +2026,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sonaselection India IPOO</t>
+          <t>NSE IPOO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹2 (2.02%) 2 ↓ / 8 ↑</t>
+          <t>₹48 (2.69%) 48 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2041,27 +2041,27 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.47x</t>
+          <t>1.04x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹141.57 Cr</t>
+          <t>₹22561.57 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 2</t>
+          <t>17-Sep GMP: 142</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2093,12 +2093,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOC</t>
+          <t>SpectraA Technology Solutions NSE SMEO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
+          <t>₹45 (38.14%) 27 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2108,47 +2108,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>177.03x</t>
+          <t>19.93x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹42.52 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 25</t>
+          <t>17-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 26.5</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2227,47 +2227,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hero Motors IPOC</t>
+          <t>Jindal Supreme IPOC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹-2 (-2.38%) -2 ↓ / 24 ↑</t>
+          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.01x</t>
+          <t>177.03x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹1000.00 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 13</t>
+          <t>16-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 0</t>
+          <t>18-Sep GMP: 26.5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2294,62 +2294,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Shakti Polytarp BSE SMECAllotted</t>
+          <t>Hero Motors IPOC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹5 (8.47%) 5 ↓ / 6 ↑</t>
+          <t>₹-2 (-2.38%) -2 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11.87x</t>
+          <t>7.01x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹26.93 Cr</t>
+          <t>₹1000.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep GMP: 13</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 6</t>
+          <t>18-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>19-Sep 17:57</t>
+          <t>20-Sep 13:36</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2495,62 +2495,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Manika Plastech IPOCAllotted</t>
+          <t>Shakti Polytarp BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹2 (4.65%) 1.60 ↓ / 20 ↑</t>
+          <t>₹5 (8.47%) 5 ↓ / 6 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>29.46x</t>
+          <t>11.87x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹125.50 Cr</t>
+          <t>₹26.93 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 2</t>
+          <t>17-Sep GMP: 6</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>19-Sep 18:01</t>
+          <t>20-Sep 13:31</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2696,12 +2696,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Injecto Polymers BSE SMEC</t>
+          <t>Manika Plastech IPOCAllotted</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹2 (4.65%) 1.60 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,32 +2711,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.23x</t>
+          <t>29.46x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹56.12 Cr</t>
+          <t>₹125.50 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>11-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>16-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>19-Sep 17:57</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2763,7 +2763,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Om Galaxy BSE SMEL@90.20 (0.22%)</t>
+          <t>Injecto Polymers BSE SMEC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2778,47 +2778,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.07x</t>
+          <t>1.23x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹105.00 Cr</t>
+          <t>₹56.12 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 0</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>18-Sep 9:36</t>
+          <t>20-Sep 13:28</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2830,12 +2830,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Raksan Transformers BSE SMEL@273.00 (0%)</t>
+          <t>Panchatv Bharat BSE SMEL@128.95 (-7.89%)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹12 (4.40%) 11 ↓ / 61 ↑</t>
+          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>47.43x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹150.50 Cr</t>
+          <t>₹24.58 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 28</t>
+          <t>10-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 50</t>
+          <t>15-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 12</t>
+          <t>18-Sep GMP: 3</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -2964,47 +2964,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Panchatv Bharat BSE SMEL@128.95 (-7.89%)</t>
+          <t>Maharaja &amp; Speedex India BSE SMEL@250.00 (34.41%)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
+          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>32.41x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹24.58 Cr</t>
+          <t>₹80.13 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 7</t>
+          <t>10-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 3</t>
+          <t>15-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 3</t>
+          <t>18-Sep GMP: 28</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3024,54 +3024,54 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Maharaja &amp; Speedex India BSE SMEL@250.00 (34.41%)</t>
+          <t>Raksan Transformers BSE SMEL@273.00 (0%)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
+          <t>₹12 (4.40%) 11 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>32.41x</t>
+          <t>47.43x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>273</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹80.13 Cr</t>
+          <t>₹150.50 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 30</t>
+          <t>10-Sep GMP: 28</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 28</t>
+          <t>15-Sep GMP: 50</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 28</t>
+          <t>18-Sep GMP: 12</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3098,62 +3098,62 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Karamtara Engineering IPOL@320.00 (25.98%)</t>
+          <t>Om Galaxy BSE SMEL@90.20 (0.22%)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>₹46 (18.11%) 40 ↓ / 75 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>66.01x</t>
+          <t>2.07x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹875.00 Cr</t>
+          <t>₹105.00 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 75</t>
+          <t>10-Sep</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 67</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 46</t>
+          <t>18-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>17-Sep 9:29</t>
+          <t>18-Sep 9:36</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3165,47 +3165,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Amtech Esters BSE SMEL@100.00 (33.33%)</t>
+          <t>Vinod Texworld NSE SMEL@94.00 (0%)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹16 (21.33%) 5 ↓ / 16 ↑</t>
+          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>25.7x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹17.88 Cr</t>
+          <t>₹42.83 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 11</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3215,64 +3215,64 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 16</t>
+          <t>17-Sep GMP: 1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>17-Sep 9:36</t>
+          <t>17-Sep 9:33</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Vinod Texworld NSE SMEL@94.00 (0%)</t>
+          <t>Asset Reconstruction IPOL@139.00 (0%)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
+          <t>₹12 (8.63%) 12 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>20.1x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹42.83 Cr</t>
+          <t>₹732.97 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>9-Sep GMP: 24</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>11-Sep GMP: 14.5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3282,64 +3282,64 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 1</t>
+          <t>17-Sep GMP: 12</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>17-Sep 9:33</t>
+          <t>17-Sep 9:30</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Infrax Renewable BSE SMEL@104.00 (0%)</t>
+          <t>Steamhouse IPOL@94.50 (16.67%)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹13.5 (16.67%) 13.50 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>32.07x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹40.88 Cr</t>
+          <t>₹414.00 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>11-Sep GMP: 21</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3349,64 +3349,64 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 0</t>
+          <t>17-Sep GMP: 13.5</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>17-Sep 9:31</t>
+          <t>17-Sep 9:34</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Asset Reconstruction IPOL@139.00 (0%)</t>
+          <t>Rentomojo IPOL@482.45 (19.42%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>₹12 (8.63%) 12 ↓ / 30 ↑</t>
+          <t>₹87 (21.53%) 79 ↓ / 160 ↑</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20.1x</t>
+          <t>72.89x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹732.97 Cr</t>
+          <t>₹1255.57 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 24</t>
+          <t>9-Sep GMP: 143</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 14.5</t>
+          <t>11-Sep GMP: 148</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 12</t>
+          <t>17-Sep GMP: 87</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>17-Sep 9:30</t>
+          <t>17-Sep 9:32</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3433,47 +3433,47 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Steamhouse IPOL@94.50 (16.67%)</t>
+          <t>LCC Projects IPOL@189.00 (29.45%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹13.5 (16.67%) 13.50 ↓ / 24 ↑</t>
+          <t>₹36 (24.66%) 17 ↓ / 78 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>32.07x</t>
+          <t>49.57x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹414.00 Cr</t>
+          <t>₹427.14 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>9-Sep GMP: 40</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 21</t>
+          <t>11-Sep GMP: 78</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 13.5</t>
+          <t>17-Sep GMP: 36</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3500,47 +3500,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Rentomojo IPOL@482.45 (19.42%)</t>
+          <t>Karamtara Engineering IPOL@320.00 (25.98%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>₹87 (21.53%) 79 ↓ / 160 ↑</t>
+          <t>₹46 (18.11%) 40 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>72.89x</t>
+          <t>66.01x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹1255.57 Cr</t>
+          <t>₹875.00 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 143</t>
+          <t>9-Sep GMP: 75</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 148</t>
+          <t>11-Sep GMP: 67</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 87</t>
+          <t>17-Sep GMP: 46</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>17-Sep 9:32</t>
+          <t>17-Sep 9:29</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3567,47 +3567,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Manipal Payment and Identity Solutions IPOL@330.00 (-2.65%)</t>
+          <t>Amtech Esters BSE SMEL@100.00 (33.33%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹-6 (-1.77%) -10 ↓ / 38 ↑</t>
+          <t>₹16 (21.33%) 5 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>25.7x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹805.00 Cr</t>
+          <t>₹17.88 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 8</t>
+          <t>9-Sep GMP: 11</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>11-Sep GMP: 7</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>17-Sep GMP: -6</t>
+          <t>17-Sep GMP: 16</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3701,47 +3701,47 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LCC Projects IPOL@189.00 (29.45%)</t>
+          <t>Infrax Renewable BSE SMEL@104.00 (0%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹36 (24.66%) 17 ↓ / 78 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>49.57x</t>
+          <t>2.05x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹427.14 Cr</t>
+          <t>₹40.88 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 40</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 78</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3751,79 +3751,79 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 36</t>
+          <t>17-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>17-Sep 9:34</t>
+          <t>17-Sep 9:31</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kanohar Electricals IPOL@685.50 (8.47%)</t>
+          <t>Manipal Payment and Identity Solutions IPOL@330.00 (-2.65%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹182 (28.80%) 182 ↓ / 241 ↑</t>
+          <t>₹-6 (-1.77%) -10 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>90.59x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>339</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹1055.74 Cr</t>
+          <t>₹805.00 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 218</t>
+          <t>9-Sep GMP: 8</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 240</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 182</t>
+          <t>17-Sep GMP: -6</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>16-Sep 9:33</t>
+          <t>17-Sep 9:36</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3969,67 +3969,67 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Apana Logistics BSE SMEL@60.00 (0%)</t>
+          <t>Kanohar Electricals IPOL@685.50 (8.47%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
+          <t>₹182 (28.80%) 182 ↓ / 241 ↑</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.26x</t>
+          <t>90.59x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹34.14 Cr</t>
+          <t>₹1055.74 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>7-Sep GMP: 10</t>
+          <t>8-Sep GMP: 218</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 1</t>
+          <t>10-Sep GMP: 240</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 0</t>
+          <t>16-Sep GMP: 182</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>15-Sep 9:28</t>
+          <t>16-Sep 9:33</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>20-Sep 13:34</t>
+          <t>20-Sep 18:31</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>20-Sep 13:34</t>
+          <t>20-Sep 18:34</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>20-Sep 13:29</t>
+          <t>20-Sep 18:28</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>20-Sep 13:31</t>
+          <t>20-Sep 18:34</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>20-Sep 13:36</t>
+          <t>20-Sep 18:34</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>20-Sep 13:31</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>20-Sep 13:33</t>
+          <t>20-Sep 18:36</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>20-Sep 13:31</t>
+          <t>20-Sep 18:31</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>20-Sep 13:28</t>
+          <t>20-Sep 18:30</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>20-Sep 13:29</t>
+          <t>20-Sep 18:34</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹7 (6.93%) 7 ↓ / 10 ↑</t>
+          <t>₹5 (4.95%) 5 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹48 (2.69%) 48 ↓ / 310 ↑</t>
+          <t>₹45 (2.52%) 45 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>20-Sep 13:36</t>
+          <t>20-Sep 18:30</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>20-Sep 13:31</t>
+          <t>20-Sep 18:36</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>20-Sep 13:28</t>
+          <t>20-Sep 18:34</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,12 +506,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
+          <t>₹12 (10.91%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,13 +519,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>₹42.44 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>25-Sep</t>
@@ -548,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20-Sep 5:55</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -560,17 +568,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A-One Steels IPOU</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹64 (15.80%) 55 ↓ / 64 ↑</t>
-        </is>
-      </c>
+          <t>Himalayan Solar NSE SMEU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -580,44 +584,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1-Oct</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>20-Sep 18:37</t>
-        </is>
-      </c>
+          <t>5-Oct</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
@@ -627,12 +627,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEU</t>
+          <t>Sai Urja Indo BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -645,48 +645,56 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>₹24.95 Cr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>20-Sep 5:55</t>
+          <t>21-Sep 14:01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEU</t>
+          <t>Moneyview IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -706,42 +714,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>20-Sep 18:31</t>
+          <t>21-Sep 14:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -753,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEU</t>
+          <t>Peshwa Wheat BSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -773,42 +781,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>20-Sep 5:55</t>
+          <t>21-Sep 14:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -820,14 +828,10 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOU</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>₹3 (1.62%) 3 ↓ / 5 ↑</t>
-        </is>
-      </c>
+          <t>Green Asia Impex NSE SMEU</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -840,61 +844,53 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹160.88 Cr</t>
+          <t>₹60.10 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>30-Sep</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>20-Sep 18:37</t>
-        </is>
-      </c>
+          <t>1-Oct</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
-        </is>
-      </c>
+          <t>Roopa Screen BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -907,44 +903,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>30-Sep</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>20-Sep 18:34</t>
-        </is>
-      </c>
+          <t>1-Oct</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>✅</t>
@@ -954,17 +946,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOU</t>
+          <t>A-One Steels IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹16 (4.42%) 15 ↓ / 16 ↑</t>
+          <t>₹60 (14.81%) 55 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -974,42 +966,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1021,12 +1013,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOU</t>
+          <t>S.K.Offset BSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹1 (0.27%) 1 ↓ / 1 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1041,17 +1033,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1076,7 +1068,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 13:57</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1088,12 +1080,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEU</t>
+          <t>Elevate Campuses IPOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹16 (4.42%) 15 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1108,17 +1100,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1143,7 +1135,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>20-Sep 18:28</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1160,7 +1152,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹35 (26.12%) 35 ↓ / 37 ↑</t>
+          <t>₹32 (23.88%) 32 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1210,7 +1202,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1222,7 +1214,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEU</t>
+          <t>Core Integra Consulting NSE SMEU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1242,17 +1234,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1277,24 +1269,24 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>20-Sep 18:34</t>
+          <t>21-Sep 5:55</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEU</t>
+          <t>ArMee Infotech IPOU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (0.27%) 1 ↓ / 1 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1309,17 +1301,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1344,29 +1336,29 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>20-Sep 18:34</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOU</t>
+          <t>Swastika Infra IPOU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹12 (8.11%) 10 ↓ / 15 ↑</t>
+          <t>₹3 (1.62%) 3 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1376,42 +1368,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹708.02 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1423,7 +1415,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEU</t>
+          <t>Unitec Fibres BSE SMEU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1443,42 +1435,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 13:54</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1557,7 +1549,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMEU</t>
+          <t>Pooja Logistics NSE SMEU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1577,54 +1569,54 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹25.52 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>20-Sep 18:36</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMEU</t>
+          <t>Liqvd Digital BSE SMEU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1644,64 +1636,64 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹22.20 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>20-Sep 18:31</t>
+          <t>21-Sep 13:59</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMEU</t>
+          <t>Varmora Granito IPOU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹9 (6.08%) 9 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1711,42 +1703,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹45.24 Cr</t>
+          <t>₹708.02 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>20-Sep 18:30</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1758,17 +1750,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEU</t>
+          <t>Anand Seamless BSE SMEU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹51 (48.11%) 45 ↓ / 51 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1778,54 +1770,54 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹25.52 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 13:59</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMEO</t>
+          <t>Himalaya Nutravedics BSE SMEU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1840,47 +1832,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.62x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹50.75 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>20-Sep 18:34</t>
+          <t>21-Sep 13:59</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1892,12 +1884,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kheria Autocomp NSE SMEO</t>
+          <t>Vivekanand Cotspin BSE SMEO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹5 (4.95%) 5 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1907,47 +1899,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.41x</t>
+          <t>0.07x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹46.44 Cr</t>
+          <t>₹22.20 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 10</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 14:00</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1959,62 +1951,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sonaselection India IPOO</t>
+          <t>Robokidz Eduventures BSE SMEO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹2 (2.02%) 2 ↓ / 8 ↑</t>
+          <t>₹55 (51.89%) 45 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.47x</t>
+          <t>5.05x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹141.57 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 2</t>
+          <t>21-Sep GMP: 55</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2026,12 +2018,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NSE IPOO</t>
+          <t>FX Multitech BSE SMEO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹45 (2.52%) 45 ↓ / 310 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2041,47 +2033,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.04x</t>
+          <t>0.1x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹22561.57 Cr</t>
+          <t>₹45.24 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 142</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 14:01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2093,62 +2085,62 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMEO</t>
+          <t>Axiom Gas Engineering NSE SMEO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹45 (38.14%) 27 ↓ / 50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19.93x</t>
+          <t>0.78x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹42.52 Cr</t>
+          <t>₹50.75 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 30</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 13:54</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2160,62 +2152,62 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SS Retail IPOC</t>
+          <t>Kheria Autocomp NSE SMECT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹147 (34.67%) 30 ↓ / 147 ↑</t>
+          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>107.41x</t>
+          <t>1.26x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹46.44 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 90</t>
+          <t>17-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 145</t>
+          <t>21-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2227,12 +2219,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOC</t>
+          <t>SpectraA Technology Solutions NSE SMECT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
+          <t>₹45 (38.14%) 27 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2242,47 +2234,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>177.03x</t>
+          <t>152.54x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹42.52 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 25</t>
+          <t>17-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 26.5</t>
+          <t>21-Sep GMP: 45</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2294,12 +2286,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hero Motors IPOC</t>
+          <t>Sonaselection India IPOCT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹-2 (-2.38%) -2 ↓ / 24 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2309,47 +2301,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7.01x</t>
+          <t>1.51x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹1000.00 Cr</t>
+          <t>₹141.57 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 13</t>
+          <t>17-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 0</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2361,12 +2353,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Vama Wovenfab BSE SMECAllotted</t>
+          <t>NSE IPOCT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹3 (0.88%) 3 ↓ / 70 ↑</t>
+          <t>₹60 (3.36%) 48 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2376,64 +2368,64 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.53x</t>
+          <t>3.79x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹49.54 Cr</t>
+          <t>₹22561.57 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 30</t>
+          <t>17-Sep GMP: 142</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 3</t>
+          <t>21-Sep GMP: 60</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Quanto Agroworld BSE SMECAllotted</t>
+          <t>Hero Motors IPOC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-2 (-2.38%) -2 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2443,114 +2435,114 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>7.01x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹31.02 Cr</t>
+          <t>₹1000.00 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep GMP: 13</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>20-Sep 18:30</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Shakti Polytarp BSE SMECAllotted</t>
+          <t>Jindal Supreme IPOC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹5 (8.47%) 5 ↓ / 6 ↑</t>
+          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>11.87x</t>
+          <t>177.03x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹26.93 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 6</t>
+          <t>18-Sep GMP: 26.5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2629,62 +2621,62 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Century Business Media BSE SMECAllotted</t>
+          <t>SS Retail IPOC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹156 (36.79%) 30 ↓ / 156 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>57.93x</t>
+          <t>107.41x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹17.11 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>16-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep GMP: 145</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>20-Sep 18:36</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2696,12 +2688,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Manika Plastech IPOCAllotted</t>
+          <t>Quanto Agroworld BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹2 (4.65%) 1.60 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,114 +2703,114 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>29.46x</t>
+          <t>1.39x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹125.50 Cr</t>
+          <t>₹31.02 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 2</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 13:59</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Injecto Polymers BSE SMEC</t>
+          <t>Shakti Polytarp BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6 (10.17%) 5 ↓ / 6 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.23x</t>
+          <t>11.87x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹56.12 Cr</t>
+          <t>₹26.93 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep GMP: 6</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>20-Sep 18:34</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2830,12 +2822,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Panchatv Bharat BSE SMEL@128.95 (-7.89%)</t>
+          <t>Vama Wovenfab BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
+          <t>₹3 (0.88%) 3 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2845,47 +2837,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>2.53x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹24.58 Cr</t>
+          <t>₹49.54 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 7</t>
+          <t>15-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 3</t>
+          <t>17-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 3</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2897,62 +2889,62 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Veegaland Developers IPOL@154.00 (10%)</t>
+          <t>Century Business Media BSE SMEL@74.00 (0%)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹8 (5.71%) 5 ↓ / 33 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>14.6x</t>
+          <t>57.93x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹210.00 Cr</t>
+          <t>₹17.11 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 25</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 10</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 8</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>21-Sep 9:28</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2964,62 +2956,62 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Maharaja &amp; Speedex India BSE SMEL@250.00 (34.41%)</t>
+          <t>Injecto Polymers BSE SMEL@99.00 (-1%)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>32.41x</t>
+          <t>1.23x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹80.13 Cr</t>
+          <t>₹56.12 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 30</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 28</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 28</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>21-Sep 9:37</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3031,12 +3023,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Raksan Transformers BSE SMEL@273.00 (0%)</t>
+          <t>Manika Plastech IPOL@43.00 (0%)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹12 (4.40%) 11 ↓ / 61 ↑</t>
+          <t>₹1 (2.33%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3046,47 +3038,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>47.43x</t>
+          <t>29.46x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹150.50 Cr</t>
+          <t>₹125.50 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 28</t>
+          <t>11-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 50</t>
+          <t>16-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 12</t>
+          <t>21-Sep GMP: 1</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>21-Sep 9:37</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3098,12 +3090,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Om Galaxy BSE SMEL@90.20 (0.22%)</t>
+          <t>Panchatv Bharat BSE SMEL@128.95 (-7.89%)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3113,32 +3105,32 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.07x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹105.00 Cr</t>
+          <t>₹24.58 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>10-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>15-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3148,146 +3140,146 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 0</t>
+          <t>18-Sep GMP: 3</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>18-Sep 9:36</t>
+          <t>18-Sep 9:37</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Vinod Texworld NSE SMEL@94.00 (0%)</t>
+          <t>Veegaland Developers IPOL@154.00 (10%)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
+          <t>₹8 (5.71%) 5 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>14.6x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹42.83 Cr</t>
+          <t>₹210.00 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>10-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>15-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 1</t>
+          <t>18-Sep GMP: 8</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>17-Sep 9:33</t>
+          <t>18-Sep 9:37</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Asset Reconstruction IPOL@139.00 (0%)</t>
+          <t>Raksan Transformers BSE SMEL@273.00 (0%)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>₹12 (8.63%) 12 ↓ / 30 ↑</t>
+          <t>₹12 (4.40%) 11 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20.1x</t>
+          <t>47.43x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>273</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹732.97 Cr</t>
+          <t>₹150.50 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 24</t>
+          <t>10-Sep GMP: 28</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 14.5</t>
+          <t>15-Sep GMP: 50</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 12</t>
+          <t>18-Sep GMP: 12</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>17-Sep 9:30</t>
+          <t>18-Sep 9:37</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3299,62 +3291,62 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Steamhouse IPOL@94.50 (16.67%)</t>
+          <t>Om Galaxy BSE SMEL@90.20 (0.22%)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹13.5 (16.67%) 13.50 ↓ / 24 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>32.07x</t>
+          <t>2.07x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹414.00 Cr</t>
+          <t>₹105.00 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>10-Sep</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 21</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 13.5</t>
+          <t>18-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>17-Sep 9:34</t>
+          <t>18-Sep 9:36</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3366,62 +3358,62 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Rentomojo IPOL@482.45 (19.42%)</t>
+          <t>Maharaja &amp; Speedex India BSE SMEL@250.00 (34.41%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>₹87 (21.53%) 79 ↓ / 160 ↑</t>
+          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>72.89x</t>
+          <t>32.41x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹1255.57 Cr</t>
+          <t>₹80.13 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 143</t>
+          <t>10-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 148</t>
+          <t>15-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 87</t>
+          <t>18-Sep GMP: 28</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>17-Sep 9:32</t>
+          <t>18-Sep 9:37</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3433,47 +3425,47 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LCC Projects IPOL@189.00 (29.45%)</t>
+          <t>Vinod Texworld NSE SMEL@94.00 (0%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹36 (24.66%) 17 ↓ / 78 ↑</t>
+          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>49.57x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹427.14 Cr</t>
+          <t>₹42.83 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 40</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 78</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3483,29 +3475,29 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 36</t>
+          <t>17-Sep GMP: 1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>17-Sep 9:34</t>
+          <t>17-Sep 9:33</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Karamtara Engineering IPOL@320.00 (25.98%)</t>
+          <t>Steamhouse IPOL@94.50 (16.67%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>₹46 (18.11%) 40 ↓ / 75 ↑</t>
+          <t>₹13.5 (16.67%) 13.50 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3515,32 +3507,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>66.01x</t>
+          <t>32.07x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹875.00 Cr</t>
+          <t>₹414.00 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 75</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 67</t>
+          <t>11-Sep GMP: 21</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3550,12 +3542,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 46</t>
+          <t>17-Sep GMP: 13.5</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>17-Sep 9:29</t>
+          <t>17-Sep 9:34</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3567,12 +3559,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Amtech Esters BSE SMEL@100.00 (33.33%)</t>
+          <t>Rentomojo IPOL@482.45 (19.42%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹16 (21.33%) 5 ↓ / 16 ↑</t>
+          <t>₹87 (21.53%) 79 ↓ / 160 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3582,32 +3574,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>25.7x</t>
+          <t>72.89x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹17.88 Cr</t>
+          <t>₹1255.57 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 11</t>
+          <t>9-Sep GMP: 143</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>11-Sep GMP: 148</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3617,12 +3609,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 16</t>
+          <t>17-Sep GMP: 87</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>17-Sep 9:36</t>
+          <t>17-Sep 9:32</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3701,12 +3693,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Infrax Renewable BSE SMEL@104.00 (0%)</t>
+          <t>Manipal Payment and Identity Solutions IPOL@330.00 (-2.65%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-6 (-1.77%) -10 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3716,32 +3708,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>339</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹40.88 Cr</t>
+          <t>₹805.00 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>9-Sep GMP: 8</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3751,64 +3743,64 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 0</t>
+          <t>17-Sep GMP: -6</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>17-Sep 9:31</t>
+          <t>17-Sep 9:36</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Manipal Payment and Identity Solutions IPOL@330.00 (-2.65%)</t>
+          <t>Asset Reconstruction IPOL@139.00 (0%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹-6 (-1.77%) -10 ↓ / 38 ↑</t>
+          <t>₹12 (8.63%) 12 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>20.1x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹805.00 Cr</t>
+          <t>₹732.97 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 8</t>
+          <t>9-Sep GMP: 24</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>11-Sep GMP: 14.5</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3818,12 +3810,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>17-Sep GMP: -6</t>
+          <t>17-Sep GMP: 12</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>17-Sep 9:36</t>
+          <t>17-Sep 9:30</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3835,62 +3827,62 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Prasol Chemicals IPOL@610.00 (-9.76%)</t>
+          <t>LCC Projects IPOL@189.00 (29.45%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹-13 (-1.92%) -15 ↓ / 165 ↑</t>
+          <t>₹36 (24.66%) 17 ↓ / 78 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3.47x</t>
+          <t>49.57x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹427.14 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 30</t>
+          <t>9-Sep GMP: 40</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 0</t>
+          <t>11-Sep GMP: 78</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>16-Sep GMP: -13</t>
+          <t>17-Sep GMP: 36</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>16-Sep 9:36</t>
+          <t>17-Sep 9:34</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3902,62 +3894,62 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Glass Wall Systems IPOL@194.00 (6.59%)</t>
+          <t>Karamtara Engineering IPOL@320.00 (25.98%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹39 (21.43%) 20 ↓ / 66 ↑</t>
+          <t>₹46 (18.11%) 40 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>81.65x</t>
+          <t>66.01x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹427.89 Cr</t>
+          <t>₹875.00 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 56</t>
+          <t>9-Sep GMP: 75</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 45</t>
+          <t>11-Sep GMP: 67</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 39</t>
+          <t>17-Sep GMP: 46</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>16-Sep 9:36</t>
+          <t>17-Sep 9:29</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3969,12 +3961,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kanohar Electricals IPOL@685.50 (8.47%)</t>
+          <t>Amtech Esters BSE SMEL@100.00 (33.33%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>₹182 (28.80%) 182 ↓ / 241 ↑</t>
+          <t>₹16 (21.33%) 5 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3984,47 +3976,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>90.59x</t>
+          <t>25.7x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹1055.74 Cr</t>
+          <t>₹17.88 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8-Sep GMP: 218</t>
+          <t>9-Sep GMP: 11</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 240</t>
+          <t>11-Sep GMP: 7</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 182</t>
+          <t>17-Sep GMP: 16</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>16-Sep 9:33</t>
+          <t>17-Sep 9:36</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEU</t>
+          <t>Acevector IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹12 (10.91%) 12 ↓ / 12 ↑</t>
+          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,21 +519,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹42.44 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>25-Sep</t>
@@ -556,7 +544,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 18:40</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -568,10 +556,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEU</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Sai Urja Indo BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -584,12 +576,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -617,7 +609,11 @@
           <t>5-Oct</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>21-Sep 20:55</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
@@ -627,7 +623,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEU</t>
+          <t>Himalayan Solar NSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -647,12 +643,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,7 +678,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>21-Sep 14:01</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -694,17 +690,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Moneyview IPOU</t>
+          <t>Bench Mark Infotech Services NSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹12 (10.91%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -714,42 +710,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21-Sep 14:00</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -761,7 +757,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEU</t>
+          <t>Moneyview IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -781,17 +777,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -816,22 +812,26 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21-Sep 14:00</t>
+          <t>21-Sep 20:58</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEU</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>Roopa Screen BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -844,17 +844,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹60.10 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -877,23 +877,31 @@
           <t>1-Oct</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>21-Sep 21:01</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>A-One Steels IPOU</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>₹60 (14.81%) 55 ↓ / 64 ↑</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -903,17 +911,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -936,7 +944,11 @@
           <t>1-Oct</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>21-Sep 21:02</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>✅</t>
@@ -946,17 +958,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A-One Steels IPOU</t>
+          <t>Peshwa Wheat BSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹60 (14.81%) 55 ↓ / 64 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -966,17 +978,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1001,26 +1013,22 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 20:56</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
-        </is>
-      </c>
+          <t>Green Asia Impex NSE SMEU</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -1033,47 +1041,43 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹60.10 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>30-Sep</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>21-Sep 13:57</t>
-        </is>
-      </c>
+          <t>1-Oct</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1139,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1147,17 +1151,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOU</t>
+          <t>S.K.Offset BSE SMEU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹32 (23.88%) 32 ↓ / 37 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1167,17 +1171,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1202,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1214,12 +1218,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEU</t>
+          <t>ArMee Infotech IPOU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹12 (3.20%) 1 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1234,17 +1238,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1269,24 +1273,24 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>21-Sep 5:55</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOU</t>
+          <t>Core Integra Consulting NSE SMEU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹1 (0.27%) 1 ↓ / 1 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1301,17 +1305,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1336,24 +1340,24 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 20:53</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOU</t>
+          <t>Unitec Fibres BSE SMEU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹3 (1.62%) 3 ↓ / 5 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1368,17 +1372,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹160.88 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1403,7 +1407,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 20:59</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1415,12 +1419,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEU</t>
+          <t>Swastika Infra IPOU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹3 (1.62%) 3 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1435,17 +1439,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1470,7 +1474,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>21-Sep 13:54</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1549,17 +1553,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEU</t>
+          <t>Adroit Industries IPOU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹32 (23.88%) 32 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1569,17 +1573,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1604,7 +1608,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1616,7 +1620,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEU</t>
+          <t>Pooja Logistics NSE SMEU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1636,17 +1640,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1671,29 +1675,29 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>21-Sep 13:59</t>
+          <t>21-Sep 20:57</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOU</t>
+          <t>Liqvd Digital BSE SMEU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹9 (6.08%) 9 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1703,64 +1707,64 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹708.02 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 20:56</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMEU</t>
+          <t>Varmora Granito IPOU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹9 (6.08%) 9 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1770,17 +1774,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹25.52 Cr</t>
+          <t>₹708.02 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1805,19 +1809,19 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>21-Sep 13:59</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEU</t>
+          <t>Anand Seamless BSE SMEU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1837,17 +1841,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹25.52 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1872,19 +1876,19 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>21-Sep 13:59</t>
+          <t>21-Sep 20:55</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMEO</t>
+          <t>Himalaya Nutravedics BSE SMEU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1899,47 +1903,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.07x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹22.20 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>21-Sep 14:00</t>
+          <t>21-Sep 20:57</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1951,32 +1955,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEO</t>
+          <t>FX Multitech BSE SMEO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹55 (51.89%) 45 ↓ / 55 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5.05x</t>
+          <t>0.29x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹45.24 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1986,7 +1990,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 55</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2006,7 +2010,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 20:53</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2018,32 +2022,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMEO</t>
+          <t>Robokidz Eduventures BSE SMEO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹55 (51.89%) 45 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.1x</t>
+          <t>9.29x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹45.24 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2053,7 +2057,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>21-Sep GMP: 55</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2073,7 +2077,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>21-Sep 14:01</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2085,7 +2089,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMEO</t>
+          <t>Vivekanand Cotspin BSE SMEO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2100,47 +2104,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.78x</t>
+          <t>0.08x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹50.75 Cr</t>
+          <t>₹22.20 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>21-Sep 13:54</t>
+          <t>21-Sep 20:55</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2152,12 +2156,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kheria Autocomp NSE SMECT</t>
+          <t>Axiom Gas Engineering NSE SMEO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2167,47 +2171,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.26x</t>
+          <t>0.85x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹46.44 Cr</t>
+          <t>₹50.75 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 10</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 3</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 20:58</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2219,22 +2223,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMECT</t>
+          <t>SpectraA Technology Solutions NSE SMEC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹45 (38.14%) 27 ↓ / 50 ↑</t>
+          <t>₹60 (50.85%) 27 ↓ / 60 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>152.54x</t>
+          <t>304.06x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2259,7 +2263,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 45</t>
+          <t>21-Sep GMP: 60</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2274,7 +2278,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2286,12 +2290,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sonaselection India IPOCT</t>
+          <t>Kheria Autocomp NSE SMEC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
+          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2301,32 +2305,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.51x</t>
+          <t>2.48x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹141.57 Cr</t>
+          <t>₹46.44 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 2</t>
+          <t>17-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>21-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2341,7 +2345,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2353,12 +2357,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NSE IPOCT</t>
+          <t>NSE IPOC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹60 (3.36%) 48 ↓ / 310 ↑</t>
+          <t>₹61.5 (3.45%) 48 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2368,7 +2372,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.79x</t>
+          <t>5.71x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2393,7 +2397,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 60</t>
+          <t>21-Sep GMP: 61.5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2408,7 +2412,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2420,12 +2424,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Hero Motors IPOC</t>
+          <t>Sonaselection India IPOC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹-2 (-2.38%) -2 ↓ / 24 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2435,47 +2439,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7.01x</t>
+          <t>2.01x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹1000.00 Cr</t>
+          <t>₹141.57 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 13</t>
+          <t>17-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 0</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2487,12 +2491,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOC</t>
+          <t>SS Retail IPOC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
+          <t>₹155 (36.56%) 30 ↓ / 155 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2502,32 +2506,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>177.03x</t>
+          <t>107.41x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 25</t>
+          <t>16-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 26.5</t>
+          <t>18-Sep GMP: 145</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2542,7 +2546,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2621,12 +2625,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SS Retail IPOC</t>
+          <t>Jindal Supreme IPOCAllotted</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹156 (36.79%) 30 ↓ / 156 ↑</t>
+          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2636,32 +2640,32 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>107.41x</t>
+          <t>177.03x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 90</t>
+          <t>16-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 145</t>
+          <t>18-Sep GMP: 26.5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2676,7 +2680,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2688,12 +2692,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Quanto Agroworld BSE SMECAllotted</t>
+          <t>Hero Motors IPOC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-2 (-2.38%) -2 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2703,99 +2707,99 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>7.01x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹31.02 Cr</t>
+          <t>₹1000.00 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep GMP: 13</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>21-Sep 13:59</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Shakti Polytarp BSE SMECAllotted</t>
+          <t>Vama Wovenfab BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹6 (10.17%) 5 ↓ / 6 ↑</t>
+          <t>₹3 (0.88%) 3 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11.87x</t>
+          <t>2.53x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹26.93 Cr</t>
+          <t>₹49.54 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>15-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 6</t>
+          <t>17-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2810,59 +2814,59 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Vama Wovenfab BSE SMECAllotted</t>
+          <t>Shakti Polytarp BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹3 (0.88%) 3 ↓ / 70 ↑</t>
+          <t>₹12 (20.34%) 5 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2.53x</t>
+          <t>11.87x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹49.54 Cr</t>
+          <t>₹26.93 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 30</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 3</t>
+          <t>17-Sep GMP: 6</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2877,19 +2881,19 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Century Business Media BSE SMEL@74.00 (0%)</t>
+          <t>Quanto Agroworld BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2904,64 +2908,64 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>57.93x</t>
+          <t>1.39x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹17.11 Cr</t>
+          <t>₹31.02 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>21-Sep 9:28</t>
+          <t>21-Sep 21:01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Injecto Polymers BSE SMEL@99.00 (-1%)</t>
+          <t>Manika Plastech IPOL@43.00 (0%)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (2.33%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,32 +2975,32 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.23x</t>
+          <t>29.46x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹56.12 Cr</t>
+          <t>₹125.50 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>11-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>16-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3006,7 +3010,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>21-Sep GMP: 1</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3023,12 +3027,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Manika Plastech IPOL@43.00 (0%)</t>
+          <t>Injecto Polymers BSE SMEL@99.00 (-1%)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹1 (2.33%) 1 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3038,32 +3042,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>29.46x</t>
+          <t>1.23x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹125.50 Cr</t>
+          <t>₹56.12 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 2</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3073,7 +3077,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 1</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3090,12 +3094,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Panchatv Bharat BSE SMEL@128.95 (-7.89%)</t>
+          <t>Century Business Media BSE SMEL@74.00 (0%)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3105,52 +3109,52 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>57.93x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹24.58 Cr</t>
+          <t>₹17.11 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 7</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 3</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 3</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>21-Sep 9:28</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3228,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Raksan Transformers BSE SMEL@273.00 (0%)</t>
+          <t>Panchatv Bharat BSE SMEL@128.95 (-7.89%)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>₹12 (4.40%) 11 ↓ / 61 ↑</t>
+          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3239,32 +3243,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>47.43x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹150.50 Cr</t>
+          <t>₹24.58 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 28</t>
+          <t>10-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 50</t>
+          <t>15-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,7 +3278,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 12</t>
+          <t>18-Sep GMP: 3</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3284,7 +3288,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -3358,47 +3362,47 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Maharaja &amp; Speedex India BSE SMEL@250.00 (34.41%)</t>
+          <t>Raksan Transformers BSE SMEL@273.00 (0%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
+          <t>₹12 (4.40%) 11 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>32.41x</t>
+          <t>47.43x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>273</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹80.13 Cr</t>
+          <t>₹150.50 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 30</t>
+          <t>10-Sep GMP: 28</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 28</t>
+          <t>15-Sep GMP: 50</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3408,7 +3412,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 28</t>
+          <t>18-Sep GMP: 12</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3425,104 +3429,104 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Vinod Texworld NSE SMEL@94.00 (0%)</t>
+          <t>Maharaja &amp; Speedex India BSE SMEL@250.00 (34.41%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
+          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>32.41x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹42.83 Cr</t>
+          <t>₹80.13 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>10-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>15-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 1</t>
+          <t>18-Sep GMP: 28</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>17-Sep 9:33</t>
+          <t>18-Sep 9:37</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Steamhouse IPOL@94.50 (16.67%)</t>
+          <t>Vinod Texworld NSE SMEL@94.00 (0%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>₹13.5 (16.67%) 13.50 ↓ / 24 ↑</t>
+          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>32.07x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹414.00 Cr</t>
+          <t>₹42.83 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3532,7 +3536,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 21</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3542,64 +3546,64 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 13.5</t>
+          <t>17-Sep GMP: 1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>17-Sep 9:34</t>
+          <t>17-Sep 9:33</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Rentomojo IPOL@482.45 (19.42%)</t>
+          <t>Asset Reconstruction IPOL@139.00 (0%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹87 (21.53%) 79 ↓ / 160 ↑</t>
+          <t>₹12 (8.63%) 12 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>72.89x</t>
+          <t>20.1x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹1255.57 Cr</t>
+          <t>₹732.97 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 143</t>
+          <t>9-Sep GMP: 24</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 148</t>
+          <t>11-Sep GMP: 14.5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3609,12 +3613,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 87</t>
+          <t>17-Sep GMP: 12</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>17-Sep 9:32</t>
+          <t>17-Sep 9:30</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3693,47 +3697,47 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Manipal Payment and Identity Solutions IPOL@330.00 (-2.65%)</t>
+          <t>Steamhouse IPOL@94.50 (16.67%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹-6 (-1.77%) -10 ↓ / 38 ↑</t>
+          <t>₹13.5 (16.67%) 13.50 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>32.07x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹805.00 Cr</t>
+          <t>₹414.00 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 8</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>11-Sep GMP: 21</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3743,12 +3747,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>17-Sep GMP: -6</t>
+          <t>17-Sep GMP: 13.5</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>17-Sep 9:36</t>
+          <t>17-Sep 9:34</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3760,47 +3764,47 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Asset Reconstruction IPOL@139.00 (0%)</t>
+          <t>Manipal Payment and Identity Solutions IPOL@330.00 (-2.65%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹12 (8.63%) 12 ↓ / 30 ↑</t>
+          <t>₹-6 (-1.77%) -10 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>20.1x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>339</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹732.97 Cr</t>
+          <t>₹805.00 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 24</t>
+          <t>9-Sep GMP: 8</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 14.5</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3810,12 +3814,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 12</t>
+          <t>17-Sep GMP: -6</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>17-Sep 9:30</t>
+          <t>17-Sep 9:36</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3827,12 +3831,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LCC Projects IPOL@189.00 (29.45%)</t>
+          <t>Rentomojo IPOL@482.45 (19.42%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹36 (24.66%) 17 ↓ / 78 ↑</t>
+          <t>₹87 (21.53%) 79 ↓ / 160 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3842,32 +3846,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>49.57x</t>
+          <t>72.89x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹427.14 Cr</t>
+          <t>₹1255.57 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 40</t>
+          <t>9-Sep GMP: 143</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 78</t>
+          <t>11-Sep GMP: 148</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3877,12 +3881,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 36</t>
+          <t>17-Sep GMP: 87</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>17-Sep 9:34</t>
+          <t>17-Sep 9:32</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3894,47 +3898,47 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Karamtara Engineering IPOL@320.00 (25.98%)</t>
+          <t>Infrax Renewable BSE SMEL@104.00 (0%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹46 (18.11%) 40 ↓ / 75 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>66.01x</t>
+          <t>2.05x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹875.00 Cr</t>
+          <t>₹40.88 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 75</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 67</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3944,64 +3948,64 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 46</t>
+          <t>17-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>17-Sep 9:29</t>
+          <t>17-Sep 9:31</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Amtech Esters BSE SMEL@100.00 (33.33%)</t>
+          <t>Karamtara Engineering IPOL@320.00 (25.98%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>₹16 (21.33%) 5 ↓ / 16 ↑</t>
+          <t>₹46 (18.11%) 40 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>25.7x</t>
+          <t>66.01x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹17.88 Cr</t>
+          <t>₹875.00 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 11</t>
+          <t>9-Sep GMP: 75</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>11-Sep GMP: 67</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4011,12 +4015,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 16</t>
+          <t>17-Sep GMP: 46</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>17-Sep 9:36</t>
+          <t>17-Sep 9:29</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,14 +501,10 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Acevector IPOU</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
-        </is>
-      </c>
+          <t>Pind Hospitality BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -519,54 +515,62 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹17.82 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5-Oct</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>21-Sep 18:40</t>
-        </is>
-      </c>
+          <t>6-Oct</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEU</t>
+          <t>Bench Mark Infotech Services NSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹12 (10.91%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -576,12 +580,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -611,7 +615,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>21-Sep 20:55</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -623,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEU</t>
+          <t>Runwal Enterprises IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -643,17 +647,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹499.83 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -678,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:29</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -690,17 +694,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEU</t>
+          <t>Sai Urja Indo BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹12 (10.91%) 12 ↓ / 12 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -710,12 +714,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -745,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:33</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -757,17 +761,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Moneyview IPOU</t>
+          <t>German Green Steel IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹15 (10.79%) 15 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -777,42 +781,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹303.90 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21-Sep 20:58</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -824,7 +828,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEU</t>
+          <t>Orient Cables IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -844,42 +848,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>21-Sep 21:01</t>
+          <t>22-Sep 13:36</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -891,17 +895,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A-One Steels IPOU</t>
+          <t>Dudani Retail BSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹60 (14.81%) 55 ↓ / 64 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -911,54 +915,54 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:36</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEU</t>
+          <t>Himalayan Solar NSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -978,12 +982,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -993,42 +997,46 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>21-Sep 20:56</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEU</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>Acevector IPOU</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -1041,60 +1049,64 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹60.10 Cr</t>
+          <t>₹420.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1-Oct</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>5-Oct</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>22-Sep 13:37</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOU</t>
+          <t>A-One Steels IPOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹16 (4.42%) 15 ↓ / 16 ↑</t>
+          <t>₹58 (14.32%) 55 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1104,42 +1116,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1151,7 +1163,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEU</t>
+          <t>Green Asia Impex NSE SMEU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1171,59 +1183,59 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹60.10 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:35</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOU</t>
+          <t>Peshwa Wheat BSE SMEU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹12 (3.20%) 1 ↓ / 12 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1238,64 +1250,64 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:28</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEU</t>
+          <t>Moneyview IPOU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹8.5 (25.00%) 5 ↓ / 8.50 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1305,64 +1317,64 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>21-Sep 20:53</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEU</t>
+          <t>Roopa Screen BSE SMEU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹14 (21.88%) 14 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1372,42 +1384,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>21-Sep 20:59</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1419,17 +1431,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOU</t>
+          <t>Adroit Industries IPOU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹3 (1.62%) 3 ↓ / 5 ↑</t>
+          <t>₹26 (19.40%) 26 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1439,17 +1451,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹160.88 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1474,7 +1486,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1553,17 +1565,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOU</t>
+          <t>ArMee Infotech IPOU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹32 (23.88%) 32 ↓ / 37 ↑</t>
+          <t>₹12 (3.20%) 1 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1573,17 +1585,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1608,7 +1620,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1675,7 +1687,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>21-Sep 20:57</t>
+          <t>22-Sep 13:29</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1687,7 +1699,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEU</t>
+          <t>Core Integra Consulting NSE SMEU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1707,17 +1719,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1742,7 +1754,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>21-Sep 20:56</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1754,17 +1766,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOU</t>
+          <t>Liqvd Digital BSE SMEU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹9 (6.08%) 9 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1774,54 +1786,54 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹708.02 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:36</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMEU</t>
+          <t>S.K.Offset BSE SMEU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1841,59 +1853,59 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹25.52 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>21-Sep 20:55</t>
+          <t>22-Sep 13:30</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEU</t>
+          <t>Elevate Campuses IPOU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹10 (2.76%) 10 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1908,42 +1920,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>21-Sep 20:57</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1955,7 +1967,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMEO</t>
+          <t>Unitec Fibres BSE SMEU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1970,47 +1982,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.29x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹45.24 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>21-Sep 20:53</t>
+          <t>22-Sep 13:32</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2022,62 +2034,62 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEO</t>
+          <t>Swastika Infra IPOU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹55 (51.89%) 45 ↓ / 55 ↑</t>
+          <t>₹3 (1.62%) 3 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>9.29x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 55</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2089,7 +2101,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMEO</t>
+          <t>Himalaya Nutravedics BSE SMEO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2104,47 +2116,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.08x</t>
+          <t>0.07x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹22.20 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>22-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>21-Sep 20:55</t>
+          <t>22-Sep 13:32</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2156,12 +2168,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMEO</t>
+          <t>Varmora Granito IPOO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6 (4.05%) 6 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2171,47 +2183,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.85x</t>
+          <t>0.08x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹50.75 Cr</t>
+          <t>₹708.02 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep GMP: 6</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>21-Sep 20:58</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2223,79 +2235,79 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMEC</t>
+          <t>Anand Seamless BSE SMEO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹60 (50.85%) 27 ↓ / 60 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>304.06x</t>
+          <t>0.07x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹42.52 Cr</t>
+          <t>₹25.52 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 30</t>
+          <t>22-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 60</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:33</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kheria Autocomp NSE SMEC</t>
+          <t>FX Multitech BSE SMEO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2305,17 +2317,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.48x</t>
+          <t>0.29x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹46.44 Cr</t>
+          <t>₹45.24 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2325,27 +2337,27 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 10</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 3</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2357,12 +2369,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NSE IPOC</t>
+          <t>Vivekanand Cotspin BSE SMEO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹61.5 (3.45%) 48 ↓ / 310 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2372,47 +2384,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5.71x</t>
+          <t>0.14x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹22561.57 Cr</t>
+          <t>₹22.20 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 142</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 61.5</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:35</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2424,62 +2436,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sonaselection India IPOC</t>
+          <t>Robokidz Eduventures BSE SMEO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
+          <t>₹55 (51.89%) 45 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.01x</t>
+          <t>43.18x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹141.57 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 2</t>
+          <t>21-Sep GMP: 55</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2491,62 +2503,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SS Retail IPOC</t>
+          <t>Axiom Gas Engineering NSE SMECT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹155 (36.56%) 30 ↓ / 155 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>107.41x</t>
+          <t>1.18x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹50.75 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 90</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 145</t>
+          <t>22-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:29</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2625,62 +2637,62 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOCAllotted</t>
+          <t>Kheria Autocomp NSE SMEC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
+          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>177.03x</t>
+          <t>2.48x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹46.44 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 25</t>
+          <t>17-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 26.5</t>
+          <t>21-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2692,62 +2704,62 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Hero Motors IPOC</t>
+          <t>SpectraA Technology Solutions NSE SMEC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹-2 (-2.38%) -2 ↓ / 24 ↑</t>
+          <t>₹67 (56.78%) 27 ↓ / 67 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7.01x</t>
+          <t>304.06x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹1000.00 Cr</t>
+          <t>₹42.52 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 13</t>
+          <t>17-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 0</t>
+          <t>21-Sep GMP: 67</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2759,12 +2771,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Vama Wovenfab BSE SMECAllotted</t>
+          <t>Sonaselection India IPOC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹3 (0.88%) 3 ↓ / 70 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2774,114 +2786,114 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.53x</t>
+          <t>2.01x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹49.54 Cr</t>
+          <t>₹141.57 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 30</t>
+          <t>17-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 3</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Shakti Polytarp BSE SMECAllotted</t>
+          <t>NSE IPOC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹12 (20.34%) 5 ↓ / 12 ↑</t>
+          <t>₹52 (2.91%) 48 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11.87x</t>
+          <t>5.71x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹26.93 Cr</t>
+          <t>₹22561.57 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>17-Sep GMP: 142</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 6</t>
+          <t>21-Sep GMP: 65</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2893,79 +2905,79 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Quanto Agroworld BSE SMECAllotted</t>
+          <t>Jindal Supreme IPOCAllotted</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>177.03x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹31.02 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep GMP: 26.5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>21-Sep 21:01</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Manika Plastech IPOL@43.00 (0%)</t>
+          <t>Hero Motors IPOCAllotted</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹1 (2.33%) 1 ↓ / 20 ↑</t>
+          <t>₹-2 (-2.38%) -2 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2975,47 +2987,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>29.46x</t>
+          <t>7.01x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹125.50 Cr</t>
+          <t>₹1000.00 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>16-Sep GMP: 13</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 2</t>
+          <t>18-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 1</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>21-Sep 9:37</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3027,62 +3039,62 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Injecto Polymers BSE SMEL@99.00 (-1%)</t>
+          <t>SS Retail IPOCAllotted</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹139 (32.78%) 30 ↓ / 147 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.23x</t>
+          <t>107.41x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹56.12 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>16-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep GMP: 145</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>21-Sep 9:37</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3094,62 +3106,62 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Century Business Media BSE SMEL@74.00 (0%)</t>
+          <t>Shakti Polytarp BSE SMEL@58.90 (-0.17%)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹10 (16.95%) 5 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>57.93x</t>
+          <t>11.87x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹17.11 Cr</t>
+          <t>₹26.93 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep GMP: 6</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>22-Sep GMP: 10</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>21-Sep 9:28</t>
+          <t>22-Sep 9:37</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3161,79 +3173,79 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Veegaland Developers IPOL@154.00 (10%)</t>
+          <t>Quanto Agroworld BSE SMEL@66.99 (-0.01%)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹8 (5.71%) 5 ↓ / 33 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>14.6x</t>
+          <t>1.39x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹210.00 Cr</t>
+          <t>₹31.02 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 25</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 10</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 8</t>
+          <t>22-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>22-Sep 9:36</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Panchatv Bharat BSE SMEL@128.95 (-7.89%)</t>
+          <t>Vama Wovenfab BSE SMEL@341.00 (0%)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
+          <t>₹3 (0.88%) 3 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3243,47 +3255,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>2.53x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹24.58 Cr</t>
+          <t>₹49.54 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 7</t>
+          <t>15-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 3</t>
+          <t>17-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 3</t>
+          <t>22-Sep GMP: 3</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>22-Sep 9:37</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3295,12 +3307,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Om Galaxy BSE SMEL@90.20 (0.22%)</t>
+          <t>Manika Plastech IPOL@43.00 (0%)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (2.33%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3310,47 +3322,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.07x</t>
+          <t>29.46x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹105.00 Cr</t>
+          <t>₹125.50 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>11-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 0</t>
+          <t>21-Sep GMP: 1</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>18-Sep 9:36</t>
+          <t>21-Sep 9:37</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3362,12 +3374,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Raksan Transformers BSE SMEL@273.00 (0%)</t>
+          <t>Century Business Media BSE SMEL@74.00 (0%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>₹12 (4.40%) 11 ↓ / 61 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3377,47 +3389,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>47.43x</t>
+          <t>57.93x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹150.50 Cr</t>
+          <t>₹17.11 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 28</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 50</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 12</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>21-Sep 9:28</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3429,62 +3441,62 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Maharaja &amp; Speedex India BSE SMEL@250.00 (34.41%)</t>
+          <t>Injecto Polymers BSE SMEL@99.00 (-1%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>32.41x</t>
+          <t>1.23x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹80.13 Cr</t>
+          <t>₹56.12 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 30</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 28</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 28</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>21-Sep 9:37</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3496,12 +3508,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Vinod Texworld NSE SMEL@94.00 (0%)</t>
+          <t>Om Galaxy BSE SMEL@90.20 (0.22%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3511,119 +3523,119 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>2.07x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹42.83 Cr</t>
+          <t>₹105.00 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>10-Sep</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 1</t>
+          <t>18-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>17-Sep 9:33</t>
+          <t>18-Sep 9:36</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Asset Reconstruction IPOL@139.00 (0%)</t>
+          <t>Panchatv Bharat BSE SMEL@128.95 (-7.89%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹12 (8.63%) 12 ↓ / 30 ↑</t>
+          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20.1x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹732.97 Cr</t>
+          <t>₹24.58 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 24</t>
+          <t>10-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 14.5</t>
+          <t>15-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 12</t>
+          <t>18-Sep GMP: 3</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>17-Sep 9:30</t>
+          <t>18-Sep 9:37</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -3697,12 +3709,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Steamhouse IPOL@94.50 (16.67%)</t>
+          <t>Maharaja &amp; Speedex India BSE SMEL@250.00 (34.41%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹13.5 (16.67%) 13.50 ↓ / 24 ↑</t>
+          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3712,47 +3724,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>32.07x</t>
+          <t>32.41x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹414.00 Cr</t>
+          <t>₹80.13 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>10-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 21</t>
+          <t>15-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 13.5</t>
+          <t>18-Sep GMP: 28</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>17-Sep 9:34</t>
+          <t>18-Sep 9:37</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3764,12 +3776,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Manipal Payment and Identity Solutions IPOL@330.00 (-2.65%)</t>
+          <t>Raksan Transformers BSE SMEL@273.00 (0%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹-6 (-1.77%) -10 ↓ / 38 ↑</t>
+          <t>₹12 (4.40%) 11 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3779,47 +3791,47 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>47.43x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>273</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹805.00 Cr</t>
+          <t>₹150.50 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 8</t>
+          <t>10-Sep GMP: 28</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>15-Sep GMP: 50</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>17-Sep GMP: -6</t>
+          <t>18-Sep GMP: 12</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>17-Sep 9:36</t>
+          <t>18-Sep 9:37</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3831,62 +3843,62 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Rentomojo IPOL@482.45 (19.42%)</t>
+          <t>Veegaland Developers IPOL@154.00 (10%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹87 (21.53%) 79 ↓ / 160 ↑</t>
+          <t>₹8 (5.71%) 5 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>72.89x</t>
+          <t>14.6x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹1255.57 Cr</t>
+          <t>₹210.00 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 143</t>
+          <t>10-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 148</t>
+          <t>15-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 87</t>
+          <t>18-Sep GMP: 8</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>17-Sep 9:32</t>
+          <t>18-Sep 9:37</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3898,12 +3910,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Infrax Renewable BSE SMEL@104.00 (0%)</t>
+          <t>Manipal Payment and Identity Solutions IPOL@330.00 (-2.65%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-6 (-1.77%) -10 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3913,32 +3925,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.05x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>339</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹40.88 Cr</t>
+          <t>₹805.00 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>9-Sep</t>
+          <t>9-Sep GMP: 8</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3948,64 +3960,64 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 0</t>
+          <t>17-Sep GMP: -6</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>17-Sep 9:31</t>
+          <t>17-Sep 9:36</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Karamtara Engineering IPOL@320.00 (25.98%)</t>
+          <t>Vinod Texworld NSE SMEL@94.00 (0%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>₹46 (18.11%) 40 ↓ / 75 ↑</t>
+          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>66.01x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹875.00 Cr</t>
+          <t>₹42.83 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 75</t>
+          <t>9-Sep GMP: 20</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 67</t>
+          <t>11-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4015,17 +4027,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 46</t>
+          <t>17-Sep GMP: 1</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>17-Sep 9:29</t>
+          <t>17-Sep 9:33</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -504,7 +504,11 @@
           <t>Pind Hospitality BSE SMEU</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -550,7 +554,11 @@
           <t>6-Oct</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>22-Sep 18:59</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>❌</t>
@@ -615,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -632,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹15 (4.92%) 15 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>22-Sep 13:29</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -749,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>22-Sep 13:33</t>
+          <t>22-Sep 18:54</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -833,12 +841,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹34 (12.50%) 34 ↓ / 34 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -883,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>22-Sep 13:36</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -950,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>22-Sep 13:36</t>
+          <t>22-Sep 18:54</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1017,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 18:59</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1084,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 18:57</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1109,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹58 (14.32%) 55 ↓ / 64 ↑</t>
+          <t>₹50 (12.35%) 50 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1218,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>22-Sep 13:35</t>
+          <t>22-Sep 19:00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1285,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>22-Sep 13:28</t>
+          <t>22-Sep 18:56</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1302,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹8.5 (25.00%) 5 ↓ / 8.50 ↑</t>
+          <t>₹10 (29.41%) 5 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1352,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1419,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,12 +1444,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹26 (19.40%) 26 ↓ / 37 ↑</t>
+          <t>₹32 (23.88%) 32 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1486,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1620,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1687,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>22-Sep 13:29</t>
+          <t>22-Sep 19:00</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1754,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1821,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>22-Sep 13:36</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1888,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>22-Sep 13:30</t>
+          <t>22-Sep 18:58</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1905,7 +1913,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹10 (2.76%) 10 ↓ / 16 ↑</t>
+          <t>₹5 (1.38%) 5 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1955,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2022,7 +2030,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>22-Sep 13:32</t>
+          <t>22-Sep 19:01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2039,7 +2047,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹3 (1.62%) 3 ↓ / 8 ↑</t>
+          <t>₹8.5 (4.59%) 3 ↓ / 8.50 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2089,7 +2097,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2116,7 +2124,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.07x</t>
+          <t>0.11x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2156,7 +2164,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>22-Sep 13:32</t>
+          <t>22-Sep 19:00</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2173,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹6 (4.05%) 6 ↓ / 15 ↑</t>
+          <t>₹5 (3.38%) 5 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2183,7 +2191,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.08x</t>
+          <t>0.12x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2203,7 +2211,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 6</t>
+          <t>22-Sep GMP: 5</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2223,7 +2231,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2250,7 +2258,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.07x</t>
+          <t>0.59x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2290,7 +2298,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>22-Sep 13:33</t>
+          <t>22-Sep 18:54</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2317,7 +2325,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.29x</t>
+          <t>0.38x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2357,7 +2365,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2384,7 +2392,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.14x</t>
+          <t>0.17x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2424,7 +2432,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>22-Sep 13:35</t>
+          <t>22-Sep 19:00</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2441,7 +2449,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹55 (51.89%) 45 ↓ / 55 ↑</t>
+          <t>₹65 (61.32%) 45 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,7 +2459,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>43.18x</t>
+          <t>72.74x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2491,7 +2499,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2503,7 +2511,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMECT</t>
+          <t>Axiom Gas Engineering NSE SMEC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2518,7 +2526,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.18x</t>
+          <t>1.39x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2558,7 +2566,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>22-Sep 13:29</t>
+          <t>22-Sep 18:56</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2692,7 +2700,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2759,7 +2767,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2826,7 +2834,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2843,7 +2851,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹52 (2.91%) 48 ↓ / 310 ↑</t>
+          <t>₹43 (2.41%) 43 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2893,7 +2901,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2910,7 +2918,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
+          <t>₹27 (29.03%) 11 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2960,7 +2968,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2977,7 +2985,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹-2 (-2.38%) -2 ↓ / 24 ↑</t>
+          <t>₹-3 (-3.57%) -3 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3027,7 +3035,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3044,7 +3052,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹139 (32.78%) 30 ↓ / 147 ↑</t>
+          <t>₹152 (35.85%) 30 ↓ / 152 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3094,7 +3102,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,14 +501,10 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
-        </is>
-      </c>
+          <t>Omara Ventures India BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -521,44 +517,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>6-Oct</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>22-Sep 18:59</t>
-        </is>
-      </c>
+          <t>8-Oct</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>❌</t>
@@ -568,17 +560,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEU</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹12 (10.91%) 12 ↓ / 12 ↑</t>
-        </is>
-      </c>
+          <t>EverestIMS Technologies BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -588,44 +576,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>5-Oct</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>22-Sep 19:02</t>
-        </is>
-      </c>
+          <t>8-Oct</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
@@ -635,14 +619,10 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOU</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>₹15 (4.92%) 15 ↓ / 15 ↑</t>
-        </is>
-      </c>
+          <t>Black Opal Consultants BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -655,44 +635,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹499.83 Cr</t>
+          <t>₹55.08 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>5-Oct</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>22-Sep 19:02</t>
-        </is>
-      </c>
+          <t>7-Oct</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
@@ -702,7 +678,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEU</t>
+          <t>Acme Universal Safezone 9 BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -722,42 +698,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹35.93 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>22-Sep 18:54</t>
+          <t>23-Sep 13:34</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -769,17 +745,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>German Green Steel IPOU</t>
+          <t>Pind Hospitality BSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹15 (10.79%) 15 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -789,64 +765,60 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹303.90 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:28</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Orient Cables IPOU</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>₹34 (12.50%) 34 ↓ / 34 ↑</t>
-        </is>
-      </c>
+          <t>SRIT India IPOU</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -856,44 +828,40 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>5-Oct</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>22-Sep 19:02</t>
-        </is>
-      </c>
+          <t>6-Oct</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>✅</t>
@@ -903,14 +871,10 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
-        </is>
-      </c>
+          <t>Shah Investor's Home IPOU</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -923,54 +887,50 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5-Oct</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>22-Sep 18:54</t>
-        </is>
-      </c>
+          <t>6-Oct</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEU</t>
+          <t>Shivchem Agro BSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -990,54 +950,54 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>22-Sep 18:59</t>
+          <t>23-Sep 13:34</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Acevector IPOU</t>
+          <t>Himalayan Solar NSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1057,17 +1017,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹420.00 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1092,7 +1052,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>22-Sep 18:57</t>
+          <t>23-Sep 13:28</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1104,17 +1064,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-One Steels IPOU</t>
+          <t>Dudani Retail BSE SMEU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹50 (12.35%) 50 ↓ / 64 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1124,64 +1084,64 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:30</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEU</t>
+          <t>Runwal Enterprises IPOU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹17 (5.57%) 17 ↓ / 18 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1191,61 +1151,57 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹60.10 Cr</t>
+          <t>₹499.83 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>22-Sep 19:00</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
-        </is>
-      </c>
+          <t>Shree TNB Polymers BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -1258,64 +1214,60 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹31.20 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1-Oct</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>22-Sep 18:56</t>
-        </is>
-      </c>
+          <t>5-Oct</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Moneyview IPOU</t>
+          <t>Sai Urja Indo BSE SMEU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹10 (29.41%) 5 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1325,42 +1277,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:29</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1372,17 +1324,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEU</t>
+          <t>Orient Cables IPOU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹14 (21.88%) 14 ↓ / 14 ↑</t>
+          <t>₹40 (14.71%) 34 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1392,42 +1344,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1439,17 +1391,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOU</t>
+          <t>Acevector IPOU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹32 (23.88%) 32 ↓ / 37 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1459,42 +1411,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹420.00 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:28</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1573,17 +1525,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOU</t>
+          <t>Bench Mark Infotech Services NSE SMEU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹12 (3.20%) 1 ↓ / 12 ↑</t>
+          <t>₹12 (10.91%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1593,42 +1545,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1640,17 +1592,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEU</t>
+          <t>German Green Steel IPOU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹15 (10.79%) 15 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1660,42 +1612,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹303.90 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>22-Sep 19:00</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1707,17 +1659,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEU</t>
+          <t>A-One Steels IPOU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹50 (12.35%) 50 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1727,54 +1679,54 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEU</t>
+          <t>Peshwa Wheat BSE SMEU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1794,42 +1746,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:34</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1841,17 +1793,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEU</t>
+          <t>Roopa Screen BSE SMEU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹14 (21.88%) 14 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1861,42 +1813,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>22-Sep 18:58</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1908,12 +1860,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOU</t>
+          <t>Green Asia Impex NSE SMEU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹5 (1.38%) 5 ↓ / 16 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1928,64 +1880,64 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹60.10 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:36</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEU</t>
+          <t>Moneyview IPOU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹12.5 (36.76%) 5 ↓ / 12.50 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1995,42 +1947,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>22-Sep 19:01</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2042,12 +1994,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOU</t>
+          <t>S.K.Offset BSE SMEO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹8.5 (4.59%) 3 ↓ / 8.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2057,27 +2009,27 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.11x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹160.88 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2097,7 +2049,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:28</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2109,7 +2061,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEO</t>
+          <t>Unitec Fibres BSE SMEO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2124,47 +2076,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.11x</t>
+          <t>0.04x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 0</t>
+          <t>23-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>22-Sep 19:00</t>
+          <t>23-Sep 13:34</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2176,12 +2128,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOO</t>
+          <t>Swastika Infra IPOO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹5 (3.38%) 5 ↓ / 15 ↑</t>
+          <t>₹7 (3.78%) 3 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,47 +2143,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.12x</t>
+          <t>0.56x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹708.02 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 5</t>
+          <t>23-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2243,7 +2195,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMEO</t>
+          <t>Liqvd Digital BSE SMEO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2258,47 +2210,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.59x</t>
+          <t>0.55x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹25.52 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 0</t>
+          <t>23-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>22-Sep 18:54</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2310,62 +2262,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMEO</t>
+          <t>Adroit Industries IPOO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹33 (24.63%) 32 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.38x</t>
+          <t>2.89x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹45.24 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep GMP: 33</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>22-Sep 19:01</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2377,7 +2329,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMEO</t>
+          <t>Pooja Logistics NSE SMEO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2392,47 +2344,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.17x</t>
+          <t>0.23x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹22.20 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>22-Sep 19:00</t>
+          <t>23-Sep 13:30</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2444,62 +2396,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEO</t>
+          <t>ArMee Infotech IPOO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹65 (61.32%) 45 ↓ / 65 ↑</t>
+          <t>₹56 (14.93%) 1 ↓ / 56 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>72.74x</t>
+          <t>0.41x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 55</t>
+          <t>23-Sep GMP: 56</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2511,12 +2463,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMEC</t>
+          <t>Elevate Campuses IPOO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹3 (0.83%) 3 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2526,47 +2478,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>0.11x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹50.75 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>23-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 0</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>22-Sep 18:56</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2645,12 +2597,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kheria Autocomp NSE SMEC</t>
+          <t>Core Integra Consulting NSE SMEO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2660,114 +2612,114 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.48x</t>
+          <t>0.11x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹46.44 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 10</t>
+          <t>23-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 3</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:36</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMEC</t>
+          <t>Varmora Granito IPOO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹67 (56.78%) 27 ↓ / 67 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>304.06x</t>
+          <t>0.19x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹42.52 Cr</t>
+          <t>₹708.02 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 30</t>
+          <t>22-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 67</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2779,12 +2731,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sonaselection India IPOC</t>
+          <t>Anand Seamless BSE SMEO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2794,64 +2746,64 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.01x</t>
+          <t>0.59x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹141.57 Cr</t>
+          <t>₹25.52 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 2</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:32</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NSE IPOC</t>
+          <t>Himalaya Nutravedics BSE SMEO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹43 (2.41%) 43 ↓ / 310 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2861,47 +2813,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5.71x</t>
+          <t>0.29x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹22561.57 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 142</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 65</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:31</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2913,62 +2865,62 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOCAllotted</t>
+          <t>Robokidz Eduventures BSE SMECT</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹27 (29.03%) 11 ↓ / 30 ↑</t>
+          <t>₹65 (61.32%) 45 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>177.03x</t>
+          <t>471.12x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 25</t>
+          <t>21-Sep GMP: 55</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 26.5</t>
+          <t>23-Sep GMP: 65</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2980,12 +2932,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Hero Motors IPOCAllotted</t>
+          <t>Vivekanand Cotspin BSE SMECT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹-3 (-3.57%) -3 ↓ / 24 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2995,47 +2947,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>7.01x</t>
+          <t>1.31x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹1000.00 Cr</t>
+          <t>₹22.20 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 13</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 0</t>
+          <t>23-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:36</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3047,62 +2999,62 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SS Retail IPOCAllotted</t>
+          <t>FX Multitech BSE SMECT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹152 (35.85%) 30 ↓ / 152 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>107.41x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹45.24 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 90</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 145</t>
+          <t>23-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3114,32 +3066,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Shakti Polytarp BSE SMEL@58.90 (-0.17%)</t>
+          <t>Axiom Gas Engineering NSE SMEC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>₹10 (16.95%) 5 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11.87x</t>
+          <t>1.39x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹26.93 Cr</t>
+          <t>₹50.75 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3149,27 +3101,27 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 6</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 10</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>22-Sep 9:37</t>
+          <t>23-Sep 13:35</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3181,12 +3133,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Quanto Agroworld BSE SMEL@66.99 (-0.01%)</t>
+          <t>NSE IPOCAllotted</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹76 (4.26%) 43 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3196,64 +3148,64 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>5.71x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹31.02 Cr</t>
+          <t>₹22561.57 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>17-Sep GMP: 142</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep GMP: 65</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 0</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>22-Sep 9:36</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Vama Wovenfab BSE SMEL@341.00 (0%)</t>
+          <t>Sonaselection India IPOCAllotted</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>₹3 (0.88%) 3 ↓ / 70 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3263,114 +3215,114 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2.53x</t>
+          <t>2.01x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹49.54 Cr</t>
+          <t>₹141.57 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 30</t>
+          <t>17-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 3</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 3</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>22-Sep 9:37</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Manika Plastech IPOL@43.00 (0%)</t>
+          <t>SpectraA Technology Solutions NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹1 (2.33%) 1 ↓ / 20 ↑</t>
+          <t>₹77 (65.25%) 27 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>29.46x</t>
+          <t>304.06x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹125.50 Cr</t>
+          <t>₹42.52 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>17-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 2</t>
+          <t>21-Sep GMP: 67</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 1</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>21-Sep 9:37</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3382,12 +3334,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Century Business Media BSE SMEL@74.00 (0%)</t>
+          <t>Kheria Autocomp NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3397,47 +3349,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>57.93x</t>
+          <t>2.48x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹17.11 Cr</t>
+          <t>₹46.44 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>17-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>21-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>21-Sep 9:28</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3449,62 +3401,62 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Injecto Polymers BSE SMEL@99.00 (-1%)</t>
+          <t>Jindal Supreme IPOL@120.00 (29.03%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.23x</t>
+          <t>177.03x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹56.12 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>16-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep GMP: 26.5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>23-Sep GMP: 29</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>21-Sep 9:37</t>
+          <t>23-Sep 9:37</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3516,12 +3468,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Om Galaxy BSE SMEL@90.20 (0.22%)</t>
+          <t>Hero Motors IPOL@82.00 (-2.38%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-3 (-3.57%) -3 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3531,47 +3483,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2.07x</t>
+          <t>7.01x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹105.00 Cr</t>
+          <t>₹1000.00 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>10-Sep</t>
+          <t>16-Sep GMP: 13</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>18-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 0</t>
+          <t>23-Sep GMP: -3</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>18-Sep 9:36</t>
+          <t>23-Sep 9:37</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3583,67 +3535,67 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Panchatv Bharat BSE SMEL@128.95 (-7.89%)</t>
+          <t>SS Retail IPOL@624.00 (47.17%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹3 (2.14%) 3 ↓ / 21 ↑</t>
+          <t>₹160 (37.74%) 30 ↓ / 160 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>107.41x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹24.58 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 7</t>
+          <t>16-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 3</t>
+          <t>18-Sep GMP: 145</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 3</t>
+          <t>23-Sep GMP: 160</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>23-Sep 9:37</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3717,129 +3669,129 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Maharaja &amp; Speedex India BSE SMEL@250.00 (34.41%)</t>
+          <t>Quanto Agroworld BSE SMEL@66.99 (-0.01%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹28 (15.05%) 15 ↓ / 48 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>32.41x</t>
+          <t>1.39x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹80.13 Cr</t>
+          <t>₹31.02 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 30</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 28</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 28</t>
+          <t>22-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>22-Sep 9:36</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Raksan Transformers BSE SMEL@273.00 (0%)</t>
+          <t>Shakti Polytarp BSE SMEL@58.90 (-0.17%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹12 (4.40%) 11 ↓ / 61 ↑</t>
+          <t>₹10 (16.95%) 5 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>47.43x</t>
+          <t>11.87x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹150.50 Cr</t>
+          <t>₹26.93 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 28</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 50</t>
+          <t>17-Sep GMP: 6</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 12</t>
+          <t>22-Sep GMP: 10</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>22-Sep 9:37</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3851,79 +3803,79 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Veegaland Developers IPOL@154.00 (10%)</t>
+          <t>Vama Wovenfab BSE SMEL@341.00 (0%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹8 (5.71%) 5 ↓ / 33 ↑</t>
+          <t>₹3 (0.88%) 3 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>14.6x</t>
+          <t>2.53x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹210.00 Cr</t>
+          <t>₹49.54 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>10-Sep GMP: 25</t>
+          <t>15-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 10</t>
+          <t>17-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 8</t>
+          <t>22-Sep GMP: 3</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>18-Sep 9:37</t>
+          <t>22-Sep 9:37</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Manipal Payment and Identity Solutions IPOL@330.00 (-2.65%)</t>
+          <t>Manika Plastech IPOL@43.00 (0%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹-6 (-1.77%) -10 ↓ / 38 ↑</t>
+          <t>₹1 (2.33%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3933,47 +3885,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>29.46x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹805.00 Cr</t>
+          <t>₹125.50 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 8</t>
+          <t>11-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>16-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>17-Sep GMP: -6</t>
+          <t>21-Sep GMP: 1</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>17-Sep 9:36</t>
+          <t>21-Sep 9:37</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3985,12 +3937,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Vinod Texworld NSE SMEL@94.00 (0%)</t>
+          <t>Century Business Media BSE SMEL@74.00 (0%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>₹1 (1.06%) 1 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4000,52 +3952,52 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>57.93x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹42.83 Cr</t>
+          <t>₹17.11 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>9-Sep GMP: 20</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 1</t>
+          <t>16-Sep</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 1</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>17-Sep 9:33</t>
+          <t>21-Sep 9:28</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>23-Sep 13:34</t>
+          <t>23-Sep 18:55</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23-Sep 13:28</t>
+          <t>23-Sep 18:54</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -815,10 +815,14 @@
           <t>SRIT India IPOU</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>₹12 (9.23%) 12 ↓ / 12 ↑</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -861,7 +865,11 @@
           <t>6-Oct</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>23-Sep 19:02</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>✅</t>
@@ -874,10 +882,14 @@
           <t>Shah Investor's Home IPOU</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>₹10 (5.99%) 10 ↓ / 10 ↑</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -920,7 +932,11 @@
           <t>6-Oct</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>23-Sep 19:02</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>✅</t>
@@ -985,7 +1001,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>23-Sep 13:34</t>
+          <t>23-Sep 19:01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1052,7 +1068,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>23-Sep 13:28</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1119,7 +1135,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>23-Sep 13:30</t>
+          <t>23-Sep 18:56</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1186,7 +1202,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1201,7 +1217,11 @@
           <t>Shree TNB Polymers BSE SMEU</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -1247,7 +1267,11 @@
           <t>5-Oct</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>23-Sep 18:54</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>✅</t>
@@ -1312,7 +1336,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>23-Sep 13:29</t>
+          <t>23-Sep 19:01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1329,7 +1353,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹40 (14.71%) 34 ↓ / 40 ↑</t>
+          <t>₹45 (16.54%) 34 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1379,7 +1403,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1446,7 +1470,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>23-Sep 13:28</t>
+          <t>23-Sep 18:55</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1580,7 +1604,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1597,7 +1621,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹15 (10.79%) 15 ↓ / 15 ↑</t>
+          <t>₹20 (14.39%) 15 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1647,7 +1671,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1664,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹50 (12.35%) 50 ↓ / 64 ↑</t>
+          <t>₹51 (12.59%) 50 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1714,7 +1738,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1781,7 +1805,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>23-Sep 13:34</t>
+          <t>23-Sep 18:55</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1798,12 +1822,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹14 (21.88%) 14 ↓ / 14 ↑</t>
+          <t>₹10 (15.62%) 10 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1848,7 +1872,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1915,7 +1939,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>23-Sep 13:36</t>
+          <t>23-Sep 19:00</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1932,7 +1956,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹12.5 (36.76%) 5 ↓ / 12.50 ↑</t>
+          <t>₹14 (41.18%) 5 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1982,7 +2006,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2009,7 +2033,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.11x</t>
+          <t>0.12x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2049,7 +2073,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>23-Sep 13:28</t>
+          <t>23-Sep 19:00</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2076,7 +2100,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.04x</t>
+          <t>0.13x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2116,7 +2140,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>23-Sep 13:34</t>
+          <t>23-Sep 18:57</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2133,17 +2157,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹7 (3.78%) 3 ↓ / 8 ↑</t>
+          <t>₹9.5 (5.14%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.56x</t>
+          <t>1x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2163,7 +2187,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 7</t>
+          <t>23-Sep GMP: 9.5</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2183,7 +2207,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2210,7 +2234,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.55x</t>
+          <t>1.03x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2250,7 +2274,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:00</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2267,7 +2291,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹33 (24.63%) 32 ↓ / 37 ↑</t>
+          <t>₹35 (26.12%) 32 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2277,7 +2301,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.89x</t>
+          <t>5.22x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2297,7 +2321,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 33</t>
+          <t>23-Sep GMP: 35</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2317,7 +2341,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2344,7 +2368,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.23x</t>
+          <t>0.34x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2384,7 +2408,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>23-Sep 13:30</t>
+          <t>23-Sep 18:56</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2401,7 +2425,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹56 (14.93%) 1 ↓ / 56 ↑</t>
+          <t>₹51 (13.60%) 1 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2411,7 +2435,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.41x</t>
+          <t>0.57x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2431,7 +2455,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 56</t>
+          <t>23-Sep GMP: 51</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2451,7 +2475,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2468,7 +2492,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹3 (0.83%) 3 ↓ / 16 ↑</t>
+          <t>₹4.5 (1.24%) 4.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2478,7 +2502,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.11x</t>
+          <t>0.21x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2498,7 +2522,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 3</t>
+          <t>23-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2518,7 +2542,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2612,7 +2636,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.11x</t>
+          <t>0.14x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2652,7 +2676,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>23-Sep 13:36</t>
+          <t>23-Sep 18:56</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2679,7 +2703,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.19x</t>
+          <t>0.27x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2719,7 +2743,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2746,7 +2770,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.59x</t>
+          <t>0.74x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2786,7 +2810,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>23-Sep 13:32</t>
+          <t>23-Sep 18:53</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2813,7 +2837,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.29x</t>
+          <t>0.4x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2853,7 +2877,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>23-Sep 13:31</t>
+          <t>23-Sep 18:58</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2865,12 +2889,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMECT</t>
+          <t>Robokidz Eduventures BSE SMEC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹65 (61.32%) 45 ↓ / 65 ↑</t>
+          <t>₹55 (51.89%) 45 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2880,7 +2904,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>471.12x</t>
+          <t>833.56x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2905,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 65</t>
+          <t>23-Sep GMP: 55</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2920,7 +2944,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2932,7 +2956,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMECT</t>
+          <t>Vivekanand Cotspin BSE SMEC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2947,7 +2971,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.31x</t>
+          <t>1.79x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2987,7 +3011,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>23-Sep 13:36</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2999,12 +3023,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMECT</t>
+          <t>FX Multitech BSE SMEC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹4 (3.45%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3014,7 +3038,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>17.72x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3039,7 +3063,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 0</t>
+          <t>23-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3054,7 +3078,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3121,7 +3145,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>23-Sep 13:35</t>
+          <t>23-Sep 18:53</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3138,7 +3162,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹76 (4.26%) 43 ↓ / 310 ↑</t>
+          <t>₹81 (4.54%) 43 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3188,7 +3212,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3255,7 +3279,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3322,7 +3346,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3389,7 +3413,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMEU</t>
+          <t>Papadmalji Agro Foods NSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -517,37 +517,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹20.18 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>1-Oct</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>5-Oct</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>6-Oct</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -560,7 +560,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEU</t>
+          <t>Dove Soft BSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -576,22 +576,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹73.26 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -612,14 +612,14 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMEU</t>
+          <t>Vans Electroengineerings BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -635,17 +635,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹55.08 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMEU</t>
+          <t>Paramount Syntex BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -698,54 +698,54 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹35.93 Cr</t>
+          <t>₹81.79 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>9-Oct</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>23-Sep 18:55</t>
+          <t>24-Sep 5:55</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEU</t>
+          <t>Omara Ventures India BSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -765,42 +765,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23-Sep 18:54</t>
+          <t>24-Sep 5:55</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -812,17 +812,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SRIT India IPOU</t>
+          <t>EverestIMS Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹12 (9.23%) 12 ↓ / 12 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -832,42 +832,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹218.40 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 5:55</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -879,17 +879,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOU</t>
+          <t>Black Opal Consultants BSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹10 (5.99%) 10 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -899,42 +899,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹55.08 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:31</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMEU</t>
+          <t>Acme Universal Safezone 9 BSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -966,17 +966,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹14.01 Cr</t>
+          <t>₹35.93 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1001,29 +1001,29 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>23-Sep 19:01</t>
+          <t>24-Sep 9:35</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEU</t>
+          <t>Shah Investor's Home IPOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹10 (5.99%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1033,42 +1033,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1080,17 +1080,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEU</t>
+          <t>SRIT India IPOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹12 (9.23%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1100,64 +1100,64 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>23-Sep 18:56</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOU</t>
+          <t>Pind Hospitality BSE SMEU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹17 (5.57%) 17 ↓ / 18 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1167,54 +1167,54 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹499.83 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:34</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shree TNB Polymers BSE SMEU</t>
+          <t>Shivchem Agro BSE SMEU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹31.20 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1249,32 +1249,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23-Sep 18:54</t>
+          <t>24-Sep 9:32</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>23-Sep 19:01</t>
+          <t>24-Sep 9:31</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1348,17 +1348,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Orient Cables IPOU</t>
+          <t>Himalayan Solar NSE SMEU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹45 (16.54%) 34 ↓ / 45 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:28</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>23-Sep 18:55</t>
+          <t>24-Sep 9:34</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1549,12 +1549,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEU</t>
+          <t>Orient Cables IPOU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹12 (10.91%) 12 ↓ / 12 ↑</t>
+          <t>₹45 (16.54%) 34 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1569,17 +1569,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹20 (14.39%) 15 ↓ / 20 ↑</t>
+          <t>₹24 (17.27%) 15 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1683,17 +1683,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A-One Steels IPOU</t>
+          <t>Dudani Retail BSE SMEU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹51 (12.59%) 50 ↓ / 64 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1703,64 +1703,64 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:34</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEU</t>
+          <t>Bench Mark Infotech Services NSE SMEU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹12 (10.91%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1785,49 +1785,49 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>23-Sep 18:55</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEU</t>
+          <t>Shree TNB Polymers BSE SMEU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹10 (15.62%) 10 ↓ / 14 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹31.20 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1852,27 +1852,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:29</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1884,17 +1884,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEU</t>
+          <t>Runwal Enterprises IPOU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹17 (5.57%) 17 ↓ / 18 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1904,64 +1904,64 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹60.10 Cr</t>
+          <t>₹499.83 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>23-Sep 19:00</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Moneyview IPOU</t>
+          <t>Green Asia Impex NSE SMEO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹14 (41.18%) 5 ↓ / 14 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1971,22 +1971,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹60.10 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2006,74 +2006,74 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:34</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEO</t>
+          <t>Moneyview IPOO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹14 (41.18%) 5 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.12x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 0</t>
+          <t>24-Sep GMP: 14</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>23-Sep 19:00</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2085,7 +2085,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEO</t>
+          <t>Peshwa Wheat BSE SMEO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2100,114 +2100,114 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.13x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 0</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>23-Sep 18:57</t>
+          <t>24-Sep 9:34</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOO</t>
+          <t>Roopa Screen BSE SMEO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹9.5 (5.14%) 3 ↓ / 9.50 ↑</t>
+          <t>₹8 (12.50%) 8 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹160.88 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 9.5</t>
+          <t>24-Sep GMP: 8</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2219,109 +2219,109 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEO</t>
+          <t>A-One Steels IPOO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹55 (13.58%) 50 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.03x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 0</t>
+          <t>24-Sep GMP: 55</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>23-Sep 19:00</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOO</t>
+          <t>Liqvd Digital BSE SMEO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹35 (26.12%) 32 ↓ / 37 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5.22x</t>
+          <t>1.03x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 35</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2341,54 +2341,54 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:31</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEO</t>
+          <t>Swastika Infra IPOO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹9.5 (5.14%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.34x</t>
+          <t>1x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 0</t>
+          <t>23-Sep GMP: 9.5</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>23-Sep 18:56</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2420,42 +2420,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOO</t>
+          <t>Elevate Campuses IPOO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹51 (13.60%) 1 ↓ / 51 ↑</t>
+          <t>₹4.5 (1.24%) 4.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.57x</t>
+          <t>0.21x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 51</t>
+          <t>23-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2487,12 +2487,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOO</t>
+          <t>Pooja Logistics NSE SMEO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹4.5 (1.24%) 4.50 ↓ / 16 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2502,27 +2502,27 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.21x</t>
+          <t>0.34x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4.5</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:36</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 0</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>23-Sep 18:56</t>
+          <t>24-Sep 9:32</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2688,12 +2688,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOO</t>
+          <t>S.K.Offset BSE SMEO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2703,47 +2703,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.27x</t>
+          <t>0.12x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹708.02 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 3</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:33</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2755,129 +2755,129 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMEO</t>
+          <t>Adroit Industries IPOO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹34 (25.37%) 32 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.74x</t>
+          <t>5.22x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹25.52 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>23-Sep 18:53</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEO</t>
+          <t>ArMee Infotech IPOO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹51 (13.60%) 1 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.4x</t>
+          <t>0.57x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep GMP: 51</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>23-Sep 18:58</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2889,62 +2889,62 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEC</t>
+          <t>Unitec Fibres BSE SMEO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹55 (51.89%) 45 ↓ / 65 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>833.56x</t>
+          <t>0.13x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 55</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 55</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:30</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2956,12 +2956,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMEC</t>
+          <t>Varmora Granito IPOCT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,47 +2971,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.79x</t>
+          <t>0.27x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹22.20 Cr</t>
+          <t>₹708.02 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 0</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3023,12 +3023,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMEC</t>
+          <t>Himalaya Nutravedics BSE SMECT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹4 (3.45%) 4 ↓ / 4 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3038,17 +3038,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>17.72x</t>
+          <t>0.4x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹45.24 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3058,27 +3058,27 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:36</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3090,7 +3090,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMEC</t>
+          <t>Anand Seamless BSE SMECT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3105,64 +3105,64 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>0.74x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹50.75 Cr</t>
+          <t>₹25.52 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>23-Sep 18:53</t>
+          <t>24-Sep 9:28</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NSE IPOCAllotted</t>
+          <t>FX Multitech BSE SMEC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹81 (4.54%) 43 ↓ / 310 ↑</t>
+          <t>₹4 (3.45%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3172,47 +3172,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5.71x</t>
+          <t>17.72x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹22561.57 Cr</t>
+          <t>₹45.24 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 142</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 65</t>
+          <t>23-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3224,62 +3224,62 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sonaselection India IPOCAllotted</t>
+          <t>Robokidz Eduventures BSE SMEC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
+          <t>₹55 (51.89%) 45 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2.01x</t>
+          <t>833.56x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹141.57 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 2</t>
+          <t>21-Sep GMP: 55</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>23-Sep GMP: 55</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3291,62 +3291,62 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMECAllotted</t>
+          <t>Vivekanand Cotspin BSE SMEC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹77 (65.25%) 27 ↓ / 77 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>304.06x</t>
+          <t>1.79x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹42.52 Cr</t>
+          <t>₹22.20 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 30</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 67</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:35</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3358,12 +3358,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kheria Autocomp NSE SMECAllotted</t>
+          <t>Axiom Gas Engineering NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3373,47 +3373,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.48x</t>
+          <t>1.39x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹46.44 Cr</t>
+          <t>₹50.75 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 10</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 3</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:28</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3425,62 +3425,62 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOL@120.00 (29.03%)</t>
+          <t>Sonaselection India IPOLT</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>177.03x</t>
+          <t>2.01x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹141.57 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 25</t>
+          <t>17-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 26.5</t>
+          <t>21-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 29</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>23-Sep 9:37</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3492,62 +3492,62 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Hero Motors IPOL@82.00 (-2.38%)</t>
+          <t>SpectraA Technology Solutions NSE SMELT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>₹-3 (-3.57%) -3 ↓ / 24 ↑</t>
+          <t>₹81 (68.64%) 27 ↓ / 81 ↑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>7.01x</t>
+          <t>304.06x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹1000.00 Cr</t>
+          <t>₹42.52 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 13</t>
+          <t>17-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 0</t>
+          <t>21-Sep GMP: 67</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>23-Sep GMP: -3</t>
+          <t>24-Sep GMP: 81</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>23-Sep 9:37</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3559,62 +3559,62 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SS Retail IPOL@624.00 (47.17%)</t>
+          <t>NSE IPOLT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹160 (37.74%) 30 ↓ / 160 ↑</t>
+          <t>₹40 (2.24%) 40 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>107.41x</t>
+          <t>5.71x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹22561.57 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 90</t>
+          <t>17-Sep GMP: 142</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 145</t>
+          <t>21-Sep GMP: 65</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 160</t>
+          <t>24-Sep GMP: 40</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>23-Sep 9:37</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3693,12 +3693,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Quanto Agroworld BSE SMEL@66.99 (-0.01%)</t>
+          <t>Kheria Autocomp NSE SMELT</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3708,114 +3708,114 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>2.48x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹31.02 Cr</t>
+          <t>₹46.44 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>17-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 0</t>
+          <t>24-Sep GMP: 3</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>22-Sep 9:36</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Shakti Polytarp BSE SMEL@58.90 (-0.17%)</t>
+          <t>Jindal Supreme IPOL@120.00 (29.03%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹10 (16.95%) 5 ↓ / 10 ↑</t>
+          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>11.87x</t>
+          <t>177.03x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹26.93 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>16-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 6</t>
+          <t>18-Sep GMP: 26.5</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 10</t>
+          <t>23-Sep GMP: 29</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>22-Sep 9:37</t>
+          <t>23-Sep 9:37</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3827,79 +3827,79 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vama Wovenfab BSE SMEL@341.00 (0%)</t>
+          <t>SS Retail IPOL@624.00 (47.17%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹3 (0.88%) 3 ↓ / 70 ↑</t>
+          <t>₹160 (37.74%) 30 ↓ / 160 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2.53x</t>
+          <t>107.41x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹49.54 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>15-Sep GMP: 30</t>
+          <t>16-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 3</t>
+          <t>18-Sep GMP: 145</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 3</t>
+          <t>23-Sep GMP: 160</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>22-Sep 9:37</t>
+          <t>23-Sep 9:37</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Manika Plastech IPOL@43.00 (0%)</t>
+          <t>Hero Motors IPOL@82.00 (-2.38%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹1 (2.33%) 1 ↓ / 20 ↑</t>
+          <t>₹-3 (-3.57%) -3 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3909,47 +3909,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>29.46x</t>
+          <t>7.01x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹125.50 Cr</t>
+          <t>₹1000.00 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>11-Sep GMP: 7</t>
+          <t>16-Sep GMP: 13</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 2</t>
+          <t>18-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 1</t>
+          <t>23-Sep GMP: -3</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>21-Sep 9:37</t>
+          <t>23-Sep 9:37</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Century Business Media BSE SMEL@74.00 (0%)</t>
+          <t>Quanto Agroworld BSE SMEL@66.99 (-0.01%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3976,52 +3976,52 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>57.93x</t>
+          <t>1.39x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹17.11 Cr</t>
+          <t>₹31.02 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>11-Sep</t>
+          <t>15-Sep</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>17-Sep</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>22-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>21-Sep 9:28</t>
+          <t>22-Sep 9:36</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,10 +501,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMEU</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>Paramount Syntex BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -517,40 +521,44 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹20.18 Cr</t>
+          <t>₹81.79 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>7-Oct</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>24-Sep 5:55</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>❌</t>
@@ -560,10 +568,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dove Soft BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Omara Ventures India BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -576,17 +588,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹73.26 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -609,7 +621,11 @@
           <t>8-Oct</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>24-Sep 16:01</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>❌</t>
@@ -619,10 +635,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>Dove Soft BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -635,12 +655,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹73.26 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -650,35 +670,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>7-Oct</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>8-Oct</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>24-Sep 16:00</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Paramount Syntex BSE SMEU</t>
+          <t>EverestIMS Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -698,37 +722,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹81.79 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>5-Oct</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>6-Oct</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>7-Oct</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>9-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -738,21 +762,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
-        </is>
-      </c>
+          <t>Vans Electroengineerings BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -765,61 +785,53 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>1-Oct</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>5-Oct</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>6-Oct</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8-Oct</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>24-Sep 5:55</t>
-        </is>
-      </c>
+          <t>7-Oct</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
-        </is>
-      </c>
+          <t>Papadmalji Agro Foods NSE SMEU</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -832,12 +844,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹20.18 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -852,27 +864,23 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>1-Oct</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>5-Oct</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>6-Oct</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8-Oct</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>24-Sep 5:55</t>
-        </is>
-      </c>
+          <t>7-Oct</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -934,7 +942,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24-Sep 9:31</t>
+          <t>24-Sep 15:56</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1001,7 +1009,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24-Sep 9:35</t>
+          <t>24-Sep 15:57</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1013,17 +1021,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOU</t>
+          <t>Shivchem Agro BSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹10 (5.99%) 10 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1033,17 +1041,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1068,12 +1076,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 15:58</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1143,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1147,17 +1155,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEU</t>
+          <t>Shah Investor's Home IPOU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹12 (7.19%) 10 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1167,17 +1175,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1202,19 +1210,19 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>24-Sep 9:34</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMEU</t>
+          <t>Pind Hospitality BSE SMEU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1234,17 +1242,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹14.01 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1269,7 +1277,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>24-Sep 9:32</t>
+          <t>24-Sep 15:58</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1281,7 +1289,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEU</t>
+          <t>Dudani Retail BSE SMEU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1301,17 +1309,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1336,19 +1344,19 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>24-Sep 9:31</t>
+          <t>24-Sep 15:58</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEU</t>
+          <t>Sai Urja Indo BSE SMEU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1368,12 +1376,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1403,7 +1411,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24-Sep 9:28</t>
+          <t>24-Sep 15:55</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1415,17 +1423,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Acevector IPOU</t>
+          <t>Runwal Enterprises IPOU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹28 (9.18%) 17 ↓ / 28 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1435,17 +1443,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹420.00 Cr</t>
+          <t>₹499.83 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1470,7 +1478,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>24-Sep 9:34</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1549,17 +1557,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Orient Cables IPOU</t>
+          <t>German Green Steel IPOU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹45 (16.54%) 34 ↓ / 45 ↑</t>
+          <t>₹28.5 (20.50%) 15 ↓ / 28.50 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1569,17 +1577,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹303.90 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1604,7 +1612,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1616,17 +1624,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>German Green Steel IPOU</t>
+          <t>Acevector IPOU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹24 (17.27%) 15 ↓ / 24 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1636,17 +1644,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹303.90 Cr</t>
+          <t>₹420.00 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1671,7 +1679,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 15:54</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1683,7 +1691,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEU</t>
+          <t>Himalayan Solar NSE SMEU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1703,17 +1711,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1738,29 +1746,29 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>24-Sep 9:34</t>
+          <t>24-Sep 15:54</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEU</t>
+          <t>Orient Cables IPOU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹12 (10.91%) 12 ↓ / 12 ↑</t>
+          <t>₹58 (21.32%) 34 ↓ / 58 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1770,17 +1778,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1805,7 +1813,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1817,17 +1825,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shree TNB Polymers BSE SMEU</t>
+          <t>Bench Mark Infotech Services NSE SMEU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹12 (10.91%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1837,17 +1845,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹31.20 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1872,7 +1880,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>24-Sep 9:29</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1884,17 +1892,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOU</t>
+          <t>Shree TNB Polymers BSE SMEU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹17 (5.57%) 17 ↓ / 18 ↑</t>
+          <t>₹8 (15.38%) 8 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1904,17 +1912,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹499.83 Cr</t>
+          <t>₹31.20 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1939,7 +1947,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1951,7 +1959,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEO</t>
+          <t>Peshwa Wheat BSE SMEO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1966,22 +1974,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.58x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹60.10 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2006,7 +2014,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>24-Sep 9:34</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2018,12 +2026,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Moneyview IPOO</t>
+          <t>Roopa Screen BSE SMEO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹14 (41.18%) 5 ↓ / 14 ↑</t>
+          <t>₹29 (45.31%) 8 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2033,27 +2041,27 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.12x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 14</t>
+          <t>24-Sep GMP: 29</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2073,7 +2081,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2085,7 +2093,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEO</t>
+          <t>Green Asia Impex NSE SMEO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2100,22 +2108,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹60.10 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2140,7 +2148,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>24-Sep 9:34</t>
+          <t>24-Sep 15:57</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2152,42 +2160,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEO</t>
+          <t>Moneyview IPOO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹8 (12.50%) 8 ↓ / 14 ↑</t>
+          <t>₹12.75 (37.50%) 5 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.26x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 8</t>
+          <t>24-Sep GMP: 12.75</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2207,7 +2215,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2224,7 +2232,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹55 (13.58%) 50 ↓ / 64 ↑</t>
+          <t>₹48 (11.85%) 48 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2234,7 +2242,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.53x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2254,7 +2262,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 55</t>
+          <t>24-Sep GMP: 48</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2274,7 +2282,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2286,42 +2294,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEO</t>
+          <t>Adroit Industries IPOO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹34 (25.37%) 32 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.03x</t>
+          <t>16.48x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2341,54 +2349,54 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>24-Sep 9:31</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOO</t>
+          <t>Core Integra Consulting NSE SMEO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹9.5 (5.14%) 3 ↓ / 9.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1x</t>
+          <t>0.38x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹160.88 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 9.5</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2408,24 +2416,24 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 16:00</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOO</t>
+          <t>Unitec Fibres BSE SMEO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹4.5 (1.24%) 4.50 ↓ / 16 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2435,27 +2443,27 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.21x</t>
+          <t>0.13x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4.5</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2475,7 +2483,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 15:57</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2502,7 +2510,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.34x</t>
+          <t>0.44x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2542,7 +2550,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>24-Sep 9:36</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2621,12 +2629,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEO</t>
+          <t>Swastika Infra IPOO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹5 (2.70%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2636,27 +2644,27 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.14x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 9.5</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2676,12 +2684,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>24-Sep 9:32</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2711,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.12x</t>
+          <t>0.24x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2743,7 +2751,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>24-Sep 9:33</t>
+          <t>24-Sep 15:54</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2755,42 +2763,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOO</t>
+          <t>ArMee Infotech IPOO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹34 (25.37%) 32 ↓ / 37 ↑</t>
+          <t>₹20 (5.33%) 1 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5.22x</t>
+          <t>1.18x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 34</t>
+          <t>23-Sep GMP: 51</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2810,7 +2818,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2822,42 +2830,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOO</t>
+          <t>Elevate Campuses IPOO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹51 (13.60%) 1 ↓ / 51 ↑</t>
+          <t>₹2 (0.55%) 2 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.57x</t>
+          <t>0.24x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 51</t>
+          <t>23-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2877,7 +2885,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2889,7 +2897,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEO</t>
+          <t>Liqvd Digital BSE SMEO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2904,22 +2912,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.13x</t>
+          <t>1.21x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2944,24 +2952,24 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>24-Sep 9:30</t>
+          <t>24-Sep 15:55</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOCT</t>
+          <t>Himalaya Nutravedics BSE SMECT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,27 +2979,27 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.27x</t>
+          <t>2.27x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹708.02 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 3</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3011,7 +3019,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 16:00</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3023,12 +3031,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMECT</t>
+          <t>Varmora Granito IPOCT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹0.5 (0.34%) 0.50 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3038,32 +3046,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.4x</t>
+          <t>1.56x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹708.02 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>22-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>24-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3078,7 +3086,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>24-Sep 9:36</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3105,7 +3113,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.74x</t>
+          <t>1.46x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3145,7 +3153,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>24-Sep 9:28</t>
+          <t>24-Sep 16:00</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3212,7 +3220,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3224,47 +3232,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEC</t>
+          <t>Vivekanand Cotspin BSE SMEC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>₹55 (51.89%) 45 ↓ / 65 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>833.56x</t>
+          <t>1.79x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹22.20 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 55</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 55</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3279,7 +3287,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 15:58</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3291,47 +3299,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMEC</t>
+          <t>Robokidz Eduventures BSE SMEC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹55 (51.89%) 45 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.79x</t>
+          <t>833.56x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹22.20 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>21-Sep GMP: 55</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 55</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3346,7 +3354,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>24-Sep 9:35</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3413,7 +3421,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>24-Sep 9:28</t>
+          <t>24-Sep 15:56</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3425,7 +3433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sonaselection India IPOLT</t>
+          <t>Sonaselection India IPOL@102.31 (3.34%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3492,32 +3500,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMELT</t>
+          <t>Kheria Autocomp NSE SMEL@104.90 (3.86%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>₹81 (68.64%) 27 ↓ / 81 ↑</t>
+          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>304.06x</t>
+          <t>2.48x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹42.52 Cr</t>
+          <t>₹46.44 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3527,12 +3535,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 30</t>
+          <t>17-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 67</t>
+          <t>21-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3542,7 +3550,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 81</t>
+          <t>24-Sep GMP: 3</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3559,47 +3567,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NSE IPOLT</t>
+          <t>SpectraA Technology Solutions NSE SMEL@224.20 (90%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹40 (2.24%) 40 ↓ / 310 ↑</t>
+          <t>₹81 (68.64%) 27 ↓ / 81 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5.71x</t>
+          <t>304.06x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹22561.57 Cr</t>
+          <t>₹42.52 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 142</t>
+          <t>17-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 65</t>
+          <t>21-Sep GMP: 67</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3609,7 +3617,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 40</t>
+          <t>24-Sep GMP: 81</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3693,12 +3701,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kheria Autocomp NSE SMELT</t>
+          <t>NSE IPOL@1800.00 (0.84%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
+          <t>₹40 (2.24%) 40 ↓ / 310 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3708,32 +3716,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.48x</t>
+          <t>5.71x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹46.44 Cr</t>
+          <t>₹22561.57 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 10</t>
+          <t>17-Sep GMP: 142</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 3</t>
+          <t>21-Sep GMP: 65</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3743,7 +3751,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 3</t>
+          <t>24-Sep GMP: 40</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3760,47 +3768,47 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOL@120.00 (29.03%)</t>
+          <t>Hero Motors IPOL@82.00 (-2.38%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
+          <t>₹-3 (-3.57%) -3 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>177.03x</t>
+          <t>7.01x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹1000.00 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 25</t>
+          <t>16-Sep GMP: 13</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 26.5</t>
+          <t>18-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3810,7 +3818,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 29</t>
+          <t>23-Sep GMP: -3</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3827,12 +3835,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SS Retail IPOL@624.00 (47.17%)</t>
+          <t>Jindal Supreme IPOL@120.00 (29.03%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹160 (37.74%) 30 ↓ / 160 ↑</t>
+          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3842,32 +3850,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>107.41x</t>
+          <t>177.03x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 90</t>
+          <t>16-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 145</t>
+          <t>18-Sep GMP: 26.5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3877,7 +3885,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 160</t>
+          <t>23-Sep GMP: 29</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3894,47 +3902,47 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Hero Motors IPOL@82.00 (-2.38%)</t>
+          <t>SS Retail IPOL@624.00 (47.17%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹-3 (-3.57%) -3 ↓ / 24 ↑</t>
+          <t>₹160 (37.74%) 30 ↓ / 160 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7.01x</t>
+          <t>107.41x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹1000.00 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 13</t>
+          <t>16-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 0</t>
+          <t>18-Sep GMP: 145</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3944,7 +3952,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>23-Sep GMP: -3</t>
+          <t>23-Sep GMP: 160</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Paramount Syntex BSE SMEU</t>
+          <t>TNA Solutions BSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹81.79 Cr</t>
+          <t>₹37.86 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -556,26 +556,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24-Sep 5:55</t>
+          <t>25-Sep 14:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
-        </is>
-      </c>
+          <t>Acme India Industries BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -588,17 +584,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹121.69 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,34 +604,30 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8-Oct</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>24-Sep 16:01</t>
-        </is>
-      </c>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dove Soft BSE SMEU</t>
+          <t>Paramount Syntex BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -655,17 +647,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹73.26 Cr</t>
+          <t>₹81.79 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -675,22 +667,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>9-Oct</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24-Sep 16:00</t>
+          <t>25-Sep 13:54</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -702,7 +694,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEU</t>
+          <t>Dove Soft BSE SMEU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -722,22 +714,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹73.26 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -757,22 +749,26 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24-Sep 5:55</t>
+          <t>25-Sep 13:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>Omara Ventures India BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -785,53 +781,61 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>7-Oct</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>8-Oct</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>25-Sep 13:54</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMEU</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>EverestIMS Technologies BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -844,12 +848,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹20.18 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -864,37 +868,37 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>7-Oct</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>8-Oct</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>25-Sep 14:00</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
-        </is>
-      </c>
+          <t>Nityas Gems &amp; Jewellery IPOU</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -907,44 +911,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹55.08 Cr</t>
+          <t>₹108.35 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>7-Oct</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>24-Sep 15:56</t>
-        </is>
-      </c>
+          <t>8-Oct</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>✅</t>
@@ -954,14 +954,10 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
-        </is>
-      </c>
+          <t>Eventions NSE SMEU</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -974,44 +970,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹35.93 Cr</t>
+          <t>₹38.12 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6-Oct</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>24-Sep 15:57</t>
-        </is>
-      </c>
+          <t>8-Oct</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>✅</t>
@@ -1021,14 +1013,10 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
-        </is>
-      </c>
+          <t>Sollfege Smart Electronics BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -1041,12 +1029,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹14.01 Cr</t>
+          <t>₹21.78 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1056,29 +1044,25 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6-Oct</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>24-Sep 15:58</t>
-        </is>
-      </c>
+          <t>8-Oct</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>❌</t>
@@ -1088,17 +1072,13 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SRIT India IPOU</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>₹12 (9.23%) 12 ↓ / 12 ↑</t>
-        </is>
-      </c>
+          <t>SJP Ultrasonic BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1108,64 +1088,60 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹218.40 Cr</t>
+          <t>₹23.45 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6-Oct</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>24-Sep 16:02</t>
-        </is>
-      </c>
+          <t>8-Oct</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOU</t>
+          <t>Shree TNB Polymers BSE SMEU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹12 (7.19%) 10 ↓ / 12 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1175,17 +1151,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹31.80 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1195,22 +1171,22 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 13:58</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1222,7 +1198,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEU</t>
+          <t>Papadmalji Agro Foods NSE SMEU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1242,42 +1218,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹20.18 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>24-Sep 15:58</t>
+          <t>25-Sep 14:01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1289,7 +1265,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEU</t>
+          <t>Black Opal Consultants BSE SMEU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1309,54 +1285,54 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹55.08 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>24-Sep 15:58</t>
+          <t>25-Sep 13:53</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEU</t>
+          <t>Vans Electroengineerings BSE SMEU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1376,12 +1352,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1391,27 +1367,27 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24-Sep 15:55</t>
+          <t>25-Sep 13:56</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1423,17 +1399,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOU</t>
+          <t>Shivchem Agro BSE SMEU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹28 (9.18%) 17 ↓ / 28 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1443,47 +1419,47 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹499.83 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 13:57</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1557,17 +1533,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>German Green Steel IPOU</t>
+          <t>Acme Universal Safezone 9 BSE SMEU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹28.5 (20.50%) 15 ↓ / 28.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1577,42 +1553,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹303.90 Cr</t>
+          <t>₹35.93 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1624,17 +1600,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Acevector IPOU</t>
+          <t>SRIT India IPOU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹22 (16.92%) 12 ↓ / 22 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1644,42 +1620,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹420.00 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>24-Sep 15:54</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1691,7 +1667,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEU</t>
+          <t>Pind Hospitality BSE SMEU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1711,12 +1687,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1726,49 +1702,49 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>24-Sep 15:54</t>
+          <t>25-Sep 13:56</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Orient Cables IPOU</t>
+          <t>Shah Investor's Home IPOU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹58 (21.32%) 34 ↓ / 58 ↑</t>
+          <t>₹12 (7.19%) 10 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1778,42 +1754,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1825,42 +1801,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEU</t>
+          <t>Orient Cables IPOO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹12 (10.91%) 12 ↓ / 12 ↑</t>
+          <t>₹70 (25.74%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.26x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 70</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1880,7 +1856,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1892,12 +1868,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shree TNB Polymers BSE SMEU</t>
+          <t>Bench Mark Infotech Services NSE SMEO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹8 (15.38%) 8 ↓ / 8 ↑</t>
+          <t>₹16 (14.55%) 12 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1907,27 +1883,27 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.14x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹31.20 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1947,7 +1923,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1959,129 +1935,129 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEO</t>
+          <t>German Green Steel IPOO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹31.5 (22.66%) 15 ↓ / 31.50 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.58x</t>
+          <t>1.09x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹303.90 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>25-Sep GMP: 31.5</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEO</t>
+          <t>Runwal Enterprises IPOO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹29 (45.31%) 8 ↓ / 29 ↑</t>
+          <t>₹5 (1.64%) 5 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.12x</t>
+          <t>0.23x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹499.83 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 29</t>
+          <t>25-Sep GMP: 5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2093,7 +2069,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEO</t>
+          <t>Sai Urja Indo BSE SMEO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2108,114 +2084,114 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.01x</t>
+          <t>0.03x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹60.10 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>25-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>24-Sep 15:57</t>
+          <t>25-Sep 13:57</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Moneyview IPOO</t>
+          <t>Acevector IPOO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹12.75 (37.50%) 5 ↓ / 14 ↑</t>
+          <t>₹3 (9.38%) 2 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.26x</t>
+          <t>0.09x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹420.00 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 12.75</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2227,12 +2203,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A-One Steels IPOO</t>
+          <t>Dudani Retail BSE SMEO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹48 (11.85%) 48 ↓ / 64 ↑</t>
+          <t>₹3 (10.34%) 3 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2242,114 +2218,114 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.53x</t>
+          <t>0.06x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 48</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOO</t>
+          <t>Himalayan Solar NSE SMEO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹34 (25.37%) 32 ↓ / 37 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>16.48x</t>
+          <t>0.28x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 34</t>
+          <t>25-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 13:56</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2361,12 +2337,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEO</t>
+          <t>Roopa Screen BSE SMEO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2376,59 +2352,59 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.38x</t>
+          <t>3.15x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>24-Sep 16:00</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEO</t>
+          <t>Green Asia Impex NSE SMEO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2443,17 +2419,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.13x</t>
+          <t>0.02x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹60.00 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2463,94 +2439,94 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>24-Sep 15:57</t>
+          <t>25-Sep 13:55</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEO</t>
+          <t>A-One Steels IPOO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹50 (12.35%) 49 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.44x</t>
+          <t>1.09x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep GMP: 49</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2629,62 +2605,62 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOO</t>
+          <t>Moneyview IPOO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹5 (2.70%) 3 ↓ / 9.50 ↑</t>
+          <t>₹14 (41.18%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>4.41x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹160.88 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 9.5</t>
+          <t>24-Sep GMP: 15.5</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2696,7 +2672,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEO</t>
+          <t>Peshwa Wheat BSE SMEO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,99 +2687,99 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.24x</t>
+          <t>1.94x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>24-Sep 15:54</t>
+          <t>25-Sep 13:54</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOO</t>
+          <t>Adroit Industries IPOCT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹20 (5.33%) 1 ↓ / 51 ↑</t>
+          <t>₹37 (27.61%) 32 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.18x</t>
+          <t>96.73x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 51</t>
+          <t>23-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 37</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2818,7 +2794,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2830,12 +2806,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOO</t>
+          <t>Pooja Logistics NSE SMECT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹2 (0.55%) 2 ↓ / 16 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2845,32 +2821,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.24x</t>
+          <t>0.91x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4.5</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2885,7 +2861,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 13:57</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2897,12 +2873,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEO</t>
+          <t>Swastika Infra IPOCT</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2912,32 +2888,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.21x</t>
+          <t>1.7x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 9.5</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 7</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2952,19 +2928,19 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>24-Sep 15:55</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMECT</t>
+          <t>Unitec Fibres BSE SMECT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2979,47 +2955,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.27x</t>
+          <t>0.97x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>25-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>24-Sep 16:00</t>
+          <t>25-Sep 13:53</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3031,12 +3007,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOCT</t>
+          <t>Liqvd Digital BSE SMECT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹0.5 (0.34%) 0.50 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3046,59 +3022,59 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.56x</t>
+          <t>2.79x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹708.02 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 3</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0.5</t>
+          <t>25-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 13:55</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMECT</t>
+          <t>S.K.Offset BSE SMECT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3113,64 +3089,64 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.46x</t>
+          <t>0.58x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹25.52 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>25-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>24-Sep 16:00</t>
+          <t>25-Sep 14:00</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMEC</t>
+          <t>ArMee Infotech IPOCT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹4 (3.45%) 4 ↓ / 4 ↑</t>
+          <t>₹10 (2.67%) 1 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3180,47 +3156,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>17.72x</t>
+          <t>2.16x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹45.24 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep GMP: 51</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4</t>
+          <t>25-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3232,7 +3208,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMEC</t>
+          <t>Core Integra Consulting NSE SMECT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3247,114 +3223,114 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.79x</t>
+          <t>1.2x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹22.20 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>24-Sep 15:58</t>
+          <t>25-Sep 13:53</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEC</t>
+          <t>Elevate Campuses IPOCT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹55 (51.89%) 45 ↓ / 65 ↑</t>
+          <t>₹2 (0.55%) 2 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>833.56x</t>
+          <t>0.64x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 55</t>
+          <t>23-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 55</t>
+          <t>25-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3366,7 +3342,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMECAllotted</t>
+          <t>Anand Seamless BSE SMEC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3381,64 +3357,64 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>1.47x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹50.75 Cr</t>
+          <t>₹25.52 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>24-Sep 15:56</t>
+          <t>25-Sep 14:00</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sonaselection India IPOL@102.31 (3.34%)</t>
+          <t>Varmora Granito IPOC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 8 ↑</t>
+          <t>₹0.5 (0.34%) 0.50 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3448,47 +3424,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2.01x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹141.57 Cr</t>
+          <t>₹708.02 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 2</t>
+          <t>22-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 0</t>
+          <t>24-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3500,12 +3476,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kheria Autocomp NSE SMEL@104.90 (3.86%)</t>
+          <t>Himalaya Nutravedics BSE SMEC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3515,17 +3491,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2.48x</t>
+          <t>2.33x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹46.44 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3535,27 +3511,27 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 10</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 3</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 3</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>25-Sep 13:53</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3567,12 +3543,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMEL@224.20 (90%)</t>
+          <t>Robokidz Eduventures BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹81 (68.64%) 27 ↓ / 81 ↑</t>
+          <t>₹70 (66.04%) 45 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3582,17 +3558,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>304.06x</t>
+          <t>833.56x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹42.52 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3602,27 +3578,27 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 30</t>
+          <t>21-Sep GMP: 55</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 67</t>
+          <t>23-Sep GMP: 55</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 81</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3701,12 +3677,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NSE IPOL@1800.00 (0.84%)</t>
+          <t>FX Multitech BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹40 (2.24%) 40 ↓ / 310 ↑</t>
+          <t>₹4 (3.45%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3716,47 +3692,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5.71x</t>
+          <t>17.72x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹22561.57 Cr</t>
+          <t>₹45.24 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 142</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 65</t>
+          <t>23-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 40</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3768,12 +3744,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hero Motors IPOL@82.00 (-2.38%)</t>
+          <t>Vivekanand Cotspin BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹-3 (-3.57%) -3 ↓ / 24 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3783,47 +3759,47 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7.01x</t>
+          <t>1.79x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹1000.00 Cr</t>
+          <t>₹22.20 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 13</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 0</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>23-Sep GMP: -3</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>23-Sep 9:37</t>
+          <t>25-Sep 13:58</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3835,62 +3811,62 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOL@120.00 (29.03%)</t>
+          <t>Axiom Gas Engineering NSE SMEL@54.75 (1.39%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹29 (31.18%) 11 ↓ / 30 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>177.03x</t>
+          <t>1.39x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹50.75 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 25</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 26.5</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 29</t>
+          <t>25-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>23-Sep 9:37</t>
+          <t>25-Sep 8:56</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3902,62 +3878,62 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SS Retail IPOL@624.00 (47.17%)</t>
+          <t>Kheria Autocomp NSE SMEL@104.90 (3.86%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹160 (37.74%) 30 ↓ / 160 ↑</t>
+          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>107.41x</t>
+          <t>2.48x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹46.44 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 90</t>
+          <t>17-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>18-Sep GMP: 145</t>
+          <t>21-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 160</t>
+          <t>24-Sep GMP: 3</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>23-Sep 9:37</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3969,67 +3945,67 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Quanto Agroworld BSE SMEL@66.99 (-0.01%)</t>
+          <t>SpectraA Technology Solutions NSE SMEL@224.20 (90%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹81 (68.64%) 27 ↓ / 81 ↑</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>304.06x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹31.02 Cr</t>
+          <t>₹42.52 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>15-Sep</t>
+          <t>17-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep GMP: 67</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 0</t>
+          <t>24-Sep GMP: 81</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>22-Sep 9:36</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-Sep 14:00</t>
+          <t>25-Sep 19:34</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25-Sep 13:54</t>
+          <t>25-Sep 19:28</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25-Sep 13:57</t>
+          <t>25-Sep 19:29</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25-Sep 13:54</t>
+          <t>25-Sep 19:33</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25-Sep 14:00</t>
+          <t>25-Sep 19:28</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25-Sep 13:58</t>
+          <t>25-Sep 19:31</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>25-Sep 14:01</t>
+          <t>25-Sep 19:34</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>25-Sep 13:53</t>
+          <t>25-Sep 19:30</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25-Sep 13:56</t>
+          <t>25-Sep 19:32</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25-Sep 13:57</t>
+          <t>25-Sep 19:34</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>25-Sep 14:00</t>
+          <t>25-Sep 19:30</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹22 (16.92%) 12 ↓ / 22 ↑</t>
+          <t>₹24 (18.46%) 12 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>25-Sep 13:56</t>
+          <t>25-Sep 19:31</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹70 (25.74%) 34 ↓ / 113 ↑</t>
+          <t>₹72 (26.47%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.26x</t>
+          <t>2.07x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 70</t>
+          <t>25-Sep GMP: 72</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.14x</t>
+          <t>0.26x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹31.5 (22.66%) 15 ↓ / 31.50 ↑</t>
+          <t>₹28 (20.14%) 15 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.09x</t>
+          <t>1.82x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 31.5</t>
+          <t>25-Sep GMP: 28</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹5 (1.64%) 5 ↓ / 37 ↑</t>
+          <t>₹28 (9.18%) 17 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.23x</t>
+          <t>0.44x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 5</t>
+          <t>25-Sep GMP: 28</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.03x</t>
+          <t>0.04x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>25-Sep 13:57</t>
+          <t>25-Sep 19:36</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹3 (9.38%) 2 ↓ / 3 ↑</t>
+          <t>₹2 (6.25%) 2 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.09x</t>
+          <t>0.24x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 3</t>
+          <t>25-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.06x</t>
+          <t>0.08x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.28x</t>
+          <t>0.51x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>25-Sep 13:56</t>
+          <t>25-Sep 19:30</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.15x</t>
+          <t>5.35x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.02x</t>
+          <t>0.03x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>25-Sep 13:55</t>
+          <t>25-Sep 19:31</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹50 (12.35%) 49 ↓ / 64 ↑</t>
+          <t>₹51 (12.59%) 49 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.09x</t>
+          <t>1.43x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4.41x</t>
+          <t>6.22x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.94x</t>
+          <t>2.03x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>25-Sep 13:54</t>
+          <t>25-Sep 19:33</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2739,12 +2739,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOCT</t>
+          <t>Adroit Industries IPOC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹37 (27.61%) 32 ↓ / 37 ↑</t>
+          <t>₹47 (35.07%) 32 ↓ / 47 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>96.73x</t>
+          <t>176.85x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 37</t>
+          <t>25-Sep GMP: 47</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2806,7 +2806,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMECT</t>
+          <t>Pooja Logistics NSE SMEC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.91x</t>
+          <t>3.11x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>25-Sep 13:57</t>
+          <t>25-Sep 19:31</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2873,12 +2873,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOCT</t>
+          <t>Swastika Infra IPOC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
+          <t>₹4.5 (2.43%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.7x</t>
+          <t>7.91x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 7</t>
+          <t>25-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2940,7 +2940,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMECT</t>
+          <t>Unitec Fibres BSE SMEC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.97x</t>
+          <t>3.92x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>25-Sep 13:53</t>
+          <t>25-Sep 19:31</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3007,7 +3007,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMECT</t>
+          <t>Liqvd Digital BSE SMEC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.79x</t>
+          <t>5.08x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>25-Sep 13:55</t>
+          <t>25-Sep 19:31</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMECT</t>
+          <t>S.K.Offset BSE SMEC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.58x</t>
+          <t>1.18x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>25-Sep 14:00</t>
+          <t>25-Sep 19:32</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3141,12 +3141,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOCT</t>
+          <t>ArMee Infotech IPOC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹10 (2.67%) 1 ↓ / 51 ↑</t>
+          <t>₹8 (2.13%) 1 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.16x</t>
+          <t>2.62x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 10</t>
+          <t>25-Sep GMP: 8</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3208,7 +3208,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMECT</t>
+          <t>Core Integra Consulting NSE SMEC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.2x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>25-Sep 13:53</t>
+          <t>25-Sep 19:29</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOCT</t>
+          <t>Elevate Campuses IPOC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹2 (0.55%) 2 ↓ / 16 ↑</t>
+          <t>₹3 (0.83%) 2.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.64x</t>
+          <t>1.89x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 2</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>25-Sep 14:00</t>
+          <t>25-Sep 19:35</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>25-Sep 13:53</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹70 (66.04%) 45 ↓ / 70 ↑</t>
+          <t>₹77 (72.64%) 45 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>25-Sep 13:58</t>
+          <t>25-Sep 19:35</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-Sep 19:34</t>
+          <t>26-Sep 13:33</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -568,10 +568,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Acme India Industries BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Paramount Syntex BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -584,17 +588,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹121.69 Cr</t>
+          <t>₹81.79 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -617,17 +621,21 @@
           <t>9-Oct</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>26-Sep 13:33</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Paramount Syntex BSE SMEU</t>
+          <t>Acme India Industries BSE SMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -647,17 +655,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹81.79 Cr</t>
+          <t>₹121.69 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -682,19 +690,19 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25-Sep 19:28</t>
+          <t>26-Sep 5:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dove Soft BSE SMEU</t>
+          <t>Nityas Gems &amp; Jewellery IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -714,17 +722,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹73.26 Cr</t>
+          <t>₹108.35 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -749,19 +757,19 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25-Sep 19:29</t>
+          <t>26-Sep 5:55</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMEU</t>
+          <t>Eventions NSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -781,17 +789,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹38.12 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -816,19 +824,19 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25-Sep 19:33</t>
+          <t>26-Sep 5:55</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEU</t>
+          <t>Sollfege Smart Electronics BSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -848,22 +856,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹21.78 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -883,22 +891,26 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25-Sep 19:28</t>
+          <t>26-Sep 5:55</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nityas Gems &amp; Jewellery IPOU</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>SJP Ultrasonic BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -911,17 +923,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹108.35 Cr</t>
+          <t>₹23.45 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -944,17 +956,21 @@
           <t>8-Oct</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>26-Sep 5:55</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Eventions NSE SMEU</t>
+          <t>Vishal Nirmiti IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -970,17 +986,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹38.12 Cr</t>
+          <t>₹178.00 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1006,17 +1022,21 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sollfege Smart Electronics BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>Shree TNB Polymers BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -1029,12 +1049,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹21.78 Cr</t>
+          <t>₹31.80 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1044,7 +1064,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1062,20 +1082,28 @@
           <t>8-Oct</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>26-Sep 13:34</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SJP Ultrasonic BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>Dove Soft BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -1088,17 +1116,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹23.45 Cr</t>
+          <t>₹73.26 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1121,7 +1149,11 @@
           <t>8-Oct</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>26-Sep 13:29</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>❌</t>
@@ -1131,7 +1163,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shree TNB Polymers BSE SMEU</t>
+          <t>Omara Ventures India BSE SMEU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1151,22 +1183,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹31.80 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1186,29 +1218,29 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25-Sep 19:31</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMEU</t>
+          <t>EverestIMS Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹8 (9.41%) 8 ↓ / 8 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1218,12 +1250,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹20.18 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1238,34 +1270,34 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>25-Sep 19:34</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMEU</t>
+          <t>Papadmalji Agro Foods NSE SMEU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1285,17 +1317,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹55.08 Cr</t>
+          <t>₹20.18 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1320,19 +1352,19 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>25-Sep 19:30</t>
+          <t>26-Sep 13:28</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEU</t>
+          <t>Black Opal Consultants BSE SMEU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1352,17 +1384,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹55.08 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1387,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25-Sep 19:32</t>
+          <t>26-Sep 13:34</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1399,17 +1431,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMEU</t>
+          <t>Vans Electroengineerings BSE SMEU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹18 (15.25%) 18 ↓ / 18 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1419,47 +1451,47 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹14.01 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25-Sep 19:34</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1533,17 +1565,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMEU</t>
+          <t>Shah Investor's Home IPOU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹12 (7.19%) 10 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1553,17 +1585,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹35.93 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1588,7 +1620,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>25-Sep 19:30</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1600,17 +1632,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SRIT India IPOU</t>
+          <t>Shivchem Agro BSE SMEU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹24 (18.46%) 12 ↓ / 24 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1620,17 +1652,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹218.40 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1655,29 +1687,29 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:32</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEU</t>
+          <t>SRIT India IPOU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹32 (24.62%) 12 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1687,17 +1719,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1722,29 +1754,29 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>25-Sep 19:31</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOU</t>
+          <t>Pind Hospitality BSE SMEU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹12 (7.19%) 10 ↓ / 12 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1754,17 +1786,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,74 +1821,74 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:35</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Orient Cables IPOO</t>
+          <t>Acme Universal Safezone 9 BSE SMEU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹72 (26.47%) 34 ↓ / 113 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.07x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹35.93 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 72</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:34</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1868,32 +1900,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEO</t>
+          <t>Himalayan Solar NSE SMEO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹16 (14.55%) 12 ↓ / 16 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.26x</t>
+          <t>0.51x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1903,7 +1935,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1923,7 +1955,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:36</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1935,42 +1967,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>German Green Steel IPOO</t>
+          <t>Runwal Enterprises IPOO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹28 (20.14%) 15 ↓ / 29 ↑</t>
+          <t>₹14 (4.59%) 14 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.82x</t>
+          <t>0.44x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹303.90 Cr</t>
+          <t>₹499.83 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 28</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1990,7 +2022,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2002,42 +2034,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOO</t>
+          <t>Dudani Retail BSE SMEO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹28 (9.18%) 17 ↓ / 37 ↑</t>
+          <t>₹3 (10.34%) 3 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.44x</t>
+          <t>0.08x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹499.83 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 28</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2057,54 +2089,54 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEO</t>
+          <t>Orient Cables IPOO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹85 (31.25%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.04x</t>
+          <t>2.07x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 0</t>
+          <t>25-Sep GMP: 80</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2124,7 +2156,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>25-Sep 19:36</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2191,7 +2223,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2203,12 +2235,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEO</t>
+          <t>German Green Steel IPOO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹3 (10.34%) 3 ↓ / 3 ↑</t>
+          <t>₹26.5 (19.06%) 15 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2218,27 +2250,27 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.08x</t>
+          <t>1.82x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹303.90 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 3</t>
+          <t>25-Sep GMP: 26</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2258,19 +2290,19 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEO</t>
+          <t>Sai Urja Indo BSE SMEO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2285,17 +2317,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.51x</t>
+          <t>0.04x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2305,7 +2337,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 0</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2325,7 +2357,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>25-Sep 19:30</t>
+          <t>26-Sep 13:30</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2337,62 +2369,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEO</t>
+          <t>Bench Mark Infotech Services NSE SMEO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 14 ↑</t>
+          <t>₹16 (14.55%) 12 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5.35x</t>
+          <t>0.26x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2404,7 +2436,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEO</t>
+          <t>Peshwa Wheat BSE SMEO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2419,22 +2451,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.03x</t>
+          <t>2.03x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹60.00 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2459,7 +2491,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>25-Sep 19:31</t>
+          <t>26-Sep 13:31</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2476,7 +2508,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹51 (12.59%) 49 ↓ / 64 ↑</t>
+          <t>₹52 (12.84%) 49 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2526,7 +2558,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2610,7 +2642,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹14 (41.18%) 5 ↓ / 15.50 ↑</t>
+          <t>₹13.75 (40.44%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2660,7 +2692,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2672,7 +2704,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEO</t>
+          <t>Green Asia Impex NSE SMEO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2687,22 +2719,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.03x</t>
+          <t>0.03x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹60.00 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2727,7 +2759,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>25-Sep 19:33</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2739,62 +2771,62 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOC</t>
+          <t>Roopa Screen BSE SMEO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹47 (35.07%) 32 ↓ / 47 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>176.85x</t>
+          <t>5.35x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 34</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 47</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2806,7 +2838,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEC</t>
+          <t>S.K.Offset BSE SMEC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2821,22 +2853,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.11x</t>
+          <t>1.18x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2846,7 +2878,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 0</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2861,7 +2893,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>25-Sep 19:31</t>
+          <t>26-Sep 13:33</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2928,7 +2960,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2940,47 +2972,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEC</t>
+          <t>Adroit Industries IPOC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹48 (35.82%) 32 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.92x</t>
+          <t>176.85x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 0</t>
+          <t>25-Sep GMP: 47</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2995,7 +3027,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>25-Sep 19:31</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3007,7 +3039,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEC</t>
+          <t>Pooja Logistics NSE SMEC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3022,22 +3054,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5.08x</t>
+          <t>3.11x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3047,7 +3079,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 0</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3062,24 +3094,24 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>25-Sep 19:31</t>
+          <t>26-Sep 13:28</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEC</t>
+          <t>ArMee Infotech IPOC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹8 (2.13%) 1 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3089,32 +3121,32 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.18x</t>
+          <t>2.62x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 51</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 0</t>
+          <t>25-Sep GMP: 8</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3129,7 +3161,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>25-Sep 19:32</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3141,12 +3173,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOC</t>
+          <t>Elevate Campuses IPOC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹8 (2.13%) 1 ↓ / 51 ↑</t>
+          <t>₹4 (1.10%) 2.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3156,32 +3188,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.62x</t>
+          <t>1.89x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 51</t>
+          <t>23-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 8</t>
+          <t>25-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3196,7 +3228,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3208,7 +3240,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEC</t>
+          <t>Liqvd Digital BSE SMEC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3223,22 +3255,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>5.08x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3248,7 +3280,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 0</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3263,7 +3295,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>25-Sep 19:29</t>
+          <t>26-Sep 13:36</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3275,12 +3307,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOC</t>
+          <t>Core Integra Consulting NSE SMEC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹3 (0.83%) 2.50 ↓ / 16 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3290,32 +3322,32 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.89x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4.5</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 3</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3330,19 +3362,19 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:32</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMEC</t>
+          <t>Unitec Fibres BSE SMEC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3357,17 +3389,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.47x</t>
+          <t>3.92x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹25.52 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3377,44 +3409,44 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>25-Sep 19:35</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOC</t>
+          <t>Himalaya Nutravedics BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹0.5 (0.34%) 0.50 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3424,32 +3456,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>2.33x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹708.02 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 3</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0.5</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3464,7 +3496,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:28</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3476,7 +3508,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEC</t>
+          <t>Anand Seamless BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,22 +3523,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2.33x</t>
+          <t>1.47x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹25.52 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3531,74 +3563,74 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:36</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMECAllotted</t>
+          <t>Varmora Granito IPOCAllotted</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹77 (72.64%) 45 ↓ / 77 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>833.56x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹708.02 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 55</t>
+          <t>22-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 55</t>
+          <t>24-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3677,32 +3709,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMECAllotted</t>
+          <t>Robokidz Eduventures BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹4 (3.45%) 4 ↓ / 4 ↑</t>
+          <t>₹77 (72.64%) 45 ↓ / 77 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>17.72x</t>
+          <t>833.56x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹45.24 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3712,12 +3744,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>21-Sep GMP: 55</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4</t>
+          <t>23-Sep GMP: 55</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3732,7 +3764,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3744,37 +3776,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMECAllotted</t>
+          <t>FX Multitech BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6 (5.17%) 4 ↓ / 6 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.79x</t>
+          <t>17.72x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹22.20 Cr</t>
+          <t>₹45.24 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3784,7 +3816,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3799,7 +3831,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>25-Sep 19:35</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3811,7 +3843,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMEL@54.75 (1.39%)</t>
+          <t>Vivekanand Cotspin BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3826,47 +3858,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>1.79x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹50.75 Cr</t>
+          <t>₹22.20 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 0</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>25-Sep 8:56</t>
+          <t>26-Sep 13:33</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3878,12 +3910,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kheria Autocomp NSE SMEL@104.90 (3.86%)</t>
+          <t>Axiom Gas Engineering NSE SMEL@54.75 (1.39%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3893,47 +3925,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.48x</t>
+          <t>1.39x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹46.44 Cr</t>
+          <t>₹50.75 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 10</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 3</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 3</t>
+          <t>25-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>25-Sep 8:56</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3945,32 +3977,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMEL@224.20 (90%)</t>
+          <t>Kheria Autocomp NSE SMEL@104.90 (3.86%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>₹81 (68.64%) 27 ↓ / 81 ↑</t>
+          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>304.06x</t>
+          <t>2.48x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹42.52 Cr</t>
+          <t>₹46.44 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3980,12 +4012,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 30</t>
+          <t>17-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 67</t>
+          <t>21-Sep GMP: 3</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3995,7 +4027,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 81</t>
+          <t>24-Sep GMP: 3</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-Sep 13:33</t>
+          <t>26-Sep 18:53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-Sep 13:33</t>
+          <t>26-Sep 18:54</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>26-Sep 5:55</t>
+          <t>26-Sep 18:58</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>26-Sep 5:55</t>
+          <t>26-Sep 18:59</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>26-Sep 13:34</t>
+          <t>26-Sep 18:59</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>26-Sep 13:29</t>
+          <t>26-Sep 19:01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹8 (9.41%) 8 ↓ / 8 ↑</t>
+          <t>₹13 (15.29%) 13 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>26-Sep 13:28</t>
+          <t>26-Sep 18:58</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>26-Sep 13:34</t>
+          <t>26-Sep 18:57</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹18 (15.25%) 18 ↓ / 18 ↑</t>
+          <t>₹28 (23.73%) 28 ↓ / 28 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹12 (7.19%) 10 ↓ / 12 ↑</t>
+          <t>₹9 (5.39%) 9 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>26-Sep 13:32</t>
+          <t>26-Sep 18:58</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>26-Sep 13:35</t>
+          <t>26-Sep 18:53</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>26-Sep 13:34</t>
+          <t>26-Sep 18:57</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>26-Sep 13:36</t>
+          <t>26-Sep 18:56</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹14 (4.59%) 14 ↓ / 37 ↑</t>
+          <t>₹14.5 (4.75%) 14.50 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹85 (31.25%) 34 ↓ / 113 ↑</t>
+          <t>₹86 (31.62%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹26.5 (19.06%) 15 ↓ / 29 ↑</t>
+          <t>₹27.5 (19.78%) 15 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>26-Sep 13:30</t>
+          <t>26-Sep 18:53</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>26-Sep 13:31</t>
+          <t>26-Sep 18:57</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹52 (12.84%) 49 ↓ / 64 ↑</t>
+          <t>₹57 (14.07%) 49 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹13.75 (40.44%) 5 ↓ / 15.50 ↑</t>
+          <t>₹14 (41.18%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 18:57</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 14 ↑</t>
+          <t>₹32 (50.00%) 8 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>26-Sep 13:33</t>
+          <t>26-Sep 18:58</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹4.5 (2.43%) 3 ↓ / 9.50 ↑</t>
+          <t>₹6 (3.24%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹48 (35.82%) 32 ↓ / 48 ↑</t>
+          <t>₹53.5 (39.93%) 32 ↓ / 53.50 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>26-Sep 13:28</t>
+          <t>26-Sep 18:53</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>26-Sep 13:36</t>
+          <t>26-Sep 18:56</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>26-Sep 13:32</t>
+          <t>26-Sep 19:00</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>26-Sep 13:28</t>
+          <t>26-Sep 19:01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>26-Sep 13:36</t>
+          <t>26-Sep 18:53</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹77 (72.64%) 45 ↓ / 77 ↑</t>
+          <t>₹80 (75.47%) 45 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>26-Sep 13:33</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-Sep 18:53</t>
+          <t>27-Sep 14:30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-Sep 18:54</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>26-Sep 5:55</t>
+          <t>27-Sep 5:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>26-Sep 5:55</t>
+          <t>27-Sep 5:55</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>26-Sep 5:55</t>
+          <t>27-Sep 5:55</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>26-Sep 18:58</t>
+          <t>27-Sep 14:30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>26-Sep 18:59</t>
+          <t>27-Sep 14:35</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -973,7 +973,11 @@
           <t>Vishal Nirmiti IPOU</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -1019,7 +1023,11 @@
           <t>8-Oct</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>27-Sep 5:55</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>❌</t>
@@ -1084,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>26-Sep 18:59</t>
+          <t>27-Sep 14:30</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1151,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>26-Sep 19:01</t>
+          <t>27-Sep 14:35</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1218,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>26-Sep 19:00</t>
+          <t>27-Sep 14:32</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1285,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1352,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>26-Sep 18:58</t>
+          <t>27-Sep 14:36</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1419,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>26-Sep 18:57</t>
+          <t>27-Sep 14:30</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1444,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹28 (23.73%) 28 ↓ / 28 ↑</t>
+          <t>₹45 (38.14%) 45 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1486,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1620,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1687,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>26-Sep 18:58</t>
+          <t>27-Sep 14:32</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1704,7 +1712,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹32 (24.62%) 12 ↓ / 32 ↑</t>
+          <t>₹33 (25.38%) 12 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1754,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1821,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>26-Sep 18:53</t>
+          <t>27-Sep 14:36</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1888,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>26-Sep 18:57</t>
+          <t>27-Sep 14:32</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1955,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>26-Sep 18:56</t>
+          <t>27-Sep 14:30</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2022,7 +2030,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2089,7 +2097,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2106,7 +2114,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹86 (31.62%) 34 ↓ / 113 ↑</t>
+          <t>₹90 (33.09%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2156,7 +2164,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2173,12 +2181,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹2 (6.25%) 2 ↓ / 2 ↑</t>
+          <t>₹1 (3.12%) 1 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2223,7 +2231,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2240,12 +2248,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹27.5 (19.78%) 15 ↓ / 29 ↑</t>
+          <t>₹29 (20.86%) 15 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2290,7 +2298,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2357,7 +2365,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>26-Sep 18:53</t>
+          <t>27-Sep 14:35</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2424,7 +2432,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2491,7 +2499,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>26-Sep 18:57</t>
+          <t>27-Sep 14:33</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2508,7 +2516,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹57 (14.07%) 49 ↓ / 64 ↑</t>
+          <t>₹58 (14.32%) 49 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2558,7 +2566,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2692,7 +2700,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2759,7 +2767,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>26-Sep 18:57</t>
+          <t>27-Sep 14:33</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2826,7 +2834,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2893,7 +2901,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>26-Sep 18:58</t>
+          <t>27-Sep 14:31</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2910,7 +2918,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹6 (3.24%) 3 ↓ / 9.50 ↑</t>
+          <t>₹6.5 (3.51%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2960,7 +2968,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2977,7 +2985,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹53.5 (39.93%) 32 ↓ / 53.50 ↑</t>
+          <t>₹57 (42.54%) 32 ↓ / 57 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3027,7 +3035,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3094,7 +3102,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>26-Sep 18:53</t>
+          <t>27-Sep 14:29</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3161,7 +3169,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3178,7 +3186,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹4 (1.10%) 2.50 ↓ / 16 ↑</t>
+          <t>₹9.5 (2.62%) 2.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3228,7 +3236,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3295,7 +3303,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>26-Sep 18:56</t>
+          <t>27-Sep 14:29</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3362,7 +3370,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>26-Sep 19:00</t>
+          <t>27-Sep 14:30</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3429,7 +3437,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>26-Sep 19:01</t>
+          <t>27-Sep 14:36</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3496,7 +3504,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>26-Sep 19:01</t>
+          <t>27-Sep 14:34</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3563,7 +3571,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>26-Sep 18:53</t>
+          <t>27-Sep 14:31</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3630,7 +3638,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3714,7 +3722,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹80 (75.47%) 45 ↓ / 80 ↑</t>
+          <t>₹82 (77.36%) 45 ↓ / 82 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3764,7 +3772,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3831,7 +3839,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3898,7 +3906,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:36</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-Sep 14:30</t>
+          <t>27-Sep 19:29</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹30 (15.31%) 30 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>27-Sep 5:55</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>27-Sep 5:55</t>
+          <t>27-Sep 19:34</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>27-Sep 5:55</t>
+          <t>27-Sep 19:31</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>27-Sep 14:30</t>
+          <t>27-Sep 19:33</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>27-Sep 14:35</t>
+          <t>27-Sep 19:28</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>27-Sep 5:55</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>27-Sep 14:30</t>
+          <t>27-Sep 19:33</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>27-Sep 14:35</t>
+          <t>27-Sep 19:34</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>27-Sep 14:32</t>
+          <t>27-Sep 19:33</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>27-Sep 14:36</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>27-Sep 14:30</t>
+          <t>27-Sep 19:36</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6 (9.68%) 6 ↓ / 6 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>27-Sep 14:32</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>27-Sep 14:36</t>
+          <t>27-Sep 19:29</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>27-Sep 14:32</t>
+          <t>27-Sep 19:36</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>27-Sep 14:30</t>
+          <t>27-Sep 19:31</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹14.5 (4.75%) 14.50 ↓ / 37 ↑</t>
+          <t>₹16 (5.25%) 14.50 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹29 (20.86%) 15 ↓ / 29 ↑</t>
+          <t>₹27 (19.42%) 15 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>27-Sep 14:35</t>
+          <t>27-Sep 19:33</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>27-Sep 14:33</t>
+          <t>27-Sep 19:34</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>27-Sep 14:33</t>
+          <t>27-Sep 19:30</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>27-Sep 14:31</t>
+          <t>27-Sep 19:31</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹57 (42.54%) 32 ↓ / 57 ↑</t>
+          <t>₹58 (43.28%) 32 ↓ / 58 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>27-Sep 14:29</t>
+          <t>27-Sep 19:31</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>27-Sep 14:29</t>
+          <t>27-Sep 19:29</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>27-Sep 14:30</t>
+          <t>27-Sep 19:34</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>27-Sep 14:36</t>
+          <t>27-Sep 19:36</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>27-Sep 14:34</t>
+          <t>27-Sep 19:32</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>27-Sep 14:31</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>27-Sep 14:36</t>
+          <t>27-Sep 19:31</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,12 +506,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹7 (10.00%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-Sep 19:29</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 14:58</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6 (8.00%) 6 ↓ / 6 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>27-Sep 19:34</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>27-Sep 19:31</t>
+          <t>28-Sep 14:53</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>27-Sep 19:33</t>
+          <t>28-Sep 15:01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>27-Sep 19:28</t>
+          <t>28-Sep 14:56</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 14:57</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1037,7 +1037,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shree TNB Polymers BSE SMEU</t>
+          <t>Omara Ventures India BSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹31.80 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1092,29 +1092,29 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>27-Sep 19:33</t>
+          <t>28-Sep 14:54</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dove Soft BSE SMEU</t>
+          <t>EverestIMS Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹20 (23.53%) 13 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1124,22 +1124,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹73.26 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1159,19 +1159,19 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>27-Sep 19:34</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMEU</t>
+          <t>Dove Soft BSE SMEU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹73.26 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>27-Sep 19:33</t>
+          <t>28-Sep 15:00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1238,17 +1238,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEU</t>
+          <t>Papadmalji Agro Foods NSE SMEU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹13 (15.29%) 13 ↓ / 13 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹20.18 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1278,34 +1278,34 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>1-Oct</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>5-Oct</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>6-Oct</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 14:56</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMEU</t>
+          <t>Black Opal Consultants BSE SMEU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹20.18 Cr</t>
+          <t>₹55.08 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1360,29 +1360,29 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMEU</t>
+          <t>Vans Electroengineerings BSE SMEU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹45 (38.14%) 45 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹55.08 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>27-Sep 19:36</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1439,62 +1439,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEU</t>
+          <t>Shree TNB Polymers BSE SMEO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹45 (38.14%) 45 ↓ / 45 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.27x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹31.80 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>28-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 14:53</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1573,42 +1573,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOU</t>
+          <t>Pind Hospitality BSE SMEO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹9 (5.39%) 9 ↓ / 12 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.02x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1628,24 +1628,24 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 14:53</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMEU</t>
+          <t>Shah Investor's Home IPOO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹6 (9.68%) 6 ↓ / 6 ↑</t>
+          <t>₹12.5 (7.49%) 9 ↓ / 12.50 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1655,27 +1655,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.26x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹14.01 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 12.5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1695,24 +1695,24 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SRIT India IPOU</t>
+          <t>SRIT India IPOO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹33 (25.38%) 12 ↓ / 33 ↑</t>
+          <t>₹34 (26.15%) 12 ↓ / 34 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.74x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1774,7 +1774,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEU</t>
+          <t>Acme Universal Safezone 9 BSE SMEO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.09x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹35.93 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1829,54 +1829,54 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>27-Sep 19:29</t>
+          <t>28-Sep 14:55</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMEU</t>
+          <t>Shivchem Agro BSE SMEO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6 (9.68%) 6 ↓ / 6 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.1x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹35.93 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 6</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1896,44 +1896,44 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>27-Sep 19:36</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEO</t>
+          <t>Bench Mark Infotech Services NSE SMEO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹19 (17.27%) 12 ↓ / 19 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.51x</t>
+          <t>0.96x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>27-Sep 19:31</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1975,42 +1975,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOO</t>
+          <t>Sai Urja Indo BSE SMEO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹16 (5.25%) 14.50 ↓ / 37 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.44x</t>
+          <t>0.14x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹499.83 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 14:58</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2042,42 +2042,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEO</t>
+          <t>Acevector IPOO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹3 (10.34%) 3 ↓ / 3 ↑</t>
+          <t>₹1.25 (3.91%) 1 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.08x</t>
+          <t>1.03x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹420.00 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 3</t>
+          <t>25-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹90 (33.09%) 34 ↓ / 113 ↑</t>
+          <t>₹80 (29.41%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.07x</t>
+          <t>7.15x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2176,42 +2176,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Acevector IPOO</t>
+          <t>Dudani Retail BSE SMEO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹1 (3.12%) 1 ↓ / 2 ↑</t>
+          <t>₹3 (10.34%) 3 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.24x</t>
+          <t>0.25x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹420.00 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 2</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2231,54 +2231,54 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>German Green Steel IPOO</t>
+          <t>Himalayan Solar NSE SMEO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹27 (19.42%) 15 ↓ / 29 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.82x</t>
+          <t>0.62x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹303.90 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 26</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:00</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2310,42 +2310,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEO</t>
+          <t>German Green Steel IPOO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹27.5 (19.78%) 15 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.04x</t>
+          <t>4.51x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹303.90 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 26</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>27-Sep 19:33</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2377,37 +2377,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEO</t>
+          <t>Runwal Enterprises IPOO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹16 (14.55%) 12 ↓ / 16 ↑</t>
+          <t>₹13 (4.26%) 13 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.26x</t>
+          <t>0.58x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2444,12 +2444,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEO</t>
+          <t>A-One Steels IPOCT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹20 (4.94%) 20 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2459,32 +2459,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.03x</t>
+          <t>8.81x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>24-Sep GMP: 49</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 20</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2499,59 +2499,59 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>27-Sep 19:34</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A-One Steels IPOO</t>
+          <t>Peshwa Wheat BSE SMECT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹58 (14.32%) 49 ↓ / 64 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.43x</t>
+          <t>2.62x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 49</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 14:59</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -2645,12 +2645,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Moneyview IPOO</t>
+          <t>Moneyview IPOCT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹14 (41.18%) 5 ↓ / 15.50 ↑</t>
+          <t>₹12.5 (36.76%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6.22x</t>
+          <t>72.81x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 12.5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2712,7 +2712,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEO</t>
+          <t>Green Asia Impex NSE SMECT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.03x</t>
+          <t>0.36x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>27-Sep 19:30</t>
+          <t>28-Sep 15:00</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2779,12 +2779,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEO</t>
+          <t>Roopa Screen BSE SMECT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹32 (50.00%) 8 ↓ / 32 ↑</t>
+          <t>₹38 (59.38%) 8 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5.35x</t>
+          <t>206.23x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 38</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>27-Sep 19:31</t>
+          <t>28-Sep 15:00</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹6.5 (3.51%) 3 ↓ / 9.50 ↑</t>
+          <t>₹5 (2.70%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>27-Sep 19:31</t>
+          <t>28-Sep 14:58</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>₹8 (2.13%) 1 ↓ / 51 ↑</t>
+          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹9.5 (2.62%) 2.50 ↓ / 16 ↑</t>
+          <t>₹9 (2.49%) 2.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>27-Sep 19:29</t>
+          <t>28-Sep 14:53</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>27-Sep 19:34</t>
+          <t>28-Sep 14:58</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>27-Sep 19:36</t>
+          <t>28-Sep 14:59</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>27-Sep 19:32</t>
+          <t>28-Sep 15:00</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 14:53</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 15 ↑</t>
+          <t>₹1.5 (1.01%) 0.50 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3717,12 +3717,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMECAllotted</t>
+          <t>Robokidz Eduventures BSE SMEL@201.40 (90%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹82 (77.36%) 45 ↓ / 82 ↑</t>
+          <t>₹86 (81.13%) 45 ↓ / 86 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 86</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 9:37</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3784,12 +3784,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMECAllotted</t>
+          <t>FX Multitech BSE SMEL@123.05 (6.08%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹6 (5.17%) 4 ↓ / 6 ↑</t>
+          <t>₹6.5 (5.60%) 4 ↓ / 6.50 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 6.5</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 9:37</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3851,7 +3851,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMECAllotted</t>
+          <t>Vivekanand Cotspin BSE SMEL@38.00 (2.7%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3901,12 +3901,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>27-Sep 19:31</t>
+          <t>28-Sep 9:30</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>28-Sep 14:58</t>
+          <t>29-Sep 15:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹6 (8.00%) 6 ↓ / 6 ↑</t>
+          <t>₹9 (12.00%) 9 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>28-Sep 14:53</t>
+          <t>29-Sep 14:58</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>28-Sep 15:01</t>
+          <t>29-Sep 14:54</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>28-Sep 14:56</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹2 (0.91%) 2 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>28-Sep 14:57</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1037,7 +1037,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMEU</t>
+          <t>Dove Soft BSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹73.26 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>28-Sep 14:54</t>
+          <t>29-Sep 14:58</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1104,17 +1104,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEU</t>
+          <t>Omara Ventures India BSE SMEU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹20 (23.53%) 13 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1124,22 +1124,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1159,54 +1159,54 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 14:58</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dove Soft BSE SMEU</t>
+          <t>EverestIMS Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹17 (20.00%) 13 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.11x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹73.26 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>29-Sep GMP: 17</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1226,19 +1226,19 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>28-Sep 15:00</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMEU</t>
+          <t>Shree TNB Polymers BSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1253,59 +1253,59 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.39x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹20.18 Cr</t>
+          <t>₹31.80 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>28-Sep 14:56</t>
+          <t>29-Sep 14:55</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMEU</t>
+          <t>Green Asia Impex NSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1320,27 +1320,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.52x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹55.08 Cr</t>
+          <t>₹59.34 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1360,54 +1360,54 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 14:55</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEU</t>
+          <t>Black Opal Consultants BSE SMEO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹45 (38.14%) 45 ↓ / 45 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.27x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹55.08 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 14:57</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1439,62 +1439,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Shree TNB Polymers BSE SMEO</t>
+          <t>Vans Electroengineerings BSE SMEO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹45 (38.14%) 45 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.27x</t>
+          <t>1.84x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹31.80 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 0</t>
+          <t>29-Sep GMP: 45</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>1-Oct</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>5-Oct</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>6-Oct</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>28-Sep 14:53</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEO</t>
+          <t>Papadmalji Agro Foods NSE SMEO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1588,47 +1588,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.02x</t>
+          <t>1.29x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹20.18 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 0</t>
+          <t>29-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>28-Sep 14:53</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1640,42 +1640,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOO</t>
+          <t>Pind Hospitality BSE SMEO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹12.5 (7.49%) 9 ↓ / 12.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.26x</t>
+          <t>0.27x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 12.5</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 14:57</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1712,17 +1712,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹34 (26.15%) 12 ↓ / 34 ↑</t>
+          <t>₹23 (17.69%) 12 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.74x</t>
+          <t>3.31x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 34</t>
+          <t>28-Sep GMP: 33</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.09x</t>
+          <t>0.37x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 0</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>28-Sep 14:55</t>
+          <t>29-Sep 14:59</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1841,12 +1841,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMEO</t>
+          <t>Shah Investor's Home IPOO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹6 (9.68%) 6 ↓ / 6 ↑</t>
+          <t>₹13 (7.78%) 9 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1856,27 +1856,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.1x</t>
+          <t>0.87x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹14.01 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 6</t>
+          <t>28-Sep GMP: 14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1896,111 +1896,111 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEO</t>
+          <t>Shivchem Agro BSE SMEO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹19 (17.27%) 12 ↓ / 19 ↑</t>
+          <t>₹13 (20.97%) 6 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.96x</t>
+          <t>0.5x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>28-Sep GMP: 6</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEO</t>
+          <t>Bench Mark Infotech Services NSE SMECT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹30 (27.27%) 12 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.14x</t>
+          <t>69.36x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>28-Sep 14:58</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2042,12 +2042,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Acevector IPOO</t>
+          <t>Sai Urja Indo BSE SMECT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹1.25 (3.91%) 1 ↓ / 2 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2057,32 +2057,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.03x</t>
+          <t>2.79x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹420.00 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 2</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:00</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2109,47 +2109,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Orient Cables IPOO</t>
+          <t>Acevector IPOCT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹80 (29.41%) 34 ↓ / 113 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7.15x</t>
+          <t>3.24x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹420.00 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 80</t>
+          <t>25-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2176,47 +2176,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEO</t>
+          <t>Orient Cables IPOCT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹3 (10.34%) 3 ↓ / 3 ↑</t>
+          <t>₹85 (31.25%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.25x</t>
+          <t>63.8x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 3</t>
+          <t>25-Sep GMP: 80</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 85</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2231,24 +2231,24 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEO</t>
+          <t>Dudani Retail BSE SMECT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2258,32 +2258,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.62x</t>
+          <t>1.26x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2298,59 +2298,59 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>28-Sep 15:00</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>German Green Steel IPOO</t>
+          <t>Runwal Enterprises IPOCT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹27.5 (19.78%) 15 ↓ / 29 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4.51x</t>
+          <t>1.93x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹303.90 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 26</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2377,47 +2377,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOO</t>
+          <t>German Green Steel IPOCT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹13 (4.26%) 13 ↓ / 37 ↑</t>
+          <t>₹12.5 (8.99%) 12.50 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.58x</t>
+          <t>5.39x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹303.90 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>25-Sep GMP: 26</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 12.5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2444,12 +2444,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A-One Steels IPOCT</t>
+          <t>Himalayan Solar NSE SMECT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹20 (4.94%) 20 ↓ / 64 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2459,47 +2459,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.81x</t>
+          <t>1.12x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 49</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 20</t>
+          <t>29-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 14:59</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2511,47 +2511,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMECT</t>
+          <t>A-One Steels IPOC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹27 (6.67%) 27 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.62x</t>
+          <t>12.23x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>24-Sep GMP: 49</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 0</t>
+          <t>28-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>28-Sep 14:59</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2645,12 +2645,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Moneyview IPOCT</t>
+          <t>Moneyview IPOC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹12.5 (36.76%) 5 ↓ / 15.50 ↑</t>
+          <t>₹12.75 (37.50%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>72.81x</t>
+          <t>101.87x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 12.5</t>
+          <t>28-Sep GMP: 12.75</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2712,7 +2712,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMECT</t>
+          <t>Peshwa Wheat BSE SMEC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2727,22 +2727,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.36x</t>
+          <t>2.77x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹60.00 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 0</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>28-Sep 15:00</t>
+          <t>29-Sep 14:59</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2779,7 +2779,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMECT</t>
+          <t>Roopa Screen BSE SMEC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>206.23x</t>
+          <t>271.94x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2846,7 +2846,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEC</t>
+          <t>S.K.Offset BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>28-Sep 15:00</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2913,12 +2913,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOC</t>
+          <t>Swastika Infra IPOCAllotted</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹5 (2.70%) 3 ↓ / 9.50 ↑</t>
+          <t>₹6 (3.24%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹58 (43.28%) 32 ↓ / 58 ↑</t>
+          <t>₹53 (39.55%) 32 ↓ / 58 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3047,7 +3047,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEC</t>
+          <t>Pooja Logistics NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>28-Sep 14:58</t>
+          <t>29-Sep 14:56</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3181,12 +3181,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOC</t>
+          <t>Elevate Campuses IPOCAllotted</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹9 (2.49%) 2.50 ↓ / 16 ↑</t>
+          <t>₹6 (1.66%) 2.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>28-Sep 14:53</t>
+          <t>29-Sep 14:58</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>28-Sep 14:58</t>
+          <t>29-Sep 14:53</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>28-Sep 14:59</t>
+          <t>29-Sep 14:53</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3449,7 +3449,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMECAllotted</t>
+          <t>Himalaya Nutravedics BSE SMEL@118.00 (11.32%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>28-Sep 15:00</t>
+          <t>29-Sep 9:33</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3516,7 +3516,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMECAllotted</t>
+          <t>Anand Seamless BSE SMEL@72.10 (0.14%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>28-Sep 14:53</t>
+          <t>29-Sep 9:31</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3583,12 +3583,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOCAllotted</t>
+          <t>Varmora Granito IPOL@155.00 (4.73%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹1.5 (1.01%) 0.50 ↓ / 15 ↑</t>
+          <t>₹1 (0.68%) 0.50 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 1</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 9:37</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TNA Solutions BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹7 (10.00%) 7 ↓ / 7 ↑</t>
-        </is>
-      </c>
+          <t>R.K.Fashion Accessories NSE SMEU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -521,89 +517,85 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹37.86 Cr</t>
+          <t>₹34.99 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>9-Oct</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>29-Sep 15:02</t>
-        </is>
-      </c>
+          <t>12-Oct</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Paramount Syntex BSE SMEU</t>
+          <t>TNA Solutions BSE SMEO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹7 (10.00%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.16x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹81.79 Cr</t>
+          <t>₹37.86 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -623,19 +615,19 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>29-Sep 15:00</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Acme India Industries BSE SMEU</t>
+          <t>Acme India Industries BSE SMEO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -650,7 +642,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.34x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -670,7 +662,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -690,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -702,109 +694,109 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nityas Gems &amp; Jewellery IPOU</t>
+          <t>Paramount Syntex BSE SMEO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹9 (12.00%) 9 ↓ / 9 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.17x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹108.35 Cr</t>
+          <t>₹81.79 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>9-Oct</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:29</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Eventions NSE SMEU</t>
+          <t>EverestIMS Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹20 (23.53%) 13 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.36x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹38.12 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>29-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -824,7 +816,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>29-Sep 14:58</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -836,7 +828,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sollfege Smart Electronics BSE SMEU</t>
+          <t>Dove Soft BSE SMEO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -851,27 +843,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.1x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹21.78 Cr</t>
+          <t>₹73.26 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -891,7 +883,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>29-Sep 14:54</t>
+          <t>30-Sep 14:30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -903,12 +895,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SJP Ultrasonic BSE SMEU</t>
+          <t>Nityas Gems &amp; Jewellery IPOO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -918,27 +910,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.17x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹23.45 Cr</t>
+          <t>₹108.35 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -958,24 +950,24 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vishal Nirmiti IPOU</t>
+          <t>Vishal Nirmiti IPOO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹2 (0.91%) 2 ↓ / 2 ↑</t>
+          <t>₹10 (4.55%) 2 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -985,7 +977,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.05x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1005,7 +997,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1025,7 +1017,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1037,7 +1029,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dove Soft BSE SMEU</t>
+          <t>Eventions NSE SMEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1052,17 +1044,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.11x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹73.26 Cr</t>
+          <t>₹38.12 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1072,7 +1064,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1092,19 +1084,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>29-Sep 14:58</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMEU</t>
+          <t>Sollfege Smart Electronics BSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1119,27 +1111,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.06x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹21.78 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1159,7 +1151,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>29-Sep 14:58</t>
+          <t>30-Sep 14:35</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1171,42 +1163,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEO</t>
+          <t>Shree TNB Polymers BSE SMEO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹17 (20.00%) 13 ↓ / 17 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.11x</t>
+          <t>0.5x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹31.80 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 17</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:36</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1238,7 +1230,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shree TNB Polymers BSE SMEO</t>
+          <t>SJP Ultrasonic BSE SMEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1253,17 +1245,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.39x</t>
+          <t>0.31x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹31.80 Cr</t>
+          <t>₹23.45 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1273,7 +1265,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1293,19 +1285,19 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>29-Sep 14:55</t>
+          <t>30-Sep 14:28</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEO</t>
+          <t>Omara Ventures India BSE SMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1320,47 +1312,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.52x</t>
+          <t>0.39x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹59.34 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>29-Sep 14:55</t>
+          <t>30-Sep 14:29</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1372,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMEO</t>
+          <t>Green Asia Impex NSE SMEO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1387,27 +1379,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.27x</t>
+          <t>0.59x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹55.08 Cr</t>
+          <t>₹59.34 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1427,12 +1419,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>29-Sep 14:57</t>
+          <t>30-Sep 14:31</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1444,17 +1436,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹45 (38.14%) 45 ↓ / 45 ↑</t>
+          <t>₹90 (76.27%) 45 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.84x</t>
+          <t>42.1x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1474,7 +1466,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 45</t>
+          <t>29-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1494,7 +1486,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1573,42 +1565,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMEO</t>
+          <t>Black Opal Consultants BSE SMEO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹20 (10.15%) 20 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.29x</t>
+          <t>0.91x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹20.18 Cr</t>
+          <t>₹55.08 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0</t>
+          <t>29-Sep GMP: 38</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1628,19 +1620,19 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEO</t>
+          <t>Papadmalji Agro Foods NSE SMEO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1655,47 +1647,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.27x</t>
+          <t>1.62x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹20.18 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>29-Sep 14:57</t>
+          <t>30-Sep 14:34</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1707,47 +1699,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SRIT India IPOO</t>
+          <t>Shivchem Agro BSE SMECT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹23 (17.69%) 12 ↓ / 33 ↑</t>
+          <t>₹1 (1.61%) 1 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.31x</t>
+          <t>1.81x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹218.40 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 33</t>
+          <t>28-Sep GMP: 6</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1762,59 +1754,59 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMEO</t>
+          <t>Shah Investor's Home IPOCT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹12.5 (7.49%) 9 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.37x</t>
+          <t>18.76x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹35.93 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 14</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 12.5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1829,7 +1821,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>29-Sep 14:59</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1841,47 +1833,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOO</t>
+          <t>Pind Hospitality BSE SMECT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹13 (7.78%) 9 ↓ / 14 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.87x</t>
+          <t>2.33x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 14</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1896,59 +1888,59 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMEO</t>
+          <t>Acme Universal Safezone 9 BSE SMECT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹13 (20.97%) 6 ↓ / 13 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.5x</t>
+          <t>4.56x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹14.01 Cr</t>
+          <t>₹35.93 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 6</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1963,24 +1955,24 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:35</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMECT</t>
+          <t>SRIT India IPOCT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹30 (27.27%) 12 ↓ / 30 ↑</t>
+          <t>₹38 (29.23%) 12 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1990,47 +1982,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>69.36x</t>
+          <t>69.98x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>28-Sep GMP: 33</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 30</t>
+          <t>30-Sep GMP: 38</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2042,12 +2034,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMECT</t>
+          <t>Acevector IPOC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹0.5 (1.56%) 0.50 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2057,32 +2049,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.79x</t>
+          <t>5.07x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹420.00 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0</t>
+          <t>29-Sep GMP: 1.1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2097,7 +2089,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>29-Sep 15:00</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2109,12 +2101,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Acevector IPOCT</t>
+          <t>Dudani Retail BSE SMEC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
+          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2124,32 +2116,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.24x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹420.00 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 2</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0</t>
+          <t>29-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2164,59 +2156,59 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Orient Cables IPOCT</t>
+          <t>Sai Urja Indo BSE SMEC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹85 (31.25%) 34 ↓ / 113 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>63.8x</t>
+          <t>4.95x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 80</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 85</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2231,7 +2223,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2243,47 +2235,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMECT</t>
+          <t>Orient Cables IPOC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
+          <t>₹88 (32.35%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.26x</t>
+          <t>97.28x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 3</t>
+          <t>25-Sep GMP: 80</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0.5</t>
+          <t>29-Sep GMP: 85</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2298,24 +2290,24 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOCT</t>
+          <t>Runwal Enterprises IPOC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
+          <t>₹4 (1.31%) 2 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2325,7 +2317,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.93x</t>
+          <t>2.64x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2350,7 +2342,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0</t>
+          <t>29-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2365,7 +2357,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2377,12 +2369,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>German Green Steel IPOCT</t>
+          <t>German Green Steel IPOC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹12.5 (8.99%) 12.50 ↓ / 29 ↑</t>
+          <t>₹13 (9.35%) 13 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2392,7 +2384,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5.39x</t>
+          <t>30.42x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2417,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 12.5</t>
+          <t>29-Sep GMP: 13</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2432,7 +2424,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2444,7 +2436,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMECT</t>
+          <t>Himalayan Solar NSE SMEC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2459,7 +2451,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.12x</t>
+          <t>1.19x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2484,7 +2476,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2499,7 +2491,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>29-Sep 14:59</t>
+          <t>30-Sep 14:36</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2511,62 +2503,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A-One Steels IPOC</t>
+          <t>Bench Mark Infotech Services NSE SMEC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹27 (6.67%) 27 ↓ / 64 ↑</t>
+          <t>₹28 (25.45%) 12 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12.23x</t>
+          <t>103.12x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 49</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 28</t>
+          <t>29-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2645,47 +2637,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Moneyview IPOC</t>
+          <t>A-One Steels IPOC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹12.75 (37.50%) 5 ↓ / 15.50 ↑</t>
+          <t>₹38 (9.38%) 28 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>101.87x</t>
+          <t>12.23x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 15.5</t>
+          <t>24-Sep GMP: 49</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 12.75</t>
+          <t>28-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2700,7 +2692,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2712,47 +2704,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEC</t>
+          <t>Moneyview IPOCAllotted</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹13.75 (40.44%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.77x</t>
+          <t>101.87x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>24-Sep GMP: 15.5</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 12.75</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2767,12 +2759,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>29-Sep 14:59</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2826,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2846,7 +2838,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMECAllotted</t>
+          <t>Peshwa Wheat BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2861,64 +2853,64 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.18x</t>
+          <t>2.77x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:30</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOCAllotted</t>
+          <t>Swastika Infra IPOL@200.00 (8.11%)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹6 (3.24%) 3 ↓ / 9.50 ↑</t>
+          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2963,12 +2955,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2980,47 +2972,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOC</t>
+          <t>ArMee Infotech IPOL@375.00 (0%)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹53 (39.55%) 32 ↓ / 58 ↑</t>
+          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>176.85x</t>
+          <t>2.62x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 34</t>
+          <t>23-Sep GMP: 51</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 47</t>
+          <t>25-Sep GMP: 8</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3030,12 +3022,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 6</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3047,7 +3039,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMECAllotted</t>
+          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3062,22 +3054,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3.11x</t>
+          <t>5.08x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3097,29 +3089,29 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>29-Sep 14:56</t>
+          <t>30-Sep 9:34</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOC</t>
+          <t>S.K.Offset BSE SMEL@126.00 (0.8%)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3129,32 +3121,32 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.62x</t>
+          <t>1.18x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 51</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 8</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3164,12 +3156,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 9:32</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3181,12 +3173,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOCAllotted</t>
+          <t>Core Integra Consulting NSE SMEL@78.10 (0.13%)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹6 (1.66%) 2.50 ↓ / 16 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3196,32 +3188,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.89x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4.5</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3231,24 +3223,24 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 9:31</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEC</t>
+          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3263,22 +3255,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5.08x</t>
+          <t>3.11x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3298,64 +3290,64 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>29-Sep 14:58</t>
+          <t>30-Sep 9:32</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEC</t>
+          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>176.85x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 47</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3365,29 +3357,29 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 55</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>29-Sep 14:53</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEC</t>
+          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3397,32 +3389,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.92x</t>
+          <t>1.89x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3432,12 +3424,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 6.5</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>29-Sep 14:53</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3449,7 +3441,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEL@118.00 (11.32%)</t>
+          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3464,47 +3456,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2.33x</t>
+          <t>3.92x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>29-Sep 9:33</t>
+          <t>30-Sep 9:28</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3516,7 +3508,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMEL@72.10 (0.14%)</t>
+          <t>Himalaya Nutravedics BSE SMEL@118.00 (11.32%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3531,22 +3523,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.47x</t>
+          <t>2.33x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹25.52 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3571,12 +3563,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>29-Sep 9:31</t>
+          <t>29-Sep 9:33</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3717,99 +3709,99 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEL@201.40 (90%)</t>
+          <t>Anand Seamless BSE SMEL@72.10 (0.14%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹86 (81.13%) 45 ↓ / 86 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>833.56x</t>
+          <t>1.47x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹25.52 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 55</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 55</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 86</t>
+          <t>29-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>28-Sep 9:37</t>
+          <t>29-Sep 9:31</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMEL@123.05 (6.08%)</t>
+          <t>Robokidz Eduventures BSE SMEL@201.40 (90%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹6.5 (5.60%) 4 ↓ / 6.50 ↑</t>
+          <t>₹86 (81.13%) 45 ↓ / 86 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>17.72x</t>
+          <t>833.56x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹45.24 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3819,12 +3811,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>21-Sep GMP: 55</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4</t>
+          <t>23-Sep GMP: 55</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3834,7 +3826,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 6.5</t>
+          <t>28-Sep GMP: 86</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3918,62 +3910,62 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMEL@54.75 (1.39%)</t>
+          <t>FX Multitech BSE SMEL@123.05 (6.08%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6.5 (5.60%) 4 ↓ / 6.50 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>17.72x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹50.75 Cr</t>
+          <t>₹45.24 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 0</t>
+          <t>28-Sep GMP: 6.5</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>25-Sep 8:56</t>
+          <t>28-Sep 9:37</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3985,12 +3977,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kheria Autocomp NSE SMEL@104.90 (3.86%)</t>
+          <t>Axiom Gas Engineering NSE SMEL@54.75 (1.39%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>₹3 (2.97%) 3 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4000,47 +3992,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2.48x</t>
+          <t>1.39x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹46.44 Cr</t>
+          <t>₹50.75 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>17-Sep GMP: 10</t>
+          <t>18-Sep</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 3</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 3</t>
+          <t>25-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>25-Sep 8:56</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -504,7 +504,11 @@
           <t>R.K.Fashion Accessories NSE SMEU</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -550,7 +554,11 @@
           <t>12-Oct</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1-Oct 5:55</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>❌</t>
@@ -565,17 +573,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹7 (10.00%) 7 ↓ / 7 ↑</t>
+          <t>₹6 (8.57%) 6 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.16x</t>
+          <t>1.69x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -615,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -632,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹30 (15.31%) 30 ↓ / 30 ↑</t>
+          <t>₹25 (12.76%) 25 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -642,7 +650,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.34x</t>
+          <t>1.84x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -682,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -709,7 +717,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.17x</t>
+          <t>1.34x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -729,7 +737,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>30-Sep 14:29</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -766,17 +774,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹20 (23.53%) 13 ↓ / 20 ↑</t>
+          <t>₹10 (11.76%) 10 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.36x</t>
+          <t>1.47x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -843,7 +851,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.1x</t>
+          <t>0.85x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -863,7 +871,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -883,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30-Sep 14:30</t>
+          <t>1-Oct 15:30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -900,7 +908,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 9 ↑</t>
+          <t>₹3 (4.00%) 3 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -910,7 +918,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.17x</t>
+          <t>0.53x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -930,7 +938,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -950,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -967,17 +975,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹10 (4.55%) 2 ↓ / 10 ↑</t>
+          <t>₹27 (12.27%) 2 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.05x</t>
+          <t>0.54x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1017,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1044,7 +1052,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.11x</t>
+          <t>1.69x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1064,7 +1072,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1084,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:34</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1111,7 +1119,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.06x</t>
+          <t>1.59x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1131,7 +1139,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1151,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30-Sep 14:35</t>
+          <t>1-Oct 15:35</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1178,7 +1186,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.5x</t>
+          <t>0.88x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1218,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>30-Sep 14:36</t>
+          <t>1-Oct 15:36</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1245,7 +1253,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.31x</t>
+          <t>0.47x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1265,7 +1273,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1285,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30-Sep 14:28</t>
+          <t>1-Oct 15:36</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1312,7 +1320,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.39x</t>
+          <t>0.65x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,7 +1340,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1352,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>30-Sep 14:29</t>
+          <t>1-Oct 15:36</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1364,7 +1372,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEO</t>
+          <t>Green Asia Impex NSE SMECT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1379,7 +1387,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.59x</t>
+          <t>1.03x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1404,7 +1412,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1419,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30-Sep 14:31</t>
+          <t>1-Oct 15:35</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1431,12 +1439,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEO</t>
+          <t>Vans Electroengineerings BSE SMECT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹90 (76.27%) 45 ↓ / 90 ↑</t>
+          <t>₹70 (59.32%) 45 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1446,7 +1454,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>42.1x</t>
+          <t>596.79x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1471,7 +1479,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 70</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1486,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1565,12 +1573,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMEO</t>
+          <t>Black Opal Consultants BSE SMECT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹20 (10.15%) 20 ↓ / 38 ↑</t>
+          <t>₹30 (15.23%) 30 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1580,7 +1588,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.91x</t>
+          <t>68.73x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1605,7 +1613,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1620,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1632,7 +1640,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMEO</t>
+          <t>Papadmalji Agro Foods NSE SMECT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1647,7 +1655,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.62x</t>
+          <t>2.48x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1672,7 +1680,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1687,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>30-Sep 14:34</t>
+          <t>1-Oct 15:28</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1699,7 +1707,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMECT</t>
+          <t>Shivchem Agro BSE SMEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1714,7 +1722,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.81x</t>
+          <t>2.2x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1754,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1766,12 +1774,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOCT</t>
+          <t>Shah Investor's Home IPOC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹12.5 (7.49%) 9 ↓ / 15 ↑</t>
+          <t>₹12 (7.19%) 9 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1781,7 +1789,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18.76x</t>
+          <t>38.12x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1821,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1833,7 +1841,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMECT</t>
+          <t>Pind Hospitality BSE SMEC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1848,7 +1856,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.33x</t>
+          <t>2.71x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1888,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1900,22 +1908,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMECT</t>
+          <t>Acme Universal Safezone 9 BSE SMEC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹7 (9.86%) 7 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.56x</t>
+          <t>23.41x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1940,7 +1948,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1955,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>30-Sep 14:35</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1967,12 +1975,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SRIT India IPOCT</t>
+          <t>SRIT India IPOC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹38 (29.23%) 12 ↓ / 38 ↑</t>
+          <t>₹47 (36.15%) 12 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1982,7 +1990,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>69.98x</t>
+          <t>125.16x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2007,7 +2015,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 38</t>
+          <t>30-Sep GMP: 48</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2022,7 +2030,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2039,7 +2047,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹0.5 (1.56%) 0.50 ↓ / 2 ↑</t>
+          <t>₹0.7 (2.19%) 0.50 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2089,7 +2097,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2101,7 +2109,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEC</t>
+          <t>Dudani Retail BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2156,7 +2164,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2168,7 +2176,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEC</t>
+          <t>Sai Urja Indo BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2223,7 +2231,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:34</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2235,12 +2243,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Orient Cables IPOC</t>
+          <t>Orient Cables IPOCAllotted</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹88 (32.35%) 34 ↓ / 113 ↑</t>
+          <t>₹100 (36.76%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2290,7 +2298,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2307,7 +2315,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹4 (1.31%) 2 ↓ / 37 ↑</t>
+          <t>₹-5 (-1.64%) -5 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2357,7 +2365,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2374,7 +2382,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹13 (9.35%) 13 ↓ / 29 ↑</t>
+          <t>₹13.5 (9.71%) 12.50 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2424,7 +2432,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2436,7 +2444,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEC</t>
+          <t>Himalayan Solar NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2491,7 +2499,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>30-Sep 14:36</t>
+          <t>1-Oct 15:35</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2503,12 +2511,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEC</t>
+          <t>Bench Mark Infotech Services NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹28 (25.45%) 12 ↓ / 29 ↑</t>
+          <t>₹22 (20.00%) 12 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2558,7 +2566,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2637,17 +2645,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A-One Steels IPOC</t>
+          <t>A-One Steels IPOL@455.00 (12.35%)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹38 (9.38%) 28 ↓ / 64 ↑</t>
+          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2687,12 +2695,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 46</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2704,12 +2712,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Moneyview IPOCAllotted</t>
+          <t>Moneyview IPOL@55.00 (61.76%)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹13.75 (40.44%) 5 ↓ / 15.50 ↑</t>
+          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2754,12 +2762,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 14.5</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2771,12 +2779,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEC</t>
+          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹38 (59.38%) 8 ↓ / 38 ↑</t>
+          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2821,12 +2829,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 42</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2838,7 +2846,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMECAllotted</t>
+          <t>Peshwa Wheat BSE SMEL@100.05 (-0.94%)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2888,12 +2896,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>30-Sep 14:30</t>
+          <t>1-Oct 9:33</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1-Oct 5:55</t>
+          <t>2-Oct 5:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.69x</t>
+          <t>1.71x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.84x</t>
+          <t>1.97x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.34x</t>
+          <t>1.35x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹10 (11.76%) 10 ↓ / 20 ↑</t>
+          <t>₹28 (32.94%) 13 ↓ / 28 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.47x</t>
+          <t>1.7x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.85x</t>
+          <t>0.86x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1-Oct 15:30</t>
+          <t>2-Oct 14:53</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹3 (4.00%) 3 ↓ / 9 ↑</t>
+          <t>₹4 (5.33%) 3 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.53x</t>
+          <t>0.69x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -975,17 +975,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹27 (12.27%) 2 ↓ / 27 ↑</t>
+          <t>₹20 (9.09%) 2 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.54x</t>
+          <t>0.6x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.69x</t>
+          <t>1.8x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1-Oct 15:34</t>
+          <t>2-Oct 14:54</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.59x</t>
+          <t>1.86x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1-Oct 15:35</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.88x</t>
+          <t>0.98x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1-Oct 15:36</t>
+          <t>2-Oct 14:56</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.47x</t>
+          <t>0.54x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1-Oct 15:36</t>
+          <t>2-Oct 14:59</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.65x</t>
+          <t>0.69x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1-Oct 15:36</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1372,7 +1372,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMECT</t>
+          <t>Green Asia Impex NSE SMEC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.03x</t>
+          <t>1.04x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 0</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1-Oct 15:35</t>
+          <t>2-Oct 14:54</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMECT</t>
+          <t>Vans Electroengineerings BSE SMEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>596.79x</t>
+          <t>628.73x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1573,22 +1573,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMECT</t>
+          <t>Black Opal Consultants BSE SMEC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹30 (15.23%) 30 ↓ / 48 ↑</t>
+          <t>₹75 (38.07%) 38 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>68.73x</t>
+          <t>73.8x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 30</t>
+          <t>1-Oct GMP: 66</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1640,7 +1640,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMECT</t>
+          <t>Papadmalji Agro Foods NSE SMEC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.48x</t>
+          <t>2.54x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 0</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1-Oct 15:28</t>
+          <t>2-Oct 14:59</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMEC</t>
+          <t>Shivchem Agro BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹12 (7.19%) 9 ↓ / 15 ↑</t>
+          <t>₹14.5 (8.68%) 9 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1908,17 +1908,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMEC</t>
+          <t>Acme Universal Safezone 9 BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹7 (9.86%) 7 ↓ / 10 ↑</t>
+          <t>₹11 (15.49%) 10 ↓ / 11 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹47 (36.15%) 12 ↓ / 48 ↑</t>
+          <t>₹52 (40.00%) 12 ↓ / 52 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹10 (8.85%) 8 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1-Oct 15:34</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹100 (36.76%) 34 ↓ / 113 ↑</t>
+          <t>₹122 (44.85%) 34 ↓ / 122 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹13.5 (9.71%) 12.50 ↓ / 29 ↑</t>
+          <t>₹13 (9.35%) 12.50 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1-Oct 15:35</t>
+          <t>2-Oct 14:58</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹22 (20.00%) 12 ↓ / 29 ↑</t>
+          <t>₹25 (22.73%) 12 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2-Oct 5:55</t>
+          <t>3-Oct 14:28</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹25 (12.76%) 25 ↓ / 30 ↑</t>
+          <t>₹30 (15.31%) 25 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2-Oct 15:01</t>
+          <t>3-Oct 14:31</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹28 (32.94%) 13 ↓ / 28 ↑</t>
+          <t>₹40 (47.06%) 13 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2-Oct 14:53</t>
+          <t>3-Oct 14:36</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹4 (5.33%) 3 ↓ / 9 ↑</t>
+          <t>₹3 (4.00%) 3 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2-Oct 14:54</t>
+          <t>3-Oct 14:36</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:32</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2-Oct 14:56</t>
+          <t>3-Oct 14:32</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2-Oct 14:59</t>
+          <t>3-Oct 14:30</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2-Oct 14:54</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹75 (38.07%) 38 ↓ / 75 ↑</t>
+          <t>₹80 (40.61%) 38 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2-Oct 14:59</t>
+          <t>3-Oct 14:29</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹14.5 (8.68%) 9 ↓ / 15 ↑</t>
+          <t>₹15.75 (9.43%) 9 ↓ / 15.75 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹11 (15.49%) 10 ↓ / 11 ↑</t>
+          <t>₹11.5 (16.20%) 10 ↓ / 11.50 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹52 (40.00%) 12 ↓ / 52 ↑</t>
+          <t>₹52 (40.00%) 12 ↓ / 53 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹0.7 (2.19%) 0.50 ↓ / 2 ↑</t>
+          <t>₹0.6 (1.88%) 0.50 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹10 (8.85%) 8 ↓ / 10 ↑</t>
+          <t>₹20 (17.70%) 8 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹122 (44.85%) 34 ↓ / 122 ↑</t>
+          <t>₹120 (44.12%) 34 ↓ / 123 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹13 (9.35%) 12.50 ↓ / 29 ↑</t>
+          <t>₹11.5 (8.27%) 11.50 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2-Oct 14:58</t>
+          <t>3-Oct 14:36</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3-Oct 14:28</t>
+          <t>3-Oct 19:31</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹6 (8.57%) 6 ↓ / 7 ↑</t>
+          <t>₹10 (14.29%) 6 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3-Oct 14:31</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3-Oct 14:36</t>
+          <t>3-Oct 19:29</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3-Oct 14:36</t>
+          <t>3-Oct 19:32</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3-Oct 14:32</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3-Oct 14:32</t>
+          <t>3-Oct 19:30</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>3-Oct 14:30</t>
+          <t>3-Oct 19:29</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:30</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:31</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹80 (40.61%) 38 ↓ / 80 ↑</t>
+          <t>₹85 (43.15%) 38 ↓ / 85 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3-Oct 14:29</t>
+          <t>3-Oct 19:31</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹1 (1.61%) 1 ↓ / 10 ↑</t>
+          <t>₹1.5 (2.42%) 1 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹15.75 (9.43%) 9 ↓ / 15.75 ↑</t>
+          <t>₹15.5 (9.28%) 9 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹11.5 (16.20%) 10 ↓ / 11.50 ↑</t>
+          <t>₹13 (18.31%) 10 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹20 (17.70%) 8 ↓ / 20 ↑</t>
+          <t>₹17 (15.04%) 8 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹120 (44.12%) 34 ↓ / 123 ↑</t>
+          <t>₹111 (40.81%) 34 ↓ / 123 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹-5 (-1.64%) -5 ↓ / 37 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹11.5 (8.27%) 11.50 ↓ / 29 ↑</t>
+          <t>₹10.5 (7.55%) 10.50 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>3-Oct 14:36</t>
+          <t>3-Oct 19:32</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3-Oct 19:31</t>
+          <t>4-Oct 14:58</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3-Oct 19:29</t>
+          <t>4-Oct 14:53</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3-Oct 19:32</t>
+          <t>4-Oct 14:55</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 14:54</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3-Oct 19:30</t>
+          <t>4-Oct 14:54</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>3-Oct 19:29</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>3-Oct 19:30</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3-Oct 19:31</t>
+          <t>4-Oct 14:57</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹85 (43.15%) 38 ↓ / 85 ↑</t>
+          <t>₹100 (50.76%) 38 ↓ / 100 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3-Oct 19:31</t>
+          <t>4-Oct 14:54</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹111 (40.81%) 34 ↓ / 123 ↑</t>
+          <t>₹115 (42.28%) 34 ↓ / 123 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>3-Oct 19:32</t>
+          <t>4-Oct 14:56</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R.K.Fashion Accessories NSE SMEU</t>
+          <t>Jio Platforms IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹151 (-%) 148 ↓ / 151 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -521,126 +521,106 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹34.99 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>5-Oct</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7-Oct</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>8-Oct</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>12-Oct</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4-Oct 14:58</t>
+          <t>5-Oct 15:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TNA Solutions BSE SMEO</t>
+          <t>R.K.Fashion Accessories NSE SMEO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹10 (14.29%) 6 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.71x</t>
+          <t>0.35x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹37.86 Cr</t>
+          <t>₹34.99 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 7</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>9-Oct</t>
+          <t>12-Oct</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:35</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Acme India Industries BSE SMEO</t>
+          <t>TNA Solutions BSE SMEO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹30 (15.31%) 25 ↓ / 30 ↑</t>
+          <t>₹10 (14.29%) 6 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -650,27 +630,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.97x</t>
+          <t>2.67x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹121.69 Cr</t>
+          <t>₹37.86 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 30</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -690,7 +670,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -717,7 +697,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.35x</t>
+          <t>1.43x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -757,7 +737,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:29</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -769,62 +749,62 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEO</t>
+          <t>Acme India Industries BSE SMEO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹40 (47.06%) 13 ↓ / 40 ↑</t>
+          <t>₹30 (15.31%) 25 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.7x</t>
+          <t>3.29x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹121.69 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 16</t>
+          <t>30-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>9-Oct</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:37</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -836,12 +816,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dove Soft BSE SMEO</t>
+          <t>Nityas Gems &amp; Jewellery IPOCT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -851,32 +831,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.86x</t>
+          <t>2.11x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹73.26 Cr</t>
+          <t>₹108.35 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -891,59 +871,59 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>4-Oct 14:53</t>
+          <t>5-Oct 15:37</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nityas Gems &amp; Jewellery IPOO</t>
+          <t>EverestIMS Technologies BSE SMECT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹3 (4.00%) 3 ↓ / 9 ↑</t>
+          <t>₹42 (49.41%) 13 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.69x</t>
+          <t>279.29x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹108.35 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 5</t>
+          <t>29-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 42</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -958,7 +938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:37</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -970,47 +950,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vishal Nirmiti IPOO</t>
+          <t>Omara Ventures India BSE SMECT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹20 (9.09%) 2 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.6x</t>
+          <t>1.05x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹178.00 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1025,7 +1005,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:30</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1037,12 +1017,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Eventions NSE SMEO</t>
+          <t>Vishal Nirmiti IPOCT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹4 (1.82%) 2 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1052,32 +1032,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.8x</t>
+          <t>1.71x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹38.12 Cr</t>
+          <t>₹178.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1092,19 +1072,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4-Oct 14:55</t>
+          <t>5-Oct 15:37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sollfege Smart Electronics BSE SMEO</t>
+          <t>SJP Ultrasonic BSE SMECT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1119,17 +1099,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.86x</t>
+          <t>1.76x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹21.78 Cr</t>
+          <t>₹23.45 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1144,7 +1124,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1159,7 +1139,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4-Oct 14:54</t>
+          <t>5-Oct 15:36</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1171,7 +1151,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shree TNB Polymers BSE SMEO</t>
+          <t>Eventions NSE SMECT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1186,32 +1166,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.98x</t>
+          <t>2.36x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹31.80 Cr</t>
+          <t>₹38.12 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1226,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4-Oct 14:54</t>
+          <t>5-Oct 15:28</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1238,7 +1218,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SJP Ultrasonic BSE SMEO</t>
+          <t>Dove Soft BSE SMECT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1253,22 +1233,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.54x</t>
+          <t>1.37x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹23.45 Cr</t>
+          <t>₹73.26 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1278,7 +1258,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1293,7 +1273,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:31</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1305,7 +1285,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMEO</t>
+          <t>Sollfege Smart Electronics BSE SMECT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1320,22 +1300,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.69x</t>
+          <t>2.12x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹21.78 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1345,7 +1325,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1360,7 +1340,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:34</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1372,7 +1352,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEC</t>
+          <t>Shree TNB Polymers BSE SMECT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1387,99 +1367,99 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.04x</t>
+          <t>1.86x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹59.34 Cr</t>
+          <t>₹31.80 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4-Oct 14:57</t>
+          <t>5-Oct 15:37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEC</t>
+          <t>Papadmalji Agro Foods NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹70 (59.32%) 45 ↓ / 90 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>628.73x</t>
+          <t>2.54x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹20.18 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 90</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 70</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1494,12 +1474,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:31</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1608,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1640,47 +1620,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMEC</t>
+          <t>Vans Electroengineerings BSE SMEC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹70 (59.32%) 45 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.54x</t>
+          <t>628.73x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹20.18 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 70</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1695,24 +1675,24 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>4-Oct 14:54</t>
+          <t>5-Oct 15:37</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMECAllotted</t>
+          <t>Green Asia Impex NSE SMEC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹1.5 (2.42%) 1 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1722,47 +1702,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.2x</t>
+          <t>1.04x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹14.01 Cr</t>
+          <t>₹59.34 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 6</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 1</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:32</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1774,47 +1754,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOC</t>
+          <t>SRIT India IPOC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹15.5 (9.28%) 9 ↓ / 15.50 ↑</t>
+          <t>₹55 (42.31%) 12 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>38.12x</t>
+          <t>125.16x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 14</t>
+          <t>28-Sep GMP: 33</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 12.5</t>
+          <t>30-Sep GMP: 48</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1829,7 +1809,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1841,47 +1821,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEC</t>
+          <t>Shah Investor's Home IPOC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
+          <t>₹16.5 (9.88%) 9 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.71x</t>
+          <t>38.12x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 1</t>
+          <t>30-Sep GMP: 12.5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1896,59 +1876,59 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMECAllotted</t>
+          <t>Shivchem Agro BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹13 (18.31%) 10 ↓ / 13 ↑</t>
+          <t>₹1.5 (2.42%) 1 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>23.41x</t>
+          <t>2.2x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹35.93 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 6</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>30-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1963,59 +1943,59 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SRIT India IPOC</t>
+          <t>Pind Hospitality BSE SMEC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹52 (40.00%) 12 ↓ / 53 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>125.16x</t>
+          <t>2.71x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹218.40 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 33</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 48</t>
+          <t>30-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2030,74 +2010,74 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Acevector IPOC</t>
+          <t>Acme Universal Safezone 9 BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹0.6 (1.88%) 0.50 ↓ / 2 ↑</t>
+          <t>₹12 (16.90%) 10 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5.07x</t>
+          <t>23.41x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹420.00 Cr</t>
+          <t>₹35.93 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 2</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 1.1</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2109,47 +2089,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMECAllotted</t>
+          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
+          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>4.95x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 3</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0.5</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2159,64 +2139,64 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 11</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMECAllotted</t>
+          <t>Acevector IPOL@28.32 (-11.5%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹17 (15.04%) 8 ↓ / 17 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4.95x</t>
+          <t>5.07x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹420.00 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 1.1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2226,12 +2206,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2243,12 +2223,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Orient Cables IPOCAllotted</t>
+          <t>Orient Cables IPOL@450 (65.44%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹115 (42.28%) 34 ↓ / 123 ↑</t>
+          <t>₹110 (40.44%) 34 ↓ / 123 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2293,12 +2273,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 110</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2310,7 +2290,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOC</t>
+          <t>Runwal Enterprises IPOL@305 (0%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2360,12 +2340,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2377,47 +2357,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>German Green Steel IPOC</t>
+          <t>Himalayan Solar NSE SMEL@85 (-17.48%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹10.5 (7.55%) 10.50 ↓ / 29 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>30.42x</t>
+          <t>1.19x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹303.90 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 26</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 13</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2427,12 +2407,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 9:35</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2444,47 +2424,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMECAllotted</t>
+          <t>German Green Steel IPOL@142 (2.16%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹9.5 (6.83%) 9.50 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.19x</t>
+          <t>30.42x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹303.90 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 26</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 13</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,12 +2474,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 9.5</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>4-Oct 14:56</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2511,17 +2491,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMECAllotted</t>
+          <t>Bench Mark Infotech Services NSE SMEL@110 (0%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹25 (22.73%) 12 ↓ / 29 ↑</t>
+          <t>₹15 (13.64%) 12 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2561,12 +2541,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 15</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2645,114 +2625,114 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A-One Steels IPOL@455.00 (12.35%)</t>
+          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
+          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>12.23x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 49</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 28</t>
+          <t>29-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 46</t>
+          <t>5-Oct GMP: 0.5</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1-Oct 9:37</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Moneyview IPOL@55.00 (61.76%)</t>
+          <t>A-One Steels IPOL@455.00 (12.35%)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
+          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>101.87x</t>
+          <t>12.23x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 15.5</t>
+          <t>24-Sep GMP: 49</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 12.75</t>
+          <t>28-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2762,7 +2742,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 14.5</t>
+          <t>1-Oct GMP: 46</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2779,47 +2759,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
+          <t>Peshwa Wheat BSE SMEL@100.05 (-0.94%)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>271.94x</t>
+          <t>2.77x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 38</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2829,64 +2809,64 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 42</t>
+          <t>1-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1-Oct 9:37</t>
+          <t>1-Oct 9:33</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEL@100.05 (-0.94%)</t>
+          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2.77x</t>
+          <t>271.94x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 38</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2896,79 +2876,79 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 0</t>
+          <t>1-Oct GMP: 42</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1-Oct 9:33</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOL@200.00 (8.11%)</t>
+          <t>Moneyview IPOL@55.00 (61.76%)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
+          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7.91x</t>
+          <t>101.87x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹160.88 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 9.5</t>
+          <t>24-Sep GMP: 15.5</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4.5</t>
+          <t>28-Sep GMP: 12.75</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 7</t>
+          <t>1-Oct GMP: 14.5</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2980,12 +2960,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOL@375.00 (0%)</t>
+          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2995,32 +2975,32 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.62x</t>
+          <t>3.11x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 51</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 8</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3030,12 +3010,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:32</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3047,7 +3027,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
+          <t>Core Integra Consulting NSE SMEL@78.10 (0.13%)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3062,22 +3042,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5.08x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3102,7 +3082,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>30-Sep 9:34</t>
+          <t>30-Sep 9:31</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3114,7 +3094,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEL@126.00 (0.8%)</t>
+          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3129,22 +3109,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.18x</t>
+          <t>3.92x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3169,7 +3149,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>30-Sep 9:32</t>
+          <t>30-Sep 9:28</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3181,47 +3161,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEL@78.10 (0.13%)</t>
+          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>176.85x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 47</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3231,24 +3211,24 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 55</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>30-Sep 9:31</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
+          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3263,22 +3243,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3.11x</t>
+          <t>5.08x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3303,59 +3283,59 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>30-Sep 9:32</t>
+          <t>30-Sep 9:34</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
+          <t>Swastika Infra IPOL@200.00 (8.11%)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
+          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>176.85x</t>
+          <t>7.91x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 34</t>
+          <t>23-Sep GMP: 9.5</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 47</t>
+          <t>25-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3365,7 +3345,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 55</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3382,12 +3362,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
+          <t>S.K.Offset BSE SMEL@126.00 (0.8%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3397,32 +3377,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.89x</t>
+          <t>1.18x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4.5</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3432,12 +3412,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6.5</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:32</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3449,12 +3429,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
+          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3464,32 +3444,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.92x</t>
+          <t>1.89x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3499,12 +3479,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 6.5</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>30-Sep 9:28</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3516,12 +3496,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEL@118.00 (11.32%)</t>
+          <t>ArMee Infotech IPOL@375.00 (0%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3531,47 +3511,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2.33x</t>
+          <t>2.62x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep GMP: 51</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep GMP: 8</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0</t>
+          <t>30-Sep GMP: 6</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>29-Sep 9:33</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3717,7 +3697,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMEL@72.10 (0.14%)</t>
+          <t>Himalaya Nutravedics BSE SMEL@118.00 (11.32%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3732,22 +3712,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.47x</t>
+          <t>2.33x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹25.52 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3772,116 +3752,116 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>29-Sep 9:31</t>
+          <t>29-Sep 9:33</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEL@201.40 (90%)</t>
+          <t>Anand Seamless BSE SMEL@72.10 (0.14%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹86 (81.13%) 45 ↓ / 86 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>833.56x</t>
+          <t>1.47x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹25.52 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 55</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 55</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 86</t>
+          <t>29-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>28-Sep 9:37</t>
+          <t>29-Sep 9:31</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMEL@38.00 (2.7%)</t>
+          <t>FX Multitech BSE SMEL@123.05 (6.08%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6.5 (5.60%) 4 ↓ / 6.50 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.79x</t>
+          <t>17.72x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹22.20 Cr</t>
+          <t>₹45.24 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3891,7 +3871,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3901,12 +3881,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 0</t>
+          <t>28-Sep GMP: 6.5</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>28-Sep 9:30</t>
+          <t>28-Sep 9:37</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3918,37 +3898,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMEL@123.05 (6.08%)</t>
+          <t>Vivekanand Cotspin BSE SMEL@38.00 (2.7%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹6.5 (5.60%) 4 ↓ / 6.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>17.72x</t>
+          <t>1.79x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹45.24 Cr</t>
+          <t>₹22.20 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3958,7 +3938,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3968,12 +3948,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 6.5</t>
+          <t>28-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>28-Sep 9:37</t>
+          <t>28-Sep 9:30</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3985,62 +3965,62 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Axiom Gas Engineering NSE SMEL@54.75 (1.39%)</t>
+          <t>Robokidz Eduventures BSE SMEL@201.40 (90%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹86 (81.13%) 45 ↓ / 86 ↑</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>833.56x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹50.75 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>21-Sep GMP: 55</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep GMP: 55</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 0</t>
+          <t>28-Sep GMP: 86</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>25-Sep 8:56</t>
+          <t>28-Sep 9:37</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jio Platforms IPOU</t>
+          <t>HD Fire Protect IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹151 (-%) 148 ↓ / 151 ↑</t>
+          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -519,24 +519,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15-Oct</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>16-Oct</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>21-Oct</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5-Oct 15:37</t>
+          <t>6-Oct 14:30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -548,12 +560,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R.K.Fashion Accessories NSE SMEO</t>
+          <t>Jio Platforms IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹152 (-%) 148 ↓ / 156 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -563,166 +575,146 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.35x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹34.99 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>5-Oct GMP: 0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7-Oct</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>8-Oct</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>12-Oct</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5-Oct 15:35</t>
+          <t>6-Oct 15:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TNA Solutions BSE SMEO</t>
+          <t>R.K.Fashion Accessories NSE SMEO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹10 (14.29%) 6 ↓ / 10 ↑</t>
+          <t>₹7 (8.54%) 7 ↓ / 7 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.67x</t>
+          <t>0.42x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹37.86 Cr</t>
+          <t>₹34.99 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 7</t>
+          <t>5-Oct GMP: 7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>9-Oct</t>
+          <t>12-Oct</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5-Oct 15:37</t>
+          <t>6-Oct 15:37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Paramount Syntex BSE SMEO</t>
+          <t>TNA Solutions BSE SMECT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹5 (7.14%) 5 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.43x</t>
+          <t>49.5x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹81.79 Cr</t>
+          <t>₹37.86 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>6-Oct GMP: 5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -737,59 +729,59 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5-Oct 15:29</t>
+          <t>6-Oct 15:37</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Acme India Industries BSE SMEO</t>
+          <t>Paramount Syntex BSE SMECT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹30 (15.31%) 25 ↓ / 30 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.29x</t>
+          <t>1.86x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹121.69 Cr</t>
+          <t>₹81.79 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 30</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>6-Oct GMP: 0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -804,74 +796,74 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5-Oct 15:37</t>
+          <t>6-Oct 15:30</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nityas Gems &amp; Jewellery IPOCT</t>
+          <t>Acme India Industries BSE SMECT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
+          <t>₹50 (25.51%) 25 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.11x</t>
+          <t>117.34x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹108.35 Cr</t>
+          <t>₹121.69 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 5</t>
+          <t>30-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 1</t>
+          <t>6-Oct GMP: 50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>9-Oct</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5-Oct 15:37</t>
+          <t>6-Oct 15:37</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -883,47 +875,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMECT</t>
+          <t>Nityas Gems &amp; Jewellery IPOC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹42 (49.41%) 13 ↓ / 42 ↑</t>
+          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>279.29x</t>
+          <t>2.26x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹108.35 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 16</t>
+          <t>30-Sep GMP: 5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 42</t>
+          <t>5-Oct GMP: 1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -938,7 +930,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5-Oct 15:37</t>
+          <t>6-Oct 15:37</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -950,47 +942,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMECT</t>
+          <t>EverestIMS Technologies BSE SMEC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹50 (58.82%) 13 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.05x</t>
+          <t>294.22x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>29-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct GMP: 42</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1005,24 +997,24 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5-Oct 15:30</t>
+          <t>6-Oct 15:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vishal Nirmiti IPOCT</t>
+          <t>Omara Ventures India BSE SMEC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹4 (1.82%) 2 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1032,32 +1024,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.71x</t>
+          <t>1.06x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹178.00 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 4</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1072,7 +1064,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>5-Oct 15:37</t>
+          <t>6-Oct 15:37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1084,12 +1076,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SJP Ultrasonic BSE SMECT</t>
+          <t>Vishal Nirmiti IPOC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹2 (0.91%) 2 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1099,32 +1091,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.76x</t>
+          <t>1.79x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹23.45 Cr</t>
+          <t>₹178.00 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct GMP: 2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1139,7 +1131,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5-Oct 15:36</t>
+          <t>6-Oct 15:37</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1151,7 +1143,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Eventions NSE SMECT</t>
+          <t>SJP Ultrasonic BSE SMEC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1166,22 +1158,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.36x</t>
+          <t>1.82x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹38.12 Cr</t>
+          <t>₹23.45 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1191,7 +1183,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1206,19 +1198,19 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5-Oct 15:28</t>
+          <t>6-Oct 15:30</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dove Soft BSE SMECT</t>
+          <t>Eventions NSE SMEC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1233,17 +1225,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.37x</t>
+          <t>2.39x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹73.26 Cr</t>
+          <t>₹38.12 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1258,7 +1250,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1273,19 +1265,19 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5-Oct 15:31</t>
+          <t>6-Oct 15:36</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sollfege Smart Electronics BSE SMECT</t>
+          <t>Dove Soft BSE SMEC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1300,22 +1292,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.12x</t>
+          <t>1.38x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹21.78 Cr</t>
+          <t>₹73.26 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1325,7 +1317,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1340,7 +1332,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5-Oct 15:34</t>
+          <t>6-Oct 15:30</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1352,7 +1344,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shree TNB Polymers BSE SMECT</t>
+          <t>Sollfege Smart Electronics BSE SMEC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1367,17 +1359,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.86x</t>
+          <t>2.14x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹31.80 Cr</t>
+          <t>₹21.78 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1387,12 +1379,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1407,19 +1399,19 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5-Oct 15:37</t>
+          <t>6-Oct 15:29</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMECAllotted</t>
+          <t>Shree TNB Polymers BSE SMEC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1434,52 +1426,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.54x</t>
+          <t>1.98x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹20.18 Cr</t>
+          <t>₹31.80 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>5-Oct 15:31</t>
+          <t>6-Oct 15:29</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1553,47 +1545,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMEC</t>
+          <t>Papadmalji Agro Foods NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹100 (50.76%) 38 ↓ / 100 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>73.8x</t>
+          <t>2.54x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹55.08 Cr</t>
+          <t>₹20.18 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 38</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 66</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1608,59 +1600,59 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5-Oct 15:37</t>
+          <t>6-Oct 15:28</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEC</t>
+          <t>Black Opal Consultants BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹70 (59.32%) 45 ↓ / 90 ↑</t>
+          <t>₹60 (30.46%) 38 ↓ / 100 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>628.73x</t>
+          <t>73.8x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹55.08 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 90</t>
+          <t>29-Sep GMP: 38</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 70</t>
+          <t>1-Oct GMP: 66</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1675,7 +1667,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5-Oct 15:37</t>
+          <t>6-Oct 15:37</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1687,47 +1679,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEC</t>
+          <t>Vans Electroengineerings BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹103 (87.29%) 45 ↓ / 103 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.04x</t>
+          <t>628.73x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹59.34 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>29-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 70</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1742,126 +1734,126 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>5-Oct 15:32</t>
+          <t>6-Oct 15:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SRIT India IPOC</t>
+          <t>Green Asia Impex NSE SMECAllotted</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹55 (42.31%) 12 ↓ / 55 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>125.16x</t>
+          <t>1.04x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹218.40 Cr</t>
+          <t>₹59.34 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 33</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 48</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>5-Oct 15:37</t>
+          <t>6-Oct 15:28</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOC</t>
+          <t>SRIT India IPOL@148.00 (13.85%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹16.5 (9.88%) 9 ↓ / 17 ↑</t>
+          <t>₹59 (45.38%) 12 ↓ / 62 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>38.12x</t>
+          <t>125.16x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 14</t>
+          <t>28-Sep GMP: 33</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 12.5</t>
+          <t>30-Sep GMP: 48</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1871,12 +1863,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>6-Oct GMP: 59</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>5-Oct 15:37</t>
+          <t>6-Oct 9:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1888,47 +1880,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMECAllotted</t>
+          <t>Shah Investor's Home IPOL@171.00 (2.4%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹1.5 (2.42%) 1 ↓ / 10 ↑</t>
+          <t>₹17 (10.18%) 9 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.2x</t>
+          <t>38.12x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹14.01 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 6</t>
+          <t>28-Sep GMP: 14</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 1</t>
+          <t>30-Sep GMP: 12.5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1938,29 +1930,29 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>6-Oct GMP: 17</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5-Oct 15:37</t>
+          <t>6-Oct 9:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEC</t>
+          <t>Shivchem Agro BSE SMEL@62.00 (0%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
+          <t>₹1.5 (2.42%) 1 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1970,27 +1962,27 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.71x</t>
+          <t>2.2x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 6</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2005,12 +1997,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>6-Oct GMP: 1.5</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>5-Oct 15:37</t>
+          <t>6-Oct 9:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2022,37 +2014,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMECAllotted</t>
+          <t>Pind Hospitality BSE SMEL@79.20 (-20%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹12 (16.90%) 10 ↓ / 15 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>23.41x</t>
+          <t>2.71x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹35.93 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2062,7 +2054,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>30-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2072,79 +2064,79 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>6-Oct GMP: 1</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>5-Oct 15:37</t>
+          <t>6-Oct 9:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
+          <t>Acme Universal Safezone 9 BSE SMEL@101.00 (42.25%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
+          <t>₹16 (22.54%) 10 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4.95x</t>
+          <t>23.41x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹35.93 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 11</t>
+          <t>6-Oct GMP: 16</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5-Oct 9:37</t>
+          <t>6-Oct 9:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2156,47 +2148,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Acevector IPOL@28.32 (-11.5%)</t>
+          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
+          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5.07x</t>
+          <t>4.95x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹420.00 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 2</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 1.1</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2206,7 +2198,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct GMP: 11</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2223,47 +2215,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Orient Cables IPOL@450 (65.44%)</t>
+          <t>Acevector IPOL@28.32 (-11.5%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹110 (40.44%) 34 ↓ / 123 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>97.28x</t>
+          <t>5.07x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹420.00 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 80</t>
+          <t>25-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 85</t>
+          <t>29-Sep GMP: 1.1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2273,7 +2265,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 110</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2290,47 +2282,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOL@305 (0%)</t>
+          <t>Orient Cables IPOL@450 (65.44%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
+          <t>₹110 (40.44%) 34 ↓ / 123 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.64x</t>
+          <t>97.28x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>25-Sep GMP: 80</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 2</t>
+          <t>29-Sep GMP: 85</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2340,7 +2332,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct GMP: 110</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2357,12 +2349,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEL@85 (-17.48%)</t>
+          <t>Runwal Enterprises IPOL@305 (0%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2372,32 +2364,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.19x</t>
+          <t>2.64x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2412,7 +2404,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>5-Oct 9:35</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2424,47 +2416,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>German Green Steel IPOL@142 (2.16%)</t>
+          <t>Himalayan Solar NSE SMEL@85 (-17.48%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹9.5 (6.83%) 9.50 ↓ / 29 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>30.42x</t>
+          <t>1.19x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹303.90 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 26</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 13</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2474,12 +2466,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 9.5</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>5-Oct 9:37</t>
+          <t>5-Oct 9:35</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2491,47 +2483,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEL@110 (0%)</t>
+          <t>German Green Steel IPOL@142 (2.16%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹15 (13.64%) 12 ↓ / 29 ↑</t>
+          <t>₹9.5 (6.83%) 9.50 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>103.12x</t>
+          <t>30.42x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹303.90 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>25-Sep GMP: 26</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 28</t>
+          <t>29-Sep GMP: 13</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2541,7 +2533,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 15</t>
+          <t>5-Oct GMP: 9.5</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2625,47 +2617,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
+          <t>Bench Mark Infotech Services NSE SMEL@110 (0%)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
+          <t>₹15 (13.64%) 12 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>103.12x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 3</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0.5</t>
+          <t>29-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2675,7 +2667,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0.5</t>
+          <t>5-Oct GMP: 15</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2685,121 +2677,121 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A-One Steels IPOL@455.00 (12.35%)</t>
+          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
+          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>12.23x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 49</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 28</t>
+          <t>29-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 46</t>
+          <t>5-Oct GMP: 0.5</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1-Oct 9:37</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEL@100.05 (-0.94%)</t>
+          <t>A-One Steels IPOL@455.00 (12.35%)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.77x</t>
+          <t>12.23x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>24-Sep GMP: 49</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2809,64 +2801,64 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 0</t>
+          <t>1-Oct GMP: 46</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1-Oct 9:33</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
+          <t>Peshwa Wheat BSE SMEL@100.05 (-0.94%)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>271.94x</t>
+          <t>2.77x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 38</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2876,64 +2868,64 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 42</t>
+          <t>1-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1-Oct 9:37</t>
+          <t>1-Oct 9:33</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Moneyview IPOL@55.00 (61.76%)</t>
+          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
+          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>101.87x</t>
+          <t>271.94x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 15.5</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 12.75</t>
+          <t>28-Sep GMP: 38</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2943,7 +2935,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 14.5</t>
+          <t>1-Oct GMP: 42</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2960,62 +2952,62 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
+          <t>Moneyview IPOL@55.00 (61.76%)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.11x</t>
+          <t>101.87x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep GMP: 15.5</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep GMP: 12.75</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>1-Oct GMP: 14.5</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>30-Sep 9:32</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3027,7 +3019,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEL@78.10 (0.13%)</t>
+          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3042,22 +3034,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>3.11x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3082,19 +3074,19 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>30-Sep 9:31</t>
+          <t>30-Sep 9:32</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
+          <t>Core Integra Consulting NSE SMEL@78.10 (0.13%)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3109,17 +3101,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3.92x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3149,59 +3141,59 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>30-Sep 9:28</t>
+          <t>30-Sep 9:31</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
+          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>176.85x</t>
+          <t>3.92x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 34</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 47</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3211,12 +3203,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 55</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:28</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3228,47 +3220,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
+          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5.08x</t>
+          <t>176.85x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 47</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3278,29 +3270,29 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 55</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>30-Sep 9:34</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOL@200.00 (8.11%)</t>
+          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3310,32 +3302,32 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7.91x</t>
+          <t>5.08x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹160.88 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 9.5</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4.5</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3345,29 +3337,29 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 7</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:34</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEL@126.00 (0.8%)</t>
+          <t>Swastika Infra IPOL@200.00 (8.11%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3377,32 +3369,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.18x</t>
+          <t>7.91x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 9.5</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3412,12 +3404,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>30-Sep 9:32</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3429,12 +3421,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
+          <t>S.K.Offset BSE SMEL@126.00 (0.8%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3444,32 +3436,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.89x</t>
+          <t>1.18x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4.5</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3479,12 +3471,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6.5</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:32</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3496,12 +3488,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOL@375.00 (0%)</t>
+          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
+          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3511,32 +3503,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2.62x</t>
+          <t>1.89x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 51</t>
+          <t>23-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 8</t>
+          <t>25-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3546,7 +3538,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6</t>
+          <t>30-Sep GMP: 6.5</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3563,12 +3555,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOL@155.00 (4.73%)</t>
+          <t>ArMee Infotech IPOL@375.00 (0%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹1 (0.68%) 0.50 ↓ / 15 ↑</t>
+          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3578,47 +3570,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>2.62x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹708.02 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 3</t>
+          <t>23-Sep GMP: 51</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0.5</t>
+          <t>25-Sep GMP: 8</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 1</t>
+          <t>30-Sep GMP: 6</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>29-Sep 9:37</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3697,12 +3689,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEL@118.00 (11.32%)</t>
+          <t>Varmora Granito IPOL@155.00 (4.73%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (0.68%) 0.50 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3712,32 +3704,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.33x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹708.02 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>22-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>24-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3747,12 +3739,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0</t>
+          <t>29-Sep GMP: 1</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>29-Sep 9:33</t>
+          <t>29-Sep 9:37</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3764,7 +3756,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMEL@72.10 (0.14%)</t>
+          <t>Himalaya Nutravedics BSE SMEL@118.00 (11.32%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3779,22 +3771,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.47x</t>
+          <t>2.33x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹25.52 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3819,116 +3811,116 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>29-Sep 9:31</t>
+          <t>29-Sep 9:33</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMEL@123.05 (6.08%)</t>
+          <t>Anand Seamless BSE SMEL@72.10 (0.14%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹6.5 (5.60%) 4 ↓ / 6.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>17.72x</t>
+          <t>1.47x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹45.24 Cr</t>
+          <t>₹25.52 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 6.5</t>
+          <t>29-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>28-Sep 9:37</t>
+          <t>29-Sep 9:31</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMEL@38.00 (2.7%)</t>
+          <t>FX Multitech BSE SMEL@123.05 (6.08%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6.5 (5.60%) 4 ↓ / 6.50 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.79x</t>
+          <t>17.72x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹22.20 Cr</t>
+          <t>₹45.24 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3938,7 +3930,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3948,12 +3940,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 0</t>
+          <t>28-Sep GMP: 6.5</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>28-Sep 9:30</t>
+          <t>28-Sep 9:37</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3965,47 +3957,47 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEL@201.40 (90%)</t>
+          <t>Vivekanand Cotspin BSE SMEL@38.00 (2.7%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>₹86 (81.13%) 45 ↓ / 86 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>833.56x</t>
+          <t>1.79x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹22.20 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>21-Sep GMP: 55</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 55</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4015,12 +4007,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 86</t>
+          <t>28-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>28-Sep 9:37</t>
+          <t>28-Sep 9:30</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HD Fire Protect IPOU</t>
+          <t>Jio Platforms IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
+          <t>₹177 (-%) 148 ↓ / 177 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -519,36 +519,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>13-Oct</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15-Oct</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>16-Oct</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>21-Oct</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6-Oct 14:30</t>
+          <t>7-Oct 15:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -560,12 +548,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jio Platforms IPOU</t>
+          <t>HD Fire Protect IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹152 (-%) 148 ↓ / 156 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -580,22 +568,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>₹712.31 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15-Oct</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16-Oct</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>21-Oct</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6-Oct 15:37</t>
+          <t>7-Oct 15:36</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -607,22 +615,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R.K.Fashion Accessories NSE SMEO</t>
+          <t>R.K.Fashion Accessories NSE SMECT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹7 (8.54%) 7 ↓ / 7 ↑</t>
+          <t>₹1.5 (1.83%) 1.50 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42x</t>
+          <t>2.54x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -647,7 +655,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>7-Oct GMP: 1.5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -662,7 +670,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6-Oct 15:37</t>
+          <t>7-Oct 15:37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -674,22 +682,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TNA Solutions BSE SMECT</t>
+          <t>TNA Solutions BSE SMEC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹5 (7.14%) 5 ↓ / 10 ↑</t>
+          <t>₹3 (4.29%) 3 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.5x</t>
+          <t>55.2x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -714,7 +722,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 5</t>
+          <t>6-Oct GMP: 3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -729,7 +737,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6-Oct 15:37</t>
+          <t>7-Oct 15:37</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -741,47 +749,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Paramount Syntex BSE SMECT</t>
+          <t>Acme India Industries BSE SMEC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹68 (34.69%) 25 ↓ / 68 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.86x</t>
+          <t>124.23x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹81.79 Cr</t>
+          <t>₹121.69 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 0</t>
+          <t>6-Oct GMP: 65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -796,59 +804,59 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6-Oct 15:30</t>
+          <t>7-Oct 15:37</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Acme India Industries BSE SMECT</t>
+          <t>Paramount Syntex BSE SMEC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹50 (25.51%) 25 ↓ / 50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>117.34x</t>
+          <t>1.88x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹121.69 Cr</t>
+          <t>₹81.79 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 30</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 50</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -863,24 +871,24 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6-Oct 15:37</t>
+          <t>7-Oct 15:37</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nityas Gems &amp; Jewellery IPOC</t>
+          <t>Vishal Nirmiti IPOCAllotted</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
+          <t>₹2 (0.91%) 2 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -890,32 +898,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.26x</t>
+          <t>1.79x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹108.35 Cr</t>
+          <t>₹178.00 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 5</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 1</t>
+          <t>5-Oct GMP: 2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -930,59 +938,59 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6-Oct 15:37</t>
+          <t>7-Oct 15:37</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEC</t>
+          <t>Eventions NSE SMEC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹50 (58.82%) 13 ↓ / 50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>294.22x</t>
+          <t>2.39x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹38.12 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 16</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 42</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -997,19 +1005,19 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6-Oct 15:37</t>
+          <t>7-Oct 15:30</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMEC</t>
+          <t>SJP Ultrasonic BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1024,22 +1032,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.06x</t>
+          <t>1.82x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹23.45 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1064,7 +1072,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>6-Oct 15:37</t>
+          <t>7-Oct 15:35</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1076,12 +1084,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Vishal Nirmiti IPOC</t>
+          <t>Sollfege Smart Electronics BSE SMEC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹2 (0.91%) 2 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1091,32 +1099,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.79x</t>
+          <t>2.14x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹178.00 Cr</t>
+          <t>₹21.78 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 2</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1131,7 +1139,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6-Oct 15:37</t>
+          <t>7-Oct 15:35</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1143,7 +1151,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SJP Ultrasonic BSE SMEC</t>
+          <t>Omara Ventures India BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1158,22 +1166,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.82x</t>
+          <t>1.06x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹23.45 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1198,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6-Oct 15:30</t>
+          <t>7-Oct 15:30</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1210,12 +1218,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Eventions NSE SMEC</t>
+          <t>Nityas Gems &amp; Jewellery IPOCAllotted</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1225,32 +1233,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.39x</t>
+          <t>2.26x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹38.12 Cr</t>
+          <t>₹108.35 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1265,7 +1273,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>6-Oct 15:36</t>
+          <t>7-Oct 15:37</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1332,7 +1340,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6-Oct 15:30</t>
+          <t>7-Oct 15:33</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1344,7 +1352,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sollfege Smart Electronics BSE SMEC</t>
+          <t>Shree TNB Polymers BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1359,17 +1367,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.14x</t>
+          <t>1.98x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹21.78 Cr</t>
+          <t>₹31.80 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1379,7 +1387,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1399,59 +1407,59 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>6-Oct 15:29</t>
+          <t>7-Oct 15:28</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Shree TNB Polymers BSE SMEC</t>
+          <t>EverestIMS Technologies BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹62.5 (73.53%) 13 ↓ / 62.50 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.98x</t>
+          <t>294.22x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹31.80 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 42</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1466,7 +1474,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>6-Oct 15:29</t>
+          <t>7-Oct 15:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1545,12 +1553,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMECAllotted</t>
+          <t>Black Opal Consultants BSE SMEL@200.00 (1.52%)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 100 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1560,32 +1568,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.54x</t>
+          <t>73.8x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹20.18 Cr</t>
+          <t>₹55.08 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 38</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 66</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1595,64 +1603,64 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>7-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>6-Oct 15:28</t>
+          <t>7-Oct 9:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMECAllotted</t>
+          <t>Vans Electroengineerings BSE SMEL@224.20 (90%)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹60 (30.46%) 38 ↓ / 100 ↑</t>
+          <t>₹103 (87.29%) 45 ↓ / 103 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>73.8x</t>
+          <t>628.73x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹55.08 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 38</t>
+          <t>29-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 66</t>
+          <t>1-Oct GMP: 70</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1662,12 +1670,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>7-Oct GMP: 103</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>6-Oct 15:37</t>
+          <t>7-Oct 9:37</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1679,47 +1687,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMECAllotted</t>
+          <t>Papadmalji Agro Foods NSE SMEL@72.30 (0.42%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹103 (87.29%) 45 ↓ / 103 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>628.73x</t>
+          <t>2.54x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹20.18 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 90</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 70</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1729,24 +1737,24 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>7-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6-Oct 15:37</t>
+          <t>7-Oct 9:35</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMECAllotted</t>
+          <t>Green Asia Impex NSE SMEL@89.00 (0%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1796,12 +1804,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>7-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>6-Oct 15:28</t>
+          <t>7-Oct 9:31</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1813,47 +1821,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SRIT India IPOL@148.00 (13.85%)</t>
+          <t>Shah Investor's Home IPOL@171.00 (2.4%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹59 (45.38%) 12 ↓ / 62 ↑</t>
+          <t>₹17 (10.18%) 9 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>125.16x</t>
+          <t>38.12x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹218.40 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 33</t>
+          <t>28-Sep GMP: 14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 48</t>
+          <t>30-Sep GMP: 12.5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1863,7 +1871,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 59</t>
+          <t>6-Oct GMP: 17</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1880,47 +1888,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOL@171.00 (2.4%)</t>
+          <t>Pind Hospitality BSE SMEL@79.20 (-20%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹17 (10.18%) 9 ↓ / 17 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>38.12x</t>
+          <t>2.71x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 14</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 12.5</t>
+          <t>30-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1930,7 +1938,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 17</t>
+          <t>6-Oct GMP: 1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1940,54 +1948,54 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMEL@62.00 (0%)</t>
+          <t>Acme Universal Safezone 9 BSE SMEL@101.00 (42.25%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹1.5 (2.42%) 1 ↓ / 10 ↑</t>
+          <t>₹16 (22.54%) 10 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.2x</t>
+          <t>23.41x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹14.01 Cr</t>
+          <t>₹35.93 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 6</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 1</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1997,7 +2005,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 1.5</t>
+          <t>6-Oct GMP: 16</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2007,19 +2015,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEL@79.20 (-20%)</t>
+          <t>Shivchem Agro BSE SMEL@62.00 (0%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
+          <t>₹1.5 (2.42%) 1 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2029,27 +2037,27 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.71x</t>
+          <t>2.2x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 6</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2064,7 +2072,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 1</t>
+          <t>6-Oct GMP: 1.5</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2081,12 +2089,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMEL@101.00 (42.25%)</t>
+          <t>SRIT India IPOL@148.00 (13.85%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹16 (22.54%) 10 ↓ / 16 ↑</t>
+          <t>₹59 (45.38%) 12 ↓ / 62 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2096,32 +2104,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>23.41x</t>
+          <t>125.16x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹35.93 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 33</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>30-Sep GMP: 48</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2131,7 +2139,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 16</t>
+          <t>6-Oct GMP: 59</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2148,32 +2156,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
+          <t>Himalayan Solar NSE SMEL@85 (-17.48%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4.95x</t>
+          <t>1.19x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2198,12 +2206,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 11</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>5-Oct 9:37</t>
+          <t>5-Oct 9:35</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2215,12 +2223,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Acevector IPOL@28.32 (-11.5%)</t>
+          <t>Runwal Enterprises IPOL@305 (0%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2230,32 +2238,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.07x</t>
+          <t>2.64x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹420.00 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 2</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 1.1</t>
+          <t>29-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2282,47 +2290,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Orient Cables IPOL@450 (65.44%)</t>
+          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹110 (40.44%) 34 ↓ / 123 ↑</t>
+          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>97.28x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 80</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 85</t>
+          <t>29-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2332,7 +2340,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 110</t>
+          <t>5-Oct GMP: 0.5</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2342,44 +2350,44 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOL@305 (0%)</t>
+          <t>Bench Mark Infotech Services NSE SMEL@110 (0%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
+          <t>₹15 (13.64%) 12 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.64x</t>
+          <t>103.12x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2389,7 +2397,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 2</t>
+          <t>29-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2399,7 +2407,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct GMP: 15</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2416,47 +2424,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEL@85 (-17.48%)</t>
+          <t>German Green Steel IPOL@142 (2.16%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹9.5 (6.83%) 9.50 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.19x</t>
+          <t>30.42x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹303.90 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 26</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 13</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2466,12 +2474,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct GMP: 9.5</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>5-Oct 9:35</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2483,47 +2491,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>German Green Steel IPOL@142 (2.16%)</t>
+          <t>Orient Cables IPOL@450 (65.44%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹9.5 (6.83%) 9.50 ↓ / 29 ↑</t>
+          <t>₹110 (40.44%) 34 ↓ / 123 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>30.42x</t>
+          <t>97.28x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹303.90 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 26</t>
+          <t>25-Sep GMP: 80</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 13</t>
+          <t>29-Sep GMP: 85</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2533,7 +2541,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 9.5</t>
+          <t>5-Oct GMP: 110</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2617,47 +2625,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEL@110 (0%)</t>
+          <t>Acevector IPOL@28.32 (-11.5%)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹15 (13.64%) 12 ↓ / 29 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>103.12x</t>
+          <t>5.07x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹420.00 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>25-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 28</t>
+          <t>29-Sep GMP: 1.1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2667,7 +2675,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 15</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2684,47 +2692,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
+          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
+          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>4.95x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 3</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0.5</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2734,7 +2742,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0.5</t>
+          <t>5-Oct GMP: 11</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2744,54 +2752,54 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A-One Steels IPOL@455.00 (12.35%)</t>
+          <t>Moneyview IPOL@55.00 (61.76%)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
+          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>12.23x</t>
+          <t>101.87x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 49</t>
+          <t>24-Sep GMP: 15.5</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 28</t>
+          <t>28-Sep GMP: 12.75</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2801,7 +2809,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 46</t>
+          <t>1-Oct GMP: 14.5</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2818,47 +2826,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEL@100.05 (-0.94%)</t>
+          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2.77x</t>
+          <t>271.94x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 38</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2868,64 +2876,64 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 0</t>
+          <t>1-Oct GMP: 42</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1-Oct 9:33</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
+          <t>A-One Steels IPOL@455.00 (12.35%)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
+          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>271.94x</t>
+          <t>12.23x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>24-Sep GMP: 49</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 38</t>
+          <t>28-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2935,7 +2943,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 42</t>
+          <t>1-Oct GMP: 46</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2952,47 +2960,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Moneyview IPOL@55.00 (61.76%)</t>
+          <t>Peshwa Wheat BSE SMEL@100.05 (-0.94%)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>101.87x</t>
+          <t>2.77x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 15.5</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 12.75</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3002,29 +3010,29 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 14.5</t>
+          <t>1-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1-Oct 9:37</t>
+          <t>1-Oct 9:33</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
+          <t>ArMee Infotech IPOL@375.00 (0%)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3034,32 +3042,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3.11x</t>
+          <t>2.62x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 51</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 8</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3069,12 +3077,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 6</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>30-Sep 9:32</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3086,7 +3094,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEL@78.10 (0.13%)</t>
+          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,22 +3109,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>5.08x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3141,7 +3149,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>30-Sep 9:31</t>
+          <t>30-Sep 9:34</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3153,7 +3161,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
+          <t>S.K.Offset BSE SMEL@126.00 (0.8%)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3168,22 +3176,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.92x</t>
+          <t>1.18x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3208,7 +3216,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>30-Sep 9:28</t>
+          <t>30-Sep 9:32</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3220,47 +3228,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
+          <t>Core Integra Consulting NSE SMEL@78.10 (0.13%)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>176.85x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 34</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 47</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3270,24 +3278,24 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 55</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:31</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
+          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3302,22 +3310,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5.08x</t>
+          <t>3.11x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3342,12 +3350,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>30-Sep 9:34</t>
+          <t>30-Sep 9:32</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3421,12 +3429,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEL@126.00 (0.8%)</t>
+          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3436,32 +3444,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.18x</t>
+          <t>1.89x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3471,12 +3479,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 6.5</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>30-Sep 9:32</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3488,47 +3496,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
+          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
+          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.89x</t>
+          <t>176.85x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4.5</t>
+          <t>23-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4</t>
+          <t>25-Sep GMP: 47</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3538,7 +3546,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6.5</t>
+          <t>30-Sep GMP: 55</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3555,12 +3563,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOL@375.00 (0%)</t>
+          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3570,32 +3578,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.62x</t>
+          <t>3.92x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 51</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 8</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3605,12 +3613,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:28</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹177 (-%) 148 ↓ / 177 ↑</t>
+          <t>₹159 (-%) 148 ↓ / 182 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -536,7 +536,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7-Oct 15:37</t>
+          <t>8-Oct 16:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HD Fire Protect IPOU</t>
+          <t>Vaibhav Vyapaar NSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -568,17 +568,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹712.31 Cr</t>
+          <t>₹40.54 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>7-Oct 15:36</t>
+          <t>8-Oct 16:01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -615,81 +615,77 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R.K.Fashion Accessories NSE SMECT</t>
+          <t>HD Fire Protect IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹1.5 (1.83%) 1.50 ↓ / 15 ↑</t>
+          <t>₹75 (27.68%) 75 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.54x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹34.99 Cr</t>
+          <t>₹712.31 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 7</t>
+          <t>13-Oct</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 1.5</t>
+          <t>15-Oct</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>16-Oct</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12-Oct</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>7-Oct 15:37</t>
+          <t>8-Oct 16:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TNA Solutions BSE SMEC</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>₹3 (4.29%) 3 ↓ / 10 ↑</t>
-        </is>
-      </c>
+          <t>Ravita Engineering Services NSE SMEU</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -697,49 +693,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>55.2x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹37.86 Cr</t>
+          <t>₹116.05 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 7</t>
+          <t>13-Oct</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 3</t>
+          <t>15-Oct</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>16-Oct</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>9-Oct</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>7-Oct 15:37</t>
-        </is>
-      </c>
+          <t>21-Oct</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>✅</t>
@@ -749,114 +741,114 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Acme India Industries BSE SMEC</t>
+          <t>R.K.Fashion Accessories NSE SMEC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹68 (34.69%) 25 ↓ / 68 ↑</t>
+          <t>₹1.5 (1.83%) 1.50 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>124.23x</t>
+          <t>2.7x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹121.69 Cr</t>
+          <t>₹34.99 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 30</t>
+          <t>5-Oct GMP: 7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 65</t>
+          <t>7-Oct GMP: 1.5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>9-Oct</t>
+          <t>12-Oct</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>7-Oct 15:37</t>
+          <t>8-Oct 16:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Paramount Syntex BSE SMEC</t>
+          <t>Acme India Industries BSE SMEC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹35 (17.86%) 25 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.88x</t>
+          <t>124.23x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹81.79 Cr</t>
+          <t>₹121.69 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>6-Oct GMP: 65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -871,24 +863,24 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>7-Oct 15:37</t>
+          <t>8-Oct 16:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Vishal Nirmiti IPOCAllotted</t>
+          <t>Paramount Syntex BSE SMEC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹2 (0.91%) 2 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -898,47 +890,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.79x</t>
+          <t>1.88x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹178.00 Cr</t>
+          <t>₹81.79 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 2</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>9-Oct</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>7-Oct 15:37</t>
+          <t>8-Oct 15:53</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -950,12 +942,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Eventions NSE SMEC</t>
+          <t>TNA Solutions BSE SMECAllotted</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -965,59 +957,59 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.39x</t>
+          <t>55.2x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹38.12 Cr</t>
+          <t>₹37.86 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct GMP: 3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>9-Oct</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>7-Oct 15:30</t>
+          <t>8-Oct 16:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SJP Ultrasonic BSE SMECAllotted</t>
+          <t>SJP Ultrasonic BSE SMEL@74.20 (10.75%)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1067,12 +1059,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7-Oct 15:35</t>
+          <t>8-Oct 9:36</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1084,7 +1076,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sollfege Smart Electronics BSE SMEC</t>
+          <t>Omara Ventures India BSE SMEL@319.00 (2.57%)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1099,22 +1091,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.14x</t>
+          <t>1.06x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹21.78 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1134,12 +1126,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>7-Oct 15:35</t>
+          <t>8-Oct 9:28</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1151,12 +1143,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMECAllotted</t>
+          <t>Vishal Nirmiti IPOL@215.00 (-2.27%)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹2 (0.91%) 2 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1166,32 +1158,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.06x</t>
+          <t>1.79x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹178.00 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1201,12 +1193,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>8-Oct GMP: 2</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7-Oct 15:30</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1218,12 +1210,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nityas Gems &amp; Jewellery IPOCAllotted</t>
+          <t>Eventions NSE SMEL@111.00 (-5.93%)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1233,32 +1225,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.26x</t>
+          <t>2.39x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹108.35 Cr</t>
+          <t>₹38.12 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 5</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 1</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1268,29 +1260,29 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7-Oct 15:37</t>
+          <t>8-Oct 9:35</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dove Soft BSE SMEC</t>
+          <t>Nityas Gems &amp; Jewellery IPOL@80.00 (6.67%)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1300,32 +1292,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.38x</t>
+          <t>2.26x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹73.26 Cr</t>
+          <t>₹108.35 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1335,12 +1327,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>8-Oct GMP: 1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>7-Oct 15:33</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1352,7 +1344,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shree TNB Polymers BSE SMECAllotted</t>
+          <t>Dove Soft BSE SMEL@110.30 (-0.63%)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1367,27 +1359,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.98x</t>
+          <t>1.38x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹31.80 Cr</t>
+          <t>₹73.26 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1402,29 +1394,29 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>7-Oct 15:28</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMECAllotted</t>
+          <t>EverestIMS Technologies BSE SMEL@126.00 (48.24%)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹62.5 (73.53%) 13 ↓ / 62.50 ↑</t>
+          <t>₹50 (58.82%) 13 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,12 +1461,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>8-Oct GMP: 50</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7-Oct 15:37</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1553,129 +1545,129 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMEL@200.00 (1.52%)</t>
+          <t>Sollfege Smart Electronics BSE SMEL@104.40 (89.82%)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 100 ↑</t>
+          <t>₹10 (18.18%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>73.8x</t>
+          <t>2.14x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹55.08 Cr</t>
+          <t>₹21.78 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 38</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 66</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 0</t>
+          <t>8-Oct GMP: 10</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7-Oct 9:37</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEL@224.20 (90%)</t>
+          <t>Shree TNB Polymers BSE SMEL@60.00 (13.21%)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹103 (87.29%) 45 ↓ / 103 ↑</t>
+          <t>₹4 (7.55%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>628.73x</t>
+          <t>1.98x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹31.80 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 90</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 70</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 103</t>
+          <t>8-Oct GMP: 4</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7-Oct 9:37</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1754,47 +1746,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEL@89.00 (0%)</t>
+          <t>Vans Electroengineerings BSE SMEL@224.20 (90%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹103 (87.29%) 45 ↓ / 103 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.04x</t>
+          <t>628.73x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹59.34 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>29-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 70</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1804,79 +1796,79 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 0</t>
+          <t>7-Oct GMP: 103</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>7-Oct 9:31</t>
+          <t>7-Oct 9:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOL@171.00 (2.4%)</t>
+          <t>Black Opal Consultants BSE SMEL@200.00 (1.52%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹17 (10.18%) 9 ↓ / 17 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 100 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>38.12x</t>
+          <t>73.8x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹55.08 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 14</t>
+          <t>29-Sep GMP: 38</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 12.5</t>
+          <t>1-Oct GMP: 66</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 17</t>
+          <t>7-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>6-Oct 9:37</t>
+          <t>7-Oct 9:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1888,12 +1880,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEL@79.20 (-20%)</t>
+          <t>Green Asia Impex NSE SMEL@89.00 (0%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1903,47 +1895,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.71x</t>
+          <t>1.04x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹59.34 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 1</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 1</t>
+          <t>7-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>6-Oct 9:37</t>
+          <t>7-Oct 9:31</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1955,37 +1947,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMEL@101.00 (42.25%)</t>
+          <t>Pind Hospitality BSE SMEL@79.20 (-20%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹16 (22.54%) 10 ↓ / 16 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>23.41x</t>
+          <t>2.71x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹35.93 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1995,7 +1987,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>30-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2005,7 +1997,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 16</t>
+          <t>6-Oct GMP: 1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2015,54 +2007,54 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMEL@62.00 (0%)</t>
+          <t>SRIT India IPOL@148.00 (13.85%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹1.5 (2.42%) 1 ↓ / 10 ↑</t>
+          <t>₹59 (45.38%) 12 ↓ / 62 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.2x</t>
+          <t>125.16x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹14.01 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 6</t>
+          <t>28-Sep GMP: 33</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 1</t>
+          <t>30-Sep GMP: 48</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2072,7 +2064,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 1.5</t>
+          <t>6-Oct GMP: 59</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2082,54 +2074,54 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SRIT India IPOL@148.00 (13.85%)</t>
+          <t>Shivchem Agro BSE SMEL@62.00 (0%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹59 (45.38%) 12 ↓ / 62 ↑</t>
+          <t>₹1.5 (2.42%) 1 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>125.16x</t>
+          <t>2.2x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹218.40 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 33</t>
+          <t>28-Sep GMP: 6</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 48</t>
+          <t>30-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2139,7 +2131,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 59</t>
+          <t>6-Oct GMP: 1.5</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2149,69 +2141,69 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEL@85 (-17.48%)</t>
+          <t>Shah Investor's Home IPOL@171.00 (2.4%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹17 (10.18%) 9 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.19x</t>
+          <t>38.12x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep GMP: 14</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep GMP: 12.5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>6-Oct GMP: 17</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>5-Oct 9:35</t>
+          <t>6-Oct 9:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2223,62 +2215,62 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOL@305 (0%)</t>
+          <t>Acme Universal Safezone 9 BSE SMEL@101.00 (42.25%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
+          <t>₹16 (22.54%) 10 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.64x</t>
+          <t>23.41x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹35.93 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 2</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>6-Oct GMP: 16</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>5-Oct 9:37</t>
+          <t>6-Oct 9:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2290,12 +2282,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
+          <t>Runwal Enterprises IPOL@305 (0%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2305,32 +2297,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>2.64x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 3</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0.5</t>
+          <t>29-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2340,7 +2332,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0.5</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2350,39 +2342,39 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEL@110 (0%)</t>
+          <t>Himalayan Solar NSE SMEL@85 (-17.48%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹15 (13.64%) 12 ↓ / 29 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>103.12x</t>
+          <t>1.19x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2392,12 +2384,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 28</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2407,12 +2399,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 15</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>5-Oct 9:37</t>
+          <t>5-Oct 9:35</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2692,32 +2684,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
+          <t>Bench Mark Infotech Services NSE SMEL@110 (0%)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
+          <t>₹15 (13.64%) 12 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.95x</t>
+          <t>103.12x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2727,12 +2719,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2742,7 +2734,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 11</t>
+          <t>5-Oct GMP: 15</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2759,62 +2751,62 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Moneyview IPOL@55.00 (61.76%)</t>
+          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
+          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>101.87x</t>
+          <t>4.95x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 15.5</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 12.75</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 14.5</t>
+          <t>5-Oct GMP: 11</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1-Oct 9:37</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2826,114 +2818,114 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
+          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
+          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>271.94x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 38</t>
+          <t>29-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 42</t>
+          <t>5-Oct GMP: 0.5</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1-Oct 9:37</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A-One Steels IPOL@455.00 (12.35%)</t>
+          <t>Peshwa Wheat BSE SMEL@100.05 (-0.94%)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12.23x</t>
+          <t>2.77x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 49</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 28</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2943,64 +2935,64 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 46</t>
+          <t>1-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1-Oct 9:37</t>
+          <t>1-Oct 9:33</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEL@100.05 (-0.94%)</t>
+          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.77x</t>
+          <t>271.94x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 38</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3010,79 +3002,79 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 0</t>
+          <t>1-Oct GMP: 42</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1-Oct 9:33</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOL@375.00 (0%)</t>
+          <t>Moneyview IPOL@55.00 (61.76%)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
+          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.62x</t>
+          <t>101.87x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 51</t>
+          <t>24-Sep GMP: 15.5</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 8</t>
+          <t>28-Sep GMP: 12.75</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6</t>
+          <t>1-Oct GMP: 14.5</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3094,74 +3086,74 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
+          <t>A-One Steels IPOL@455.00 (12.35%)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5.08x</t>
+          <t>12.23x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep GMP: 49</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>1-Oct GMP: 46</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>30-Sep 9:34</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEL@126.00 (0.8%)</t>
+          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3176,22 +3168,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.18x</t>
+          <t>3.11x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3228,12 +3220,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEL@78.10 (0.13%)</t>
+          <t>ArMee Infotech IPOL@375.00 (0%)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3243,32 +3235,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>2.62x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 51</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 8</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3278,24 +3270,24 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 6</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>30-Sep 9:31</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
+          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3310,22 +3302,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3.11x</t>
+          <t>3.92x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3350,7 +3342,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>30-Sep 9:32</t>
+          <t>30-Sep 9:28</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3362,12 +3354,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOL@200.00 (8.11%)</t>
+          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3377,32 +3369,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7.91x</t>
+          <t>5.08x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹160.88 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 9.5</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4.5</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3412,64 +3404,64 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 7</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:34</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
+          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
+          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.89x</t>
+          <t>176.85x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4.5</t>
+          <t>23-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4</t>
+          <t>25-Sep GMP: 47</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3479,7 +3471,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6.5</t>
+          <t>30-Sep GMP: 55</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3496,47 +3488,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
+          <t>Core Integra Consulting NSE SMEL@78.10 (0.13%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>176.85x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 34</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 47</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3546,29 +3538,29 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 55</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:31</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
+          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3578,32 +3570,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.92x</t>
+          <t>1.89x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3613,12 +3605,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 6.5</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>30-Sep 9:28</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3697,12 +3689,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOL@155.00 (4.73%)</t>
+          <t>Swastika Infra IPOL@200.00 (8.11%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹1 (0.68%) 0.50 ↓ / 15 ↑</t>
+          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3712,47 +3704,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>7.91x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹708.02 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 3</t>
+          <t>23-Sep GMP: 9.5</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0.5</t>
+          <t>25-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 1</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>29-Sep 9:37</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3764,7 +3756,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEL@118.00 (11.32%)</t>
+          <t>S.K.Offset BSE SMEL@126.00 (0.8%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3779,47 +3771,47 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2.33x</t>
+          <t>1.18x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>29-Sep 9:33</t>
+          <t>30-Sep 9:32</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3831,12 +3823,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMEL@72.10 (0.14%)</t>
+          <t>Varmora Granito IPOL@155.00 (4.73%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (0.68%) 0.50 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3846,32 +3838,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.47x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹25.52 Cr</t>
+          <t>₹708.02 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>22-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>24-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3881,91 +3873,91 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0</t>
+          <t>29-Sep GMP: 1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>29-Sep 9:31</t>
+          <t>29-Sep 9:37</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FX Multitech BSE SMEL@123.05 (6.08%)</t>
+          <t>Anand Seamless BSE SMEL@72.10 (0.14%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹6.5 (5.60%) 4 ↓ / 6.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>17.72x</t>
+          <t>1.47x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹45.24 Cr</t>
+          <t>₹25.52 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 6.5</t>
+          <t>29-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>28-Sep 9:37</t>
+          <t>29-Sep 9:31</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Vivekanand Cotspin BSE SMEL@38.00 (2.7%)</t>
+          <t>Himalaya Nutravedics BSE SMEL@118.00 (11.32%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3980,47 +3972,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.79x</t>
+          <t>2.33x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹22.20 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>22-Sep</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 0</t>
+          <t>29-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>28-Sep 9:30</t>
+          <t>29-Sep 9:33</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹159 (-%) 148 ↓ / 182 ↑</t>
+          <t>₹173 (-%) 148 ↓ / 182 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -536,7 +536,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8-Oct 16:02</t>
+          <t>9-Oct 15:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -548,17 +548,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar NSE SMEU</t>
+          <t>Fusion CX IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹55 (19.03%) 55 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -568,42 +568,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>289</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹40.54 Cr</t>
+          <t>₹702.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13-Oct</t>
+          <t>14-Oct</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>16-Oct</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16-Oct</t>
+          <t>19-Oct</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>21-Oct</t>
+          <t>22-Oct</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8-Oct 16:01</t>
+          <t>9-Oct 15:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹75 (27.68%) 75 ↓ / 80 ↑</t>
+          <t>₹73 (26.94%) 63 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8-Oct 16:02</t>
+          <t>9-Oct 15:37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -685,7 +685,11 @@
           <t>Ravita Engineering Services NSE SMEU</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>🔥</t>
@@ -731,7 +735,11 @@
           <t>21-Oct</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>9-Oct 15:31</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>✅</t>
@@ -741,12 +749,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R.K.Fashion Accessories NSE SMEC</t>
+          <t>Vaibhav Vyapaar NSE SMEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹1.5 (1.83%) 1.50 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -756,126 +764,126 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.7x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹34.99 Cr</t>
+          <t>₹42.10 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 7</t>
+          <t>13-Oct</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 1.5</t>
+          <t>15-Oct</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>16-Oct</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>12-Oct</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8-Oct 16:02</t>
+          <t>9-Oct 15:37</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Acme India Industries BSE SMEC</t>
+          <t>R.K.Fashion Accessories NSE SMEC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹35 (17.86%) 25 ↓ / 65 ↑</t>
+          <t>₹1.5 (1.83%) 1.50 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>124.23x</t>
+          <t>2.7x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹121.69 Cr</t>
+          <t>₹34.99 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 30</t>
+          <t>5-Oct GMP: 7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 65</t>
+          <t>7-Oct GMP: 1.5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>9-Oct</t>
+          <t>12-Oct</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8-Oct 16:02</t>
+          <t>9-Oct 15:37</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Paramount Syntex BSE SMEC</t>
+          <t>Paramount Syntex BSE SMEL@115.00 (-9.45%)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -925,12 +933,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>9-Oct</t>
+          <t>9-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8-Oct 15:53</t>
+          <t>9-Oct 9:31</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -942,47 +950,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TNA Solutions BSE SMECAllotted</t>
+          <t>Acme India Industries BSE SMEL@221.00 (12.76%)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
+          <t>₹43 (21.94%) 25 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>55.2x</t>
+          <t>124.23x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹37.86 Cr</t>
+          <t>₹121.69 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 7</t>
+          <t>30-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 3</t>
+          <t>6-Oct GMP: 65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -992,12 +1000,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>9-Oct</t>
+          <t>9-Oct GMP: 43</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8-Oct 16:02</t>
+          <t>9-Oct 9:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1009,12 +1017,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SJP Ultrasonic BSE SMEL@74.20 (10.75%)</t>
+          <t>TNA Solutions BSE SMEL@56.00 (-20%)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1024,17 +1032,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.82x</t>
+          <t>55.2x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹23.45 Cr</t>
+          <t>₹37.86 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1044,44 +1052,44 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct GMP: 3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 0</t>
+          <t>9-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8-Oct 9:36</t>
+          <t>9-Oct 9:37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMEL@319.00 (2.57%)</t>
+          <t>Nityas Gems &amp; Jewellery IPOL@80.00 (6.67%)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1091,32 +1099,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.06x</t>
+          <t>2.26x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹108.35 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1126,12 +1134,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 0</t>
+          <t>8-Oct GMP: 1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>8-Oct 9:28</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1210,47 +1218,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Eventions NSE SMEL@111.00 (-5.93%)</t>
+          <t>EverestIMS Technologies BSE SMEL@126.00 (48.24%)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹50 (58.82%) 13 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.39x</t>
+          <t>294.22x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹38.12 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>29-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 42</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1260,29 +1268,29 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 0</t>
+          <t>8-Oct GMP: 50</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8-Oct 9:35</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nityas Gems &amp; Jewellery IPOL@80.00 (6.67%)</t>
+          <t>SJP Ultrasonic BSE SMEL@74.20 (10.75%)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1292,32 +1300,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.26x</t>
+          <t>1.82x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹108.35 Cr</t>
+          <t>₹23.45 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 5</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 1</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1327,12 +1335,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 1</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8-Oct 9:37</t>
+          <t>8-Oct 9:36</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1344,7 +1352,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dove Soft BSE SMEL@110.30 (-0.63%)</t>
+          <t>Omara Ventures India BSE SMEL@319.00 (2.57%)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1359,22 +1367,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.38x</t>
+          <t>1.06x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹73.26 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1399,7 +1407,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8-Oct 9:37</t>
+          <t>8-Oct 9:28</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1411,47 +1419,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEL@126.00 (48.24%)</t>
+          <t>Shree TNB Polymers BSE SMEL@60.00 (13.21%)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹50 (58.82%) 13 ↓ / 55 ↑</t>
+          <t>₹4 (7.55%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>294.22x</t>
+          <t>1.98x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹31.80 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 16</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 42</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1461,7 +1469,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 50</t>
+          <t>8-Oct GMP: 4</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1545,37 +1553,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sollfege Smart Electronics BSE SMEL@104.40 (89.82%)</t>
+          <t>Dove Soft BSE SMEL@110.30 (-0.63%)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹10 (18.18%) 10 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.14x</t>
+          <t>1.38x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹21.78 Cr</t>
+          <t>₹73.26 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1595,7 +1603,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 10</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1612,42 +1620,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shree TNB Polymers BSE SMEL@60.00 (13.21%)</t>
+          <t>Eventions NSE SMEL@111.00 (-5.93%)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹4 (7.55%) 4 ↓ / 4 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.98x</t>
+          <t>2.39x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹31.80 Cr</t>
+          <t>₹38.12 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1662,79 +1670,79 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 4</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8-Oct 9:37</t>
+          <t>8-Oct 9:35</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMEL@72.30 (0.42%)</t>
+          <t>Sollfege Smart Electronics BSE SMEL@104.40 (89.82%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹10 (18.18%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.54x</t>
+          <t>2.14x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹20.18 Cr</t>
+          <t>₹21.78 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 0</t>
+          <t>8-Oct GMP: 10</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>7-Oct 9:35</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1746,47 +1754,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEL@224.20 (90%)</t>
+          <t>Black Opal Consultants BSE SMEL@200.00 (1.52%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹103 (87.29%) 45 ↓ / 103 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 100 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>628.73x</t>
+          <t>73.8x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹55.08 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 90</t>
+          <t>29-Sep GMP: 38</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 70</t>
+          <t>1-Oct GMP: 66</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1796,7 +1804,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 103</t>
+          <t>7-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1813,47 +1821,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMEL@200.00 (1.52%)</t>
+          <t>Vans Electroengineerings BSE SMEL@224.20 (90%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 100 ↑</t>
+          <t>₹103 (87.29%) 45 ↓ / 103 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>73.8x</t>
+          <t>628.73x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹55.08 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 38</t>
+          <t>29-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 66</t>
+          <t>1-Oct GMP: 70</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1863,7 +1871,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 0</t>
+          <t>7-Oct GMP: 103</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1880,7 +1888,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEL@89.00 (0%)</t>
+          <t>Papadmalji Agro Foods NSE SMEL@72.30 (0.42%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1895,17 +1903,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.04x</t>
+          <t>2.54x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹59.34 Cr</t>
+          <t>₹20.18 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1915,7 +1923,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1935,7 +1943,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>7-Oct 9:31</t>
+          <t>7-Oct 9:35</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1947,12 +1955,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEL@79.20 (-20%)</t>
+          <t>Green Asia Impex NSE SMEL@89.00 (0%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1962,47 +1970,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.71x</t>
+          <t>1.04x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹59.34 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 1</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 1</t>
+          <t>7-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>6-Oct 9:37</t>
+          <t>7-Oct 9:31</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2014,47 +2022,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SRIT India IPOL@148.00 (13.85%)</t>
+          <t>Pind Hospitality BSE SMEL@79.20 (-20%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹59 (45.38%) 12 ↓ / 62 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>125.16x</t>
+          <t>2.71x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹218.40 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 33</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 48</t>
+          <t>30-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2064,7 +2072,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 59</t>
+          <t>6-Oct GMP: 1</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2074,7 +2082,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -2148,47 +2156,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOL@171.00 (2.4%)</t>
+          <t>Acme Universal Safezone 9 BSE SMEL@101.00 (42.25%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹17 (10.18%) 9 ↓ / 17 ↑</t>
+          <t>₹16 (22.54%) 10 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>38.12x</t>
+          <t>23.41x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹35.93 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 14</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 12.5</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2198,7 +2206,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 17</t>
+          <t>6-Oct GMP: 16</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2215,47 +2223,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMEL@101.00 (42.25%)</t>
+          <t>Shah Investor's Home IPOL@171.00 (2.4%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹16 (22.54%) 10 ↓ / 16 ↑</t>
+          <t>₹17 (10.18%) 9 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>23.41x</t>
+          <t>38.12x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹35.93 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 14</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>30-Sep GMP: 12.5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2265,7 +2273,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 16</t>
+          <t>6-Oct GMP: 17</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2282,62 +2290,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOL@305 (0%)</t>
+          <t>SRIT India IPOL@148.00 (13.85%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
+          <t>₹59 (45.38%) 12 ↓ / 62 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.64x</t>
+          <t>125.16x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>28-Sep GMP: 33</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 2</t>
+          <t>30-Sep GMP: 48</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>6-Oct GMP: 59</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5-Oct 9:37</t>
+          <t>6-Oct 9:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2349,12 +2357,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEL@85 (-17.48%)</t>
+          <t>Runwal Enterprises IPOL@305 (0%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2364,32 +2372,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.19x</t>
+          <t>2.64x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2404,7 +2412,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>5-Oct 9:35</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2684,47 +2692,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEL@110 (0%)</t>
+          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹15 (13.64%) 12 ↓ / 29 ↑</t>
+          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>103.12x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 28</t>
+          <t>29-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2734,7 +2742,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 15</t>
+          <t>5-Oct GMP: 0.5</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2744,39 +2752,39 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
+          <t>Bench Mark Infotech Services NSE SMEL@110 (0%)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
+          <t>₹15 (13.64%) 12 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4.95x</t>
+          <t>103.12x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2786,12 +2794,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2801,7 +2809,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 11</t>
+          <t>5-Oct GMP: 15</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2818,47 +2826,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
+          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
+          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>4.95x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 3</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0.5</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2868,7 +2876,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0.5</t>
+          <t>5-Oct GMP: 11</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2878,14 +2886,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEL@100.05 (-0.94%)</t>
+          <t>Himalayan Solar NSE SMEL@85 (-17.48%)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2900,17 +2908,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.77x</t>
+          <t>1.19x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2920,79 +2928,79 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 0</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1-Oct 9:33</t>
+          <t>5-Oct 9:35</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
+          <t>Moneyview IPOL@55.00 (61.76%)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
+          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>271.94x</t>
+          <t>101.87x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>24-Sep GMP: 15.5</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 38</t>
+          <t>28-Sep GMP: 12.75</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3002,7 +3010,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 42</t>
+          <t>1-Oct GMP: 14.5</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3019,47 +3027,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Moneyview IPOL@55.00 (61.76%)</t>
+          <t>A-One Steels IPOL@455.00 (12.35%)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
+          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>101.87x</t>
+          <t>12.23x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 15.5</t>
+          <t>24-Sep GMP: 49</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 12.75</t>
+          <t>28-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3069,7 +3077,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 14.5</t>
+          <t>1-Oct GMP: 46</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3086,47 +3094,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A-One Steels IPOL@455.00 (12.35%)</t>
+          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
+          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>12.23x</t>
+          <t>271.94x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 49</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 28</t>
+          <t>28-Sep GMP: 38</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3136,7 +3144,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 46</t>
+          <t>1-Oct GMP: 42</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3153,7 +3161,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
+          <t>Peshwa Wheat BSE SMEL@100.05 (-0.94%)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3168,17 +3176,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.11x</t>
+          <t>2.77x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3188,44 +3196,44 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>1-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>30-Sep 9:32</t>
+          <t>1-Oct 9:33</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOL@375.00 (0%)</t>
+          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
+          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3235,32 +3243,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2.62x</t>
+          <t>1.89x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 51</t>
+          <t>23-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 8</t>
+          <t>25-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3270,7 +3278,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6</t>
+          <t>30-Sep GMP: 6.5</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3354,7 +3362,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
+          <t>S.K.Offset BSE SMEL@126.00 (0.8%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3369,22 +3377,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5.08x</t>
+          <t>1.18x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3409,59 +3417,59 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>30-Sep 9:34</t>
+          <t>30-Sep 9:32</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
+          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>176.85x</t>
+          <t>3.11x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 34</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 47</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3471,12 +3479,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 55</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:32</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3555,47 +3563,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
+          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
+          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.89x</t>
+          <t>176.85x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4.5</t>
+          <t>23-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4</t>
+          <t>25-Sep GMP: 47</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3605,7 +3613,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6.5</t>
+          <t>30-Sep GMP: 55</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3689,12 +3697,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOL@200.00 (8.11%)</t>
+          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3704,32 +3712,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7.91x</t>
+          <t>5.08x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹160.88 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 9.5</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4.5</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3739,29 +3747,29 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 7</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:34</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEL@126.00 (0.8%)</t>
+          <t>ArMee Infotech IPOL@375.00 (0%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3771,32 +3779,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.18x</t>
+          <t>2.62x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 51</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 8</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3806,12 +3814,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 6</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>30-Sep 9:32</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3823,12 +3831,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOL@155.00 (4.73%)</t>
+          <t>Swastika Infra IPOL@200.00 (8.11%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹1 (0.68%) 0.50 ↓ / 15 ↑</t>
+          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3838,47 +3846,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>7.91x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹708.02 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 3</t>
+          <t>23-Sep GMP: 9.5</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0.5</t>
+          <t>25-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 1</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>29-Sep 9:37</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3890,7 +3898,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Anand Seamless BSE SMEL@72.10 (0.14%)</t>
+          <t>Himalaya Nutravedics BSE SMEL@118.00 (11.32%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3905,22 +3913,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.47x</t>
+          <t>2.33x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹25.52 Cr</t>
+          <t>₹26.50 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3945,24 +3953,24 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>29-Sep 9:31</t>
+          <t>29-Sep 9:33</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEL@118.00 (11.32%)</t>
+          <t>Varmora Granito IPOL@155.00 (4.73%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (0.68%) 0.50 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3972,32 +3980,32 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2.33x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹708.02 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>22-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>24-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4007,12 +4015,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0</t>
+          <t>29-Sep GMP: 1</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>29-Sep 9:33</t>
+          <t>29-Sep 9:37</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹173 (-%) 148 ↓ / 182 ↑</t>
+          <t>₹168 (-%) 148 ↓ / 182 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -536,7 +536,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>9-Oct 15:37</t>
+          <t>10-Oct 15:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -548,17 +548,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fusion CX IPOU</t>
+          <t>Bonfiglioli Transmissions IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹55 (19.03%) 55 ↓ / 55 ↑</t>
+          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -566,44 +566,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹702.00 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>14-Oct</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>16-Oct</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>19-Oct</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>22-Oct</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>9-Oct 15:37</t>
+          <t>10-Oct 5:55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -615,17 +591,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HD Fire Protect IPOU</t>
+          <t>Fusion CX IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹73 (26.94%) 63 ↓ / 80 ↑</t>
+          <t>₹55 (19.03%) 55 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -635,42 +611,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>289</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹712.31 Cr</t>
+          <t>₹702.00 Cr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>13-Oct</t>
+          <t>14-Oct</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>16-Oct</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16-Oct</t>
+          <t>19-Oct</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>21-Oct</t>
+          <t>22-Oct</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>9-Oct 15:37</t>
+          <t>10-Oct 15:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -687,12 +663,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹12 (10.71%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -737,7 +713,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>9-Oct 15:31</t>
+          <t>10-Oct 15:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -749,17 +725,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar NSE SMEU</t>
+          <t>HD Fire Protect IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹73 (26.94%) 63 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -769,17 +745,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹42.10 Cr</t>
+          <t>₹712.31 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -804,7 +780,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>9-Oct 15:37</t>
+          <t>10-Oct 15:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -816,12 +792,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R.K.Fashion Accessories NSE SMEC</t>
+          <t>Vaibhav Vyapaar NSE SMEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹1.5 (1.83%) 1.50 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -831,64 +807,64 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.7x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹34.99 Cr</t>
+          <t>₹42.10 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 7</t>
+          <t>13-Oct</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 1.5</t>
+          <t>15-Oct</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>16-Oct</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>12-Oct</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>9-Oct 15:37</t>
+          <t>10-Oct 14:59</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Paramount Syntex BSE SMEL@115.00 (-9.45%)</t>
+          <t>R.K.Fashion Accessories NSE SMEC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1.5 (1.83%) 1.50 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -898,47 +874,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.88x</t>
+          <t>2.7x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹81.79 Cr</t>
+          <t>₹34.99 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct GMP: 7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct GMP: 1.5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>9-Oct GMP: 0</t>
+          <t>12-Oct</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>9-Oct 9:31</t>
+          <t>10-Oct 15:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -950,47 +926,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Acme India Industries BSE SMEL@221.00 (12.76%)</t>
+          <t>TNA Solutions BSE SMEL@56.00 (-20%)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹43 (21.94%) 25 ↓ / 65 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>124.23x</t>
+          <t>55.2x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹121.69 Cr</t>
+          <t>₹37.86 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 30</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 65</t>
+          <t>6-Oct GMP: 3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1000,7 +976,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>9-Oct GMP: 43</t>
+          <t>9-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1017,12 +993,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TNA Solutions BSE SMEL@56.00 (-20%)</t>
+          <t>Paramount Syntex BSE SMEL@115.00 (-9.45%)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1032,32 +1008,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>55.2x</t>
+          <t>1.88x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹37.86 Cr</t>
+          <t>₹81.79 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 7</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 3</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1072,91 +1048,91 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>9-Oct 9:37</t>
+          <t>9-Oct 9:31</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nityas Gems &amp; Jewellery IPOL@80.00 (6.67%)</t>
+          <t>Acme India Industries BSE SMEL@221.00 (12.76%)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
+          <t>₹43 (21.94%) 25 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.26x</t>
+          <t>124.23x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹108.35 Cr</t>
+          <t>₹121.69 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 5</t>
+          <t>30-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 1</t>
+          <t>6-Oct GMP: 65</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 1</t>
+          <t>9-Oct GMP: 43</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>8-Oct 9:37</t>
+          <t>9-Oct 9:37</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vishal Nirmiti IPOL@215.00 (-2.27%)</t>
+          <t>Dove Soft BSE SMEL@110.30 (-0.63%)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹2 (0.91%) 2 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1166,32 +1142,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.79x</t>
+          <t>1.38x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹178.00 Cr</t>
+          <t>₹73.26 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 2</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1201,7 +1177,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 2</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1218,47 +1194,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEL@126.00 (48.24%)</t>
+          <t>SJP Ultrasonic BSE SMEL@74.20 (10.75%)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹50 (58.82%) 13 ↓ / 55 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>294.22x</t>
+          <t>1.82x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹23.45 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 16</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 42</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1268,29 +1244,29 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 50</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8-Oct 9:37</t>
+          <t>8-Oct 9:36</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SJP Ultrasonic BSE SMEL@74.20 (10.75%)</t>
+          <t>Nityas Gems &amp; Jewellery IPOL@80.00 (6.67%)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1300,32 +1276,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.82x</t>
+          <t>2.26x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹23.45 Cr</t>
+          <t>₹108.35 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1335,12 +1311,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 0</t>
+          <t>8-Oct GMP: 1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8-Oct 9:36</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1352,47 +1328,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMEL@319.00 (2.57%)</t>
+          <t>EverestIMS Technologies BSE SMEL@126.00 (48.24%)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹50 (58.82%) 13 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.06x</t>
+          <t>294.22x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>29-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 42</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1402,59 +1378,59 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 0</t>
+          <t>8-Oct GMP: 50</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8-Oct 9:28</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Shree TNB Polymers BSE SMEL@60.00 (13.21%)</t>
+          <t>Eventions NSE SMEL@111.00 (-5.93%)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹4 (7.55%) 4 ↓ / 4 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.98x</t>
+          <t>2.39x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹31.80 Cr</t>
+          <t>₹38.12 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1469,17 +1445,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 4</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8-Oct 9:37</t>
+          <t>8-Oct 9:35</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1553,42 +1529,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dove Soft BSE SMEL@110.30 (-0.63%)</t>
+          <t>Shree TNB Polymers BSE SMEL@60.00 (13.21%)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹4 (7.55%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.38x</t>
+          <t>1.98x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹73.26 Cr</t>
+          <t>₹31.80 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1603,7 +1579,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 0</t>
+          <t>8-Oct GMP: 4</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1613,19 +1589,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Eventions NSE SMEL@111.00 (-5.93%)</t>
+          <t>Vishal Nirmiti IPOL@215.00 (-2.27%)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹2 (0.91%) 2 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1635,32 +1611,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.39x</t>
+          <t>1.79x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹38.12 Cr</t>
+          <t>₹178.00 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1670,12 +1646,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 0</t>
+          <t>8-Oct GMP: 2</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8-Oct 9:35</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1687,37 +1663,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sollfege Smart Electronics BSE SMEL@104.40 (89.82%)</t>
+          <t>Omara Ventures India BSE SMEL@319.00 (2.57%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹10 (18.18%) 10 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.14x</t>
+          <t>1.06x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹21.78 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1737,12 +1713,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 10</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8-Oct 9:37</t>
+          <t>8-Oct 9:28</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1754,114 +1730,114 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMEL@200.00 (1.52%)</t>
+          <t>Sollfege Smart Electronics BSE SMEL@104.40 (89.82%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 100 ↑</t>
+          <t>₹10 (18.18%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>73.8x</t>
+          <t>2.14x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹55.08 Cr</t>
+          <t>₹21.78 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 38</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 66</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 0</t>
+          <t>8-Oct GMP: 10</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>7-Oct 9:37</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEL@224.20 (90%)</t>
+          <t>Green Asia Impex NSE SMEL@89.00 (0%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹103 (87.29%) 45 ↓ / 103 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>628.73x</t>
+          <t>1.04x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹59.34 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 90</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 70</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1871,64 +1847,64 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 103</t>
+          <t>7-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>7-Oct 9:37</t>
+          <t>7-Oct 9:31</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMEL@72.30 (0.42%)</t>
+          <t>Vans Electroengineerings BSE SMEL@224.20 (90%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹103 (87.29%) 45 ↓ / 103 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.54x</t>
+          <t>628.73x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹20.18 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 70</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1938,24 +1914,24 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 0</t>
+          <t>7-Oct GMP: 103</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>7-Oct 9:35</t>
+          <t>7-Oct 9:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEL@89.00 (0%)</t>
+          <t>Papadmalji Agro Foods NSE SMEL@72.30 (0.42%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1970,17 +1946,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.04x</t>
+          <t>2.54x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹59.34 Cr</t>
+          <t>₹20.18 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1990,7 +1966,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2010,7 +1986,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>7-Oct 9:31</t>
+          <t>7-Oct 9:35</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2022,12 +1998,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEL@79.20 (-20%)</t>
+          <t>Black Opal Consultants BSE SMEL@200.00 (1.52%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 100 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2037,99 +2013,99 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.71x</t>
+          <t>73.8x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹55.08 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep GMP: 38</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 1</t>
+          <t>1-Oct GMP: 66</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 1</t>
+          <t>7-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>6-Oct 9:37</t>
+          <t>7-Oct 9:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMEL@62.00 (0%)</t>
+          <t>Acme Universal Safezone 9 BSE SMEL@101.00 (42.25%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹1.5 (2.42%) 1 ↓ / 10 ↑</t>
+          <t>₹16 (22.54%) 10 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.2x</t>
+          <t>23.41x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹14.01 Cr</t>
+          <t>₹35.93 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 6</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 1</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2139,7 +2115,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 1.5</t>
+          <t>6-Oct GMP: 16</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2149,44 +2125,44 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMEL@101.00 (42.25%)</t>
+          <t>Pind Hospitality BSE SMEL@79.20 (-20%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹16 (22.54%) 10 ↓ / 16 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>23.41x</t>
+          <t>2.71x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹35.93 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2196,7 +2172,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>30-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2206,7 +2182,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 16</t>
+          <t>6-Oct GMP: 1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2216,54 +2192,54 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOL@171.00 (2.4%)</t>
+          <t>SRIT India IPOL@148.00 (13.85%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹17 (10.18%) 9 ↓ / 17 ↑</t>
+          <t>₹59 (45.38%) 12 ↓ / 62 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>38.12x</t>
+          <t>125.16x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 14</t>
+          <t>28-Sep GMP: 33</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 12.5</t>
+          <t>30-Sep GMP: 48</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 17</t>
+          <t>6-Oct GMP: 59</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2290,47 +2266,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SRIT India IPOL@148.00 (13.85%)</t>
+          <t>Shah Investor's Home IPOL@171.00 (2.4%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹59 (45.38%) 12 ↓ / 62 ↑</t>
+          <t>₹17 (10.18%) 9 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>125.16x</t>
+          <t>38.12x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹218.40 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 33</t>
+          <t>28-Sep GMP: 14</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 48</t>
+          <t>30-Sep GMP: 12.5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2340,7 +2316,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 59</t>
+          <t>6-Oct GMP: 17</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2357,12 +2333,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOL@305 (0%)</t>
+          <t>Shivchem Agro BSE SMEL@62.00 (0%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
+          <t>₹1.5 (2.42%) 1 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2372,52 +2348,52 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.64x</t>
+          <t>2.2x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>28-Sep GMP: 6</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 2</t>
+          <t>30-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>6-Oct GMP: 1.5</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>5-Oct 9:37</t>
+          <t>6-Oct 9:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -2491,47 +2467,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Orient Cables IPOL@450 (65.44%)</t>
+          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹110 (40.44%) 34 ↓ / 123 ↑</t>
+          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>97.28x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 80</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 85</t>
+          <t>29-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2541,7 +2517,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 110</t>
+          <t>5-Oct GMP: 0.5</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2551,7 +2527,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -2625,47 +2601,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Acevector IPOL@28.32 (-11.5%)</t>
+          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
+          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5.07x</t>
+          <t>4.95x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹420.00 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 2</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 1.1</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2675,7 +2651,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct GMP: 11</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2692,47 +2668,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
+          <t>Orient Cables IPOL@450 (65.44%)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
+          <t>₹110 (40.44%) 34 ↓ / 123 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>97.28x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 3</t>
+          <t>25-Sep GMP: 80</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0.5</t>
+          <t>29-Sep GMP: 85</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2742,7 +2718,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0.5</t>
+          <t>5-Oct GMP: 110</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2752,54 +2728,54 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEL@110 (0%)</t>
+          <t>Acevector IPOL@28.32 (-11.5%)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹15 (13.64%) 12 ↓ / 29 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>103.12x</t>
+          <t>5.07x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹420.00 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>25-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 28</t>
+          <t>29-Sep GMP: 1.1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2809,7 +2785,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 15</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2826,32 +2802,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
+          <t>Himalayan Solar NSE SMEL@85 (-17.48%)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.95x</t>
+          <t>1.19x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2876,12 +2852,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 11</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5-Oct 9:37</t>
+          <t>5-Oct 9:35</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2893,32 +2869,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEL@85 (-17.48%)</t>
+          <t>Bench Mark Infotech Services NSE SMEL@110 (0%)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹15 (13.64%) 12 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.19x</t>
+          <t>103.12x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2928,12 +2904,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2943,12 +2919,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct GMP: 15</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5-Oct 9:35</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2960,62 +2936,62 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Moneyview IPOL@55.00 (61.76%)</t>
+          <t>Runwal Enterprises IPOL@305 (0%)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>101.87x</t>
+          <t>2.64x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 15.5</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 12.75</t>
+          <t>29-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 14.5</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1-Oct 9:37</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3027,47 +3003,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A-One Steels IPOL@455.00 (12.35%)</t>
+          <t>Peshwa Wheat BSE SMEL@100.05 (-0.94%)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>12.23x</t>
+          <t>2.77x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 49</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 28</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3077,64 +3053,64 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 46</t>
+          <t>1-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1-Oct 9:37</t>
+          <t>1-Oct 9:33</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
+          <t>Moneyview IPOL@55.00 (61.76%)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
+          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>271.94x</t>
+          <t>101.87x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>24-Sep GMP: 15.5</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 38</t>
+          <t>28-Sep GMP: 12.75</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,7 +3120,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 42</t>
+          <t>1-Oct GMP: 14.5</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3161,47 +3137,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEL@100.05 (-0.94%)</t>
+          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.77x</t>
+          <t>271.94x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 38</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3211,79 +3187,79 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 0</t>
+          <t>1-Oct GMP: 42</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1-Oct 9:33</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
+          <t>A-One Steels IPOL@455.00 (12.35%)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
+          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.89x</t>
+          <t>12.23x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4.5</t>
+          <t>24-Sep GMP: 49</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4</t>
+          <t>28-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6.5</t>
+          <t>1-Oct GMP: 46</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3295,12 +3271,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
+          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3310,32 +3286,32 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3.92x</t>
+          <t>1.89x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3345,12 +3321,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 6.5</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>30-Sep 9:28</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3362,7 +3338,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEL@126.00 (0.8%)</t>
+          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3377,22 +3353,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.18x</t>
+          <t>3.11x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3429,12 +3405,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
+          <t>Swastika Infra IPOL@200.00 (8.11%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3444,32 +3420,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.11x</t>
+          <t>7.91x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 9.5</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3479,12 +3455,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>30-Sep 9:32</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3496,7 +3472,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEL@78.10 (0.13%)</t>
+          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3511,17 +3487,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>3.92x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3551,59 +3527,59 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>30-Sep 9:31</t>
+          <t>30-Sep 9:28</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
+          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>176.85x</t>
+          <t>5.08x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 34</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 47</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3613,17 +3589,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 55</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:34</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3673,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
+          <t>S.K.Offset BSE SMEL@126.00 (0.8%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3712,22 +3688,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5.08x</t>
+          <t>1.18x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3752,12 +3728,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>30-Sep 9:34</t>
+          <t>30-Sep 9:32</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3831,12 +3807,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOL@200.00 (8.11%)</t>
+          <t>Core Integra Consulting NSE SMEL@78.10 (0.13%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3846,32 +3822,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7.91x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹160.88 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 9.5</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4.5</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3881,79 +3857,79 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 7</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:31</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Himalaya Nutravedics BSE SMEL@118.00 (11.32%)</t>
+          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.33x</t>
+          <t>176.85x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹26.50 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>23-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep GMP: 47</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0</t>
+          <t>30-Sep GMP: 55</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>29-Sep 9:33</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jio Platforms IPOU</t>
+          <t>Bonfiglioli Transmissions IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹168 (-%) 148 ↓ / 182 ↑</t>
+          <t>₹155 (-%) 137 ↓ / 155 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -536,7 +536,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10-Oct 15:02</t>
+          <t>11-Oct 15:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -548,12 +548,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bonfiglioli Transmissions IPOU</t>
+          <t>Jio Platforms IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
+          <t>₹170 (-%) 148 ↓ / 182 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -566,7 +566,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-</t>
@@ -579,7 +583,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10-Oct 5:55</t>
+          <t>11-Oct 15:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -591,17 +595,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fusion CX IPOU</t>
+          <t>Tonbo Imaging India IPOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹55 (19.03%) 55 ↓ / 55 ↑</t>
+          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -609,44 +613,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>₹702.00 Cr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>14-Oct</t>
+          <t>15-Oct</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16-Oct</t>
+          <t>19-Oct</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19-Oct</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>22-Oct</t>
+          <t>23-Oct</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10-Oct 15:02</t>
+          <t>11-Oct 12:10</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -658,17 +654,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services NSE SMEU</t>
+          <t>Zetwerk IPOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹12 (10.71%) 12 ↓ / 12 ↑</t>
+          <t>₹30 (-%) 30 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -678,42 +674,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>₹116.05 Cr</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>13-Oct</t>
+          <t>15-Oct</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>19-Oct</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16-Oct</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>21-Oct</t>
+          <t>23-Oct</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10-Oct 15:02</t>
+          <t>11-Oct 15:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -725,17 +713,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HD Fire Protect IPOU</t>
+          <t>Sahajanand Medical Technologies IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹73 (26.94%) 63 ↓ / 80 ↑</t>
+          <t>₹35 (-%) 35 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -745,42 +733,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹712.31 Cr</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>13-Oct</t>
+          <t>15-Oct</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>19-Oct</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16-Oct</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>21-Oct</t>
+          <t>23-Oct</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>10-Oct 15:02</t>
+          <t>11-Oct 15:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -792,17 +776,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar NSE SMEU</t>
+          <t>Fusion CX IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹25 (8.65%) 25 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -812,42 +796,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>289</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹42.10 Cr</t>
+          <t>₹702.00 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>13-Oct</t>
+          <t>14-Oct</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>16-Oct</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16-Oct</t>
+          <t>19-Oct</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>21-Oct</t>
+          <t>22-Oct</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>10-Oct 14:59</t>
+          <t>11-Oct 15:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -859,129 +843,129 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R.K.Fashion Accessories NSE SMEC</t>
+          <t>HD Fire Protect IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹1.5 (1.83%) 1.50 ↓ / 15 ↑</t>
+          <t>₹77 (28.41%) 63 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.7x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹34.99 Cr</t>
+          <t>₹712.31 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 7</t>
+          <t>13-Oct</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 1.5</t>
+          <t>15-Oct</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>16-Oct</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>12-Oct</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10-Oct 15:02</t>
+          <t>11-Oct 15:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TNA Solutions BSE SMEL@56.00 (-20%)</t>
+          <t>Ravita Engineering Services NSE SMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
+          <t>₹12 (10.71%) 12 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>55.2x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹37.86 Cr</t>
+          <t>₹116.05 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 7</t>
+          <t>13-Oct</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 3</t>
+          <t>15-Oct</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>16-Oct</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>9-Oct GMP: 0</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9-Oct 9:37</t>
+          <t>11-Oct 15:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -993,7 +977,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Paramount Syntex BSE SMEL@115.00 (-9.45%)</t>
+          <t>Vaibhav Vyapaar NSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1008,126 +992,126 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.88x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹81.79 Cr</t>
+          <t>₹42.10 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>13-Oct</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>15-Oct</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>16-Oct</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>9-Oct GMP: 0</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>9-Oct 9:31</t>
+          <t>11-Oct 15:01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Acme India Industries BSE SMEL@221.00 (12.76%)</t>
+          <t>R.K.Fashion Accessories NSE SMEC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹43 (21.94%) 25 ↓ / 65 ↑</t>
+          <t>₹1.5 (1.83%) 1.50 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>124.23x</t>
+          <t>2.7x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹121.69 Cr</t>
+          <t>₹34.99 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 30</t>
+          <t>5-Oct GMP: 7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 65</t>
+          <t>7-Oct GMP: 1.5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>9-Oct GMP: 43</t>
+          <t>12-Oct</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>9-Oct 9:37</t>
+          <t>11-Oct 15:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dove Soft BSE SMEL@110.30 (-0.63%)</t>
+          <t>Paramount Syntex BSE SMEL@115.00 (-9.45%)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1142,22 +1126,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.38x</t>
+          <t>1.88x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹73.26 Cr</t>
+          <t>₹81.79 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1167,22 +1151,22 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 0</t>
+          <t>9-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8-Oct 9:37</t>
+          <t>9-Oct 9:31</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1194,79 +1178,79 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SJP Ultrasonic BSE SMEL@74.20 (10.75%)</t>
+          <t>Acme India Industries BSE SMEL@221.00 (12.76%)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹43 (21.94%) 25 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.82x</t>
+          <t>124.23x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹23.45 Cr</t>
+          <t>₹121.69 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct GMP: 65</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 0</t>
+          <t>9-Oct GMP: 43</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8-Oct 9:36</t>
+          <t>9-Oct 9:37</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nityas Gems &amp; Jewellery IPOL@80.00 (6.67%)</t>
+          <t>TNA Solutions BSE SMEL@56.00 (-20%)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1276,99 +1260,99 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.26x</t>
+          <t>55.2x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹108.35 Cr</t>
+          <t>₹37.86 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 5</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 1</t>
+          <t>6-Oct GMP: 3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 1</t>
+          <t>9-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8-Oct 9:37</t>
+          <t>9-Oct 9:37</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEL@126.00 (48.24%)</t>
+          <t>Sollfege Smart Electronics BSE SMEL@104.40 (89.82%)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹50 (58.82%) 13 ↓ / 55 ↑</t>
+          <t>₹10 (18.18%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>294.22x</t>
+          <t>2.14x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹21.78 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 16</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 42</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1378,7 +1362,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 50</t>
+          <t>8-Oct GMP: 10</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1388,14 +1372,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Eventions NSE SMEL@111.00 (-5.93%)</t>
+          <t>SJP Ultrasonic BSE SMEL@74.20 (10.75%)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1410,22 +1394,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.39x</t>
+          <t>1.82x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹38.12 Cr</t>
+          <t>₹23.45 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1450,7 +1434,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8-Oct 9:35</t>
+          <t>8-Oct 9:36</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1529,42 +1513,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shree TNB Polymers BSE SMEL@60.00 (13.21%)</t>
+          <t>Eventions NSE SMEL@111.00 (-5.93%)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹4 (7.55%) 4 ↓ / 4 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.98x</t>
+          <t>2.39x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹31.80 Cr</t>
+          <t>₹38.12 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1579,64 +1563,64 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 4</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8-Oct 9:37</t>
+          <t>8-Oct 9:35</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Vishal Nirmiti IPOL@215.00 (-2.27%)</t>
+          <t>EverestIMS Technologies BSE SMEL@126.00 (48.24%)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹2 (0.91%) 2 ↓ / 20 ↑</t>
+          <t>₹50 (58.82%) 13 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.79x</t>
+          <t>294.22x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹178.00 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>29-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 2</t>
+          <t>5-Oct GMP: 42</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1646,7 +1630,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 2</t>
+          <t>8-Oct GMP: 50</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1656,49 +1640,49 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMEL@319.00 (2.57%)</t>
+          <t>Shree TNB Polymers BSE SMEL@60.00 (13.21%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹4 (7.55%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.06x</t>
+          <t>1.98x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹31.80 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1713,64 +1697,64 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 0</t>
+          <t>8-Oct GMP: 4</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8-Oct 9:28</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sollfege Smart Electronics BSE SMEL@104.40 (89.82%)</t>
+          <t>Vishal Nirmiti IPOL@215.00 (-2.27%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹10 (18.18%) 10 ↓ / 10 ↑</t>
+          <t>₹2 (0.91%) 2 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.14x</t>
+          <t>1.79x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹21.78 Cr</t>
+          <t>₹178.00 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1780,7 +1764,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 10</t>
+          <t>8-Oct GMP: 2</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1797,7 +1781,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEL@89.00 (0%)</t>
+          <t>Dove Soft BSE SMEL@110.30 (-0.63%)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1812,47 +1796,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.04x</t>
+          <t>1.38x</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>₹59.34 Cr</t>
+          <t>₹73.26 Cr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 0</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>7-Oct 9:31</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1864,79 +1848,79 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEL@224.20 (90%)</t>
+          <t>Omara Ventures India BSE SMEL@319.00 (2.57%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹103 (87.29%) 45 ↓ / 103 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>628.73x</t>
+          <t>1.06x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 90</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 70</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 103</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>7-Oct 9:37</t>
+          <t>8-Oct 9:28</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMEL@72.30 (0.42%)</t>
+          <t>Nityas Gems &amp; Jewellery IPOL@80.00 (6.67%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1946,47 +1930,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.54x</t>
+          <t>2.26x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹20.18 Cr</t>
+          <t>₹108.35 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep GMP: 5</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct GMP: 1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 0</t>
+          <t>8-Oct GMP: 1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>7-Oct 9:35</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1998,12 +1982,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMEL@200.00 (1.52%)</t>
+          <t>Green Asia Impex NSE SMEL@89.00 (0%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 100 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2013,32 +1997,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>73.8x</t>
+          <t>1.04x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹55.08 Cr</t>
+          <t>₹59.34 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 38</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 66</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2053,44 +2037,44 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>7-Oct 9:37</t>
+          <t>7-Oct 9:31</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMEL@101.00 (42.25%)</t>
+          <t>Papadmalji Agro Foods NSE SMEL@72.30 (0.42%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹16 (22.54%) 10 ↓ / 16 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>23.41x</t>
+          <t>2.54x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹35.93 Cr</t>
+          <t>₹20.18 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2100,64 +2084,64 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 16</t>
+          <t>7-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>6-Oct 9:37</t>
+          <t>7-Oct 9:35</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEL@79.20 (-20%)</t>
+          <t>Vans Electroengineerings BSE SMEL@224.20 (90%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
+          <t>₹103 (87.29%) 45 ↓ / 103 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.71x</t>
+          <t>628.73x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2167,94 +2151,94 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 1</t>
+          <t>1-Oct GMP: 70</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 1</t>
+          <t>7-Oct GMP: 103</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>6-Oct 9:37</t>
+          <t>7-Oct 9:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SRIT India IPOL@148.00 (13.85%)</t>
+          <t>Black Opal Consultants BSE SMEL@200.00 (1.52%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹59 (45.38%) 12 ↓ / 62 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 100 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>125.16x</t>
+          <t>73.8x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹218.40 Cr</t>
+          <t>₹55.08 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 33</t>
+          <t>29-Sep GMP: 38</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 48</t>
+          <t>1-Oct GMP: 66</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 59</t>
+          <t>7-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6-Oct 9:37</t>
+          <t>7-Oct 9:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2266,47 +2250,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOL@171.00 (2.4%)</t>
+          <t>SRIT India IPOL@148.00 (13.85%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹17 (10.18%) 9 ↓ / 17 ↑</t>
+          <t>₹59 (45.38%) 12 ↓ / 62 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>38.12x</t>
+          <t>125.16x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 14</t>
+          <t>28-Sep GMP: 33</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 12.5</t>
+          <t>30-Sep GMP: 48</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2316,7 +2300,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 17</t>
+          <t>6-Oct GMP: 59</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2333,12 +2317,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMEL@62.00 (0%)</t>
+          <t>Pind Hospitality BSE SMEL@79.20 (-20%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹1.5 (2.42%) 1 ↓ / 10 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2348,27 +2332,27 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.2x</t>
+          <t>2.71x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹14.01 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 6</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2383,7 +2367,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 1.5</t>
+          <t>6-Oct GMP: 1</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2400,62 +2384,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>German Green Steel IPOL@142 (2.16%)</t>
+          <t>Acme Universal Safezone 9 BSE SMEL@101.00 (42.25%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹9.5 (6.83%) 9.50 ↓ / 29 ↑</t>
+          <t>₹16 (22.54%) 10 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>30.42x</t>
+          <t>23.41x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹303.90 Cr</t>
+          <t>₹35.93 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 26</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 13</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 9.5</t>
+          <t>6-Oct GMP: 16</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>5-Oct 9:37</t>
+          <t>6-Oct 9:37</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2467,67 +2451,67 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
+          <t>Shah Investor's Home IPOL@171.00 (2.4%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
+          <t>₹17 (10.18%) 9 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>38.12x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 3</t>
+          <t>28-Sep GMP: 14</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0.5</t>
+          <t>30-Sep GMP: 12.5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0.5</t>
+          <t>6-Oct GMP: 17</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5-Oct 9:37</t>
+          <t>6-Oct 9:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2601,114 +2585,114 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
+          <t>Shivchem Agro BSE SMEL@62.00 (0%)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
+          <t>₹1.5 (2.42%) 1 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4.95x</t>
+          <t>2.2x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep GMP: 6</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 11</t>
+          <t>6-Oct GMP: 1.5</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>5-Oct 9:37</t>
+          <t>6-Oct 9:37</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Orient Cables IPOL@450 (65.44%)</t>
+          <t>Himalayan Solar NSE SMEL@85 (-17.48%)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹110 (40.44%) 34 ↓ / 123 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>97.28x</t>
+          <t>1.19x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 80</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 85</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2718,12 +2702,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 110</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>5-Oct 9:37</t>
+          <t>5-Oct 9:35</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2735,47 +2719,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Acevector IPOL@28.32 (-11.5%)</t>
+          <t>German Green Steel IPOL@142 (2.16%)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
+          <t>₹9.5 (6.83%) 9.50 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5.07x</t>
+          <t>30.42x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹420.00 Cr</t>
+          <t>₹303.90 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 2</t>
+          <t>25-Sep GMP: 26</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 1.1</t>
+          <t>29-Sep GMP: 13</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2785,7 +2769,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct GMP: 9.5</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2802,12 +2786,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEL@85 (-17.48%)</t>
+          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2817,32 +2801,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.19x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2852,49 +2836,49 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct GMP: 0.5</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5-Oct 9:35</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEL@110 (0%)</t>
+          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹15 (13.64%) 12 ↓ / 29 ↑</t>
+          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>103.12x</t>
+          <t>4.95x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2904,12 +2888,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 28</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2919,7 +2903,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 15</t>
+          <t>5-Oct GMP: 11</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2936,47 +2920,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOL@305 (0%)</t>
+          <t>Orient Cables IPOL@450 (65.44%)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
+          <t>₹110 (40.44%) 34 ↓ / 123 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.64x</t>
+          <t>97.28x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>25-Sep GMP: 80</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 2</t>
+          <t>29-Sep GMP: 85</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2986,7 +2970,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct GMP: 110</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3003,12 +2987,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Peshwa Wheat BSE SMEL@100.05 (-0.94%)</t>
+          <t>Acevector IPOL@28.32 (-11.5%)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3018,114 +3002,114 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.77x</t>
+          <t>5.07x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹53.52 Cr</t>
+          <t>₹420.00 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>25-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep GMP: 1.1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 0</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1-Oct 9:33</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Moneyview IPOL@55.00 (61.76%)</t>
+          <t>Bench Mark Infotech Services NSE SMEL@110 (0%)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
+          <t>₹15 (13.64%) 12 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>101.87x</t>
+          <t>103.12x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 15.5</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 12.75</t>
+          <t>29-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 14.5</t>
+          <t>5-Oct GMP: 15</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1-Oct 9:37</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3137,62 +3121,62 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
+          <t>Runwal Enterprises IPOL@305 (0%)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>271.94x</t>
+          <t>2.64x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 38</t>
+          <t>29-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 42</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1-Oct 9:37</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3204,47 +3188,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A-One Steels IPOL@455.00 (12.35%)</t>
+          <t>Moneyview IPOL@55.00 (61.76%)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
+          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>12.23x</t>
+          <t>101.87x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 49</t>
+          <t>24-Sep GMP: 15.5</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 28</t>
+          <t>28-Sep GMP: 12.75</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3254,7 +3238,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 46</t>
+          <t>1-Oct GMP: 14.5</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3271,62 +3255,62 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
+          <t>A-One Steels IPOL@455.00 (12.35%)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
+          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.89x</t>
+          <t>12.23x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4.5</t>
+          <t>24-Sep GMP: 49</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4</t>
+          <t>28-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6.5</t>
+          <t>1-Oct GMP: 46</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3338,62 +3322,62 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
+          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.11x</t>
+          <t>271.94x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep GMP: 38</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>1-Oct GMP: 42</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>30-Sep 9:32</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3405,12 +3389,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOL@200.00 (8.11%)</t>
+          <t>Peshwa Wheat BSE SMEL@100.05 (-0.94%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3420,64 +3404,64 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>7.91x</t>
+          <t>2.77x</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>₹160.88 Cr</t>
+          <t>₹53.52 Cr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 9.5</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4.5</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 7</t>
+          <t>1-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>1-Oct 9:33</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
+          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3487,32 +3471,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3.92x</t>
+          <t>1.89x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3522,12 +3506,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 6.5</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>30-Sep 9:28</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3539,7 +3523,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
+          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3554,22 +3538,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5.08x</t>
+          <t>3.92x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3594,12 +3578,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>30-Sep 9:34</t>
+          <t>30-Sep 9:28</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3740,47 +3724,47 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOL@375.00 (0%)</t>
+          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
+          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2.62x</t>
+          <t>176.85x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 51</t>
+          <t>23-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 8</t>
+          <t>25-Sep GMP: 47</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3790,7 +3774,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6</t>
+          <t>30-Sep GMP: 55</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3807,12 +3791,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEL@78.10 (0.13%)</t>
+          <t>ArMee Infotech IPOL@375.00 (0%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3822,32 +3806,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>2.62x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 51</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 8</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3857,64 +3841,64 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 6</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>30-Sep 9:31</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
+          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>176.85x</t>
+          <t>5.08x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹39.01 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 34</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 47</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3924,29 +3908,29 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 55</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:34</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Varmora Granito IPOL@155.00 (4.73%)</t>
+          <t>Swastika Infra IPOL@200.00 (8.11%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>₹1 (0.68%) 0.50 ↓ / 15 ↑</t>
+          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3956,47 +3940,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.6x</t>
+          <t>7.91x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹708.02 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>22-Sep GMP: 3</t>
+          <t>23-Sep GMP: 9.5</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0.5</t>
+          <t>25-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 1</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>29-Sep 9:37</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bonfiglioli Transmissions IPOU</t>
+          <t>Jio Platforms IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹155 (-%) 137 ↓ / 155 ↑</t>
+          <t>₹181 (-%) 148 ↓ / 182 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -536,7 +536,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>11-Oct 15:02</t>
+          <t>12-Oct 16:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -548,12 +548,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jio Platforms IPOU</t>
+          <t>Shellz India BSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹170 (-%) 148 ↓ / 182 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -568,22 +568,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>₹59.97 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>15-Oct</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>19-Oct</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>21-Oct</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>23-Oct</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>11-Oct 15:02</t>
+          <t>12-Oct 16:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -600,12 +620,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹-- (-%) 0 ↓ / 0 ↑</t>
+          <t>₹390 (55.71%) 270 ↓ / 390 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -613,13 +633,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>₹852.18 Cr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>15-Oct</t>
@@ -642,7 +670,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>11-Oct 12:10</t>
+          <t>12-Oct 16:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -659,12 +687,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹30 (-%) 30 ↓ / 30 ↑</t>
+          <t>₹13 (8.61%) 13 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -674,11 +702,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>₹5012.33 Cr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>15-Oct</t>
@@ -701,7 +737,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>11-Oct 15:02</t>
+          <t>12-Oct 16:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -713,17 +749,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sahajanand Medical Technologies IPOU</t>
+          <t>Bonfiglioli Transmissions IPOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹35 (-%) 35 ↓ / 35 ↑</t>
+          <t>₹153 (26.11%) 137 ↓ / 175 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -733,15 +769,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>586</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>₹2533.66 Cr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>15-Oct</t>
@@ -764,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>11-Oct 15:02</t>
+          <t>12-Oct 16:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -776,17 +816,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fusion CX IPOU</t>
+          <t>Sahajanand Medical Technologies IPOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹25 (8.65%) 25 ↓ / 55 ↑</t>
+          <t>₹40 (11.63%) 40 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -796,42 +836,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>344</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹702.00 Cr</t>
+          <t>₹475.48 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14-Oct</t>
+          <t>15-Oct</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>16-Oct</t>
+          <t>19-Oct</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19-Oct</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>22-Oct</t>
+          <t>23-Oct</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>11-Oct 15:02</t>
+          <t>12-Oct 16:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -843,17 +883,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HD Fire Protect IPOU</t>
+          <t>Fusion CX IPOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹77 (28.41%) 63 ↓ / 80 ↑</t>
+          <t>₹10 (3.46%) 10 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -863,42 +903,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>289</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹712.31 Cr</t>
+          <t>₹702.00 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>13-Oct</t>
+          <t>14-Oct</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>16-Oct</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16-Oct</t>
+          <t>19-Oct</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>21-Oct</t>
+          <t>22-Oct</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>11-Oct 15:02</t>
+          <t>12-Oct 16:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -910,17 +950,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services NSE SMEU</t>
+          <t>HD Fire Protect IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹12 (10.71%) 12 ↓ / 12 ↑</t>
+          <t>₹83 (30.63%) 63 ↓ / 86 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -930,17 +970,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹116.05 Cr</t>
+          <t>₹712.31 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -965,7 +1005,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>11-Oct 15:02</t>
+          <t>12-Oct 16:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -977,12 +1017,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar NSE SMEU</t>
+          <t>Ravita Engineering Services NSE SMEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹5 (4.46%) 5 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -997,17 +1037,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹42.10 Cr</t>
+          <t>₹116.05 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1032,7 +1072,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>11-Oct 15:01</t>
+          <t>12-Oct 16:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1044,12 +1084,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R.K.Fashion Accessories NSE SMEC</t>
+          <t>Vaibhav Vyapaar NSE SMEU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹1.5 (1.83%) 1.50 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1059,64 +1099,64 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.7x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹34.99 Cr</t>
+          <t>₹42.10 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 7</t>
+          <t>13-Oct</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 1.5</t>
+          <t>15-Oct</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>16-Oct</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>12-Oct</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>11-Oct 15:02</t>
+          <t>12-Oct 15:57</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Paramount Syntex BSE SMEL@115.00 (-9.45%)</t>
+          <t>R.K.Fashion Accessories NSE SMEL@80.00 (-2.44%)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1.5 (1.83%) 1.50 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1126,47 +1166,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.88x</t>
+          <t>2.7x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹81.79 Cr</t>
+          <t>₹34.99 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>5-Oct GMP: 7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct GMP: 1.5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>9-Oct GMP: 0</t>
+          <t>12-Oct GMP: 1.5</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>9-Oct 9:31</t>
+          <t>12-Oct 9:37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1245,12 +1285,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TNA Solutions BSE SMEL@56.00 (-20%)</t>
+          <t>Paramount Syntex BSE SMEL@115.00 (-9.45%)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1260,32 +1300,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55.2x</t>
+          <t>1.88x</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>₹37.86 Cr</t>
+          <t>₹81.79 Cr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 7</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 3</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1300,44 +1340,44 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>9-Oct 9:37</t>
+          <t>9-Oct 9:31</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sollfege Smart Electronics BSE SMEL@104.40 (89.82%)</t>
+          <t>TNA Solutions BSE SMEL@56.00 (-20%)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹10 (18.18%) 10 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.14x</t>
+          <t>55.2x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹21.78 Cr</t>
+          <t>₹37.86 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1347,39 +1387,39 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct GMP: 3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 10</t>
+          <t>9-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8-Oct 9:37</t>
+          <t>9-Oct 9:37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SJP Ultrasonic BSE SMEL@74.20 (10.75%)</t>
+          <t>Omara Ventures India BSE SMEL@319.00 (2.57%)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1394,22 +1434,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.82x</t>
+          <t>1.06x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹23.45 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1434,7 +1474,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8-Oct 9:36</t>
+          <t>8-Oct 9:28</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1513,47 +1553,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Eventions NSE SMEL@111.00 (-5.93%)</t>
+          <t>EverestIMS Technologies BSE SMEL@126.00 (48.24%)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹50 (58.82%) 13 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.39x</t>
+          <t>294.22x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹38.12 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>29-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 42</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1563,64 +1603,64 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 0</t>
+          <t>8-Oct GMP: 50</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8-Oct 9:35</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEL@126.00 (48.24%)</t>
+          <t>Vishal Nirmiti IPOL@215.00 (-2.27%)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹50 (58.82%) 13 ↓ / 55 ↑</t>
+          <t>₹2 (0.91%) 2 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>294.22x</t>
+          <t>1.79x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹178.00 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 16</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 42</t>
+          <t>5-Oct GMP: 2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1630,7 +1670,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 50</t>
+          <t>8-Oct GMP: 2</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1640,7 +1680,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1754,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Vishal Nirmiti IPOL@215.00 (-2.27%)</t>
+          <t>SJP Ultrasonic BSE SMEL@74.20 (10.75%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹2 (0.91%) 2 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,32 +1769,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.79x</t>
+          <t>1.82x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹178.00 Cr</t>
+          <t>₹23.45 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 2</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1764,12 +1804,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 2</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8-Oct 9:37</t>
+          <t>8-Oct 9:36</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1848,7 +1888,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMEL@319.00 (2.57%)</t>
+          <t>Eventions NSE SMEL@111.00 (-5.93%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1863,22 +1903,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.06x</t>
+          <t>2.39x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹38.12 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1903,7 +1943,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8-Oct 9:28</t>
+          <t>8-Oct 9:35</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1915,47 +1955,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nityas Gems &amp; Jewellery IPOL@80.00 (6.67%)</t>
+          <t>Sollfege Smart Electronics BSE SMEL@104.40 (89.82%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
+          <t>₹10 (18.18%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.26x</t>
+          <t>2.14x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹108.35 Cr</t>
+          <t>₹21.78 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 5</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 1</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1965,7 +2005,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 1</t>
+          <t>8-Oct GMP: 10</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1982,12 +2022,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEL@89.00 (0%)</t>
+          <t>Nityas Gems &amp; Jewellery IPOL@80.00 (6.67%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1997,47 +2037,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.04x</t>
+          <t>2.26x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹59.34 Cr</t>
+          <t>₹108.35 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>30-Sep GMP: 5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct GMP: 1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 0</t>
+          <t>8-Oct GMP: 1</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>7-Oct 9:31</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2049,12 +2089,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMEL@72.30 (0.42%)</t>
+          <t>Black Opal Consultants BSE SMEL@200.00 (1.52%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 100 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2064,32 +2104,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.54x</t>
+          <t>73.8x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹20.18 Cr</t>
+          <t>₹55.08 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 38</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 66</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2104,59 +2144,59 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>7-Oct 9:35</t>
+          <t>7-Oct 9:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEL@224.20 (90%)</t>
+          <t>Papadmalji Agro Foods NSE SMEL@72.30 (0.42%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹103 (87.29%) 45 ↓ / 103 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>628.73x</t>
+          <t>2.54x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹20.18 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 90</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 70</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2166,29 +2206,29 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 103</t>
+          <t>7-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>7-Oct 9:37</t>
+          <t>7-Oct 9:35</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMEL@200.00 (1.52%)</t>
+          <t>Green Asia Impex NSE SMEL@89.00 (0%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 100 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2198,32 +2238,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>73.8x</t>
+          <t>1.04x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹55.08 Cr</t>
+          <t>₹59.34 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 38</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 66</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2238,74 +2278,74 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>7-Oct 9:37</t>
+          <t>7-Oct 9:31</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SRIT India IPOL@148.00 (13.85%)</t>
+          <t>Vans Electroengineerings BSE SMEL@224.20 (90%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹59 (45.38%) 12 ↓ / 62 ↑</t>
+          <t>₹103 (87.29%) 45 ↓ / 103 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>125.16x</t>
+          <t>628.73x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹218.40 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 33</t>
+          <t>29-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 48</t>
+          <t>1-Oct GMP: 70</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 59</t>
+          <t>7-Oct GMP: 103</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6-Oct 9:37</t>
+          <t>7-Oct 9:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2384,47 +2424,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMEL@101.00 (42.25%)</t>
+          <t>Shivchem Agro BSE SMEL@62.00 (0%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>₹16 (22.54%) 10 ↓ / 16 ↑</t>
+          <t>₹1.5 (2.42%) 1 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23.41x</t>
+          <t>2.2x</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>₹35.93 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 6</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>30-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2434,7 +2474,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 16</t>
+          <t>6-Oct GMP: 1.5</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2444,54 +2484,54 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOL@171.00 (2.4%)</t>
+          <t>SRIT India IPOL@148.00 (13.85%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹17 (10.18%) 9 ↓ / 17 ↑</t>
+          <t>₹59 (45.38%) 12 ↓ / 62 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>38.12x</t>
+          <t>125.16x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 14</t>
+          <t>28-Sep GMP: 33</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 12.5</t>
+          <t>30-Sep GMP: 48</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2501,7 +2541,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 17</t>
+          <t>6-Oct GMP: 59</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2585,47 +2625,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Shivchem Agro BSE SMEL@62.00 (0%)</t>
+          <t>Shah Investor's Home IPOL@171.00 (2.4%)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹1.5 (2.42%) 1 ↓ / 10 ↑</t>
+          <t>₹17 (10.18%) 9 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.2x</t>
+          <t>38.12x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹14.01 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 6</t>
+          <t>28-Sep GMP: 14</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 1</t>
+          <t>30-Sep GMP: 12.5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2635,7 +2675,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 1.5</t>
+          <t>6-Oct GMP: 17</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2645,69 +2685,69 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Himalayan Solar NSE SMEL@85 (-17.48%)</t>
+          <t>Acme Universal Safezone 9 BSE SMEL@101.00 (42.25%)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹16 (22.54%) 10 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.19x</t>
+          <t>23.41x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹68.03 Cr</t>
+          <t>₹35.93 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>6-Oct GMP: 16</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>5-Oct 9:35</t>
+          <t>6-Oct 9:37</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2719,47 +2759,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>German Green Steel IPOL@142 (2.16%)</t>
+          <t>Orient Cables IPOL@450 (65.44%)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹9.5 (6.83%) 9.50 ↓ / 29 ↑</t>
+          <t>₹110 (40.44%) 34 ↓ / 123 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>30.42x</t>
+          <t>97.28x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹303.90 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 26</t>
+          <t>25-Sep GMP: 80</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 13</t>
+          <t>29-Sep GMP: 85</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2769,7 +2809,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 9.5</t>
+          <t>5-Oct GMP: 110</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2786,12 +2826,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
+          <t>Acevector IPOL@28.32 (-11.5%)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2801,32 +2841,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>5.07x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹420.00 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 3</t>
+          <t>25-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0.5</t>
+          <t>29-Sep GMP: 1.1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2836,7 +2876,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0.5</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2846,39 +2886,39 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
+          <t>Himalayan Solar NSE SMEL@85 (-17.48%)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4.95x</t>
+          <t>1.19x</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹68.03 Cr</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2903,12 +2943,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 11</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5-Oct 9:37</t>
+          <t>5-Oct 9:35</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2920,47 +2960,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Orient Cables IPOL@450 (65.44%)</t>
+          <t>Runwal Enterprises IPOL@305 (0%)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹110 (40.44%) 34 ↓ / 123 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>97.28x</t>
+          <t>2.64x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 80</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 85</t>
+          <t>29-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2970,7 +3010,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 110</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2987,47 +3027,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Acevector IPOL@28.32 (-11.5%)</t>
+          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
+          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5.07x</t>
+          <t>4.95x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹420.00 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 2</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 1.1</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3037,7 +3077,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct GMP: 11</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3121,12 +3161,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOL@305 (0%)</t>
+          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
+          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3136,32 +3176,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.64x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 2</t>
+          <t>29-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3171,7 +3211,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct GMP: 0.5</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3181,69 +3221,69 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Moneyview IPOL@55.00 (61.76%)</t>
+          <t>German Green Steel IPOL@142 (2.16%)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
+          <t>₹9.5 (6.83%) 9.50 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>101.87x</t>
+          <t>30.42x</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹303.90 Cr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 15.5</t>
+          <t>25-Sep GMP: 26</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 12.75</t>
+          <t>29-Sep GMP: 13</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 14.5</t>
+          <t>5-Oct GMP: 9.5</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1-Oct 9:37</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3255,47 +3295,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A-One Steels IPOL@455.00 (12.35%)</t>
+          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
+          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12.23x</t>
+          <t>271.94x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹405.00 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 49</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 28</t>
+          <t>28-Sep GMP: 38</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3305,7 +3345,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 46</t>
+          <t>1-Oct GMP: 42</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3322,47 +3362,47 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
+          <t>A-One Steels IPOL@455.00 (12.35%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
+          <t>₹46 (11.36%) 28 ↓ / 64 ↑</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>271.94x</t>
+          <t>12.23x</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹405.00 Cr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>24-Sep GMP: 49</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 38</t>
+          <t>28-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3372,7 +3412,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 42</t>
+          <t>1-Oct GMP: 46</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3456,62 +3496,62 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
+          <t>Moneyview IPOL@55.00 (61.76%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
+          <t>₹14.5 (42.65%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.89x</t>
+          <t>101.87x</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4.5</t>
+          <t>24-Sep GMP: 15.5</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4</t>
+          <t>28-Sep GMP: 12.75</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6.5</t>
+          <t>1-Oct GMP: 14.5</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3523,7 +3563,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
+          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3538,22 +3578,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.92x</t>
+          <t>3.11x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹44.23 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3578,7 +3618,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>30-Sep 9:28</t>
+          <t>30-Sep 9:32</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3657,12 +3697,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S.K.Offset BSE SMEL@126.00 (0.8%)</t>
+          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3672,32 +3712,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.18x</t>
+          <t>1.89x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹29.06 Cr</t>
+          <t>₹2100.00 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 4</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3707,12 +3747,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 6.5</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>30-Sep 9:32</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3724,47 +3764,47 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
+          <t>Core Integra Consulting NSE SMEL@78.10 (0.13%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>176.85x</t>
+          <t>1.4x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹21.99 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 34</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 47</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3774,29 +3814,29 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 55</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:31</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ArMee Infotech IPOL@375.00 (0%)</t>
+          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3806,32 +3846,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2.62x</t>
+          <t>3.92x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹300.00 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 51</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 8</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3841,12 +3881,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:28</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3925,47 +3965,47 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Swastika Infra IPOL@200.00 (8.11%)</t>
+          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
+          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7.91x</t>
+          <t>176.85x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹160.88 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 9.5</t>
+          <t>23-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4.5</t>
+          <t>25-Sep GMP: 47</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3975,7 +4015,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 7</t>
+          <t>30-Sep GMP: 55</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹181 (-%) 148 ↓ / 182 ↑</t>
+          <t>₹201 (-%) 148 ↓ / 201 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -536,7 +536,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12-Oct 16:02</t>
+          <t>13-Oct 16:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12-Oct 16:00</t>
+          <t>13-Oct 15:55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹390 (55.71%) 270 ↓ / 390 ↑</t>
+          <t>₹468 (66.86%) 270 ↓ / 468 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>12-Oct 16:02</t>
+          <t>13-Oct 16:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹13 (8.61%) 13 ↓ / 30 ↑</t>
+          <t>₹20.5 (13.58%) 16 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>12-Oct 16:02</t>
+          <t>13-Oct 16:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹153 (26.11%) 137 ↓ / 175 ↑</t>
+          <t>₹161 (27.47%) 137 ↓ / 175 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>12-Oct 16:02</t>
+          <t>13-Oct 16:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹40 (11.63%) 40 ↓ / 40 ↑</t>
+          <t>₹37 (10.76%) 35 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>12-Oct 16:02</t>
+          <t>13-Oct 16:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -883,12 +883,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fusion CX IPOU</t>
+          <t>Ravita Engineering Services NSE SMEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹10 (3.46%) 10 ↓ / 55 ↑</t>
+          <t>₹2 (1.79%) 2 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹702.00 Cr</t>
+          <t>₹116.05 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>12-Oct 16:02</t>
+          <t>13-Oct 16:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -950,17 +950,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HD Fire Protect IPOU</t>
+          <t>Fusion CX IPOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹83 (30.63%) 63 ↓ / 86 ↑</t>
+          <t>₹29 (10.03%) 19 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -970,42 +970,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>289</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹712.31 Cr</t>
+          <t>₹702.00 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13-Oct</t>
+          <t>14-Oct</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>16-Oct</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16-Oct</t>
+          <t>19-Oct</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>21-Oct</t>
+          <t>22-Oct</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>12-Oct 16:02</t>
+          <t>13-Oct 16:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1017,42 +1017,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services NSE SMEU</t>
+          <t>HD Fire Protect IPOO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹5 (4.46%) 5 ↓ / 12 ↑</t>
+          <t>₹89 (32.84%) 63 ↓ / 89 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.21x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹116.05 Cr</t>
+          <t>₹712.13 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13-Oct</t>
+          <t>13-Oct GMP: 89</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>12-Oct 16:02</t>
+          <t>13-Oct 16:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1084,7 +1084,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar NSE SMEU</t>
+          <t>Vaibhav Vyapaar NSE SMEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.17x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13-Oct</t>
+          <t>13-Oct GMP: 0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>12-Oct 15:57</t>
+          <t>13-Oct 16:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹201 (-%) 148 ↓ / 201 ↑</t>
+          <t>₹207 (-%) 148 ↓ / 218 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -536,7 +536,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13-Oct 16:02</t>
+          <t>14-Oct 14:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>13-Oct 15:55</t>
+          <t>14-Oct 13:57</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹468 (66.86%) 270 ↓ / 468 ↑</t>
+          <t>₹500 (71.43%) 270 ↓ / 500 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>13-Oct 16:02</t>
+          <t>14-Oct 14:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹20.5 (13.58%) 16 ↓ / 30 ↑</t>
+          <t>₹20 (13.25%) 16 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>13-Oct 16:02</t>
+          <t>14-Oct 14:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹161 (27.47%) 137 ↓ / 175 ↑</t>
+          <t>₹182 (31.06%) 137 ↓ / 182 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>13-Oct 16:02</t>
+          <t>14-Oct 14:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹37 (10.76%) 35 ↓ / 40 ↑</t>
+          <t>₹43 (12.50%) 35 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>13-Oct 16:02</t>
+          <t>14-Oct 14:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -883,22 +883,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services NSE SMEU</t>
+          <t>Ravita Engineering Services NSE SMEO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹2 (1.79%) 2 ↓ / 12 ↑</t>
+          <t>₹7 (6.25%) 2 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.66x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14-Oct</t>
+          <t>14-Oct GMP: 7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>13-Oct 16:02</t>
+          <t>14-Oct 14:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -950,12 +950,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fusion CX IPOU</t>
+          <t>Fusion CX IPOO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹29 (10.03%) 19 ↓ / 55 ↑</t>
+          <t>₹36.5 (12.63%) 19 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.27x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>14-Oct</t>
+          <t>14-Oct GMP: 36.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>13-Oct 16:02</t>
+          <t>14-Oct 14:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹89 (32.84%) 63 ↓ / 89 ↑</t>
+          <t>₹91 (33.58%) 63 ↓ / 91 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.21x</t>
+          <t>12.41x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13-Oct GMP: 89</t>
+          <t>13-Oct GMP: 91</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>13-Oct 16:02</t>
+          <t>14-Oct 14:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.17x</t>
+          <t>0.19x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13-Oct GMP: 0</t>
+          <t>13-Oct</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>13-Oct 16:02</t>
+          <t>14-Oct 14:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹207 (-%) 148 ↓ / 218 ↑</t>
+          <t>₹200 (-%) 148 ↓ / 218 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -536,7 +536,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>14-Oct 14:02</t>
+          <t>14-Oct 19:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14-Oct 13:57</t>
+          <t>14-Oct 19:31</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>14-Oct 14:02</t>
+          <t>14-Oct 19:37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹20 (13.25%) 16 ↓ / 30 ↑</t>
+          <t>₹19 (12.58%) 16 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>14-Oct 14:02</t>
+          <t>14-Oct 19:37</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹182 (31.06%) 137 ↓ / 182 ↑</t>
+          <t>₹180 (30.72%) 137 ↓ / 180 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>14-Oct 14:02</t>
+          <t>14-Oct 19:37</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹43 (12.50%) 35 ↓ / 43 ↑</t>
+          <t>₹38 (11.05%) 35 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>14-Oct 14:02</t>
+          <t>14-Oct 19:37</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.66x</t>
+          <t>1.14x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>14-Oct 14:02</t>
+          <t>14-Oct 19:37</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹36.5 (12.63%) 19 ↓ / 55 ↑</t>
+          <t>₹37 (12.80%) 19 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.27x</t>
+          <t>0.43x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>14-Oct GMP: 36.5</t>
+          <t>14-Oct GMP: 37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>14-Oct 14:02</t>
+          <t>14-Oct 19:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹91 (33.58%) 63 ↓ / 91 ↑</t>
+          <t>₹89 (32.84%) 63 ↓ / 91 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12.41x</t>
+          <t>16.56x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>14-Oct 14:02</t>
+          <t>14-Oct 19:37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.19x</t>
+          <t>0.39x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>14-Oct 14:02</t>
+          <t>14-Oct 19:36</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jio Platforms IPOU</t>
+          <t>Paras Healthcare IPOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹200 (-%) 148 ↓ / 218 ↑</t>
+          <t>₹111 (16.02%) 83 ↓ / 111 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -521,22 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>₹1450.00 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>21-Oct</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>23-Oct</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>26-Oct</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>28-Oct</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>14-Oct 19:37</t>
+          <t>15-Oct 13:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -548,17 +568,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shellz India BSE SMEU</t>
+          <t>Jio Platforms IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹220 (19.66%) 148 ↓ / 220 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -568,42 +588,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹59.97 Cr</t>
+          <t>₹30213.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>19-Oct</t>
+          <t>23-Oct</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>21-Oct</t>
+          <t>26-Oct</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>23-Oct</t>
+          <t>28-Oct</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14-Oct 19:31</t>
+          <t>15-Oct 13:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -615,7 +635,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tonbo Imaging India IPOU</t>
+          <t>Tonbo Imaging India IPOO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -630,7 +650,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.27x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -650,7 +670,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>15-Oct GMP: 500</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -670,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>14-Oct 19:37</t>
+          <t>15-Oct 13:37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -682,42 +702,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Zetwerk IPOU</t>
+          <t>Shellz India BSE SMEO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹19 (12.58%) 16 ↓ / 30 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.26x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>₹5012.33 Cr</t>
+          <t>₹59.97 Cr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>15-Oct GMP: 0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -737,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>14-Oct 19:37</t>
+          <t>15-Oct 13:30</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -749,42 +769,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bonfiglioli Transmissions IPOU</t>
+          <t>Zetwerk IPOO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹180 (30.72%) 137 ↓ / 180 ↑</t>
+          <t>₹21 (13.91%) 16 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>₹2533.66 Cr</t>
+          <t>₹5012.33 Cr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>15-Oct GMP: 21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -804,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>14-Oct 19:37</t>
+          <t>15-Oct 13:37</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -816,42 +836,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sahajanand Medical Technologies IPOU</t>
+          <t>Bonfiglioli Transmissions IPOO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹38 (11.05%) 35 ↓ / 41 ↑</t>
+          <t>₹173 (29.52%) 137 ↓ / 178 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.28x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>586</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>₹475.48 Cr</t>
+          <t>₹2533.66 Cr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>15-Oct GMP: 173</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -871,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>14-Oct 19:37</t>
+          <t>15-Oct 13:37</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -883,62 +903,62 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services NSE SMEO</t>
+          <t>Sahajanand Medical Technologies IPOO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹7 (6.25%) 2 ↓ / 12 ↑</t>
+          <t>₹46 (13.37%) 35 ↓ / 46 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.14x</t>
+          <t>0.17x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>344</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>₹116.05 Cr</t>
+          <t>₹475.48 Cr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14-Oct GMP: 7</t>
+          <t>15-Oct GMP: 46</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>16-Oct</t>
+          <t>19-Oct</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>19-Oct</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>22-Oct</t>
+          <t>23-Oct</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>14-Oct 19:37</t>
+          <t>15-Oct 13:37</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -950,42 +970,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fusion CX IPOO</t>
+          <t>Ravita Engineering Services NSE SMEO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹37 (12.80%) 19 ↓ / 55 ↑</t>
+          <t>₹3 (2.68%) 2 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.43x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>₹702.00 Cr</t>
+          <t>₹116.05 Cr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>14-Oct GMP: 37</t>
+          <t>14-Oct GMP: 7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1005,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>14-Oct 19:37</t>
+          <t>15-Oct 13:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1017,62 +1037,62 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HD Fire Protect IPOO</t>
+          <t>Fusion CX IPOO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹89 (32.84%) 63 ↓ / 91 ↑</t>
+          <t>₹30 (10.38%) 19 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16.56x</t>
+          <t>0.87x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>289</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>₹712.13 Cr</t>
+          <t>₹702.00 Cr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13-Oct GMP: 91</t>
+          <t>14-Oct GMP: 33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>16-Oct</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16-Oct</t>
+          <t>19-Oct</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>21-Oct</t>
+          <t>22-Oct</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>14-Oct 19:37</t>
+          <t>15-Oct 13:37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1084,47 +1104,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar NSE SMEO</t>
+          <t>HD Fire Protect IPOCT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹82 (30.26%) 63 ↓ / 91 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.39x</t>
+          <t>52.49x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>271</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>₹42.10 Cr</t>
+          <t>₹712.13 Cr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13-Oct</t>
+          <t>13-Oct GMP: 91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>15-Oct GMP: 82</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1139,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>14-Oct 19:36</t>
+          <t>15-Oct 13:37</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1151,12 +1171,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R.K.Fashion Accessories NSE SMEL@80.00 (-2.44%)</t>
+          <t>Vaibhav Vyapaar NSE SMECT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹1.5 (1.83%) 1.50 ↓ / 15 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1166,119 +1186,119 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.7x</t>
+          <t>1.43x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>₹34.99 Cr</t>
+          <t>₹42.10 Cr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 7</t>
+          <t>13-Oct</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 1.5</t>
+          <t>15-Oct GMP: 0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>16-Oct</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12-Oct GMP: 1.5</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12-Oct 9:37</t>
+          <t>15-Oct 13:37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Acme India Industries BSE SMEL@221.00 (12.76%)</t>
+          <t>R.K.Fashion Accessories NSE SMEL@80.00 (-2.44%)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>₹43 (21.94%) 25 ↓ / 65 ↑</t>
+          <t>₹1.5 (1.83%) 1.50 ↓ / 15 ↑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>124.23x</t>
+          <t>2.7x</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>₹121.69 Cr</t>
+          <t>₹34.99 Cr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 30</t>
+          <t>5-Oct GMP: 7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 65</t>
+          <t>7-Oct GMP: 1.5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>9-Oct GMP: 43</t>
+          <t>12-Oct GMP: 1.5</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>9-Oct 9:37</t>
+          <t>12-Oct 9:37</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -1352,47 +1372,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TNA Solutions BSE SMEL@56.00 (-20%)</t>
+          <t>Acme India Industries BSE SMEL@221.00 (12.76%)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
+          <t>₹43 (21.94%) 25 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>55.2x</t>
+          <t>124.23x</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>₹37.86 Cr</t>
+          <t>₹121.69 Cr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 7</t>
+          <t>30-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 3</t>
+          <t>6-Oct GMP: 65</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1402,7 +1422,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>9-Oct GMP: 0</t>
+          <t>9-Oct GMP: 43</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1419,12 +1439,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Omara Ventures India BSE SMEL@319.00 (2.57%)</t>
+          <t>TNA Solutions BSE SMEL@56.00 (-20%)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1434,52 +1454,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.06x</t>
+          <t>55.2x</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>₹41.99 Cr</t>
+          <t>₹37.86 Cr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct GMP: 3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 0</t>
+          <t>9-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8-Oct 9:28</t>
+          <t>9-Oct 9:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1553,47 +1573,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEL@126.00 (48.24%)</t>
+          <t>Nityas Gems &amp; Jewellery IPOL@80.00 (6.67%)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>₹50 (58.82%) 13 ↓ / 55 ↑</t>
+          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>294.22x</t>
+          <t>2.26x</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹108.35 Cr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 16</t>
+          <t>30-Sep GMP: 5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 42</t>
+          <t>5-Oct GMP: 1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1603,7 +1623,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 50</t>
+          <t>8-Oct GMP: 1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1613,19 +1633,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Vishal Nirmiti IPOL@215.00 (-2.27%)</t>
+          <t>Eventions NSE SMEL@111.00 (-5.93%)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>₹2 (0.91%) 2 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1635,32 +1655,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.79x</t>
+          <t>2.39x</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>₹178.00 Cr</t>
+          <t>₹38.12 Cr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 2</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1670,12 +1690,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 2</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8-Oct 9:37</t>
+          <t>8-Oct 9:35</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1687,32 +1707,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shree TNB Polymers BSE SMEL@60.00 (13.21%)</t>
+          <t>Sollfege Smart Electronics BSE SMEL@104.40 (89.82%)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>₹4 (7.55%) 4 ↓ / 4 ↑</t>
+          <t>₹10 (18.18%) 10 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.98x</t>
+          <t>2.14x</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>₹31.80 Cr</t>
+          <t>₹21.78 Cr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1722,7 +1742,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1737,7 +1757,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 4</t>
+          <t>8-Oct GMP: 10</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1747,54 +1767,54 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SJP Ultrasonic BSE SMEL@74.20 (10.75%)</t>
+          <t>EverestIMS Technologies BSE SMEL@126.00 (48.24%)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹50 (58.82%) 13 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.82x</t>
+          <t>294.22x</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>₹23.45 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>29-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 42</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1804,17 +1824,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 0</t>
+          <t>8-Oct GMP: 50</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8-Oct 9:36</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1888,42 +1908,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Eventions NSE SMEL@111.00 (-5.93%)</t>
+          <t>Shree TNB Polymers BSE SMEL@60.00 (13.21%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹4 (7.55%) 4 ↓ / 4 ↑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.39x</t>
+          <t>1.98x</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>₹38.12 Cr</t>
+          <t>₹31.80 Cr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1938,54 +1958,54 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 0</t>
+          <t>8-Oct GMP: 4</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8-Oct 9:35</t>
+          <t>8-Oct 9:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sollfege Smart Electronics BSE SMEL@104.40 (89.82%)</t>
+          <t>Omara Ventures India BSE SMEL@319.00 (2.57%)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>₹10 (18.18%) 10 ↓ / 10 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.14x</t>
+          <t>1.06x</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>₹21.78 Cr</t>
+          <t>₹41.99 Cr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2005,12 +2025,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 10</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>8-Oct 9:37</t>
+          <t>8-Oct 9:28</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2022,12 +2042,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nityas Gems &amp; Jewellery IPOL@80.00 (6.67%)</t>
+          <t>Vishal Nirmiti IPOL@215.00 (-2.27%)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>₹1 (1.33%) 1 ↓ / 9 ↑</t>
+          <t>₹2 (0.91%) 2 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2037,32 +2057,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.26x</t>
+          <t>1.79x</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>₹108.35 Cr</t>
+          <t>₹178.00 Cr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 5</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 1</t>
+          <t>5-Oct GMP: 2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2072,7 +2092,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>8-Oct GMP: 1</t>
+          <t>8-Oct GMP: 2</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2089,12 +2109,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Black Opal Consultants BSE SMEL@200.00 (1.52%)</t>
+          <t>SJP Ultrasonic BSE SMEL@74.20 (10.75%)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 100 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2104,99 +2124,99 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>73.8x</t>
+          <t>1.82x</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>₹55.08 Cr</t>
+          <t>₹23.45 Cr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 38</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 66</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 0</t>
+          <t>8-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>7-Oct 9:37</t>
+          <t>8-Oct 9:36</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods NSE SMEL@72.30 (0.42%)</t>
+          <t>Vans Electroengineerings BSE SMEL@224.20 (90%)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹103 (87.29%) 45 ↓ / 103 ↑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.54x</t>
+          <t>628.73x</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>₹20.18 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 70</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2206,29 +2226,29 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 0</t>
+          <t>7-Oct GMP: 103</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>7-Oct 9:35</t>
+          <t>7-Oct 9:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Green Asia Impex NSE SMEL@89.00 (0%)</t>
+          <t>Black Opal Consultants BSE SMEL@200.00 (1.52%)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 100 ↑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2238,32 +2258,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.04x</t>
+          <t>73.8x</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>₹59.34 Cr</t>
+          <t>₹55.08 Cr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>29-Sep GMP: 38</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>1-Oct GMP: 66</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2278,59 +2298,59 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>7-Oct 9:31</t>
+          <t>7-Oct 9:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEL@224.20 (90%)</t>
+          <t>Papadmalji Agro Foods NSE SMEL@72.30 (0.42%)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>₹103 (87.29%) 45 ↓ / 103 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>628.73x</t>
+          <t>2.54x</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹20.18 Cr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 90</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 70</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2340,29 +2360,29 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7-Oct GMP: 103</t>
+          <t>7-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>7-Oct 9:37</t>
+          <t>7-Oct 9:35</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pind Hospitality BSE SMEL@79.20 (-20%)</t>
+          <t>Green Asia Impex NSE SMEL@89.00 (0%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2372,47 +2392,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.71x</t>
+          <t>1.04x</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>₹17.82 Cr</t>
+          <t>₹59.34 Cr</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 1</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 1</t>
+          <t>7-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>6-Oct 9:37</t>
+          <t>7-Oct 9:31</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2491,47 +2511,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SRIT India IPOL@148.00 (13.85%)</t>
+          <t>Pind Hospitality BSE SMEL@79.20 (-20%)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>₹59 (45.38%) 12 ↓ / 62 ↑</t>
+          <t>₹1 (1.01%) 1 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>125.16x</t>
+          <t>2.71x</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>₹218.40 Cr</t>
+          <t>₹17.82 Cr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 33</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 48</t>
+          <t>30-Sep GMP: 1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2541,7 +2561,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 59</t>
+          <t>6-Oct GMP: 1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2551,7 +2571,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -2625,47 +2645,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Shah Investor's Home IPOL@171.00 (2.4%)</t>
+          <t>SRIT India IPOL@148.00 (13.85%)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>₹17 (10.18%) 9 ↓ / 17 ↑</t>
+          <t>₹59 (45.38%) 12 ↓ / 62 ↑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>38.12x</t>
+          <t>125.16x</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>₹90.17 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 14</t>
+          <t>28-Sep GMP: 33</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 12.5</t>
+          <t>30-Sep GMP: 48</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2675,7 +2695,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 17</t>
+          <t>6-Oct GMP: 59</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2692,47 +2712,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Acme Universal Safezone 9 BSE SMEL@101.00 (42.25%)</t>
+          <t>Shah Investor's Home IPOL@171.00 (2.4%)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>₹16 (22.54%) 10 ↓ / 16 ↑</t>
+          <t>₹17 (10.18%) 9 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>23.41x</t>
+          <t>38.12x</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>₹35.93 Cr</t>
+          <t>₹90.17 Cr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 14</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 10</t>
+          <t>30-Sep GMP: 12.5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2742,7 +2762,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>6-Oct GMP: 16</t>
+          <t>6-Oct GMP: 17</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2759,12 +2779,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Orient Cables IPOL@450 (65.44%)</t>
+          <t>Acme Universal Safezone 9 BSE SMEL@101.00 (42.25%)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>₹110 (40.44%) 34 ↓ / 123 ↑</t>
+          <t>₹16 (22.54%) 10 ↓ / 16 ↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2774,47 +2794,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>97.28x</t>
+          <t>23.41x</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹35.93 Cr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 80</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 85</t>
+          <t>30-Sep GMP: 10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 110</t>
+          <t>6-Oct GMP: 16</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5-Oct 9:37</t>
+          <t>6-Oct 9:37</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2826,47 +2846,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Acevector IPOL@28.32 (-11.5%)</t>
+          <t>Bench Mark Infotech Services NSE SMEL@110 (0%)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
+          <t>₹15 (13.64%) 12 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5.07x</t>
+          <t>103.12x</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>₹420.00 Cr</t>
+          <t>₹42.44 Cr</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 2</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 1.1</t>
+          <t>29-Sep GMP: 28</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2876,7 +2896,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct GMP: 15</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2960,47 +2980,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Runwal Enterprises IPOL@305 (0%)</t>
+          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
+          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.64x</t>
+          <t>4.95x</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹24.95 Cr</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 2</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3010,7 +3030,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0</t>
+          <t>5-Oct GMP: 11</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3027,47 +3047,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sai Urja Indo BSE SMEL@133.80 (18.41%)</t>
+          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>₹11 (9.73%) 8 ↓ / 32 ↑</t>
+          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4.95x</t>
+          <t>1.42x</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>₹24.95 Cr</t>
+          <t>₹10.54 Cr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 3</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 0.5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3077,7 +3097,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 11</t>
+          <t>5-Oct GMP: 0.5</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3087,54 +3107,54 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bench Mark Infotech Services NSE SMEL@110 (0%)</t>
+          <t>Acevector IPOL@28.32 (-11.5%)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>₹15 (13.64%) 12 ↓ / 29 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>103.12x</t>
+          <t>5.07x</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>₹42.44 Cr</t>
+          <t>₹420.00 Cr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 16</t>
+          <t>25-Sep GMP: 2</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 28</t>
+          <t>29-Sep GMP: 1.1</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,7 +3164,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 15</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3161,12 +3181,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Dudani Retail BSE SMEL@25 (-13.79%)</t>
+          <t>Runwal Enterprises IPOL@305 (0%)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>₹0.5 (1.72%) 0.50 ↓ / 3 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3176,32 +3196,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>2.64x</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>₹10.54 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 3</t>
+          <t>25-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 0.5</t>
+          <t>29-Sep GMP: 2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3211,7 +3231,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 0.5</t>
+          <t>5-Oct GMP: 0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3221,7 +3241,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3295,62 +3315,62 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
+          <t>Orient Cables IPOL@450 (65.44%)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
+          <t>₹110 (40.44%) 34 ↓ / 123 ↑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>271.94x</t>
+          <t>97.28x</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>25-Sep GMP: 80</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 38</t>
+          <t>29-Sep GMP: 85</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 42</t>
+          <t>5-Oct GMP: 110</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1-Oct 9:37</t>
+          <t>5-Oct 9:37</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3563,62 +3583,62 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pooja Logistics NSE SMEL@118.00 (2.61%)</t>
+          <t>Roopa Screen BSE SMEL@121.60 (90%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹42 (65.62%) 8 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.11x</t>
+          <t>271.94x</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>₹44.23 Cr</t>
+          <t>₹19.20 Cr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep GMP: 0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep GMP: 38</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>1-Oct GMP: 42</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>30-Sep 9:32</t>
+          <t>1-Oct 9:37</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3697,12 +3717,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Elevate Campuses IPOL@355.10 (-1.91%)</t>
+          <t>Swastika Infra IPOL@200.00 (8.11%)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>₹6.5 (1.80%) 2.50 ↓ / 16 ↑</t>
+          <t>₹7 (3.78%) 3 ↓ / 9.50 ↑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3712,32 +3732,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.89x</t>
+          <t>7.91x</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>₹2100.00 Cr</t>
+          <t>₹160.88 Cr</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 4.5</t>
+          <t>23-Sep GMP: 9.5</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 4</t>
+          <t>25-Sep GMP: 4.5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3747,7 +3767,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 6.5</t>
+          <t>30-Sep GMP: 7</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3764,7 +3784,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Core Integra Consulting NSE SMEL@78.10 (0.13%)</t>
+          <t>S.K.Offset BSE SMEL@126.00 (0.8%)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3779,22 +3799,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>1.18x</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>₹21.99 Cr</t>
+          <t>₹29.06 Cr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3819,24 +3839,24 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>30-Sep 9:31</t>
+          <t>30-Sep 9:32</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
+          <t>ArMee Infotech IPOL@375.00 (0%)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹6 (1.60%) 1 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3846,32 +3866,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3.92x</t>
+          <t>2.62x</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>₹34.47 Cr</t>
+          <t>₹300.00 Cr</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 51</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 8</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3881,12 +3901,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 6</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>30-Sep 9:28</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3898,47 +3918,47 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Liqvd Digital BSE SMEL@53.73 (-0.5%)</t>
+          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5.08x</t>
+          <t>176.85x</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>₹39.01 Cr</t>
+          <t>₹150.71 Cr</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 47</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3948,64 +3968,64 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 0</t>
+          <t>30-Sep GMP: 55</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>30-Sep 9:34</t>
+          <t>30-Sep 9:37</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOL@235.00 (75.37%)</t>
+          <t>Unitec Fibres BSE SMEL@90.00 (2.27%)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>₹55 (41.04%) 32 ↓ / 58 ↑</t>
+          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>176.85x</t>
+          <t>3.92x</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹34.47 Cr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 34</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 47</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4015,12 +4035,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>30-Sep GMP: 55</t>
+          <t>30-Sep GMP: 0</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>30-Sep 9:37</t>
+          <t>30-Sep 9:28</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rating▲▼</t>
+          <t>🔥Rating▲▼</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹111 (16.02%) 83 ↓ / 111 ↑</t>
+          <t>₹115 (16.59%) 83 ↓ / 115 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15-Oct 13:37</t>
+          <t>15-Oct 19:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹220 (19.66%) 148 ↓ / 220 ↑</t>
+          <t>₹229 (20.46%) 148 ↓ / 229 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>15-Oct 13:37</t>
+          <t>15-Oct 19:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹500 (71.43%) 270 ↓ / 500 ↑</t>
+          <t>₹495 (70.71%) 270 ↓ / 500 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.27x</t>
+          <t>4.01x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>15-Oct GMP: 500</t>
+          <t>15-Oct GMP: 495</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>15-Oct 13:37</t>
+          <t>15-Oct 19:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.26x</t>
+          <t>0.76x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>15-Oct 13:30</t>
+          <t>15-Oct 18:54</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹21 (13.91%) 16 ↓ / 30 ↑</t>
+          <t>₹14.75 (9.77%) 14.75 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.08x</t>
+          <t>0.23x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>15-Oct GMP: 21</t>
+          <t>15-Oct GMP: 14.75</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15-Oct 13:37</t>
+          <t>15-Oct 19:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹173 (29.52%) 137 ↓ / 178 ↑</t>
+          <t>₹147 (25.09%) 137 ↓ / 178 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.28x</t>
+          <t>0.48x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15-Oct GMP: 173</t>
+          <t>15-Oct GMP: 147</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>15-Oct 13:37</t>
+          <t>15-Oct 19:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.17x</t>
+          <t>0.35x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>15-Oct 13:37</t>
+          <t>15-Oct 19:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹3 (2.68%) 2 ↓ / 12 ↑</t>
+          <t>₹2 (1.79%) 2 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.42x</t>
+          <t>1.7x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>15-Oct 13:37</t>
+          <t>15-Oct 19:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹30 (10.38%) 19 ↓ / 55 ↑</t>
+          <t>₹21.5 (7.44%) 19 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.87x</t>
+          <t>1.16x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>15-Oct 13:37</t>
+          <t>15-Oct 19:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1104,7 +1104,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HD Fire Protect IPOCT</t>
+          <t>HD Fire Protect IPOC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>52.49x</t>
+          <t>131.73x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>15-Oct 13:37</t>
+          <t>15-Oct 19:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1171,12 +1171,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar NSE SMECT</t>
+          <t>Vaibhav Vyapaar NSE SMEC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹2 (3.70%) 2 ↓ / 2 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.43x</t>
+          <t>3.23x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15-Oct GMP: 0</t>
+          <t>15-Oct GMP: 2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15-Oct 13:37</t>
+          <t>15-Oct 19:02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>🔥Rating</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>🔥Rating</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>🔥Rating</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹115 (16.59%) 83 ↓ / 115 ↑</t>
+          <t>₹88 (12.70%) 83 ↓ / 95 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15-Oct 19:02</t>
+          <t>16-Oct 12:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹229 (20.46%) 148 ↓ / 229 ↑</t>
+          <t>₹222 (19.84%) 148 ↓ / 222 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>15-Oct 19:02</t>
+          <t>16-Oct 12:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹495 (70.71%) 270 ↓ / 500 ↑</t>
+          <t>₹500 (71.43%) 270 ↓ / 500 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.01x</t>
+          <t>5.6x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>15-Oct GMP: 495</t>
+          <t>15-Oct GMP: 500</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>15-Oct 19:02</t>
+          <t>16-Oct 12:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>15-Oct GMP: 0</t>
+          <t>15-Oct</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>15-Oct 18:54</t>
+          <t>16-Oct 12:01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹14.75 (9.77%) 14.75 ↓ / 30 ↑</t>
+          <t>₹10.75 (7.12%) 10.75 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.23x</t>
+          <t>0.25x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>15-Oct GMP: 14.75</t>
+          <t>15-Oct GMP: 14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15-Oct 19:02</t>
+          <t>16-Oct 12:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹147 (25.09%) 137 ↓ / 178 ↑</t>
+          <t>₹138 (23.55%) 137 ↓ / 178 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.48x</t>
+          <t>0.68x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15-Oct GMP: 147</t>
+          <t>15-Oct GMP: 140</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>15-Oct 19:02</t>
+          <t>16-Oct 12:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹46 (13.37%) 35 ↓ / 46 ↑</t>
+          <t>₹40 (11.63%) 35 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.35x</t>
+          <t>0.47x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>15-Oct GMP: 46</t>
+          <t>15-Oct GMP: 43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>15-Oct 19:02</t>
+          <t>16-Oct 12:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -970,7 +970,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services NSE SMEO</t>
+          <t>Ravita Engineering Services NSE SMECT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.7x</t>
+          <t>2.19x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>16-Oct</t>
+          <t>16-Oct GMP: 2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>15-Oct 19:02</t>
+          <t>16-Oct 12:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1037,12 +1037,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fusion CX IPOO</t>
+          <t>Fusion CX IPOCT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹21.5 (7.44%) 19 ↓ / 55 ↑</t>
+          <t>₹20.5 (7.09%) 19 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.16x</t>
+          <t>1.55x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16-Oct</t>
+          <t>16-Oct GMP: 20.5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>15-Oct 19:02</t>
+          <t>16-Oct 12:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>15-Oct 19:02</t>
+          <t>16-Oct 12:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15-Oct 19:02</t>
+          <t>16-Oct 12:02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹88 (12.70%) 83 ↓ / 95 ↑</t>
+          <t>₹97 (14.00%) 83 ↓ / 97 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-Oct 12:02</t>
+          <t>16-Oct 19:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹222 (19.84%) 148 ↓ / 222 ↑</t>
+          <t>₹219 (19.57%) 148 ↓ / 221 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16-Oct 12:02</t>
+          <t>16-Oct 19:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.6x</t>
+          <t>7.78x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>16-Oct 12:02</t>
+          <t>16-Oct 19:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.76x</t>
+          <t>0.89x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>16-Oct 12:01</t>
+          <t>16-Oct 18:57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹10.75 (7.12%) 10.75 ↓ / 30 ↑</t>
+          <t>₹5 (3.31%) 5 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.25x</t>
+          <t>0.31x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>16-Oct 12:02</t>
+          <t>16-Oct 19:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹138 (23.55%) 137 ↓ / 178 ↑</t>
+          <t>₹128 (21.84%) 128 ↓ / 178 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.68x</t>
+          <t>0.99x</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>16-Oct 12:02</t>
+          <t>16-Oct 19:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹40 (11.63%) 35 ↓ / 43 ↑</t>
+          <t>₹38 (11.05%) 35 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.47x</t>
+          <t>0.83x</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16-Oct 12:02</t>
+          <t>16-Oct 19:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -970,7 +970,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services NSE SMECT</t>
+          <t>Ravita Engineering Services NSE SMEC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.19x</t>
+          <t>7.11x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16-Oct 12:02</t>
+          <t>16-Oct 19:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1037,22 +1037,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fusion CX IPOCT</t>
+          <t>Fusion CX IPOC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹20.5 (7.09%) 19 ↓ / 55 ↑</t>
+          <t>₹9.5 (3.29%) 9.50 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.55x</t>
+          <t>4.68x</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16-Oct GMP: 20.5</t>
+          <t>16-Oct GMP: 9.5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16-Oct 12:02</t>
+          <t>16-Oct 19:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹82 (30.26%) 63 ↓ / 91 ↑</t>
+          <t>₹78 (28.78%) 63 ↓ / 91 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16-Oct 12:02</t>
+          <t>16-Oct 19:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16-Oct 12:02</t>
+          <t>16-Oct 19:02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹97 (14.00%) 83 ↓ / 97 ↑</t>
+          <t>₹95 (13.71%) 83 ↓ / 95 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-Oct 19:02</t>
+          <t>17-Oct 13:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹219 (19.57%) 148 ↓ / 221 ↑</t>
+          <t>₹221 (19.75%) 148 ↓ / 221 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16-Oct 19:02</t>
+          <t>17-Oct 13:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹500 (71.43%) 270 ↓ / 500 ↑</t>
+          <t>₹520 (74.29%) 270 ↓ / 520 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>16-Oct 19:02</t>
+          <t>17-Oct 13:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>16-Oct 18:57</t>
+          <t>17-Oct 13:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹5 (3.31%) 5 ↓ / 30 ↑</t>
+          <t>₹7.5 (4.97%) 7.50 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>16-Oct 19:02</t>
+          <t>17-Oct 13:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹128 (21.84%) 128 ↓ / 178 ↑</t>
+          <t>₹131 (22.35%) 129 ↓ / 178 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>16-Oct 19:02</t>
+          <t>17-Oct 13:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹38 (11.05%) 35 ↓ / 43 ↑</t>
+          <t>₹28 (8.14%) 28 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16-Oct 19:02</t>
+          <t>17-Oct 13:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16-Oct 19:02</t>
+          <t>17-Oct 13:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹9.5 (3.29%) 9.50 ↓ / 55 ↑</t>
+          <t>₹10.5 (3.63%) 10 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16-Oct GMP: 9.5</t>
+          <t>16-Oct GMP: 10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16-Oct 19:02</t>
+          <t>17-Oct 13:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1104,12 +1104,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HD Fire Protect IPOC</t>
+          <t>HD Fire Protect IPOCAllotted</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹78 (28.78%) 63 ↓ / 91 ↑</t>
+          <t>₹72 (26.57%) 63 ↓ / 91 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16-Oct 19:02</t>
+          <t>17-Oct 13:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹2 (3.70%) 2 ↓ / 2 ↑</t>
+          <t>₹3 (5.56%) 2 ↓ / 3 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16-Oct 19:02</t>
+          <t>17-Oct 13:02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹95 (13.71%) 83 ↓ / 95 ↑</t>
+          <t>₹96 (13.85%) 83 ↓ / 96 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>17-Oct 13:02</t>
+          <t>17-Oct 18:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>17-Oct 13:02</t>
+          <t>17-Oct 18:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹520 (74.29%) 270 ↓ / 520 ↑</t>
+          <t>₹505 (72.14%) 270 ↓ / 516 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>17-Oct 13:02</t>
+          <t>17-Oct 18:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>17-Oct 13:02</t>
+          <t>17-Oct 17:53</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹7.5 (4.97%) 7.50 ↓ / 30 ↑</t>
+          <t>₹5.5 (3.64%) 5.50 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>17-Oct 13:02</t>
+          <t>17-Oct 18:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹131 (22.35%) 129 ↓ / 178 ↑</t>
+          <t>₹132 (22.53%) 129 ↓ / 178 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>17-Oct 13:02</t>
+          <t>17-Oct 18:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹28 (8.14%) 28 ↓ / 43 ↑</t>
+          <t>₹18 (5.23%) 18 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>17-Oct 13:02</t>
+          <t>17-Oct 18:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹2 (1.79%) 2 ↓ / 12 ↑</t>
+          <t>₹3 (2.68%) 2 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>17-Oct 13:02</t>
+          <t>17-Oct 18:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹10.5 (3.63%) 10 ↓ / 55 ↑</t>
+          <t>₹12.5 (4.33%) 10 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>17-Oct 13:02</t>
+          <t>17-Oct 18:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>₹72 (26.57%) 63 ↓ / 91 ↑</t>
+          <t>₹70 (25.83%) 63 ↓ / 91 ↑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17-Oct 13:02</t>
+          <t>17-Oct 18:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>₹3 (5.56%) 2 ↓ / 3 ↑</t>
+          <t>₹5 (9.26%) 2 ↓ / 5 ↑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>17-Oct 13:02</t>
+          <t>17-Oct 18:02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>17-Oct 18:02</t>
+          <t>18-Oct 13:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹221 (19.75%) 148 ↓ / 221 ↑</t>
+          <t>₹242 (21.63%) 148 ↓ / 242 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>17-Oct 18:02</t>
+          <t>18-Oct 13:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>17-Oct 18:02</t>
+          <t>18-Oct 13:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹-- (0.00%) 0 ↓ / 0 ↑</t>
+          <t>₹25 (13.97%) 25 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>17-Oct 17:53</t>
+          <t>18-Oct 13:02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹5.5 (3.64%) 5.50 ↓ / 30 ↑</t>
+          <t>₹6.5 (4.30%) 6.50 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>17-Oct 18:02</t>
+          <t>18-Oct 13:02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>17-Oct 18:02</t>
+          <t>18-Oct 13:02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹18 (5.23%) 18 ↓ / 43 ↑</t>
+          <t>₹21 (6.10%) 15 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>17-Oct 18:02</t>
+          <t>18-Oct 13:02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>17-Oct 18:02</t>
+          <t>18-Oct 13:02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>₹12.5 (4.33%) 10 ↓ / 55 ↑</t>
+          <t>₹15 (5.19%) 10 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>17-Oct 18:02</t>
+          <t>18-Oct 13:02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17-Oct 18:02</t>
+          <t>18-Oct 13:02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>17-Oct 18:02</t>
+          <t>18-Oct 13:02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">

--- a/files/gmp.xlsx
+++ b/files/gmp.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹96 (13.85%) 83 ↓ / 96 ↑</t>
+          <t>₹92 (13.28%) 83 ↓ / 96 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18-Oct 13:02</t>
+          <t>18-Oct 18:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹242 (21.63%) 148 ↓ / 242 ↑</t>
+          <t>₹249 (22.25%) 148 ↓ / 249 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>18-Oct 13:02</t>
+          <t>18-Oct 18:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹505 (72.14%) 270 ↓ / 516 ↑</t>
+          <t>₹515 (73.57%) 270 ↓ / 516 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>18-Oct 13:02</t>
+          <t>18-Oct 18:37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹25 (13.97%) 25 ↓ / 25 ↑</t>
+          <t>₹35 (19.55%) 25 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>18-Oct 13:02</t>
+          <t>18-Oct 18:37</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹6.5 (4.30%) 6.50 ↓ / 30 ↑</t>
+          <t>₹6 (3.97%) 6 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>18-Oct 13:02</t>
+          <t>18-Oct 18:37</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹132 (22.53%) 129 ↓ / 178 ↑</t>
+          <t>₹130 (22.18%) 129 ↓ / 178 ↑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>18-Oct 13:02</t>
+          <t>18-Oct 18:37</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹21 (6.10%) 15 ↓ / 43 ↑</t>
+          <t>₹29 (8.43%) 15 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>18-Oct 13:02</t>
+          <t>18-Oct 18:37</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>₹3 (2.68%) 2 ↓ / 12 ↑</t>
+          <t>₹4.5 (4.02%) 2 ↓ / 12 ↑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>18-Oct 13:02</t>
+          <t>18-Oct 18:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>